--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R0cabcb6fb19c4dcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R893b8566a8d042bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R28074cc146af440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R0b4e023b829141ea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5986,7 +5986,7 @@
         <x:v>Placeholder</x:v>
       </x:c>
       <x:c r="D243" s="11" t="str">
-        <x:v>+381 62 000 0000</x:v>
+        <x:v>+7 (999) 000-00-00</x:v>
       </x:c>
       <x:c r="E243" s="17"/>
       <x:c r="F243" s="17"/>
@@ -7350,7 +7350,7 @@
         <x:v>Сообщение ошибки формы</x:v>
       </x:c>
       <x:c r="D305" s="11" t="str">
-        <x:v>Проверьте формат телефона</x:v>
+        <x:v>Введите российский номер в формате +7 (999) 000-00-00</x:v>
       </x:c>
       <x:c r="E305" s="17"/>
       <x:c r="F305" s="17"/>
@@ -8180,7 +8180,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd080a2693ae84bce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R185bb372bad247ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R4c5096a0538645fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="Raf7a23bccd6447b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="Ra7be548619224717"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="Rd6ec64e0301b415f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,7 +319,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SiteContent" displayName="SiteContent" ref="A1:L331" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SiteContent" displayName="SiteContent" ref="A1:L332" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="key"/>
     <x:tableColumn id="2" name="section"/>
@@ -4814,7 +4814,7 @@
         <x:v>Тариф Первичное подключение</x:v>
       </x:c>
       <x:c r="D190" s="11" t="str">
-        <x:v>Подключение готовой системы на базе таблицы текущего формата.</x:v>
+        <x:v>Подключение ассистента и базы данных в стандартном формате</x:v>
       </x:c>
       <x:c r="E190" s="17"/>
       <x:c r="F190" s="17"/>
@@ -4858,7 +4858,7 @@
         <x:v>Тариф Первичное подключение</x:v>
       </x:c>
       <x:c r="D192" s="11" t="str">
-        <x:v>Подключение клиентской таблицы текущего формата</x:v>
+        <x:v>Настройка ассистента</x:v>
       </x:c>
       <x:c r="E192" s="17"/>
       <x:c r="F192" s="17"/>
@@ -4880,7 +4880,7 @@
         <x:v>Тариф Первичное подключение</x:v>
       </x:c>
       <x:c r="D193" s="11" t="str">
-        <x:v>Настройка ассистента</x:v>
+        <x:v>Подключение базы данных и хранилища фото</x:v>
       </x:c>
       <x:c r="E193" s="17"/>
       <x:c r="F193" s="17"/>
@@ -4902,7 +4902,7 @@
         <x:v>Тариф Первичное подключение</x:v>
       </x:c>
       <x:c r="D194" s="11" t="str">
-        <x:v>Подключение базовых интеграций</x:v>
+        <x:v>Тестирование системы</x:v>
       </x:c>
       <x:c r="E194" s="17"/>
       <x:c r="F194" s="17"/>
@@ -4924,7 +4924,7 @@
         <x:v>Тариф Первичное подключение</x:v>
       </x:c>
       <x:c r="D195" s="11" t="str">
-        <x:v>Базовое тестирование системы</x:v>
+        <x:v>Инструкция по работе и запуск</x:v>
       </x:c>
       <x:c r="E195" s="17"/>
       <x:c r="F195" s="17"/>
@@ -4946,7 +4946,7 @@
         <x:v>Тариф Первичное подключение</x:v>
       </x:c>
       <x:c r="D196" s="11" t="str">
-        <x:v>Инструкция по работе и запуск</x:v>
+        <x:v>1 неделя поддержки</x:v>
       </x:c>
       <x:c r="E196" s="17"/>
       <x:c r="F196" s="17"/>
@@ -5011,9 +5011,7 @@
       <x:c r="C199" s="8" t="str">
         <x:v>Тариф Онлайн-поддержка</x:v>
       </x:c>
-      <x:c r="D199" s="11" t="str">
-        <x:v>Удалённая помощь, консультации и контроль качества работы системы.</x:v>
-      </x:c>
+      <x:c r="D199" s="11" t="str"/>
       <x:c r="E199" s="17"/>
       <x:c r="F199" s="17"/>
       <x:c r="G199" s="17"/>
@@ -5056,7 +5054,7 @@
         <x:v>Тариф Онлайн-поддержка</x:v>
       </x:c>
       <x:c r="D201" s="11" t="str">
-        <x:v>Удалённая помощь по вопросам работы системы</x:v>
+        <x:v>Проверка работоспособности всей системы</x:v>
       </x:c>
       <x:c r="E201" s="17"/>
       <x:c r="F201" s="17"/>
@@ -5078,7 +5076,7 @@
         <x:v>Тариф Онлайн-поддержка</x:v>
       </x:c>
       <x:c r="D202" s="11" t="str">
-        <x:v>Консультации по использованию клиентской базы</x:v>
+        <x:v>Корректировка</x:v>
       </x:c>
       <x:c r="E202" s="17"/>
       <x:c r="F202" s="17"/>
@@ -5100,7 +5098,7 @@
         <x:v>Тариф Онлайн-поддержка</x:v>
       </x:c>
       <x:c r="D203" s="11" t="str">
-        <x:v>Проверка работоспособности всех подключённых интеграций</x:v>
+        <x:v>Исправление</x:v>
       </x:c>
       <x:c r="E203" s="17"/>
       <x:c r="F203" s="17"/>
@@ -5122,7 +5120,7 @@
         <x:v>Тариф Онлайн-поддержка</x:v>
       </x:c>
       <x:c r="D204" s="11" t="str">
-        <x:v>Корректировка и улучшение промптов для ИИ</x:v>
+        <x:v>Устранение</x:v>
       </x:c>
       <x:c r="E204" s="17"/>
       <x:c r="F204" s="17"/>
@@ -5144,7 +5142,7 @@
         <x:v>Тариф Онлайн-поддержка</x:v>
       </x:c>
       <x:c r="D205" s="11" t="str">
-        <x:v>Исправление накопительных ошибок в работе ИИ</x:v>
+        <x:v>Проверка</x:v>
       </x:c>
       <x:c r="E205" s="17"/>
       <x:c r="F205" s="17"/>
@@ -5254,7 +5252,7 @@
         <x:v>Доп. опция Безопасность базы данных</x:v>
       </x:c>
       <x:c r="D210" s="11" t="str">
-        <x:v>Автоматическое резервное копирование в удобное место: каждый день, раз в неделю или раз в месяц.</x:v>
+        <x:v>Дублирование всей информации в специальное хранилище, к которому имеете доступ только вы. Защищает от случайного удаления данных или попытки удалить всю базу данных.</x:v>
       </x:c>
       <x:c r="E210" s="17"/>
       <x:c r="F210" s="17"/>
@@ -7564,7 +7562,7 @@
         <x:v>Пункт индивидуального тарифа 1</x:v>
       </x:c>
       <x:c r="D315" s="11" t="str">
-        <x:v>Всё, что входит в базовый тариф</x:v>
+        <x:v>Настройка ассистента</x:v>
       </x:c>
       <x:c r="E315" s="17"/>
       <x:c r="F315" s="17"/>
@@ -7586,7 +7584,7 @@
         <x:v>Пункт индивидуального тарифа 2</x:v>
       </x:c>
       <x:c r="D316" s="11" t="str">
-        <x:v>Адаптация таблицы под ваши нужды</x:v>
+        <x:v>Подключение базы данных и хранилища фото</x:v>
       </x:c>
       <x:c r="E316" s="17"/>
       <x:c r="F316" s="17"/>
@@ -7608,7 +7606,7 @@
         <x:v>Пункт индивидуального тарифа 3</x:v>
       </x:c>
       <x:c r="D317" s="11" t="str">
-        <x:v>Индивидуальные условия внедрения</x:v>
+        <x:v>Тестирование системы</x:v>
       </x:c>
       <x:c r="E317" s="17"/>
       <x:c r="F317" s="17"/>
@@ -7630,7 +7628,7 @@
         <x:v>Пункт индивидуального тарифа 4</x:v>
       </x:c>
       <x:c r="D318" s="11" t="str">
-        <x:v>Индивидуальное обсуждение рабочего процесса</x:v>
+        <x:v>Инструкция по работе и запуск</x:v>
       </x:c>
       <x:c r="E318" s="17"/>
       <x:c r="F318" s="17"/>
@@ -7652,7 +7650,7 @@
         <x:v>Пункт индивидуального тарифа 5</x:v>
       </x:c>
       <x:c r="D319" s="11" t="str">
-        <x:v>Индивидуальные инструкции</x:v>
+        <x:v>Полная адаптация системы под ваши нужды</x:v>
       </x:c>
       <x:c r="E319" s="17"/>
       <x:c r="F319" s="17"/>
@@ -7674,7 +7672,7 @@
         <x:v>Пункт индивидуального тарифа 6</x:v>
       </x:c>
       <x:c r="D320" s="11" t="str">
-        <x:v>Один месяц удалённой поддержки в подарок</x:v>
+        <x:v>Индивидуальные инструкции для работы с адаптированной системой</x:v>
       </x:c>
       <x:c r="E320" s="17"/>
       <x:c r="F320" s="17"/>
@@ -7696,7 +7694,7 @@
         <x:v>Пункт онлайн-поддержки 6</x:v>
       </x:c>
       <x:c r="D321" s="11" t="str">
-        <x:v>Устранение повторяющихся неточностей в распознавании и структурировании данных</x:v>
+        <x:v>Помощь</x:v>
       </x:c>
       <x:c r="E321" s="17"/>
       <x:c r="F321" s="17"/>
@@ -7718,7 +7716,7 @@
         <x:v>Пункт онлайн-поддержки 7</x:v>
       </x:c>
       <x:c r="D322" s="11" t="str">
-        <x:v>Проверка качества сохранённых данных</x:v>
+        <x:v>Поддержка</x:v>
       </x:c>
       <x:c r="E322" s="17"/>
       <x:c r="F322" s="17"/>
@@ -7929,16 +7927,16 @@
     </x:row>
     <x:row r="332" ht="15">
       <x:c r="A332" s="23" t="str">
-        <x:v>hero.review_3_role</x:v>
+        <x:v>contact.profession_other</x:v>
       </x:c>
       <x:c r="B332" s="24" t="str">
-        <x:v>Hero</x:v>
+        <x:v>Контакты</x:v>
       </x:c>
       <x:c r="C332" s="25" t="str">
-        <x:v>Роль автора третьего отзыва</x:v>
+        <x:v>Пункт выбора для ввода своей профессии</x:v>
       </x:c>
       <x:c r="D332" s="26" t="str">
-        <x:v>частный специалист</x:v>
+        <x:v>Другое — указать свой вариант</x:v>
       </x:c>
       <x:c r="E332" s="22"/>
       <x:c r="F332" s="22"/>
@@ -8082,10 +8080,18 @@
       <x:c r="L338" s="22"/>
     </x:row>
     <x:row r="339" ht="15">
-      <x:c r="A339" s="23"/>
-      <x:c r="B339" s="27"/>
-      <x:c r="C339" s="28"/>
-      <x:c r="D339" s="29"/>
+      <x:c r="A339" s="23" t="str">
+        <x:v>hero.review_3_role</x:v>
+      </x:c>
+      <x:c r="B339" s="27" t="str">
+        <x:v>Hero</x:v>
+      </x:c>
+      <x:c r="C339" s="28" t="str">
+        <x:v>Роль автора третьего отзыва</x:v>
+      </x:c>
+      <x:c r="D339" s="29" t="str">
+        <x:v>частный специалист</x:v>
+      </x:c>
       <x:c r="E339" s="22"/>
       <x:c r="F339" s="22"/>
       <x:c r="G339" s="22"/>
@@ -8235,6 +8241,28 @@
       <x:c r="K349" s="22"/>
       <x:c r="L349" s="22"/>
     </x:row>
+    <x:row r="350">
+      <x:c r="A350" t="str">
+        <x:v>pricing.plan.custom.feature_7</x:v>
+      </x:c>
+      <x:c r="B350" t="str">
+        <x:v>Стоимость</x:v>
+      </x:c>
+      <x:c r="C350" t="str">
+        <x:v>Пункт индивидуального тарифа 6</x:v>
+      </x:c>
+      <x:c r="D350" t="str">
+        <x:v>2 недели поддержки</x:v>
+      </x:c>
+      <x:c r="E350" t="str"/>
+      <x:c r="F350" t="str"/>
+      <x:c r="G350" t="str"/>
+      <x:c r="H350" t="str"/>
+      <x:c r="I350" t="str"/>
+      <x:c r="J350" t="str"/>
+      <x:c r="K350" t="str"/>
+      <x:c r="L350" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="K2:K331">
@@ -8246,7 +8274,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cdd4010007e4100"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd0732620ce04299"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WebDev\stark-electronic-base\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C476F3A-2BE7-41E1-B3AB-99C05257E0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004086AF-F1AA-45B9-9EAD-7890C6F47C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -751,9 +751,6 @@
     <t>demo.step.visit-details.title</t>
   </si>
   <si>
-    <t>Ассистент возвращает данные в чат</t>
-  </si>
-  <si>
     <t>demo.step.visit-details.description</t>
   </si>
   <si>
@@ -2516,6 +2513,9 @@
   </si>
   <si>
     <t>15 000 ₽</t>
+  </si>
+  <si>
+    <t>В любой момент вы можете запросить сводку по конктеному посещению или по всей истории клиента</t>
   </si>
 </sst>
 </file>
@@ -5004,7 +5004,7 @@
         <v>239</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>241</v>
+        <v>829</v>
       </c>
       <c r="E85" s="17"/>
       <c r="F85" s="17"/>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="86" spans="1:12" ht="30" customHeight="1">
       <c r="A86" s="20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>180</v>
@@ -5026,7 +5026,7 @@
         <v>239</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E86" s="17"/>
       <c r="F86" s="17"/>
@@ -5039,16 +5039,16 @@
     </row>
     <row r="87" spans="1:12" ht="30" customHeight="1">
       <c r="A87" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C87" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="B87" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C87" s="8" t="s">
+      <c r="D87" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>246</v>
       </c>
       <c r="E87" s="17"/>
       <c r="F87" s="17"/>
@@ -5061,16 +5061,16 @@
     </row>
     <row r="88" spans="1:12" ht="30" customHeight="1">
       <c r="A88" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D88" s="11" t="s">
         <v>247</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>248</v>
       </c>
       <c r="E88" s="17"/>
       <c r="F88" s="17"/>
@@ -5083,16 +5083,16 @@
     </row>
     <row r="89" spans="1:12" ht="30" customHeight="1">
       <c r="A89" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D89" s="11" t="s">
         <v>249</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>250</v>
       </c>
       <c r="E89" s="17"/>
       <c r="F89" s="17"/>
@@ -5105,16 +5105,16 @@
     </row>
     <row r="90" spans="1:12" ht="30" customHeight="1">
       <c r="A90" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D90" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>252</v>
       </c>
       <c r="E90" s="17"/>
       <c r="F90" s="17"/>
@@ -5127,16 +5127,16 @@
     </row>
     <row r="91" spans="1:12" ht="30" customHeight="1">
       <c r="A91" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D91" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="E91" s="17"/>
       <c r="F91" s="17"/>
@@ -5149,16 +5149,16 @@
     </row>
     <row r="92" spans="1:12" ht="30" customHeight="1">
       <c r="A92" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D92" s="11" t="s">
         <v>255</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>256</v>
       </c>
       <c r="E92" s="17"/>
       <c r="F92" s="17"/>
@@ -5171,16 +5171,16 @@
     </row>
     <row r="93" spans="1:12" ht="30" customHeight="1">
       <c r="A93" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D93" s="11" t="s">
         <v>257</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>258</v>
       </c>
       <c r="E93" s="17"/>
       <c r="F93" s="17"/>
@@ -5193,16 +5193,16 @@
     </row>
     <row r="94" spans="1:12" ht="30" customHeight="1">
       <c r="A94" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D94" s="11" t="s">
         <v>259</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D94" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="E94" s="17"/>
       <c r="F94" s="17"/>
@@ -5215,16 +5215,16 @@
     </row>
     <row r="95" spans="1:12" ht="30" customHeight="1">
       <c r="A95" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D95" s="11" t="s">
         <v>261</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>262</v>
       </c>
       <c r="E95" s="17"/>
       <c r="F95" s="17"/>
@@ -5237,16 +5237,16 @@
     </row>
     <row r="96" spans="1:12" ht="30" customHeight="1">
       <c r="A96" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D96" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D96" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="E96" s="17"/>
       <c r="F96" s="17"/>
@@ -5259,16 +5259,16 @@
     </row>
     <row r="97" spans="1:12" ht="30" customHeight="1">
       <c r="A97" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D97" s="11" t="s">
         <v>265</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>266</v>
       </c>
       <c r="E97" s="17"/>
       <c r="F97" s="17"/>
@@ -5281,16 +5281,16 @@
     </row>
     <row r="98" spans="1:12" ht="30" customHeight="1">
       <c r="A98" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C98" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="B98" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C98" s="8" t="s">
+      <c r="D98" s="11" t="s">
         <v>268</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>269</v>
       </c>
       <c r="E98" s="17"/>
       <c r="F98" s="17"/>
@@ -5303,16 +5303,16 @@
     </row>
     <row r="99" spans="1:12" ht="30" customHeight="1">
       <c r="A99" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B99" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C99" s="8" t="s">
+      <c r="D99" s="11" t="s">
         <v>271</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>272</v>
       </c>
       <c r="E99" s="17"/>
       <c r="F99" s="17"/>
@@ -5325,16 +5325,16 @@
     </row>
     <row r="100" spans="1:12" ht="30" customHeight="1">
       <c r="A100" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D100" s="11" t="s">
         <v>273</v>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>274</v>
       </c>
       <c r="E100" s="17"/>
       <c r="F100" s="17"/>
@@ -5347,16 +5347,16 @@
     </row>
     <row r="101" spans="1:12" ht="30" customHeight="1">
       <c r="A101" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D101" s="11" t="s">
         <v>275</v>
-      </c>
-      <c r="B101" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>276</v>
       </c>
       <c r="E101" s="17"/>
       <c r="F101" s="17"/>
@@ -5369,16 +5369,16 @@
     </row>
     <row r="102" spans="1:12" ht="30" customHeight="1">
       <c r="A102" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D102" s="11" t="s">
         <v>277</v>
-      </c>
-      <c r="B102" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D102" s="11" t="s">
-        <v>278</v>
       </c>
       <c r="E102" s="17"/>
       <c r="F102" s="17"/>
@@ -5391,16 +5391,16 @@
     </row>
     <row r="103" spans="1:12" ht="30" customHeight="1">
       <c r="A103" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="B103" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D103" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="B103" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D103" s="11" t="s">
-        <v>280</v>
       </c>
       <c r="E103" s="17"/>
       <c r="F103" s="17"/>
@@ -5413,16 +5413,16 @@
     </row>
     <row r="104" spans="1:12" ht="30" customHeight="1">
       <c r="A104" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D104" s="11" t="s">
         <v>281</v>
-      </c>
-      <c r="B104" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D104" s="11" t="s">
-        <v>282</v>
       </c>
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
@@ -5435,16 +5435,16 @@
     </row>
     <row r="105" spans="1:12" ht="30" customHeight="1">
       <c r="A105" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B105" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D105" s="11" t="s">
         <v>283</v>
-      </c>
-      <c r="B105" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D105" s="11" t="s">
-        <v>284</v>
       </c>
       <c r="E105" s="17"/>
       <c r="F105" s="17"/>
@@ -5457,16 +5457,16 @@
     </row>
     <row r="106" spans="1:12" ht="30" customHeight="1">
       <c r="A106" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D106" s="11" t="s">
         <v>285</v>
-      </c>
-      <c r="B106" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D106" s="11" t="s">
-        <v>286</v>
       </c>
       <c r="E106" s="17"/>
       <c r="F106" s="17"/>
@@ -5479,16 +5479,16 @@
     </row>
     <row r="107" spans="1:12" ht="30" customHeight="1">
       <c r="A107" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="B107" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D107" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="B107" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D107" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="E107" s="17"/>
       <c r="F107" s="17"/>
@@ -5501,16 +5501,16 @@
     </row>
     <row r="108" spans="1:12" ht="30" customHeight="1">
       <c r="A108" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="B108" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D108" s="11" t="s">
         <v>289</v>
-      </c>
-      <c r="B108" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D108" s="11" t="s">
-        <v>290</v>
       </c>
       <c r="E108" s="17"/>
       <c r="F108" s="17"/>
@@ -5523,16 +5523,16 @@
     </row>
     <row r="109" spans="1:12" ht="30" customHeight="1">
       <c r="A109" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="B109" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D109" s="11" t="s">
         <v>291</v>
-      </c>
-      <c r="B109" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>292</v>
       </c>
       <c r="E109" s="17"/>
       <c r="F109" s="17"/>
@@ -5545,16 +5545,16 @@
     </row>
     <row r="110" spans="1:12" ht="30" customHeight="1">
       <c r="A110" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="B110" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D110" s="11" t="s">
         <v>293</v>
-      </c>
-      <c r="B110" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>294</v>
       </c>
       <c r="E110" s="17"/>
       <c r="F110" s="17"/>
@@ -5567,16 +5567,16 @@
     </row>
     <row r="111" spans="1:12" ht="30" customHeight="1">
       <c r="A111" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="B111" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D111" s="11" t="s">
         <v>295</v>
-      </c>
-      <c r="B111" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>296</v>
       </c>
       <c r="E111" s="17"/>
       <c r="F111" s="17"/>
@@ -5589,16 +5589,16 @@
     </row>
     <row r="112" spans="1:12" ht="30" customHeight="1">
       <c r="A112" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="B112" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D112" s="11" t="s">
         <v>297</v>
-      </c>
-      <c r="B112" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D112" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="E112" s="17"/>
       <c r="F112" s="17"/>
@@ -5611,16 +5611,16 @@
     </row>
     <row r="113" spans="1:12" ht="30" customHeight="1">
       <c r="A113" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C113" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="B113" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C113" s="8" t="s">
+      <c r="D113" s="11" t="s">
         <v>300</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>301</v>
       </c>
       <c r="E113" s="17"/>
       <c r="F113" s="17"/>
@@ -5633,16 +5633,16 @@
     </row>
     <row r="114" spans="1:12" ht="30" customHeight="1">
       <c r="A114" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="B114" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D114" s="11" t="s">
         <v>302</v>
-      </c>
-      <c r="B114" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D114" s="11" t="s">
-        <v>303</v>
       </c>
       <c r="E114" s="17"/>
       <c r="F114" s="17"/>
@@ -5655,16 +5655,16 @@
     </row>
     <row r="115" spans="1:12" ht="30" customHeight="1">
       <c r="A115" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="B115" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D115" s="11" t="s">
         <v>304</v>
-      </c>
-      <c r="B115" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>305</v>
       </c>
       <c r="E115" s="17"/>
       <c r="F115" s="17"/>
@@ -5677,16 +5677,16 @@
     </row>
     <row r="116" spans="1:12" ht="30" customHeight="1">
       <c r="A116" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="B116" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D116" s="11" t="s">
         <v>306</v>
-      </c>
-      <c r="B116" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>307</v>
       </c>
       <c r="E116" s="17"/>
       <c r="F116" s="17"/>
@@ -5699,16 +5699,16 @@
     </row>
     <row r="117" spans="1:12" ht="30" customHeight="1">
       <c r="A117" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="B117" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D117" s="11" t="s">
         <v>308</v>
-      </c>
-      <c r="B117" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>309</v>
       </c>
       <c r="E117" s="17"/>
       <c r="F117" s="17"/>
@@ -5721,16 +5721,16 @@
     </row>
     <row r="118" spans="1:12" ht="30" customHeight="1">
       <c r="A118" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="B118" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D118" s="11" t="s">
         <v>310</v>
-      </c>
-      <c r="B118" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>311</v>
       </c>
       <c r="E118" s="17"/>
       <c r="F118" s="17"/>
@@ -5743,16 +5743,16 @@
     </row>
     <row r="119" spans="1:12" ht="30" customHeight="1">
       <c r="A119" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D119" s="11" t="s">
         <v>312</v>
-      </c>
-      <c r="B119" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>313</v>
       </c>
       <c r="E119" s="17"/>
       <c r="F119" s="17"/>
@@ -5765,16 +5765,16 @@
     </row>
     <row r="120" spans="1:12" ht="30" customHeight="1">
       <c r="A120" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B120" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D120" s="11" t="s">
         <v>314</v>
-      </c>
-      <c r="B120" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D120" s="11" t="s">
-        <v>315</v>
       </c>
       <c r="E120" s="17"/>
       <c r="F120" s="17"/>
@@ -5787,16 +5787,16 @@
     </row>
     <row r="121" spans="1:12" ht="30" customHeight="1">
       <c r="A121" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="B121" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D121" s="11" t="s">
         <v>316</v>
-      </c>
-      <c r="B121" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D121" s="11" t="s">
-        <v>317</v>
       </c>
       <c r="E121" s="17"/>
       <c r="F121" s="17"/>
@@ -5809,16 +5809,16 @@
     </row>
     <row r="122" spans="1:12" ht="30" customHeight="1">
       <c r="A122" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="B122" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D122" s="11" t="s">
         <v>318</v>
-      </c>
-      <c r="B122" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>319</v>
       </c>
       <c r="E122" s="17"/>
       <c r="F122" s="17"/>
@@ -5831,16 +5831,16 @@
     </row>
     <row r="123" spans="1:12" ht="30" customHeight="1">
       <c r="A123" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B123" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D123" s="11" t="s">
         <v>320</v>
-      </c>
-      <c r="B123" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>321</v>
       </c>
       <c r="E123" s="17"/>
       <c r="F123" s="17"/>
@@ -5853,16 +5853,16 @@
     </row>
     <row r="124" spans="1:12" ht="30" customHeight="1">
       <c r="A124" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="B124" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D124" s="11" t="s">
         <v>322</v>
-      </c>
-      <c r="B124" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D124" s="11" t="s">
-        <v>323</v>
       </c>
       <c r="E124" s="17"/>
       <c r="F124" s="17"/>
@@ -5875,16 +5875,16 @@
     </row>
     <row r="125" spans="1:12" ht="30" customHeight="1">
       <c r="A125" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="B125" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D125" s="11" t="s">
         <v>324</v>
-      </c>
-      <c r="B125" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>325</v>
       </c>
       <c r="E125" s="17"/>
       <c r="F125" s="17"/>
@@ -5897,16 +5897,16 @@
     </row>
     <row r="126" spans="1:12" ht="30" customHeight="1">
       <c r="A126" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B126" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D126" s="11" t="s">
         <v>326</v>
-      </c>
-      <c r="B126" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D126" s="11" t="s">
-        <v>327</v>
       </c>
       <c r="E126" s="17"/>
       <c r="F126" s="17"/>
@@ -5919,16 +5919,16 @@
     </row>
     <row r="127" spans="1:12" ht="30" customHeight="1">
       <c r="A127" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D127" s="11" t="s">
         <v>328</v>
-      </c>
-      <c r="B127" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D127" s="11" t="s">
-        <v>329</v>
       </c>
       <c r="E127" s="17"/>
       <c r="F127" s="17"/>
@@ -5941,16 +5941,16 @@
     </row>
     <row r="128" spans="1:12" ht="30" customHeight="1">
       <c r="A128" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="B128" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D128" s="11" t="s">
         <v>330</v>
-      </c>
-      <c r="B128" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>331</v>
       </c>
       <c r="E128" s="17"/>
       <c r="F128" s="17"/>
@@ -5963,16 +5963,16 @@
     </row>
     <row r="129" spans="1:12" ht="30" customHeight="1">
       <c r="A129" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="B129" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D129" s="11" t="s">
         <v>332</v>
-      </c>
-      <c r="B129" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D129" s="11" t="s">
-        <v>333</v>
       </c>
       <c r="E129" s="17"/>
       <c r="F129" s="17"/>
@@ -5985,16 +5985,16 @@
     </row>
     <row r="130" spans="1:12" ht="30" customHeight="1">
       <c r="A130" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B130" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D130" s="11" t="s">
         <v>334</v>
-      </c>
-      <c r="B130" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D130" s="11" t="s">
-        <v>335</v>
       </c>
       <c r="E130" s="17"/>
       <c r="F130" s="17"/>
@@ -6007,16 +6007,16 @@
     </row>
     <row r="131" spans="1:12" ht="30" customHeight="1">
       <c r="A131" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="B131" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D131" s="11" t="s">
         <v>336</v>
-      </c>
-      <c r="B131" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D131" s="11" t="s">
-        <v>337</v>
       </c>
       <c r="E131" s="17"/>
       <c r="F131" s="17"/>
@@ -6029,16 +6029,16 @@
     </row>
     <row r="132" spans="1:12" ht="30" customHeight="1">
       <c r="A132" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D132" s="11" t="s">
         <v>338</v>
-      </c>
-      <c r="B132" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D132" s="11" t="s">
-        <v>339</v>
       </c>
       <c r="E132" s="17"/>
       <c r="F132" s="17"/>
@@ -6051,16 +6051,16 @@
     </row>
     <row r="133" spans="1:12" ht="30" customHeight="1">
       <c r="A133" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B133" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D133" s="11" t="s">
         <v>340</v>
-      </c>
-      <c r="B133" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D133" s="11" t="s">
-        <v>341</v>
       </c>
       <c r="E133" s="17"/>
       <c r="F133" s="17"/>
@@ -6073,16 +6073,16 @@
     </row>
     <row r="134" spans="1:12" ht="30" customHeight="1">
       <c r="A134" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D134" s="11" t="s">
         <v>342</v>
-      </c>
-      <c r="B134" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D134" s="11" t="s">
-        <v>343</v>
       </c>
       <c r="E134" s="17"/>
       <c r="F134" s="17"/>
@@ -6095,16 +6095,16 @@
     </row>
     <row r="135" spans="1:12" ht="30" customHeight="1">
       <c r="A135" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D135" s="11" t="s">
         <v>344</v>
-      </c>
-      <c r="B135" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D135" s="11" t="s">
-        <v>345</v>
       </c>
       <c r="E135" s="17"/>
       <c r="F135" s="17"/>
@@ -6117,16 +6117,16 @@
     </row>
     <row r="136" spans="1:12" ht="30" customHeight="1">
       <c r="A136" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="B136" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D136" s="11" t="s">
         <v>346</v>
-      </c>
-      <c r="B136" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D136" s="11" t="s">
-        <v>347</v>
       </c>
       <c r="E136" s="17"/>
       <c r="F136" s="17"/>
@@ -6139,16 +6139,16 @@
     </row>
     <row r="137" spans="1:12" ht="30" customHeight="1">
       <c r="A137" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B137" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D137" s="11" t="s">
         <v>348</v>
-      </c>
-      <c r="B137" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D137" s="11" t="s">
-        <v>349</v>
       </c>
       <c r="E137" s="17"/>
       <c r="F137" s="17"/>
@@ -6161,16 +6161,16 @@
     </row>
     <row r="138" spans="1:12" ht="30" customHeight="1">
       <c r="A138" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="B138" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D138" s="11" t="s">
         <v>350</v>
-      </c>
-      <c r="B138" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D138" s="11" t="s">
-        <v>351</v>
       </c>
       <c r="E138" s="17"/>
       <c r="F138" s="17"/>
@@ -6183,16 +6183,16 @@
     </row>
     <row r="139" spans="1:12" ht="30" customHeight="1">
       <c r="A139" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="B139" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D139" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="B139" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D139" s="11" t="s">
-        <v>353</v>
       </c>
       <c r="E139" s="17"/>
       <c r="F139" s="17"/>
@@ -6205,16 +6205,16 @@
     </row>
     <row r="140" spans="1:12" ht="30" customHeight="1">
       <c r="A140" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B140" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D140" s="11" t="s">
         <v>354</v>
-      </c>
-      <c r="B140" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D140" s="11" t="s">
-        <v>355</v>
       </c>
       <c r="E140" s="17"/>
       <c r="F140" s="17"/>
@@ -6227,16 +6227,16 @@
     </row>
     <row r="141" spans="1:12" ht="30" customHeight="1">
       <c r="A141" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="B141" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D141" s="11" t="s">
         <v>356</v>
-      </c>
-      <c r="B141" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D141" s="11" t="s">
-        <v>357</v>
       </c>
       <c r="E141" s="17"/>
       <c r="F141" s="17"/>
@@ -6249,16 +6249,16 @@
     </row>
     <row r="142" spans="1:12" ht="30" customHeight="1">
       <c r="A142" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="B142" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D142" s="11" t="s">
         <v>358</v>
-      </c>
-      <c r="B142" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D142" s="11" t="s">
-        <v>359</v>
       </c>
       <c r="E142" s="17"/>
       <c r="F142" s="17"/>
@@ -6271,16 +6271,16 @@
     </row>
     <row r="143" spans="1:12" ht="30" customHeight="1">
       <c r="A143" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B143" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D143" s="11" t="s">
         <v>360</v>
-      </c>
-      <c r="B143" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D143" s="11" t="s">
-        <v>361</v>
       </c>
       <c r="E143" s="17"/>
       <c r="F143" s="17"/>
@@ -6293,16 +6293,16 @@
     </row>
     <row r="144" spans="1:12" ht="30" customHeight="1">
       <c r="A144" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B144" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D144" s="11" t="s">
         <v>362</v>
-      </c>
-      <c r="B144" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D144" s="11" t="s">
-        <v>363</v>
       </c>
       <c r="E144" s="17"/>
       <c r="F144" s="17"/>
@@ -6315,16 +6315,16 @@
     </row>
     <row r="145" spans="1:12" ht="30" customHeight="1">
       <c r="A145" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="B145" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D145" s="11" t="s">
         <v>364</v>
-      </c>
-      <c r="B145" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D145" s="11" t="s">
-        <v>365</v>
       </c>
       <c r="E145" s="17"/>
       <c r="F145" s="17"/>
@@ -6337,16 +6337,16 @@
     </row>
     <row r="146" spans="1:12" ht="30" customHeight="1">
       <c r="A146" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B146" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D146" s="11" t="s">
         <v>366</v>
-      </c>
-      <c r="B146" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D146" s="11" t="s">
-        <v>367</v>
       </c>
       <c r="E146" s="17"/>
       <c r="F146" s="17"/>
@@ -6359,16 +6359,16 @@
     </row>
     <row r="147" spans="1:12" ht="30" customHeight="1">
       <c r="A147" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B147" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D147" s="11" t="s">
         <v>368</v>
-      </c>
-      <c r="B147" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D147" s="11" t="s">
-        <v>369</v>
       </c>
       <c r="E147" s="17"/>
       <c r="F147" s="17"/>
@@ -6381,16 +6381,16 @@
     </row>
     <row r="148" spans="1:12" ht="30" customHeight="1">
       <c r="A148" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="B148" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C148" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="B148" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C148" s="8" t="s">
+      <c r="D148" s="11" t="s">
         <v>371</v>
-      </c>
-      <c r="D148" s="11" t="s">
-        <v>372</v>
       </c>
       <c r="E148" s="17"/>
       <c r="F148" s="17"/>
@@ -6403,16 +6403,16 @@
     </row>
     <row r="149" spans="1:12" ht="30" customHeight="1">
       <c r="A149" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="B149" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D149" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="B149" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="D149" s="11" t="s">
-        <v>374</v>
       </c>
       <c r="E149" s="17"/>
       <c r="F149" s="17"/>
@@ -6425,16 +6425,16 @@
     </row>
     <row r="150" spans="1:12" ht="30" customHeight="1">
       <c r="A150" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="B150" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D150" s="11" t="s">
         <v>375</v>
-      </c>
-      <c r="B150" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>376</v>
       </c>
       <c r="E150" s="17"/>
       <c r="F150" s="17"/>
@@ -6447,16 +6447,16 @@
     </row>
     <row r="151" spans="1:12" ht="30" customHeight="1">
       <c r="A151" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="B151" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D151" s="11" t="s">
         <v>377</v>
-      </c>
-      <c r="B151" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="D151" s="11" t="s">
-        <v>378</v>
       </c>
       <c r="E151" s="17"/>
       <c r="F151" s="17"/>
@@ -6469,16 +6469,16 @@
     </row>
     <row r="152" spans="1:12" ht="30" customHeight="1">
       <c r="A152" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="B152" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D152" s="11" t="s">
         <v>379</v>
-      </c>
-      <c r="B152" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="D152" s="11" t="s">
-        <v>380</v>
       </c>
       <c r="E152" s="17"/>
       <c r="F152" s="17"/>
@@ -6491,16 +6491,16 @@
     </row>
     <row r="153" spans="1:12" ht="30" customHeight="1">
       <c r="A153" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="B153" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D153" s="11" t="s">
         <v>381</v>
-      </c>
-      <c r="B153" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="D153" s="11" t="s">
-        <v>382</v>
       </c>
       <c r="E153" s="17"/>
       <c r="F153" s="17"/>
@@ -6513,16 +6513,16 @@
     </row>
     <row r="154" spans="1:12" ht="30" customHeight="1">
       <c r="A154" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="B154" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C154" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="B154" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C154" s="8" t="s">
+      <c r="D154" s="11" t="s">
         <v>384</v>
-      </c>
-      <c r="D154" s="11" t="s">
-        <v>385</v>
       </c>
       <c r="E154" s="17"/>
       <c r="F154" s="17"/>
@@ -6535,16 +6535,16 @@
     </row>
     <row r="155" spans="1:12" ht="30" customHeight="1">
       <c r="A155" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="B155" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D155" s="11" t="s">
         <v>386</v>
-      </c>
-      <c r="B155" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D155" s="11" t="s">
-        <v>387</v>
       </c>
       <c r="E155" s="17"/>
       <c r="F155" s="17"/>
@@ -6557,16 +6557,16 @@
     </row>
     <row r="156" spans="1:12" ht="30" customHeight="1">
       <c r="A156" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="B156" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D156" s="11" t="s">
         <v>388</v>
-      </c>
-      <c r="B156" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>389</v>
       </c>
       <c r="E156" s="17"/>
       <c r="F156" s="17"/>
@@ -6579,16 +6579,16 @@
     </row>
     <row r="157" spans="1:12" ht="30" customHeight="1">
       <c r="A157" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="B157" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D157" s="11" t="s">
         <v>390</v>
-      </c>
-      <c r="B157" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D157" s="11" t="s">
-        <v>391</v>
       </c>
       <c r="E157" s="17"/>
       <c r="F157" s="17"/>
@@ -6601,16 +6601,16 @@
     </row>
     <row r="158" spans="1:12" ht="30" customHeight="1">
       <c r="A158" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="B158" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D158" s="11" t="s">
         <v>392</v>
-      </c>
-      <c r="B158" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>393</v>
       </c>
       <c r="E158" s="17"/>
       <c r="F158" s="17"/>
@@ -6623,16 +6623,16 @@
     </row>
     <row r="159" spans="1:12" ht="30" customHeight="1">
       <c r="A159" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="B159" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D159" s="11" t="s">
         <v>394</v>
-      </c>
-      <c r="B159" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D159" s="11" t="s">
-        <v>395</v>
       </c>
       <c r="E159" s="17"/>
       <c r="F159" s="17"/>
@@ -6645,16 +6645,16 @@
     </row>
     <row r="160" spans="1:12" ht="30" customHeight="1">
       <c r="A160" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="B160" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D160" s="11" t="s">
         <v>396</v>
-      </c>
-      <c r="B160" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C160" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D160" s="11" t="s">
-        <v>397</v>
       </c>
       <c r="E160" s="17"/>
       <c r="F160" s="17"/>
@@ -6667,16 +6667,16 @@
     </row>
     <row r="161" spans="1:12" ht="30" customHeight="1">
       <c r="A161" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="B161" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D161" s="11" t="s">
         <v>398</v>
-      </c>
-      <c r="B161" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D161" s="11" t="s">
-        <v>399</v>
       </c>
       <c r="E161" s="17"/>
       <c r="F161" s="17"/>
@@ -6689,16 +6689,16 @@
     </row>
     <row r="162" spans="1:12" ht="30" customHeight="1">
       <c r="A162" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="B162" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D162" s="11" t="s">
         <v>400</v>
-      </c>
-      <c r="B162" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D162" s="11" t="s">
-        <v>401</v>
       </c>
       <c r="E162" s="17"/>
       <c r="F162" s="17"/>
@@ -6711,16 +6711,16 @@
     </row>
     <row r="163" spans="1:12" ht="30" customHeight="1">
       <c r="A163" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="B163" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D163" s="11" t="s">
         <v>402</v>
-      </c>
-      <c r="B163" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C163" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D163" s="11" t="s">
-        <v>403</v>
       </c>
       <c r="E163" s="17"/>
       <c r="F163" s="17"/>
@@ -6733,16 +6733,16 @@
     </row>
     <row r="164" spans="1:12" ht="30" customHeight="1">
       <c r="A164" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="B164" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D164" s="11" t="s">
         <v>404</v>
-      </c>
-      <c r="B164" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D164" s="11" t="s">
-        <v>405</v>
       </c>
       <c r="E164" s="17"/>
       <c r="F164" s="17"/>
@@ -6755,16 +6755,16 @@
     </row>
     <row r="165" spans="1:12" ht="30" customHeight="1">
       <c r="A165" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="B165" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D165" s="11" t="s">
         <v>406</v>
-      </c>
-      <c r="B165" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D165" s="11" t="s">
-        <v>407</v>
       </c>
       <c r="E165" s="17"/>
       <c r="F165" s="17"/>
@@ -6777,16 +6777,16 @@
     </row>
     <row r="166" spans="1:12" ht="30" customHeight="1">
       <c r="A166" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="B166" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D166" s="11" t="s">
         <v>408</v>
-      </c>
-      <c r="B166" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C166" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D166" s="11" t="s">
-        <v>409</v>
       </c>
       <c r="E166" s="17"/>
       <c r="F166" s="17"/>
@@ -6799,16 +6799,16 @@
     </row>
     <row r="167" spans="1:12" ht="30" customHeight="1">
       <c r="A167" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="B167" s="14" t="s">
         <v>410</v>
-      </c>
-      <c r="B167" s="14" t="s">
-        <v>411</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>117</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E167" s="17"/>
       <c r="F167" s="17"/>
@@ -6821,16 +6821,16 @@
     </row>
     <row r="168" spans="1:12" ht="30" customHeight="1">
       <c r="A168" s="20" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>120</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E168" s="17"/>
       <c r="F168" s="17"/>
@@ -6843,16 +6843,16 @@
     </row>
     <row r="169" spans="1:12" ht="30" customHeight="1">
       <c r="A169" s="20" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>123</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E169" s="17"/>
       <c r="F169" s="17"/>
@@ -6865,16 +6865,16 @@
     </row>
     <row r="170" spans="1:12" ht="30" customHeight="1">
       <c r="A170" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B170" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C170" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="B170" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C170" s="8" t="s">
+      <c r="D170" s="11" t="s">
         <v>418</v>
-      </c>
-      <c r="D170" s="11" t="s">
-        <v>419</v>
       </c>
       <c r="E170" s="17"/>
       <c r="F170" s="17"/>
@@ -6887,16 +6887,16 @@
     </row>
     <row r="171" spans="1:12" ht="30" customHeight="1">
       <c r="A171" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="B171" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D171" s="11" t="s">
         <v>420</v>
-      </c>
-      <c r="B171" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D171" s="11" t="s">
-        <v>421</v>
       </c>
       <c r="E171" s="17"/>
       <c r="F171" s="17"/>
@@ -6909,16 +6909,16 @@
     </row>
     <row r="172" spans="1:12" ht="30" customHeight="1">
       <c r="A172" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="B172" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D172" s="11" t="s">
         <v>422</v>
-      </c>
-      <c r="B172" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D172" s="11" t="s">
-        <v>423</v>
       </c>
       <c r="E172" s="17"/>
       <c r="F172" s="17"/>
@@ -6931,16 +6931,16 @@
     </row>
     <row r="173" spans="1:12" ht="30" customHeight="1">
       <c r="A173" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="B173" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D173" s="11" t="s">
         <v>424</v>
-      </c>
-      <c r="B173" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D173" s="11" t="s">
-        <v>425</v>
       </c>
       <c r="E173" s="17"/>
       <c r="F173" s="17"/>
@@ -6953,16 +6953,16 @@
     </row>
     <row r="174" spans="1:12" ht="30" customHeight="1">
       <c r="A174" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="B174" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D174" s="11" t="s">
         <v>426</v>
-      </c>
-      <c r="B174" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D174" s="11" t="s">
-        <v>427</v>
       </c>
       <c r="E174" s="17"/>
       <c r="F174" s="17"/>
@@ -6975,16 +6975,16 @@
     </row>
     <row r="175" spans="1:12" ht="30" customHeight="1">
       <c r="A175" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="B175" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D175" s="11" t="s">
         <v>428</v>
-      </c>
-      <c r="B175" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D175" s="11" t="s">
-        <v>429</v>
       </c>
       <c r="E175" s="17"/>
       <c r="F175" s="17"/>
@@ -6997,16 +6997,16 @@
     </row>
     <row r="176" spans="1:12" ht="30" customHeight="1">
       <c r="A176" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="B176" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D176" s="11" t="s">
         <v>430</v>
-      </c>
-      <c r="B176" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D176" s="11" t="s">
-        <v>431</v>
       </c>
       <c r="E176" s="17"/>
       <c r="F176" s="17"/>
@@ -7019,16 +7019,16 @@
     </row>
     <row r="177" spans="1:12" ht="30" customHeight="1">
       <c r="A177" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="B177" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D177" s="11" t="s">
         <v>432</v>
-      </c>
-      <c r="B177" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D177" s="11" t="s">
-        <v>433</v>
       </c>
       <c r="E177" s="17"/>
       <c r="F177" s="17"/>
@@ -7041,16 +7041,16 @@
     </row>
     <row r="178" spans="1:12" ht="30" customHeight="1">
       <c r="A178" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="B178" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D178" s="11" t="s">
         <v>434</v>
-      </c>
-      <c r="B178" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D178" s="11" t="s">
-        <v>435</v>
       </c>
       <c r="E178" s="17"/>
       <c r="F178" s="17"/>
@@ -7063,16 +7063,16 @@
     </row>
     <row r="179" spans="1:12" ht="30" customHeight="1">
       <c r="A179" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="B179" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D179" s="11" t="s">
         <v>436</v>
-      </c>
-      <c r="B179" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D179" s="11" t="s">
-        <v>437</v>
       </c>
       <c r="E179" s="17"/>
       <c r="F179" s="17"/>
@@ -7085,13 +7085,13 @@
     </row>
     <row r="180" spans="1:12" ht="30" customHeight="1">
       <c r="A180" s="20" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D180" s="11" t="s">
         <v>84</v>
@@ -7107,16 +7107,16 @@
     </row>
     <row r="181" spans="1:12" ht="30" customHeight="1">
       <c r="A181" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="B181" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D181" s="11" t="s">
         <v>439</v>
-      </c>
-      <c r="B181" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C181" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="D181" s="11" t="s">
-        <v>440</v>
       </c>
       <c r="E181" s="17"/>
       <c r="F181" s="17"/>
@@ -7129,16 +7129,16 @@
     </row>
     <row r="182" spans="1:12" ht="30" customHeight="1">
       <c r="A182" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="B182" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C182" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="B182" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C182" s="8" t="s">
+      <c r="D182" s="11" t="s">
         <v>442</v>
-      </c>
-      <c r="D182" s="11" t="s">
-        <v>443</v>
       </c>
       <c r="E182" s="17"/>
       <c r="F182" s="17"/>
@@ -7151,16 +7151,16 @@
     </row>
     <row r="183" spans="1:12" ht="30" customHeight="1">
       <c r="A183" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="B183" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C183" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="B183" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C183" s="8" t="s">
+      <c r="D183" s="11" t="s">
         <v>445</v>
-      </c>
-      <c r="D183" s="11" t="s">
-        <v>446</v>
       </c>
       <c r="E183" s="17"/>
       <c r="F183" s="17"/>
@@ -7173,7 +7173,7 @@
     </row>
     <row r="184" spans="1:12" ht="30" customHeight="1">
       <c r="A184" s="20" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B184" s="14" t="s">
         <v>54</v>
@@ -7182,7 +7182,7 @@
         <v>117</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E184" s="17"/>
       <c r="F184" s="17"/>
@@ -7195,7 +7195,7 @@
     </row>
     <row r="185" spans="1:12" ht="30" customHeight="1">
       <c r="A185" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B185" s="14" t="s">
         <v>54</v>
@@ -7204,7 +7204,7 @@
         <v>120</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E185" s="17"/>
       <c r="F185" s="17"/>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="186" spans="1:12" ht="30" customHeight="1">
       <c r="A186" s="20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B186" s="14" t="s">
         <v>54</v>
@@ -7226,7 +7226,7 @@
         <v>123</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E186" s="17"/>
       <c r="F186" s="17"/>
@@ -7239,16 +7239,16 @@
     </row>
     <row r="187" spans="1:12" ht="30" customHeight="1">
       <c r="A187" s="20" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B187" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C187" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D187" s="11" t="s">
         <v>454</v>
-      </c>
-      <c r="D187" s="11" t="s">
-        <v>455</v>
       </c>
       <c r="E187" s="17"/>
       <c r="F187" s="17"/>
@@ -7261,16 +7261,16 @@
     </row>
     <row r="188" spans="1:12" ht="30" customHeight="1">
       <c r="A188" s="20" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B188" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C188" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="D188" s="11" t="s">
         <v>457</v>
-      </c>
-      <c r="D188" s="11" t="s">
-        <v>458</v>
       </c>
       <c r="E188" s="17"/>
       <c r="F188" s="17"/>
@@ -7283,16 +7283,16 @@
     </row>
     <row r="189" spans="1:12" ht="30" customHeight="1">
       <c r="A189" s="20" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B189" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E189" s="17"/>
       <c r="F189" s="17"/>
@@ -7305,16 +7305,16 @@
     </row>
     <row r="190" spans="1:12" ht="30" customHeight="1">
       <c r="A190" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B190" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E190" s="17"/>
       <c r="F190" s="17"/>
@@ -7327,16 +7327,16 @@
     </row>
     <row r="191" spans="1:12" ht="30" customHeight="1">
       <c r="A191" s="20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B191" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E191" s="17"/>
       <c r="F191" s="17"/>
@@ -7349,16 +7349,16 @@
     </row>
     <row r="192" spans="1:12" ht="30" customHeight="1">
       <c r="A192" s="20" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B192" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E192" s="17"/>
       <c r="F192" s="17"/>
@@ -7371,16 +7371,16 @@
     </row>
     <row r="193" spans="1:12" ht="30" customHeight="1">
       <c r="A193" s="20" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B193" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E193" s="17"/>
       <c r="F193" s="17"/>
@@ -7393,16 +7393,16 @@
     </row>
     <row r="194" spans="1:12" ht="30" customHeight="1">
       <c r="A194" s="20" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B194" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E194" s="17"/>
       <c r="F194" s="17"/>
@@ -7415,16 +7415,16 @@
     </row>
     <row r="195" spans="1:12" ht="30" customHeight="1">
       <c r="A195" s="20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B195" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E195" s="17"/>
       <c r="F195" s="17"/>
@@ -7437,16 +7437,16 @@
     </row>
     <row r="196" spans="1:12" ht="30" customHeight="1">
       <c r="A196" s="20" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B196" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E196" s="17"/>
       <c r="F196" s="17"/>
@@ -7459,16 +7459,16 @@
     </row>
     <row r="197" spans="1:12" ht="30" customHeight="1">
       <c r="A197" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B197" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C197" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="D197" s="11" t="s">
         <v>476</v>
-      </c>
-      <c r="D197" s="11" t="s">
-        <v>477</v>
       </c>
       <c r="E197" s="17"/>
       <c r="F197" s="17"/>
@@ -7481,16 +7481,16 @@
     </row>
     <row r="198" spans="1:12" ht="30" customHeight="1">
       <c r="A198" s="20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B198" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E198" s="17"/>
       <c r="F198" s="17"/>
@@ -7503,13 +7503,13 @@
     </row>
     <row r="199" spans="1:12" ht="30" customHeight="1">
       <c r="A199" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D199" s="11"/>
       <c r="E199" s="17"/>
@@ -7523,16 +7523,16 @@
     </row>
     <row r="200" spans="1:12" ht="30" customHeight="1">
       <c r="A200" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B200" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E200" s="17"/>
       <c r="F200" s="17"/>
@@ -7545,16 +7545,16 @@
     </row>
     <row r="201" spans="1:12" ht="30" customHeight="1">
       <c r="A201" s="20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B201" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E201" s="17"/>
       <c r="F201" s="17"/>
@@ -7567,16 +7567,16 @@
     </row>
     <row r="202" spans="1:12" ht="30" customHeight="1">
       <c r="A202" s="20" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B202" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E202" s="17"/>
       <c r="F202" s="17"/>
@@ -7589,16 +7589,16 @@
     </row>
     <row r="203" spans="1:12" ht="30" customHeight="1">
       <c r="A203" s="20" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B203" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E203" s="17"/>
       <c r="F203" s="17"/>
@@ -7611,16 +7611,16 @@
     </row>
     <row r="204" spans="1:12" ht="30" customHeight="1">
       <c r="A204" s="20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B204" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E204" s="17"/>
       <c r="F204" s="17"/>
@@ -7633,16 +7633,16 @@
     </row>
     <row r="205" spans="1:12" ht="30" customHeight="1">
       <c r="A205" s="20" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B205" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E205" s="17"/>
       <c r="F205" s="17"/>
@@ -7655,16 +7655,16 @@
     </row>
     <row r="206" spans="1:12" ht="30" customHeight="1">
       <c r="A206" s="20" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B206" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C206" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="D206" s="11" t="s">
         <v>494</v>
-      </c>
-      <c r="D206" s="11" t="s">
-        <v>495</v>
       </c>
       <c r="E206" s="17"/>
       <c r="F206" s="17"/>
@@ -7677,16 +7677,16 @@
     </row>
     <row r="207" spans="1:12" ht="30" customHeight="1">
       <c r="A207" s="20" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C207" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="D207" s="11" t="s">
         <v>497</v>
-      </c>
-      <c r="D207" s="11" t="s">
-        <v>498</v>
       </c>
       <c r="E207" s="17"/>
       <c r="F207" s="17"/>
@@ -7699,16 +7699,16 @@
     </row>
     <row r="208" spans="1:12" ht="30" customHeight="1">
       <c r="A208" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B208" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C208" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="D208" s="11" t="s">
         <v>500</v>
-      </c>
-      <c r="D208" s="11" t="s">
-        <v>501</v>
       </c>
       <c r="E208" s="17"/>
       <c r="F208" s="17"/>
@@ -7721,16 +7721,16 @@
     </row>
     <row r="209" spans="1:12" ht="30" customHeight="1">
       <c r="A209" s="20" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B209" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E209" s="17"/>
       <c r="F209" s="17"/>
@@ -7743,16 +7743,16 @@
     </row>
     <row r="210" spans="1:12" ht="30" customHeight="1">
       <c r="A210" s="20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B210" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E210" s="17"/>
       <c r="F210" s="17"/>
@@ -7765,16 +7765,16 @@
     </row>
     <row r="211" spans="1:12" ht="30" customHeight="1">
       <c r="A211" s="20" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C211" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="D211" s="11" t="s">
         <v>507</v>
-      </c>
-      <c r="D211" s="11" t="s">
-        <v>508</v>
       </c>
       <c r="E211" s="17"/>
       <c r="F211" s="17"/>
@@ -7787,16 +7787,16 @@
     </row>
     <row r="212" spans="1:12" ht="30" customHeight="1">
       <c r="A212" s="20" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B212" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E212" s="17"/>
       <c r="F212" s="17"/>
@@ -7809,16 +7809,16 @@
     </row>
     <row r="213" spans="1:12" ht="30" customHeight="1">
       <c r="A213" s="20" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E213" s="17"/>
       <c r="F213" s="17"/>
@@ -7831,16 +7831,16 @@
     </row>
     <row r="214" spans="1:12" ht="30" customHeight="1">
       <c r="A214" s="20" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B214" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E214" s="17"/>
       <c r="F214" s="17"/>
@@ -7853,16 +7853,16 @@
     </row>
     <row r="215" spans="1:12" ht="30" customHeight="1">
       <c r="A215" s="20" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B215" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C215" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="D215" s="11" t="s">
         <v>516</v>
-      </c>
-      <c r="D215" s="11" t="s">
-        <v>517</v>
       </c>
       <c r="E215" s="17"/>
       <c r="F215" s="17"/>
@@ -7875,16 +7875,16 @@
     </row>
     <row r="216" spans="1:12" ht="30" customHeight="1">
       <c r="A216" s="20" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B216" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C216" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="D216" s="11" t="s">
         <v>519</v>
-      </c>
-      <c r="D216" s="11" t="s">
-        <v>520</v>
       </c>
       <c r="E216" s="17"/>
       <c r="F216" s="17"/>
@@ -7897,16 +7897,16 @@
     </row>
     <row r="217" spans="1:12" ht="30" customHeight="1">
       <c r="A217" s="20" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B217" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C217" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="D217" s="11" t="s">
         <v>522</v>
-      </c>
-      <c r="D217" s="11" t="s">
-        <v>523</v>
       </c>
       <c r="E217" s="17"/>
       <c r="F217" s="17"/>
@@ -7919,16 +7919,16 @@
     </row>
     <row r="218" spans="1:12" ht="30" customHeight="1">
       <c r="A218" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="B218" s="14" t="s">
         <v>524</v>
-      </c>
-      <c r="B218" s="14" t="s">
-        <v>525</v>
       </c>
       <c r="C218" s="8" t="s">
         <v>117</v>
       </c>
       <c r="D218" s="11" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E218" s="17"/>
       <c r="F218" s="17"/>
@@ -7941,16 +7941,16 @@
     </row>
     <row r="219" spans="1:12" ht="30" customHeight="1">
       <c r="A219" s="20" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C219" s="8" t="s">
         <v>120</v>
       </c>
       <c r="D219" s="11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E219" s="17"/>
       <c r="F219" s="17"/>
@@ -7963,16 +7963,16 @@
     </row>
     <row r="220" spans="1:12" ht="30" customHeight="1">
       <c r="A220" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C220" s="8" t="s">
         <v>123</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E220" s="17"/>
       <c r="F220" s="17"/>
@@ -7985,16 +7985,16 @@
     </row>
     <row r="221" spans="1:12" ht="30" customHeight="1">
       <c r="A221" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="B221" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C221" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="B221" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C221" s="8" t="s">
+      <c r="D221" s="11" t="s">
         <v>532</v>
-      </c>
-      <c r="D221" s="11" t="s">
-        <v>533</v>
       </c>
       <c r="E221" s="17"/>
       <c r="F221" s="17"/>
@@ -8007,16 +8007,16 @@
     </row>
     <row r="222" spans="1:12" ht="30" customHeight="1">
       <c r="A222" s="20" t="s">
+        <v>533</v>
+      </c>
+      <c r="B222" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C222" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="D222" s="11" t="s">
         <v>534</v>
-      </c>
-      <c r="B222" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C222" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="D222" s="11" t="s">
-        <v>535</v>
       </c>
       <c r="E222" s="17"/>
       <c r="F222" s="17"/>
@@ -8029,16 +8029,16 @@
     </row>
     <row r="223" spans="1:12" ht="30" customHeight="1">
       <c r="A223" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="B223" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C223" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="D223" s="11" t="s">
         <v>536</v>
-      </c>
-      <c r="B223" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C223" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="D223" s="11" t="s">
-        <v>537</v>
       </c>
       <c r="E223" s="17"/>
       <c r="F223" s="17"/>
@@ -8051,16 +8051,16 @@
     </row>
     <row r="224" spans="1:12" ht="30" customHeight="1">
       <c r="A224" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="B224" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C224" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="B224" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C224" s="8" t="s">
+      <c r="D224" s="11" t="s">
         <v>539</v>
-      </c>
-      <c r="D224" s="11" t="s">
-        <v>540</v>
       </c>
       <c r="E224" s="17"/>
       <c r="F224" s="17"/>
@@ -8073,16 +8073,16 @@
     </row>
     <row r="225" spans="1:12" ht="30" customHeight="1">
       <c r="A225" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="B225" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C225" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="B225" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C225" s="8" t="s">
+      <c r="D225" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="D225" s="11" t="s">
-        <v>543</v>
       </c>
       <c r="E225" s="17"/>
       <c r="F225" s="17"/>
@@ -8095,16 +8095,16 @@
     </row>
     <row r="226" spans="1:12" ht="30" customHeight="1">
       <c r="A226" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="B226" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C226" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="B226" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C226" s="8" t="s">
+      <c r="D226" s="11" t="s">
         <v>545</v>
-      </c>
-      <c r="D226" s="11" t="s">
-        <v>546</v>
       </c>
       <c r="E226" s="17"/>
       <c r="F226" s="17"/>
@@ -8117,16 +8117,16 @@
     </row>
     <row r="227" spans="1:12" ht="30" customHeight="1">
       <c r="A227" s="20" t="s">
+        <v>546</v>
+      </c>
+      <c r="B227" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C227" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="B227" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C227" s="8" t="s">
+      <c r="D227" s="11" t="s">
         <v>548</v>
-      </c>
-      <c r="D227" s="11" t="s">
-        <v>549</v>
       </c>
       <c r="E227" s="17"/>
       <c r="F227" s="17"/>
@@ -8139,16 +8139,16 @@
     </row>
     <row r="228" spans="1:12" ht="30" customHeight="1">
       <c r="A228" s="20" t="s">
+        <v>549</v>
+      </c>
+      <c r="B228" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C228" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D228" s="11" t="s">
         <v>550</v>
-      </c>
-      <c r="B228" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C228" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="D228" s="11" t="s">
-        <v>551</v>
       </c>
       <c r="E228" s="17"/>
       <c r="F228" s="17"/>
@@ -8161,16 +8161,16 @@
     </row>
     <row r="229" spans="1:12" ht="30" customHeight="1">
       <c r="A229" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="B229" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C229" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D229" s="11" t="s">
         <v>552</v>
-      </c>
-      <c r="B229" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C229" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="D229" s="11" t="s">
-        <v>553</v>
       </c>
       <c r="E229" s="17"/>
       <c r="F229" s="17"/>
@@ -8183,16 +8183,16 @@
     </row>
     <row r="230" spans="1:12" ht="30" customHeight="1">
       <c r="A230" s="20" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D230" s="11" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E230" s="17"/>
       <c r="F230" s="17"/>
@@ -8205,16 +8205,16 @@
     </row>
     <row r="231" spans="1:12" ht="30" customHeight="1">
       <c r="A231" s="20" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B231" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D231" s="11" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E231" s="17"/>
       <c r="F231" s="17"/>
@@ -8227,16 +8227,16 @@
     </row>
     <row r="232" spans="1:12" ht="30" customHeight="1">
       <c r="A232" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="B232" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C232" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="D232" s="11" t="s">
         <v>556</v>
-      </c>
-      <c r="B232" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C232" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="D232" s="11" t="s">
-        <v>557</v>
       </c>
       <c r="E232" s="17"/>
       <c r="F232" s="17"/>
@@ -8249,16 +8249,16 @@
     </row>
     <row r="233" spans="1:12" ht="30" customHeight="1">
       <c r="A233" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="B233" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C233" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="B233" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C233" s="8" t="s">
+      <c r="D233" s="11" t="s">
         <v>559</v>
-      </c>
-      <c r="D233" s="11" t="s">
-        <v>560</v>
       </c>
       <c r="E233" s="17"/>
       <c r="F233" s="17"/>
@@ -8271,16 +8271,16 @@
     </row>
     <row r="234" spans="1:12" ht="30" customHeight="1">
       <c r="A234" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="B234" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C234" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D234" s="11" t="s">
         <v>561</v>
-      </c>
-      <c r="B234" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C234" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D234" s="11" t="s">
-        <v>562</v>
       </c>
       <c r="E234" s="17"/>
       <c r="F234" s="17"/>
@@ -8293,16 +8293,16 @@
     </row>
     <row r="235" spans="1:12" ht="30" customHeight="1">
       <c r="A235" s="20" t="s">
+        <v>562</v>
+      </c>
+      <c r="B235" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C235" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D235" s="11" t="s">
         <v>563</v>
-      </c>
-      <c r="B235" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C235" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D235" s="11" t="s">
-        <v>564</v>
       </c>
       <c r="E235" s="17"/>
       <c r="F235" s="17"/>
@@ -8315,16 +8315,16 @@
     </row>
     <row r="236" spans="1:12" ht="30" customHeight="1">
       <c r="A236" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="B236" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C236" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D236" s="11" t="s">
         <v>565</v>
-      </c>
-      <c r="B236" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C236" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D236" s="11" t="s">
-        <v>566</v>
       </c>
       <c r="E236" s="17"/>
       <c r="F236" s="17"/>
@@ -8337,16 +8337,16 @@
     </row>
     <row r="237" spans="1:12" ht="30" customHeight="1">
       <c r="A237" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="B237" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C237" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D237" s="11" t="s">
         <v>567</v>
-      </c>
-      <c r="B237" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C237" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D237" s="11" t="s">
-        <v>568</v>
       </c>
       <c r="E237" s="17"/>
       <c r="F237" s="17"/>
@@ -8359,16 +8359,16 @@
     </row>
     <row r="238" spans="1:12" ht="30" customHeight="1">
       <c r="A238" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="B238" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C238" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D238" s="11" t="s">
         <v>569</v>
-      </c>
-      <c r="B238" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C238" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D238" s="11" t="s">
-        <v>570</v>
       </c>
       <c r="E238" s="17"/>
       <c r="F238" s="17"/>
@@ -8381,16 +8381,16 @@
     </row>
     <row r="239" spans="1:12" ht="30" customHeight="1">
       <c r="A239" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="B239" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C239" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="B239" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C239" s="8" t="s">
+      <c r="D239" s="11" t="s">
         <v>572</v>
-      </c>
-      <c r="D239" s="11" t="s">
-        <v>573</v>
       </c>
       <c r="E239" s="17"/>
       <c r="F239" s="17"/>
@@ -8403,16 +8403,16 @@
     </row>
     <row r="240" spans="1:12" ht="30" customHeight="1">
       <c r="A240" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="B240" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C240" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="B240" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C240" s="8" t="s">
+      <c r="D240" s="11" t="s">
         <v>575</v>
-      </c>
-      <c r="D240" s="11" t="s">
-        <v>576</v>
       </c>
       <c r="E240" s="17"/>
       <c r="F240" s="17"/>
@@ -8425,16 +8425,16 @@
     </row>
     <row r="241" spans="1:12" ht="30" customHeight="1">
       <c r="A241" s="20" t="s">
+        <v>576</v>
+      </c>
+      <c r="B241" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C241" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="D241" s="11" t="s">
         <v>577</v>
-      </c>
-      <c r="B241" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C241" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="D241" s="11" t="s">
-        <v>578</v>
       </c>
       <c r="E241" s="17"/>
       <c r="F241" s="17"/>
@@ -8447,16 +8447,16 @@
     </row>
     <row r="242" spans="1:12" ht="30" customHeight="1">
       <c r="A242" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="B242" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C242" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="D242" s="11" t="s">
         <v>579</v>
-      </c>
-      <c r="B242" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C242" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="D242" s="11" t="s">
-        <v>580</v>
       </c>
       <c r="E242" s="17"/>
       <c r="F242" s="17"/>
@@ -8469,16 +8469,16 @@
     </row>
     <row r="243" spans="1:12" ht="30" customHeight="1">
       <c r="A243" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="B243" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C243" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="D243" s="11" t="s">
         <v>581</v>
-      </c>
-      <c r="B243" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C243" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="D243" s="11" t="s">
-        <v>582</v>
       </c>
       <c r="E243" s="17"/>
       <c r="F243" s="17"/>
@@ -8491,16 +8491,16 @@
     </row>
     <row r="244" spans="1:12" ht="30" customHeight="1">
       <c r="A244" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="B244" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C244" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="D244" s="11" t="s">
         <v>583</v>
-      </c>
-      <c r="B244" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C244" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="D244" s="11" t="s">
-        <v>584</v>
       </c>
       <c r="E244" s="17"/>
       <c r="F244" s="17"/>
@@ -8513,16 +8513,16 @@
     </row>
     <row r="245" spans="1:12" ht="30" customHeight="1">
       <c r="A245" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="B245" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C245" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="D245" s="11" t="s">
         <v>585</v>
-      </c>
-      <c r="B245" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C245" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="D245" s="11" t="s">
-        <v>586</v>
       </c>
       <c r="E245" s="17"/>
       <c r="F245" s="17"/>
@@ -8535,16 +8535,16 @@
     </row>
     <row r="246" spans="1:12" ht="30" customHeight="1">
       <c r="A246" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="B246" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C246" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="D246" s="11" t="s">
         <v>587</v>
-      </c>
-      <c r="B246" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C246" s="8" t="s">
-        <v>575</v>
-      </c>
-      <c r="D246" s="11" t="s">
-        <v>588</v>
       </c>
       <c r="E246" s="17"/>
       <c r="F246" s="17"/>
@@ -8557,16 +8557,16 @@
     </row>
     <row r="247" spans="1:12" ht="30" customHeight="1">
       <c r="A247" s="20" t="s">
+        <v>588</v>
+      </c>
+      <c r="B247" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C247" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="B247" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C247" s="8" t="s">
+      <c r="D247" s="11" t="s">
         <v>590</v>
-      </c>
-      <c r="D247" s="11" t="s">
-        <v>591</v>
       </c>
       <c r="E247" s="17"/>
       <c r="F247" s="17"/>
@@ -8579,16 +8579,16 @@
     </row>
     <row r="248" spans="1:12" ht="30" customHeight="1">
       <c r="A248" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="B248" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C248" s="8" t="s">
         <v>592</v>
       </c>
-      <c r="B248" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C248" s="8" t="s">
+      <c r="D248" s="11" t="s">
         <v>593</v>
-      </c>
-      <c r="D248" s="11" t="s">
-        <v>594</v>
       </c>
       <c r="E248" s="17"/>
       <c r="F248" s="17"/>
@@ -8601,16 +8601,16 @@
     </row>
     <row r="249" spans="1:12" ht="30" customHeight="1">
       <c r="A249" s="20" t="s">
+        <v>594</v>
+      </c>
+      <c r="B249" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C249" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="B249" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C249" s="8" t="s">
+      <c r="D249" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="D249" s="11" t="s">
-        <v>597</v>
       </c>
       <c r="E249" s="17"/>
       <c r="F249" s="17"/>
@@ -8623,16 +8623,16 @@
     </row>
     <row r="250" spans="1:12" ht="30" customHeight="1">
       <c r="A250" s="20" t="s">
+        <v>597</v>
+      </c>
+      <c r="B250" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C250" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="B250" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C250" s="8" t="s">
+      <c r="D250" s="11" t="s">
         <v>599</v>
-      </c>
-      <c r="D250" s="11" t="s">
-        <v>600</v>
       </c>
       <c r="E250" s="17"/>
       <c r="F250" s="17"/>
@@ -8645,16 +8645,16 @@
     </row>
     <row r="251" spans="1:12" ht="30" customHeight="1">
       <c r="A251" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="B251" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C251" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="B251" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C251" s="8" t="s">
+      <c r="D251" s="11" t="s">
         <v>602</v>
-      </c>
-      <c r="D251" s="11" t="s">
-        <v>603</v>
       </c>
       <c r="E251" s="17"/>
       <c r="F251" s="17"/>
@@ -8667,16 +8667,16 @@
     </row>
     <row r="252" spans="1:12" ht="30" customHeight="1">
       <c r="A252" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="B252" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C252" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="B252" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C252" s="8" t="s">
+      <c r="D252" s="11" t="s">
         <v>605</v>
-      </c>
-      <c r="D252" s="11" t="s">
-        <v>606</v>
       </c>
       <c r="E252" s="17"/>
       <c r="F252" s="17"/>
@@ -8689,16 +8689,16 @@
     </row>
     <row r="253" spans="1:12" ht="30" customHeight="1">
       <c r="A253" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="B253" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C253" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="B253" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C253" s="8" t="s">
+      <c r="D253" s="11" t="s">
         <v>608</v>
-      </c>
-      <c r="D253" s="11" t="s">
-        <v>609</v>
       </c>
       <c r="E253" s="17"/>
       <c r="F253" s="17"/>
@@ -8711,16 +8711,16 @@
     </row>
     <row r="254" spans="1:12" ht="30" customHeight="1">
       <c r="A254" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="B254" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C254" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="B254" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C254" s="8" t="s">
+      <c r="D254" s="11" t="s">
         <v>611</v>
-      </c>
-      <c r="D254" s="11" t="s">
-        <v>612</v>
       </c>
       <c r="E254" s="17"/>
       <c r="F254" s="17"/>
@@ -8733,16 +8733,16 @@
     </row>
     <row r="255" spans="1:12" ht="30" customHeight="1">
       <c r="A255" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="B255" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C255" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="B255" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C255" s="8" t="s">
+      <c r="D255" s="11" t="s">
         <v>614</v>
-      </c>
-      <c r="D255" s="11" t="s">
-        <v>615</v>
       </c>
       <c r="E255" s="17"/>
       <c r="F255" s="17"/>
@@ -8755,16 +8755,16 @@
     </row>
     <row r="256" spans="1:12" ht="30" customHeight="1">
       <c r="A256" s="20" t="s">
+        <v>615</v>
+      </c>
+      <c r="B256" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C256" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="B256" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C256" s="8" t="s">
+      <c r="D256" s="11" t="s">
         <v>617</v>
-      </c>
-      <c r="D256" s="11" t="s">
-        <v>618</v>
       </c>
       <c r="E256" s="17"/>
       <c r="F256" s="17"/>
@@ -8777,16 +8777,16 @@
     </row>
     <row r="257" spans="1:12" ht="30" customHeight="1">
       <c r="A257" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="B257" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C257" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="B257" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C257" s="8" t="s">
+      <c r="D257" s="11" t="s">
         <v>620</v>
-      </c>
-      <c r="D257" s="11" t="s">
-        <v>621</v>
       </c>
       <c r="E257" s="17"/>
       <c r="F257" s="17"/>
@@ -8799,16 +8799,16 @@
     </row>
     <row r="258" spans="1:12" ht="30" customHeight="1">
       <c r="A258" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="B258" s="14" t="s">
         <v>622</v>
       </c>
-      <c r="B258" s="14" t="s">
+      <c r="C258" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="C258" s="8" t="s">
+      <c r="D258" s="11" t="s">
         <v>624</v>
-      </c>
-      <c r="D258" s="11" t="s">
-        <v>625</v>
       </c>
       <c r="E258" s="17"/>
       <c r="F258" s="17"/>
@@ -8821,16 +8821,16 @@
     </row>
     <row r="259" spans="1:12" ht="30" customHeight="1">
       <c r="A259" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="B259" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="C259" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="B259" s="14" t="s">
-        <v>623</v>
-      </c>
-      <c r="C259" s="8" t="s">
-        <v>627</v>
-      </c>
       <c r="D259" s="11" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E259" s="17"/>
       <c r="F259" s="17"/>
@@ -8843,16 +8843,16 @@
     </row>
     <row r="260" spans="1:12" ht="30" customHeight="1">
       <c r="A260" s="20" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D260" s="11" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E260" s="17"/>
       <c r="F260" s="17"/>
@@ -8865,16 +8865,16 @@
     </row>
     <row r="261" spans="1:12" ht="30" customHeight="1">
       <c r="A261" s="20" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B261" s="14" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D261" s="11" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E261" s="17"/>
       <c r="F261" s="17"/>
@@ -8887,16 +8887,16 @@
     </row>
     <row r="262" spans="1:12" ht="30" customHeight="1">
       <c r="A262" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="B262" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="C262" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="D262" s="11" t="s">
         <v>630</v>
-      </c>
-      <c r="B262" s="14" t="s">
-        <v>623</v>
-      </c>
-      <c r="C262" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="D262" s="11" t="s">
-        <v>631</v>
       </c>
       <c r="E262" s="17"/>
       <c r="F262" s="17"/>
@@ -8909,16 +8909,16 @@
     </row>
     <row r="263" spans="1:12" ht="30" customHeight="1">
       <c r="A263" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="B263" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="C263" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="B263" s="14" t="s">
-        <v>623</v>
-      </c>
-      <c r="C263" s="8" t="s">
+      <c r="D263" s="11" t="s">
         <v>633</v>
-      </c>
-      <c r="D263" s="11" t="s">
-        <v>634</v>
       </c>
       <c r="E263" s="17"/>
       <c r="F263" s="17"/>
@@ -8931,16 +8931,16 @@
     </row>
     <row r="264" spans="1:12" ht="30" customHeight="1">
       <c r="A264" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="B264" s="14" t="s">
         <v>635</v>
       </c>
-      <c r="B264" s="14" t="s">
+      <c r="C264" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="C264" s="8" t="s">
-        <v>637</v>
-      </c>
       <c r="D264" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E264" s="17"/>
       <c r="F264" s="17"/>
@@ -8953,16 +8953,16 @@
     </row>
     <row r="265" spans="1:12" ht="30" customHeight="1">
       <c r="A265" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="B265" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C265" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="B265" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C265" s="8" t="s">
+      <c r="D265" s="11" t="s">
         <v>639</v>
-      </c>
-      <c r="D265" s="11" t="s">
-        <v>640</v>
       </c>
       <c r="E265" s="17"/>
       <c r="F265" s="17"/>
@@ -8975,16 +8975,16 @@
     </row>
     <row r="266" spans="1:12" ht="30" customHeight="1">
       <c r="A266" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="B266" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C266" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="B266" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C266" s="8" t="s">
+      <c r="D266" s="11" t="s">
         <v>642</v>
-      </c>
-      <c r="D266" s="11" t="s">
-        <v>643</v>
       </c>
       <c r="E266" s="17"/>
       <c r="F266" s="17"/>
@@ -8997,16 +8997,16 @@
     </row>
     <row r="267" spans="1:12" ht="30" customHeight="1">
       <c r="A267" s="20" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B267" s="14" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C267" s="8" t="s">
         <v>60</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E267" s="17"/>
       <c r="F267" s="17"/>
@@ -9019,16 +9019,16 @@
     </row>
     <row r="268" spans="1:12" ht="30" customHeight="1">
       <c r="A268" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="B268" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C268" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="B268" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C268" s="8" t="s">
+      <c r="D268" s="11" t="s">
         <v>646</v>
-      </c>
-      <c r="D268" s="11" t="s">
-        <v>647</v>
       </c>
       <c r="E268" s="17"/>
       <c r="F268" s="17"/>
@@ -9041,16 +9041,16 @@
     </row>
     <row r="269" spans="1:12" ht="30" customHeight="1">
       <c r="A269" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="B269" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C269" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="B269" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C269" s="8" t="s">
+      <c r="D269" s="11" t="s">
         <v>649</v>
-      </c>
-      <c r="D269" s="11" t="s">
-        <v>650</v>
       </c>
       <c r="E269" s="17"/>
       <c r="F269" s="17"/>
@@ -9063,16 +9063,16 @@
     </row>
     <row r="270" spans="1:12" ht="30" customHeight="1">
       <c r="A270" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="B270" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C270" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="B270" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C270" s="8" t="s">
+      <c r="D270" s="11" t="s">
         <v>652</v>
-      </c>
-      <c r="D270" s="11" t="s">
-        <v>653</v>
       </c>
       <c r="E270" s="17"/>
       <c r="F270" s="17"/>
@@ -9085,16 +9085,16 @@
     </row>
     <row r="271" spans="1:12" ht="30" customHeight="1">
       <c r="A271" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="B271" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C271" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="D271" s="11" t="s">
         <v>654</v>
-      </c>
-      <c r="B271" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C271" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="D271" s="11" t="s">
-        <v>655</v>
       </c>
       <c r="E271" s="17"/>
       <c r="F271" s="17"/>
@@ -9107,16 +9107,16 @@
     </row>
     <row r="272" spans="1:12" ht="30" customHeight="1">
       <c r="A272" s="20" t="s">
+        <v>655</v>
+      </c>
+      <c r="B272" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C272" s="8" t="s">
         <v>656</v>
       </c>
-      <c r="B272" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C272" s="8" t="s">
+      <c r="D272" s="11" t="s">
         <v>657</v>
-      </c>
-      <c r="D272" s="11" t="s">
-        <v>658</v>
       </c>
       <c r="E272" s="17"/>
       <c r="F272" s="17"/>
@@ -9129,16 +9129,16 @@
     </row>
     <row r="273" spans="1:12" ht="30" customHeight="1">
       <c r="A273" s="20" t="s">
+        <v>658</v>
+      </c>
+      <c r="B273" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C273" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="B273" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C273" s="8" t="s">
+      <c r="D273" s="11" t="s">
         <v>660</v>
-      </c>
-      <c r="D273" s="11" t="s">
-        <v>661</v>
       </c>
       <c r="E273" s="17"/>
       <c r="F273" s="17"/>
@@ -9151,16 +9151,16 @@
     </row>
     <row r="274" spans="1:12" ht="30" customHeight="1">
       <c r="A274" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="B274" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C274" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D274" s="11" t="s">
         <v>662</v>
-      </c>
-      <c r="B274" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C274" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D274" s="11" t="s">
-        <v>663</v>
       </c>
       <c r="E274" s="17"/>
       <c r="F274" s="17"/>
@@ -9173,16 +9173,16 @@
     </row>
     <row r="275" spans="1:12" ht="30" customHeight="1">
       <c r="A275" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="B275" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C275" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D275" s="11" t="s">
         <v>664</v>
-      </c>
-      <c r="B275" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C275" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D275" s="11" t="s">
-        <v>665</v>
       </c>
       <c r="E275" s="17"/>
       <c r="F275" s="17"/>
@@ -9195,16 +9195,16 @@
     </row>
     <row r="276" spans="1:12" ht="30" customHeight="1">
       <c r="A276" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="B276" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C276" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D276" s="11" t="s">
         <v>666</v>
-      </c>
-      <c r="B276" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C276" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D276" s="11" t="s">
-        <v>667</v>
       </c>
       <c r="E276" s="17"/>
       <c r="F276" s="17"/>
@@ -9217,16 +9217,16 @@
     </row>
     <row r="277" spans="1:12" ht="30" customHeight="1">
       <c r="A277" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="B277" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C277" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D277" s="11" t="s">
         <v>668</v>
-      </c>
-      <c r="B277" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C277" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D277" s="11" t="s">
-        <v>669</v>
       </c>
       <c r="E277" s="17"/>
       <c r="F277" s="17"/>
@@ -9239,16 +9239,16 @@
     </row>
     <row r="278" spans="1:12" ht="30" customHeight="1">
       <c r="A278" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="B278" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C278" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D278" s="11" t="s">
         <v>670</v>
-      </c>
-      <c r="B278" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C278" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D278" s="11" t="s">
-        <v>671</v>
       </c>
       <c r="E278" s="17"/>
       <c r="F278" s="17"/>
@@ -9261,16 +9261,16 @@
     </row>
     <row r="279" spans="1:12" ht="30" customHeight="1">
       <c r="A279" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="B279" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C279" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D279" s="11" t="s">
         <v>672</v>
-      </c>
-      <c r="B279" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C279" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D279" s="11" t="s">
-        <v>673</v>
       </c>
       <c r="E279" s="17"/>
       <c r="F279" s="17"/>
@@ -9283,16 +9283,16 @@
     </row>
     <row r="280" spans="1:12" ht="30" customHeight="1">
       <c r="A280" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="B280" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C280" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D280" s="11" t="s">
         <v>674</v>
-      </c>
-      <c r="B280" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C280" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D280" s="11" t="s">
-        <v>675</v>
       </c>
       <c r="E280" s="17"/>
       <c r="F280" s="17"/>
@@ -9305,16 +9305,16 @@
     </row>
     <row r="281" spans="1:12" ht="30" customHeight="1">
       <c r="A281" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="B281" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C281" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D281" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="B281" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C281" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D281" s="11" t="s">
-        <v>677</v>
       </c>
       <c r="E281" s="17"/>
       <c r="F281" s="17"/>
@@ -9327,16 +9327,16 @@
     </row>
     <row r="282" spans="1:12" ht="30" customHeight="1">
       <c r="A282" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="B282" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C282" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D282" s="11" t="s">
         <v>678</v>
-      </c>
-      <c r="B282" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C282" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D282" s="11" t="s">
-        <v>679</v>
       </c>
       <c r="E282" s="17"/>
       <c r="F282" s="17"/>
@@ -9349,16 +9349,16 @@
     </row>
     <row r="283" spans="1:12" ht="30" customHeight="1">
       <c r="A283" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="B283" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C283" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D283" s="11" t="s">
         <v>680</v>
-      </c>
-      <c r="B283" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C283" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D283" s="11" t="s">
-        <v>681</v>
       </c>
       <c r="E283" s="17"/>
       <c r="F283" s="17"/>
@@ -9371,16 +9371,16 @@
     </row>
     <row r="284" spans="1:12" ht="30" customHeight="1">
       <c r="A284" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="B284" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C284" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D284" s="11" t="s">
         <v>682</v>
-      </c>
-      <c r="B284" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C284" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D284" s="11" t="s">
-        <v>683</v>
       </c>
       <c r="E284" s="17"/>
       <c r="F284" s="17"/>
@@ -9393,16 +9393,16 @@
     </row>
     <row r="285" spans="1:12" ht="30" customHeight="1">
       <c r="A285" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="B285" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C285" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D285" s="11" t="s">
         <v>684</v>
-      </c>
-      <c r="B285" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C285" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D285" s="11" t="s">
-        <v>685</v>
       </c>
       <c r="E285" s="17"/>
       <c r="F285" s="17"/>
@@ -9415,16 +9415,16 @@
     </row>
     <row r="286" spans="1:12" ht="30" customHeight="1">
       <c r="A286" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="B286" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="C286" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D286" s="11" t="s">
         <v>686</v>
-      </c>
-      <c r="B286" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="C286" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D286" s="11" t="s">
-        <v>687</v>
       </c>
       <c r="E286" s="17"/>
       <c r="F286" s="17"/>
@@ -9437,16 +9437,16 @@
     </row>
     <row r="287" spans="1:12" ht="30" customHeight="1">
       <c r="A287" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="B287" s="14" t="s">
         <v>688</v>
       </c>
-      <c r="B287" s="14" t="s">
+      <c r="C287" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="C287" s="8" t="s">
+      <c r="D287" s="11" t="s">
         <v>690</v>
-      </c>
-      <c r="D287" s="11" t="s">
-        <v>691</v>
       </c>
       <c r="E287" s="17"/>
       <c r="F287" s="17"/>
@@ -9459,16 +9459,16 @@
     </row>
     <row r="288" spans="1:12" ht="30" customHeight="1">
       <c r="A288" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="B288" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="C288" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="B288" s="14" t="s">
-        <v>689</v>
-      </c>
-      <c r="C288" s="8" t="s">
+      <c r="D288" s="11" t="s">
         <v>693</v>
-      </c>
-      <c r="D288" s="11" t="s">
-        <v>694</v>
       </c>
       <c r="E288" s="17"/>
       <c r="F288" s="17"/>
@@ -9481,16 +9481,16 @@
     </row>
     <row r="289" spans="1:12" ht="30" customHeight="1">
       <c r="A289" s="20" t="s">
+        <v>694</v>
+      </c>
+      <c r="B289" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="C289" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="B289" s="14" t="s">
-        <v>689</v>
-      </c>
-      <c r="C289" s="8" t="s">
+      <c r="D289" s="11" t="s">
         <v>696</v>
-      </c>
-      <c r="D289" s="11" t="s">
-        <v>697</v>
       </c>
       <c r="E289" s="17"/>
       <c r="F289" s="17"/>
@@ -9503,16 +9503,16 @@
     </row>
     <row r="290" spans="1:12" ht="30" customHeight="1">
       <c r="A290" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="B290" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="C290" s="8" t="s">
         <v>698</v>
       </c>
-      <c r="B290" s="14" t="s">
-        <v>689</v>
-      </c>
-      <c r="C290" s="8" t="s">
+      <c r="D290" s="11" t="s">
         <v>699</v>
-      </c>
-      <c r="D290" s="11" t="s">
-        <v>700</v>
       </c>
       <c r="E290" s="17"/>
       <c r="F290" s="17"/>
@@ -9525,16 +9525,16 @@
     </row>
     <row r="291" spans="1:12" ht="30" customHeight="1">
       <c r="A291" s="20" t="s">
+        <v>700</v>
+      </c>
+      <c r="B291" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="C291" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="B291" s="14" t="s">
-        <v>689</v>
-      </c>
-      <c r="C291" s="8" t="s">
+      <c r="D291" s="11" t="s">
         <v>702</v>
-      </c>
-      <c r="D291" s="11" t="s">
-        <v>703</v>
       </c>
       <c r="E291" s="17"/>
       <c r="F291" s="17"/>
@@ -9547,16 +9547,16 @@
     </row>
     <row r="292" spans="1:12" ht="30" customHeight="1">
       <c r="A292" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="B292" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="C292" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="B292" s="14" t="s">
-        <v>689</v>
-      </c>
-      <c r="C292" s="8" t="s">
-        <v>705</v>
-      </c>
       <c r="D292" s="11" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E292" s="17"/>
       <c r="F292" s="17"/>
@@ -9569,16 +9569,16 @@
     </row>
     <row r="293" spans="1:12" ht="30" customHeight="1">
       <c r="A293" s="20" t="s">
+        <v>705</v>
+      </c>
+      <c r="B293" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="C293" s="8" t="s">
         <v>706</v>
       </c>
-      <c r="B293" s="14" t="s">
-        <v>689</v>
-      </c>
-      <c r="C293" s="8" t="s">
+      <c r="D293" s="11" t="s">
         <v>707</v>
-      </c>
-      <c r="D293" s="11" t="s">
-        <v>708</v>
       </c>
       <c r="E293" s="17"/>
       <c r="F293" s="17"/>
@@ -9591,16 +9591,16 @@
     </row>
     <row r="294" spans="1:12" ht="30" customHeight="1">
       <c r="A294" s="20" t="s">
+        <v>708</v>
+      </c>
+      <c r="B294" s="14" t="s">
         <v>709</v>
       </c>
-      <c r="B294" s="14" t="s">
+      <c r="C294" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="C294" s="8" t="s">
+      <c r="D294" s="11" t="s">
         <v>711</v>
-      </c>
-      <c r="D294" s="11" t="s">
-        <v>712</v>
       </c>
       <c r="E294" s="17"/>
       <c r="F294" s="17"/>
@@ -9613,16 +9613,16 @@
     </row>
     <row r="295" spans="1:12" ht="30" customHeight="1">
       <c r="A295" s="20" t="s">
+        <v>712</v>
+      </c>
+      <c r="B295" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="C295" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D295" s="11" t="s">
         <v>713</v>
-      </c>
-      <c r="B295" s="14" t="s">
-        <v>710</v>
-      </c>
-      <c r="C295" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="D295" s="11" t="s">
-        <v>714</v>
       </c>
       <c r="E295" s="17"/>
       <c r="F295" s="17"/>
@@ -9635,16 +9635,16 @@
     </row>
     <row r="296" spans="1:12" ht="30" customHeight="1">
       <c r="A296" s="20" t="s">
+        <v>714</v>
+      </c>
+      <c r="B296" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="C296" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D296" s="11" t="s">
         <v>715</v>
-      </c>
-      <c r="B296" s="14" t="s">
-        <v>710</v>
-      </c>
-      <c r="C296" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="D296" s="11" t="s">
-        <v>716</v>
       </c>
       <c r="E296" s="17"/>
       <c r="F296" s="17"/>
@@ -9657,16 +9657,16 @@
     </row>
     <row r="297" spans="1:12" ht="30" customHeight="1">
       <c r="A297" s="20" t="s">
+        <v>716</v>
+      </c>
+      <c r="B297" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="C297" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D297" s="11" t="s">
         <v>717</v>
-      </c>
-      <c r="B297" s="14" t="s">
-        <v>710</v>
-      </c>
-      <c r="C297" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="D297" s="11" t="s">
-        <v>718</v>
       </c>
       <c r="E297" s="17"/>
       <c r="F297" s="17"/>
@@ -9679,16 +9679,16 @@
     </row>
     <row r="298" spans="1:12" ht="30" customHeight="1">
       <c r="A298" s="20" t="s">
+        <v>718</v>
+      </c>
+      <c r="B298" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="C298" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D298" s="11" t="s">
         <v>719</v>
-      </c>
-      <c r="B298" s="14" t="s">
-        <v>710</v>
-      </c>
-      <c r="C298" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="D298" s="11" t="s">
-        <v>720</v>
       </c>
       <c r="E298" s="17"/>
       <c r="F298" s="17"/>
@@ -9701,16 +9701,16 @@
     </row>
     <row r="299" spans="1:12" ht="30" customHeight="1">
       <c r="A299" s="20" t="s">
+        <v>720</v>
+      </c>
+      <c r="B299" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="C299" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D299" s="11" t="s">
         <v>721</v>
-      </c>
-      <c r="B299" s="14" t="s">
-        <v>710</v>
-      </c>
-      <c r="C299" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="D299" s="11" t="s">
-        <v>722</v>
       </c>
       <c r="E299" s="17"/>
       <c r="F299" s="17"/>
@@ -9723,16 +9723,16 @@
     </row>
     <row r="300" spans="1:12" ht="30" customHeight="1">
       <c r="A300" s="20" t="s">
+        <v>722</v>
+      </c>
+      <c r="B300" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C300" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="B300" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C300" s="8" t="s">
+      <c r="D300" s="11" t="s">
         <v>724</v>
-      </c>
-      <c r="D300" s="11" t="s">
-        <v>725</v>
       </c>
       <c r="E300" s="17"/>
       <c r="F300" s="17"/>
@@ -9745,16 +9745,16 @@
     </row>
     <row r="301" spans="1:12" ht="30" customHeight="1">
       <c r="A301" s="20" t="s">
+        <v>725</v>
+      </c>
+      <c r="B301" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C301" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D301" s="11" t="s">
         <v>726</v>
-      </c>
-      <c r="B301" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C301" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D301" s="11" t="s">
-        <v>727</v>
       </c>
       <c r="E301" s="17"/>
       <c r="F301" s="17"/>
@@ -9767,16 +9767,16 @@
     </row>
     <row r="302" spans="1:12" ht="30" customHeight="1">
       <c r="A302" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="B302" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C302" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D302" s="11" t="s">
         <v>728</v>
-      </c>
-      <c r="B302" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C302" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D302" s="11" t="s">
-        <v>729</v>
       </c>
       <c r="E302" s="17"/>
       <c r="F302" s="17"/>
@@ -9789,16 +9789,16 @@
     </row>
     <row r="303" spans="1:12" ht="30" customHeight="1">
       <c r="A303" s="20" t="s">
+        <v>729</v>
+      </c>
+      <c r="B303" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C303" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D303" s="11" t="s">
         <v>730</v>
-      </c>
-      <c r="B303" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C303" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D303" s="11" t="s">
-        <v>731</v>
       </c>
       <c r="E303" s="17"/>
       <c r="F303" s="17"/>
@@ -9811,16 +9811,16 @@
     </row>
     <row r="304" spans="1:12" ht="30" customHeight="1">
       <c r="A304" s="20" t="s">
+        <v>731</v>
+      </c>
+      <c r="B304" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C304" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D304" s="11" t="s">
         <v>732</v>
-      </c>
-      <c r="B304" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C304" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D304" s="11" t="s">
-        <v>733</v>
       </c>
       <c r="E304" s="17"/>
       <c r="F304" s="17"/>
@@ -9833,16 +9833,16 @@
     </row>
     <row r="305" spans="1:12" ht="30" customHeight="1">
       <c r="A305" s="20" t="s">
+        <v>733</v>
+      </c>
+      <c r="B305" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C305" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D305" s="11" t="s">
         <v>734</v>
-      </c>
-      <c r="B305" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C305" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D305" s="11" t="s">
-        <v>735</v>
       </c>
       <c r="E305" s="17"/>
       <c r="F305" s="17"/>
@@ -9855,16 +9855,16 @@
     </row>
     <row r="306" spans="1:12" ht="30" customHeight="1">
       <c r="A306" s="20" t="s">
+        <v>735</v>
+      </c>
+      <c r="B306" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C306" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D306" s="11" t="s">
         <v>736</v>
-      </c>
-      <c r="B306" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C306" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D306" s="11" t="s">
-        <v>737</v>
       </c>
       <c r="E306" s="17"/>
       <c r="F306" s="17"/>
@@ -9877,16 +9877,16 @@
     </row>
     <row r="307" spans="1:12" ht="30" customHeight="1">
       <c r="A307" s="20" t="s">
+        <v>737</v>
+      </c>
+      <c r="B307" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C307" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D307" s="11" t="s">
         <v>738</v>
-      </c>
-      <c r="B307" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C307" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D307" s="11" t="s">
-        <v>739</v>
       </c>
       <c r="E307" s="17"/>
       <c r="F307" s="17"/>
@@ -9899,16 +9899,16 @@
     </row>
     <row r="308" spans="1:12" ht="30" customHeight="1">
       <c r="A308" s="20" t="s">
+        <v>739</v>
+      </c>
+      <c r="B308" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C308" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D308" s="11" t="s">
         <v>740</v>
-      </c>
-      <c r="B308" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C308" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D308" s="11" t="s">
-        <v>741</v>
       </c>
       <c r="E308" s="17"/>
       <c r="F308" s="17"/>
@@ -9921,16 +9921,16 @@
     </row>
     <row r="309" spans="1:12" ht="30" customHeight="1">
       <c r="A309" s="20" t="s">
+        <v>741</v>
+      </c>
+      <c r="B309" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C309" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D309" s="11" t="s">
         <v>742</v>
-      </c>
-      <c r="B309" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C309" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D309" s="11" t="s">
-        <v>743</v>
       </c>
       <c r="E309" s="17"/>
       <c r="F309" s="17"/>
@@ -9943,16 +9943,16 @@
     </row>
     <row r="310" spans="1:12" ht="30" customHeight="1">
       <c r="A310" s="20" t="s">
+        <v>743</v>
+      </c>
+      <c r="B310" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="C310" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D310" s="11" t="s">
         <v>744</v>
-      </c>
-      <c r="B310" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C310" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D310" s="11" t="s">
-        <v>745</v>
       </c>
       <c r="E310" s="17"/>
       <c r="F310" s="17"/>
@@ -9965,16 +9965,16 @@
     </row>
     <row r="311" spans="1:12" ht="30" customHeight="1">
       <c r="A311" s="20" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B311" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C311" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="D311" s="11" t="s">
         <v>747</v>
-      </c>
-      <c r="D311" s="11" t="s">
-        <v>748</v>
       </c>
       <c r="E311" s="17"/>
       <c r="F311" s="17"/>
@@ -9987,16 +9987,16 @@
     </row>
     <row r="312" spans="1:12" ht="30" customHeight="1">
       <c r="A312" s="20" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B312" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C312" s="8" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D312" s="11" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E312" s="17"/>
       <c r="F312" s="17"/>
@@ -10009,16 +10009,16 @@
     </row>
     <row r="313" spans="1:12" ht="30" customHeight="1">
       <c r="A313" s="20" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B313" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C313" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="D313" s="11" t="s">
         <v>752</v>
-      </c>
-      <c r="D313" s="11" t="s">
-        <v>753</v>
       </c>
       <c r="E313" s="17"/>
       <c r="F313" s="17"/>
@@ -10031,13 +10031,13 @@
     </row>
     <row r="314" spans="1:12" ht="30" customHeight="1">
       <c r="A314" s="20" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B314" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C314" s="8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D314" s="11" t="s">
         <v>76</v>
@@ -10053,16 +10053,16 @@
     </row>
     <row r="315" spans="1:12" ht="30" customHeight="1">
       <c r="A315" s="20" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B315" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C315" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E315" s="17"/>
       <c r="F315" s="17"/>
@@ -10075,16 +10075,16 @@
     </row>
     <row r="316" spans="1:12" ht="30" customHeight="1">
       <c r="A316" s="20" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B316" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C316" s="8" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E316" s="17"/>
       <c r="F316" s="17"/>
@@ -10097,16 +10097,16 @@
     </row>
     <row r="317" spans="1:12" ht="30" customHeight="1">
       <c r="A317" s="20" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B317" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C317" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E317" s="17"/>
       <c r="F317" s="17"/>
@@ -10119,16 +10119,16 @@
     </row>
     <row r="318" spans="1:12" ht="30" customHeight="1">
       <c r="A318" s="20" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B318" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E318" s="17"/>
       <c r="F318" s="17"/>
@@ -10141,16 +10141,16 @@
     </row>
     <row r="319" spans="1:12" ht="30" customHeight="1">
       <c r="A319" s="20" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B319" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C319" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="D319" s="11" t="s">
         <v>765</v>
-      </c>
-      <c r="D319" s="11" t="s">
-        <v>766</v>
       </c>
       <c r="E319" s="17"/>
       <c r="F319" s="17"/>
@@ -10163,16 +10163,16 @@
     </row>
     <row r="320" spans="1:12" ht="30" customHeight="1">
       <c r="A320" s="20" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B320" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C320" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="D320" s="11" t="s">
         <v>768</v>
-      </c>
-      <c r="D320" s="11" t="s">
-        <v>769</v>
       </c>
       <c r="E320" s="17"/>
       <c r="F320" s="17"/>
@@ -10185,16 +10185,16 @@
     </row>
     <row r="321" spans="1:12" ht="30" customHeight="1">
       <c r="A321" s="20" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B321" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C321" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="D321" s="11" t="s">
         <v>771</v>
-      </c>
-      <c r="D321" s="11" t="s">
-        <v>772</v>
       </c>
       <c r="E321" s="17"/>
       <c r="F321" s="17"/>
@@ -10207,16 +10207,16 @@
     </row>
     <row r="322" spans="1:12" ht="30" customHeight="1">
       <c r="A322" s="20" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B322" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C322" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="D322" s="11" t="s">
         <v>774</v>
-      </c>
-      <c r="D322" s="11" t="s">
-        <v>775</v>
       </c>
       <c r="E322" s="17"/>
       <c r="F322" s="17"/>
@@ -10229,16 +10229,16 @@
     </row>
     <row r="323" spans="1:12" ht="30" customHeight="1">
       <c r="A323" s="20" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B323" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C323" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="D323" s="11" t="s">
         <v>777</v>
-      </c>
-      <c r="D323" s="11" t="s">
-        <v>778</v>
       </c>
       <c r="E323" s="17"/>
       <c r="F323" s="17"/>
@@ -10251,16 +10251,16 @@
     </row>
     <row r="324" spans="1:12" ht="30" customHeight="1">
       <c r="A324" s="20" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B324" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C324" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="D324" s="11" t="s">
         <v>780</v>
-      </c>
-      <c r="D324" s="11" t="s">
-        <v>781</v>
       </c>
       <c r="E324" s="17"/>
       <c r="F324" s="17"/>
@@ -10273,16 +10273,16 @@
     </row>
     <row r="325" spans="1:12" ht="30" customHeight="1">
       <c r="A325" s="20" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B325" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C325" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="D325" s="11" t="s">
         <v>783</v>
-      </c>
-      <c r="D325" s="11" t="s">
-        <v>784</v>
       </c>
       <c r="E325" s="17"/>
       <c r="F325" s="17"/>
@@ -10295,16 +10295,16 @@
     </row>
     <row r="326" spans="1:12" ht="30" customHeight="1">
       <c r="A326" s="20" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B326" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C326" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="D326" s="11" t="s">
         <v>786</v>
-      </c>
-      <c r="D326" s="11" t="s">
-        <v>787</v>
       </c>
       <c r="E326" s="17"/>
       <c r="F326" s="17"/>
@@ -10317,16 +10317,16 @@
     </row>
     <row r="327" spans="1:12" ht="30" customHeight="1">
       <c r="A327" s="20" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B327" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C327" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="D327" s="11" t="s">
         <v>789</v>
-      </c>
-      <c r="D327" s="11" t="s">
-        <v>790</v>
       </c>
       <c r="E327" s="17"/>
       <c r="F327" s="17"/>
@@ -10339,16 +10339,16 @@
     </row>
     <row r="328" spans="1:12" ht="30" customHeight="1">
       <c r="A328" s="20" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B328" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C328" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="D328" s="11" t="s">
         <v>792</v>
-      </c>
-      <c r="D328" s="11" t="s">
-        <v>793</v>
       </c>
       <c r="E328" s="17"/>
       <c r="F328" s="17"/>
@@ -10361,16 +10361,16 @@
     </row>
     <row r="329" spans="1:12" ht="30" customHeight="1">
       <c r="A329" s="20" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B329" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C329" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="D329" s="11" t="s">
         <v>795</v>
-      </c>
-      <c r="D329" s="11" t="s">
-        <v>796</v>
       </c>
       <c r="E329" s="17"/>
       <c r="F329" s="17"/>
@@ -10383,16 +10383,16 @@
     </row>
     <row r="330" spans="1:12" ht="30" customHeight="1">
       <c r="A330" s="20" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B330" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C330" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="D330" s="11" t="s">
         <v>798</v>
-      </c>
-      <c r="D330" s="11" t="s">
-        <v>799</v>
       </c>
       <c r="E330" s="17"/>
       <c r="F330" s="17"/>
@@ -10405,16 +10405,16 @@
     </row>
     <row r="331" spans="1:12" ht="30" customHeight="1">
       <c r="A331" s="21" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B331" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C331" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="D331" s="12" t="s">
         <v>801</v>
-      </c>
-      <c r="D331" s="12" t="s">
-        <v>802</v>
       </c>
       <c r="E331" s="18"/>
       <c r="F331" s="18"/>
@@ -10427,16 +10427,16 @@
     </row>
     <row r="332" spans="1:12" ht="15">
       <c r="A332" s="23" t="s">
+        <v>802</v>
+      </c>
+      <c r="B332" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="C332" s="25" t="s">
         <v>803</v>
       </c>
-      <c r="B332" s="24" t="s">
-        <v>525</v>
-      </c>
-      <c r="C332" s="25" t="s">
+      <c r="D332" s="26" t="s">
         <v>804</v>
-      </c>
-      <c r="D332" s="26" t="s">
-        <v>805</v>
       </c>
       <c r="E332" s="22"/>
       <c r="F332" s="22"/>
@@ -10449,16 +10449,16 @@
     </row>
     <row r="333" spans="1:12" ht="15">
       <c r="A333" s="23" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B333" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C333" s="28" t="s">
+        <v>806</v>
+      </c>
+      <c r="D333" s="29" t="s">
         <v>807</v>
-      </c>
-      <c r="D333" s="29" t="s">
-        <v>808</v>
       </c>
       <c r="E333" s="22"/>
       <c r="F333" s="22"/>
@@ -10471,16 +10471,16 @@
     </row>
     <row r="334" spans="1:12" ht="15">
       <c r="A334" s="23" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B334" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C334" s="25" t="s">
+        <v>809</v>
+      </c>
+      <c r="D334" s="26" t="s">
         <v>810</v>
-      </c>
-      <c r="D334" s="26" t="s">
-        <v>811</v>
       </c>
       <c r="E334" s="22"/>
       <c r="F334" s="22"/>
@@ -10493,16 +10493,16 @@
     </row>
     <row r="335" spans="1:12" ht="15">
       <c r="A335" s="23" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B335" s="27" t="s">
         <v>50</v>
       </c>
       <c r="C335" s="28" t="s">
+        <v>812</v>
+      </c>
+      <c r="D335" s="29" t="s">
         <v>813</v>
-      </c>
-      <c r="D335" s="29" t="s">
-        <v>814</v>
       </c>
       <c r="E335" s="22"/>
       <c r="F335" s="22"/>
@@ -10515,16 +10515,16 @@
     </row>
     <row r="336" spans="1:12" ht="15">
       <c r="A336" s="23" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B336" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C336" s="25" t="s">
+        <v>815</v>
+      </c>
+      <c r="D336" s="26" t="s">
         <v>816</v>
-      </c>
-      <c r="D336" s="26" t="s">
-        <v>817</v>
       </c>
       <c r="E336" s="22"/>
       <c r="F336" s="22"/>
@@ -10537,16 +10537,16 @@
     </row>
     <row r="337" spans="1:12" ht="15">
       <c r="A337" s="23" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B337" s="27" t="s">
         <v>50</v>
       </c>
       <c r="C337" s="28" t="s">
+        <v>818</v>
+      </c>
+      <c r="D337" s="29" t="s">
         <v>819</v>
-      </c>
-      <c r="D337" s="29" t="s">
-        <v>820</v>
       </c>
       <c r="E337" s="22"/>
       <c r="F337" s="22"/>
@@ -10559,16 +10559,16 @@
     </row>
     <row r="338" spans="1:12" ht="15">
       <c r="A338" s="23" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B338" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C338" s="25" t="s">
+        <v>821</v>
+      </c>
+      <c r="D338" s="26" t="s">
         <v>822</v>
-      </c>
-      <c r="D338" s="26" t="s">
-        <v>823</v>
       </c>
       <c r="E338" s="22"/>
       <c r="F338" s="22"/>
@@ -10581,16 +10581,16 @@
     </row>
     <row r="339" spans="1:12" ht="15">
       <c r="A339" s="23" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B339" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C339" s="28" t="s">
+        <v>824</v>
+      </c>
+      <c r="D339" s="29" t="s">
         <v>825</v>
-      </c>
-      <c r="D339" s="29" t="s">
-        <v>826</v>
       </c>
       <c r="E339" s="22"/>
       <c r="F339" s="22"/>
@@ -10743,16 +10743,16 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B350" t="s">
         <v>54</v>
       </c>
       <c r="C350" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D350" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>

--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WebDev\stark-electronic-base\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004086AF-F1AA-45B9-9EAD-7890C6F47C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C10BD9-DC3C-4247-95CC-AE9D54868666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -352,9 +352,6 @@
     <t>Первый ответ ассистента</t>
   </si>
   <si>
-    <t>После приёма надиктовываю всё за 2 минуты — раньше на записи и таблицы уходило 15–20. В конце дня остаются силы, а не бумажная рутина.</t>
-  </si>
-  <si>
     <t>hero.audio_short</t>
   </si>
   <si>
@@ -370,9 +367,6 @@
     <t>Второй ответ ассистента</t>
   </si>
   <si>
-    <t>Перед визитом история клиента находится за секунды. Не листаю переписки и сразу помню, что делали и что рекомендовала.</t>
-  </si>
-  <si>
     <t>problem.section</t>
   </si>
   <si>
@@ -2404,9 +2398,6 @@
     <t>Роль автора второго отзыва</t>
   </si>
   <si>
-    <t>мастер ногтевого сервиса</t>
-  </si>
-  <si>
     <t>hero.review_2_metric</t>
   </si>
   <si>
@@ -2422,9 +2413,6 @@
     <t>Текст третьего отзыва</t>
   </si>
   <si>
-    <t>Наконец-то база заполняется по ходу работы, а не поздно вечером. Ничего не забываю и спокойно ухожу домой вовремя.</t>
-  </si>
-  <si>
     <t>hero.review_3_name</t>
   </si>
   <si>
@@ -2503,9 +2491,6 @@
     <t>Роль автора третьего отзыва</t>
   </si>
   <si>
-    <t>частный специалист</t>
-  </si>
-  <si>
     <t>pricing.plan.custom.feature_7</t>
   </si>
   <si>
@@ -2516,6 +2501,21 @@
   </si>
   <si>
     <t>В любой момент вы можете запросить сводку по конктеному посещению или по всей истории клиента</t>
+  </si>
+  <si>
+    <t>После приёма надиктовываю всё за 2 минуты — раньше на записи и таблицы уходило 15–20. Теперь в конце дня остаются силы на себя.</t>
+  </si>
+  <si>
+    <t>Клиент пришёл спустя полгода, а я за минуту подняла всю историю: с чем обращался, что делали и какие были рекомендации. Очень удобно.</t>
+  </si>
+  <si>
+    <t>У меня несколько клиентов подряд, и после рабочего дня уже сложно вспомнить детали каждого. Теперь фиксирую всё сразу и вечером ничего восстанавливать не приходится.</t>
+  </si>
+  <si>
+    <t>психолог</t>
+  </si>
+  <si>
+    <t>стоматолог</t>
   </si>
 </sst>
 </file>
@@ -3734,7 +3734,7 @@
         <v>107</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>108</v>
+        <v>825</v>
       </c>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
@@ -3747,16 +3747,16 @@
     </row>
     <row r="28" spans="1:12" ht="30" customHeight="1">
       <c r="A28" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
@@ -3769,16 +3769,16 @@
     </row>
     <row r="29" spans="1:12" ht="30" customHeight="1">
       <c r="A29" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>114</v>
+        <v>827</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -3791,16 +3791,16 @@
     </row>
     <row r="30" spans="1:12" ht="30" customHeight="1">
       <c r="A30" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="D30" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -3813,16 +3813,16 @@
     </row>
     <row r="31" spans="1:12" ht="30" customHeight="1">
       <c r="A31" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -3835,16 +3835,16 @@
     </row>
     <row r="32" spans="1:12" ht="30" customHeight="1">
       <c r="A32" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>124</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
@@ -3857,16 +3857,16 @@
     </row>
     <row r="33" spans="1:12" ht="30" customHeight="1">
       <c r="A33" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
@@ -3879,16 +3879,16 @@
     </row>
     <row r="34" spans="1:12" ht="30" customHeight="1">
       <c r="A34" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>129</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
@@ -3901,16 +3901,16 @@
     </row>
     <row r="35" spans="1:12" ht="30" customHeight="1">
       <c r="A35" s="20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
@@ -3923,16 +3923,16 @@
     </row>
     <row r="36" spans="1:12" ht="30" customHeight="1">
       <c r="A36" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
@@ -3945,16 +3945,16 @@
     </row>
     <row r="37" spans="1:12" ht="30" customHeight="1">
       <c r="A37" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="17"/>
@@ -3967,16 +3967,16 @@
     </row>
     <row r="38" spans="1:12" ht="30" customHeight="1">
       <c r="A38" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>139</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
@@ -3989,16 +3989,16 @@
     </row>
     <row r="39" spans="1:12" ht="30" customHeight="1">
       <c r="A39" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="17"/>
@@ -4011,16 +4011,16 @@
     </row>
     <row r="40" spans="1:12" ht="30" customHeight="1">
       <c r="A40" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>142</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>144</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
@@ -4033,16 +4033,16 @@
     </row>
     <row r="41" spans="1:12" ht="30" customHeight="1">
       <c r="A41" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="17"/>
@@ -4055,16 +4055,16 @@
     </row>
     <row r="42" spans="1:12" ht="30" customHeight="1">
       <c r="A42" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
@@ -4077,16 +4077,16 @@
     </row>
     <row r="43" spans="1:12" ht="30" customHeight="1">
       <c r="A43" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
@@ -4099,16 +4099,16 @@
     </row>
     <row r="44" spans="1:12" ht="30" customHeight="1">
       <c r="A44" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
@@ -4121,16 +4121,16 @@
     </row>
     <row r="45" spans="1:12" ht="30" customHeight="1">
       <c r="A45" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="17"/>
@@ -4143,16 +4143,16 @@
     </row>
     <row r="46" spans="1:12" ht="30" customHeight="1">
       <c r="A46" s="20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
@@ -4165,16 +4165,16 @@
     </row>
     <row r="47" spans="1:12" ht="30" customHeight="1">
       <c r="A47" s="20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E47" s="17"/>
       <c r="F47" s="17"/>
@@ -4187,16 +4187,16 @@
     </row>
     <row r="48" spans="1:12" ht="30" customHeight="1">
       <c r="A48" s="20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E48" s="17"/>
       <c r="F48" s="17"/>
@@ -4209,16 +4209,16 @@
     </row>
     <row r="49" spans="1:12" ht="30" customHeight="1">
       <c r="A49" s="20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E49" s="17"/>
       <c r="F49" s="17"/>
@@ -4231,16 +4231,16 @@
     </row>
     <row r="50" spans="1:12" ht="30" customHeight="1">
       <c r="A50" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E50" s="17"/>
       <c r="F50" s="17"/>
@@ -4253,16 +4253,16 @@
     </row>
     <row r="51" spans="1:12" ht="30" customHeight="1">
       <c r="A51" s="20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E51" s="17"/>
       <c r="F51" s="17"/>
@@ -4275,16 +4275,16 @@
     </row>
     <row r="52" spans="1:12" ht="30" customHeight="1">
       <c r="A52" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E52" s="17"/>
       <c r="F52" s="17"/>
@@ -4297,16 +4297,16 @@
     </row>
     <row r="53" spans="1:12" ht="30" customHeight="1">
       <c r="A53" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E53" s="17"/>
       <c r="F53" s="17"/>
@@ -4319,16 +4319,16 @@
     </row>
     <row r="54" spans="1:12" ht="30" customHeight="1">
       <c r="A54" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="B54" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>181</v>
       </c>
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
@@ -4341,16 +4341,16 @@
     </row>
     <row r="55" spans="1:12" ht="30" customHeight="1">
       <c r="A55" s="20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E55" s="17"/>
       <c r="F55" s="17"/>
@@ -4363,16 +4363,16 @@
     </row>
     <row r="56" spans="1:12" ht="30" customHeight="1">
       <c r="A56" s="20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E56" s="17"/>
       <c r="F56" s="17"/>
@@ -4385,16 +4385,16 @@
     </row>
     <row r="57" spans="1:12" ht="30" customHeight="1">
       <c r="A57" s="20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E57" s="17"/>
       <c r="F57" s="17"/>
@@ -4407,16 +4407,16 @@
     </row>
     <row r="58" spans="1:12" ht="30" customHeight="1">
       <c r="A58" s="20" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C58" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D58" t="s">
         <v>187</v>
-      </c>
-      <c r="D58" t="s">
-        <v>189</v>
       </c>
       <c r="E58" s="17"/>
       <c r="F58" s="17"/>
@@ -4429,16 +4429,16 @@
     </row>
     <row r="59" spans="1:12" ht="30" customHeight="1">
       <c r="A59" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E59" s="17"/>
       <c r="F59" s="17"/>
@@ -4451,16 +4451,16 @@
     </row>
     <row r="60" spans="1:12" ht="30" customHeight="1">
       <c r="A60" s="20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
@@ -4473,16 +4473,16 @@
     </row>
     <row r="61" spans="1:12" ht="30" customHeight="1">
       <c r="A61" s="20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C61" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D61" s="11" t="s">
         <v>193</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>195</v>
       </c>
       <c r="E61" s="17"/>
       <c r="F61" s="17"/>
@@ -4495,16 +4495,16 @@
     </row>
     <row r="62" spans="1:12" ht="30" customHeight="1">
       <c r="A62" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E62" s="17"/>
       <c r="F62" s="17"/>
@@ -4517,16 +4517,16 @@
     </row>
     <row r="63" spans="1:12" ht="30" customHeight="1">
       <c r="A63" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E63" s="17"/>
       <c r="F63" s="17"/>
@@ -4539,16 +4539,16 @@
     </row>
     <row r="64" spans="1:12" ht="30" customHeight="1">
       <c r="A64" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D64" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>201</v>
       </c>
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
@@ -4561,13 +4561,13 @@
     </row>
     <row r="65" spans="1:12" ht="30" customHeight="1">
       <c r="A65" s="20" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="17"/>
@@ -4581,16 +4581,16 @@
     </row>
     <row r="66" spans="1:12" ht="30" customHeight="1">
       <c r="A66" s="20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
@@ -4603,16 +4603,16 @@
     </row>
     <row r="67" spans="1:12" ht="30" customHeight="1">
       <c r="A67" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C67" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" s="11" t="s">
         <v>204</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>206</v>
       </c>
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
@@ -4625,13 +4625,13 @@
     </row>
     <row r="68" spans="1:12" ht="30" customHeight="1">
       <c r="A68" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D68" s="11"/>
       <c r="E68" s="17"/>
@@ -4645,16 +4645,16 @@
     </row>
     <row r="69" spans="1:12" ht="30" customHeight="1">
       <c r="A69" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D69" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>210</v>
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
@@ -4667,16 +4667,16 @@
     </row>
     <row r="70" spans="1:12" ht="30" customHeight="1">
       <c r="A70" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
@@ -4689,16 +4689,16 @@
     </row>
     <row r="71" spans="1:12" ht="30" customHeight="1">
       <c r="A71" s="20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E71" s="17"/>
       <c r="F71" s="17"/>
@@ -4711,16 +4711,16 @@
     </row>
     <row r="72" spans="1:12" ht="30" customHeight="1">
       <c r="A72" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E72" s="17"/>
       <c r="F72" s="17"/>
@@ -4733,16 +4733,16 @@
     </row>
     <row r="73" spans="1:12" ht="30" customHeight="1">
       <c r="A73" s="20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C73" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D73" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="E73" s="17"/>
       <c r="F73" s="17"/>
@@ -4755,13 +4755,13 @@
     </row>
     <row r="74" spans="1:12" ht="30" customHeight="1">
       <c r="A74" s="20" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="17"/>
@@ -4775,16 +4775,16 @@
     </row>
     <row r="75" spans="1:12" ht="30" customHeight="1">
       <c r="A75" s="20" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E75" s="17"/>
       <c r="F75" s="17"/>
@@ -4797,16 +4797,16 @@
     </row>
     <row r="76" spans="1:12" ht="30" customHeight="1">
       <c r="A76" s="20" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C76" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D76" s="11" t="s">
         <v>221</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="E76" s="17"/>
       <c r="F76" s="17"/>
@@ -4819,16 +4819,16 @@
     </row>
     <row r="77" spans="1:12" ht="30" customHeight="1">
       <c r="A77" s="20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E77" s="17"/>
       <c r="F77" s="17"/>
@@ -4841,16 +4841,16 @@
     </row>
     <row r="78" spans="1:12" ht="30" customHeight="1">
       <c r="A78" s="20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E78" s="17"/>
       <c r="F78" s="17"/>
@@ -4863,16 +4863,16 @@
     </row>
     <row r="79" spans="1:12" ht="30" customHeight="1">
       <c r="A79" s="20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C79" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D79" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>229</v>
       </c>
       <c r="E79" s="17"/>
       <c r="F79" s="17"/>
@@ -4885,16 +4885,16 @@
     </row>
     <row r="80" spans="1:12" ht="30" customHeight="1">
       <c r="A80" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E80" s="17"/>
       <c r="F80" s="17"/>
@@ -4907,16 +4907,16 @@
     </row>
     <row r="81" spans="1:12" ht="30" customHeight="1">
       <c r="A81" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E81" s="17"/>
       <c r="F81" s="17"/>
@@ -4929,16 +4929,16 @@
     </row>
     <row r="82" spans="1:12" ht="30" customHeight="1">
       <c r="A82" s="20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C82" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D82" s="11" t="s">
         <v>233</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>235</v>
       </c>
       <c r="E82" s="17"/>
       <c r="F82" s="17"/>
@@ -4951,16 +4951,16 @@
     </row>
     <row r="83" spans="1:12" ht="30" customHeight="1">
       <c r="A83" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E83" s="17"/>
       <c r="F83" s="17"/>
@@ -4973,16 +4973,16 @@
     </row>
     <row r="84" spans="1:12" ht="30" customHeight="1">
       <c r="A84" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E84" s="17"/>
       <c r="F84" s="17"/>
@@ -4995,16 +4995,16 @@
     </row>
     <row r="85" spans="1:12" ht="30" customHeight="1">
       <c r="A85" s="20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="E85" s="17"/>
       <c r="F85" s="17"/>
@@ -5017,16 +5017,16 @@
     </row>
     <row r="86" spans="1:12" ht="30" customHeight="1">
       <c r="A86" s="20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E86" s="17"/>
       <c r="F86" s="17"/>
@@ -5039,16 +5039,16 @@
     </row>
     <row r="87" spans="1:12" ht="30" customHeight="1">
       <c r="A87" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D87" s="11" t="s">
         <v>243</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="E87" s="17"/>
       <c r="F87" s="17"/>
@@ -5061,16 +5061,16 @@
     </row>
     <row r="88" spans="1:12" ht="30" customHeight="1">
       <c r="A88" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E88" s="17"/>
       <c r="F88" s="17"/>
@@ -5083,16 +5083,16 @@
     </row>
     <row r="89" spans="1:12" ht="30" customHeight="1">
       <c r="A89" s="20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E89" s="17"/>
       <c r="F89" s="17"/>
@@ -5105,16 +5105,16 @@
     </row>
     <row r="90" spans="1:12" ht="30" customHeight="1">
       <c r="A90" s="20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E90" s="17"/>
       <c r="F90" s="17"/>
@@ -5127,16 +5127,16 @@
     </row>
     <row r="91" spans="1:12" ht="30" customHeight="1">
       <c r="A91" s="20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E91" s="17"/>
       <c r="F91" s="17"/>
@@ -5149,16 +5149,16 @@
     </row>
     <row r="92" spans="1:12" ht="30" customHeight="1">
       <c r="A92" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E92" s="17"/>
       <c r="F92" s="17"/>
@@ -5171,16 +5171,16 @@
     </row>
     <row r="93" spans="1:12" ht="30" customHeight="1">
       <c r="A93" s="20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E93" s="17"/>
       <c r="F93" s="17"/>
@@ -5193,16 +5193,16 @@
     </row>
     <row r="94" spans="1:12" ht="30" customHeight="1">
       <c r="A94" s="20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E94" s="17"/>
       <c r="F94" s="17"/>
@@ -5215,16 +5215,16 @@
     </row>
     <row r="95" spans="1:12" ht="30" customHeight="1">
       <c r="A95" s="20" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E95" s="17"/>
       <c r="F95" s="17"/>
@@ -5237,16 +5237,16 @@
     </row>
     <row r="96" spans="1:12" ht="30" customHeight="1">
       <c r="A96" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E96" s="17"/>
       <c r="F96" s="17"/>
@@ -5259,16 +5259,16 @@
     </row>
     <row r="97" spans="1:12" ht="30" customHeight="1">
       <c r="A97" s="20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E97" s="17"/>
       <c r="F97" s="17"/>
@@ -5281,16 +5281,16 @@
     </row>
     <row r="98" spans="1:12" ht="30" customHeight="1">
       <c r="A98" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="D98" s="11" t="s">
         <v>266</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>268</v>
       </c>
       <c r="E98" s="17"/>
       <c r="F98" s="17"/>
@@ -5303,16 +5303,16 @@
     </row>
     <row r="99" spans="1:12" ht="30" customHeight="1">
       <c r="A99" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D99" s="11" t="s">
         <v>269</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>271</v>
       </c>
       <c r="E99" s="17"/>
       <c r="F99" s="17"/>
@@ -5325,16 +5325,16 @@
     </row>
     <row r="100" spans="1:12" ht="30" customHeight="1">
       <c r="A100" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E100" s="17"/>
       <c r="F100" s="17"/>
@@ -5347,16 +5347,16 @@
     </row>
     <row r="101" spans="1:12" ht="30" customHeight="1">
       <c r="A101" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E101" s="17"/>
       <c r="F101" s="17"/>
@@ -5369,16 +5369,16 @@
     </row>
     <row r="102" spans="1:12" ht="30" customHeight="1">
       <c r="A102" s="20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E102" s="17"/>
       <c r="F102" s="17"/>
@@ -5391,16 +5391,16 @@
     </row>
     <row r="103" spans="1:12" ht="30" customHeight="1">
       <c r="A103" s="20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E103" s="17"/>
       <c r="F103" s="17"/>
@@ -5413,16 +5413,16 @@
     </row>
     <row r="104" spans="1:12" ht="30" customHeight="1">
       <c r="A104" s="20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
@@ -5435,16 +5435,16 @@
     </row>
     <row r="105" spans="1:12" ht="30" customHeight="1">
       <c r="A105" s="20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E105" s="17"/>
       <c r="F105" s="17"/>
@@ -5457,16 +5457,16 @@
     </row>
     <row r="106" spans="1:12" ht="30" customHeight="1">
       <c r="A106" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E106" s="17"/>
       <c r="F106" s="17"/>
@@ -5479,16 +5479,16 @@
     </row>
     <row r="107" spans="1:12" ht="30" customHeight="1">
       <c r="A107" s="20" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E107" s="17"/>
       <c r="F107" s="17"/>
@@ -5501,16 +5501,16 @@
     </row>
     <row r="108" spans="1:12" ht="30" customHeight="1">
       <c r="A108" s="20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E108" s="17"/>
       <c r="F108" s="17"/>
@@ -5523,16 +5523,16 @@
     </row>
     <row r="109" spans="1:12" ht="30" customHeight="1">
       <c r="A109" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E109" s="17"/>
       <c r="F109" s="17"/>
@@ -5545,16 +5545,16 @@
     </row>
     <row r="110" spans="1:12" ht="30" customHeight="1">
       <c r="A110" s="20" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E110" s="17"/>
       <c r="F110" s="17"/>
@@ -5567,16 +5567,16 @@
     </row>
     <row r="111" spans="1:12" ht="30" customHeight="1">
       <c r="A111" s="20" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E111" s="17"/>
       <c r="F111" s="17"/>
@@ -5589,16 +5589,16 @@
     </row>
     <row r="112" spans="1:12" ht="30" customHeight="1">
       <c r="A112" s="20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E112" s="17"/>
       <c r="F112" s="17"/>
@@ -5611,16 +5611,16 @@
     </row>
     <row r="113" spans="1:12" ht="30" customHeight="1">
       <c r="A113" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D113" s="11" t="s">
         <v>298</v>
-      </c>
-      <c r="B113" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>300</v>
       </c>
       <c r="E113" s="17"/>
       <c r="F113" s="17"/>
@@ -5633,16 +5633,16 @@
     </row>
     <row r="114" spans="1:12" ht="30" customHeight="1">
       <c r="A114" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E114" s="17"/>
       <c r="F114" s="17"/>
@@ -5655,16 +5655,16 @@
     </row>
     <row r="115" spans="1:12" ht="30" customHeight="1">
       <c r="A115" s="20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E115" s="17"/>
       <c r="F115" s="17"/>
@@ -5677,16 +5677,16 @@
     </row>
     <row r="116" spans="1:12" ht="30" customHeight="1">
       <c r="A116" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E116" s="17"/>
       <c r="F116" s="17"/>
@@ -5699,16 +5699,16 @@
     </row>
     <row r="117" spans="1:12" ht="30" customHeight="1">
       <c r="A117" s="20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E117" s="17"/>
       <c r="F117" s="17"/>
@@ -5721,16 +5721,16 @@
     </row>
     <row r="118" spans="1:12" ht="30" customHeight="1">
       <c r="A118" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E118" s="17"/>
       <c r="F118" s="17"/>
@@ -5743,16 +5743,16 @@
     </row>
     <row r="119" spans="1:12" ht="30" customHeight="1">
       <c r="A119" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E119" s="17"/>
       <c r="F119" s="17"/>
@@ -5765,16 +5765,16 @@
     </row>
     <row r="120" spans="1:12" ht="30" customHeight="1">
       <c r="A120" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E120" s="17"/>
       <c r="F120" s="17"/>
@@ -5787,16 +5787,16 @@
     </row>
     <row r="121" spans="1:12" ht="30" customHeight="1">
       <c r="A121" s="20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E121" s="17"/>
       <c r="F121" s="17"/>
@@ -5809,16 +5809,16 @@
     </row>
     <row r="122" spans="1:12" ht="30" customHeight="1">
       <c r="A122" s="20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E122" s="17"/>
       <c r="F122" s="17"/>
@@ -5831,16 +5831,16 @@
     </row>
     <row r="123" spans="1:12" ht="30" customHeight="1">
       <c r="A123" s="20" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E123" s="17"/>
       <c r="F123" s="17"/>
@@ -5853,16 +5853,16 @@
     </row>
     <row r="124" spans="1:12" ht="30" customHeight="1">
       <c r="A124" s="20" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E124" s="17"/>
       <c r="F124" s="17"/>
@@ -5875,16 +5875,16 @@
     </row>
     <row r="125" spans="1:12" ht="30" customHeight="1">
       <c r="A125" s="20" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E125" s="17"/>
       <c r="F125" s="17"/>
@@ -5897,16 +5897,16 @@
     </row>
     <row r="126" spans="1:12" ht="30" customHeight="1">
       <c r="A126" s="20" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E126" s="17"/>
       <c r="F126" s="17"/>
@@ -5919,16 +5919,16 @@
     </row>
     <row r="127" spans="1:12" ht="30" customHeight="1">
       <c r="A127" s="20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B127" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E127" s="17"/>
       <c r="F127" s="17"/>
@@ -5941,16 +5941,16 @@
     </row>
     <row r="128" spans="1:12" ht="30" customHeight="1">
       <c r="A128" s="20" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E128" s="17"/>
       <c r="F128" s="17"/>
@@ -5963,16 +5963,16 @@
     </row>
     <row r="129" spans="1:12" ht="30" customHeight="1">
       <c r="A129" s="20" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B129" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E129" s="17"/>
       <c r="F129" s="17"/>
@@ -5985,16 +5985,16 @@
     </row>
     <row r="130" spans="1:12" ht="30" customHeight="1">
       <c r="A130" s="20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B130" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E130" s="17"/>
       <c r="F130" s="17"/>
@@ -6007,16 +6007,16 @@
     </row>
     <row r="131" spans="1:12" ht="30" customHeight="1">
       <c r="A131" s="20" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E131" s="17"/>
       <c r="F131" s="17"/>
@@ -6029,16 +6029,16 @@
     </row>
     <row r="132" spans="1:12" ht="30" customHeight="1">
       <c r="A132" s="20" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E132" s="17"/>
       <c r="F132" s="17"/>
@@ -6051,16 +6051,16 @@
     </row>
     <row r="133" spans="1:12" ht="30" customHeight="1">
       <c r="A133" s="20" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E133" s="17"/>
       <c r="F133" s="17"/>
@@ -6073,16 +6073,16 @@
     </row>
     <row r="134" spans="1:12" ht="30" customHeight="1">
       <c r="A134" s="20" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E134" s="17"/>
       <c r="F134" s="17"/>
@@ -6095,16 +6095,16 @@
     </row>
     <row r="135" spans="1:12" ht="30" customHeight="1">
       <c r="A135" s="20" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E135" s="17"/>
       <c r="F135" s="17"/>
@@ -6117,16 +6117,16 @@
     </row>
     <row r="136" spans="1:12" ht="30" customHeight="1">
       <c r="A136" s="20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E136" s="17"/>
       <c r="F136" s="17"/>
@@ -6139,16 +6139,16 @@
     </row>
     <row r="137" spans="1:12" ht="30" customHeight="1">
       <c r="A137" s="20" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B137" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E137" s="17"/>
       <c r="F137" s="17"/>
@@ -6161,16 +6161,16 @@
     </row>
     <row r="138" spans="1:12" ht="30" customHeight="1">
       <c r="A138" s="20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E138" s="17"/>
       <c r="F138" s="17"/>
@@ -6183,16 +6183,16 @@
     </row>
     <row r="139" spans="1:12" ht="30" customHeight="1">
       <c r="A139" s="20" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E139" s="17"/>
       <c r="F139" s="17"/>
@@ -6205,16 +6205,16 @@
     </row>
     <row r="140" spans="1:12" ht="30" customHeight="1">
       <c r="A140" s="20" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B140" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E140" s="17"/>
       <c r="F140" s="17"/>
@@ -6227,16 +6227,16 @@
     </row>
     <row r="141" spans="1:12" ht="30" customHeight="1">
       <c r="A141" s="20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B141" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E141" s="17"/>
       <c r="F141" s="17"/>
@@ -6249,16 +6249,16 @@
     </row>
     <row r="142" spans="1:12" ht="30" customHeight="1">
       <c r="A142" s="20" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B142" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E142" s="17"/>
       <c r="F142" s="17"/>
@@ -6271,16 +6271,16 @@
     </row>
     <row r="143" spans="1:12" ht="30" customHeight="1">
       <c r="A143" s="20" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E143" s="17"/>
       <c r="F143" s="17"/>
@@ -6293,16 +6293,16 @@
     </row>
     <row r="144" spans="1:12" ht="30" customHeight="1">
       <c r="A144" s="20" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E144" s="17"/>
       <c r="F144" s="17"/>
@@ -6315,16 +6315,16 @@
     </row>
     <row r="145" spans="1:12" ht="30" customHeight="1">
       <c r="A145" s="20" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B145" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E145" s="17"/>
       <c r="F145" s="17"/>
@@ -6337,16 +6337,16 @@
     </row>
     <row r="146" spans="1:12" ht="30" customHeight="1">
       <c r="A146" s="20" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B146" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E146" s="17"/>
       <c r="F146" s="17"/>
@@ -6359,16 +6359,16 @@
     </row>
     <row r="147" spans="1:12" ht="30" customHeight="1">
       <c r="A147" s="20" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B147" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E147" s="17"/>
       <c r="F147" s="17"/>
@@ -6381,16 +6381,16 @@
     </row>
     <row r="148" spans="1:12" ht="30" customHeight="1">
       <c r="A148" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B148" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D148" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="B148" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="D148" s="11" t="s">
-        <v>371</v>
       </c>
       <c r="E148" s="17"/>
       <c r="F148" s="17"/>
@@ -6403,16 +6403,16 @@
     </row>
     <row r="149" spans="1:12" ht="30" customHeight="1">
       <c r="A149" s="20" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B149" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E149" s="17"/>
       <c r="F149" s="17"/>
@@ -6425,16 +6425,16 @@
     </row>
     <row r="150" spans="1:12" ht="30" customHeight="1">
       <c r="A150" s="20" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B150" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E150" s="17"/>
       <c r="F150" s="17"/>
@@ -6447,16 +6447,16 @@
     </row>
     <row r="151" spans="1:12" ht="30" customHeight="1">
       <c r="A151" s="20" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B151" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E151" s="17"/>
       <c r="F151" s="17"/>
@@ -6469,16 +6469,16 @@
     </row>
     <row r="152" spans="1:12" ht="30" customHeight="1">
       <c r="A152" s="20" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B152" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E152" s="17"/>
       <c r="F152" s="17"/>
@@ -6491,16 +6491,16 @@
     </row>
     <row r="153" spans="1:12" ht="30" customHeight="1">
       <c r="A153" s="20" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B153" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E153" s="17"/>
       <c r="F153" s="17"/>
@@ -6513,16 +6513,16 @@
     </row>
     <row r="154" spans="1:12" ht="30" customHeight="1">
       <c r="A154" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="B154" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="D154" s="11" t="s">
         <v>382</v>
-      </c>
-      <c r="B154" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="D154" s="11" t="s">
-        <v>384</v>
       </c>
       <c r="E154" s="17"/>
       <c r="F154" s="17"/>
@@ -6535,16 +6535,16 @@
     </row>
     <row r="155" spans="1:12" ht="30" customHeight="1">
       <c r="A155" s="20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B155" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E155" s="17"/>
       <c r="F155" s="17"/>
@@ -6557,16 +6557,16 @@
     </row>
     <row r="156" spans="1:12" ht="30" customHeight="1">
       <c r="A156" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B156" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E156" s="17"/>
       <c r="F156" s="17"/>
@@ -6579,16 +6579,16 @@
     </row>
     <row r="157" spans="1:12" ht="30" customHeight="1">
       <c r="A157" s="20" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B157" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E157" s="17"/>
       <c r="F157" s="17"/>
@@ -6601,16 +6601,16 @@
     </row>
     <row r="158" spans="1:12" ht="30" customHeight="1">
       <c r="A158" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B158" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E158" s="17"/>
       <c r="F158" s="17"/>
@@ -6623,16 +6623,16 @@
     </row>
     <row r="159" spans="1:12" ht="30" customHeight="1">
       <c r="A159" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B159" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E159" s="17"/>
       <c r="F159" s="17"/>
@@ -6645,16 +6645,16 @@
     </row>
     <row r="160" spans="1:12" ht="30" customHeight="1">
       <c r="A160" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B160" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E160" s="17"/>
       <c r="F160" s="17"/>
@@ -6667,16 +6667,16 @@
     </row>
     <row r="161" spans="1:12" ht="30" customHeight="1">
       <c r="A161" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B161" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E161" s="17"/>
       <c r="F161" s="17"/>
@@ -6689,16 +6689,16 @@
     </row>
     <row r="162" spans="1:12" ht="30" customHeight="1">
       <c r="A162" s="20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B162" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E162" s="17"/>
       <c r="F162" s="17"/>
@@ -6711,16 +6711,16 @@
     </row>
     <row r="163" spans="1:12" ht="30" customHeight="1">
       <c r="A163" s="20" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B163" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E163" s="17"/>
       <c r="F163" s="17"/>
@@ -6733,16 +6733,16 @@
     </row>
     <row r="164" spans="1:12" ht="30" customHeight="1">
       <c r="A164" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B164" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E164" s="17"/>
       <c r="F164" s="17"/>
@@ -6755,16 +6755,16 @@
     </row>
     <row r="165" spans="1:12" ht="30" customHeight="1">
       <c r="A165" s="20" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B165" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E165" s="17"/>
       <c r="F165" s="17"/>
@@ -6777,16 +6777,16 @@
     </row>
     <row r="166" spans="1:12" ht="30" customHeight="1">
       <c r="A166" s="20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B166" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E166" s="17"/>
       <c r="F166" s="17"/>
@@ -6799,16 +6799,16 @@
     </row>
     <row r="167" spans="1:12" ht="30" customHeight="1">
       <c r="A167" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="B167" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D167" s="11" t="s">
         <v>409</v>
-      </c>
-      <c r="B167" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D167" s="11" t="s">
-        <v>411</v>
       </c>
       <c r="E167" s="17"/>
       <c r="F167" s="17"/>
@@ -6821,16 +6821,16 @@
     </row>
     <row r="168" spans="1:12" ht="30" customHeight="1">
       <c r="A168" s="20" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E168" s="17"/>
       <c r="F168" s="17"/>
@@ -6843,16 +6843,16 @@
     </row>
     <row r="169" spans="1:12" ht="30" customHeight="1">
       <c r="A169" s="20" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E169" s="17"/>
       <c r="F169" s="17"/>
@@ -6865,16 +6865,16 @@
     </row>
     <row r="170" spans="1:12" ht="30" customHeight="1">
       <c r="A170" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="B170" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="D170" s="11" t="s">
         <v>416</v>
-      </c>
-      <c r="B170" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="D170" s="11" t="s">
-        <v>418</v>
       </c>
       <c r="E170" s="17"/>
       <c r="F170" s="17"/>
@@ -6887,16 +6887,16 @@
     </row>
     <row r="171" spans="1:12" ht="30" customHeight="1">
       <c r="A171" s="20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E171" s="17"/>
       <c r="F171" s="17"/>
@@ -6909,16 +6909,16 @@
     </row>
     <row r="172" spans="1:12" ht="30" customHeight="1">
       <c r="A172" s="20" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E172" s="17"/>
       <c r="F172" s="17"/>
@@ -6931,16 +6931,16 @@
     </row>
     <row r="173" spans="1:12" ht="30" customHeight="1">
       <c r="A173" s="20" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E173" s="17"/>
       <c r="F173" s="17"/>
@@ -6953,16 +6953,16 @@
     </row>
     <row r="174" spans="1:12" ht="30" customHeight="1">
       <c r="A174" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E174" s="17"/>
       <c r="F174" s="17"/>
@@ -6975,16 +6975,16 @@
     </row>
     <row r="175" spans="1:12" ht="30" customHeight="1">
       <c r="A175" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E175" s="17"/>
       <c r="F175" s="17"/>
@@ -6997,16 +6997,16 @@
     </row>
     <row r="176" spans="1:12" ht="30" customHeight="1">
       <c r="A176" s="20" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B176" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E176" s="17"/>
       <c r="F176" s="17"/>
@@ -7019,16 +7019,16 @@
     </row>
     <row r="177" spans="1:12" ht="30" customHeight="1">
       <c r="A177" s="20" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E177" s="17"/>
       <c r="F177" s="17"/>
@@ -7041,16 +7041,16 @@
     </row>
     <row r="178" spans="1:12" ht="30" customHeight="1">
       <c r="A178" s="20" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E178" s="17"/>
       <c r="F178" s="17"/>
@@ -7063,16 +7063,16 @@
     </row>
     <row r="179" spans="1:12" ht="30" customHeight="1">
       <c r="A179" s="20" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E179" s="17"/>
       <c r="F179" s="17"/>
@@ -7085,13 +7085,13 @@
     </row>
     <row r="180" spans="1:12" ht="30" customHeight="1">
       <c r="A180" s="20" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D180" s="11" t="s">
         <v>84</v>
@@ -7107,16 +7107,16 @@
     </row>
     <row r="181" spans="1:12" ht="30" customHeight="1">
       <c r="A181" s="20" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E181" s="17"/>
       <c r="F181" s="17"/>
@@ -7129,16 +7129,16 @@
     </row>
     <row r="182" spans="1:12" ht="30" customHeight="1">
       <c r="A182" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="B182" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="D182" s="11" t="s">
         <v>440</v>
-      </c>
-      <c r="B182" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="D182" s="11" t="s">
-        <v>442</v>
       </c>
       <c r="E182" s="17"/>
       <c r="F182" s="17"/>
@@ -7151,16 +7151,16 @@
     </row>
     <row r="183" spans="1:12" ht="30" customHeight="1">
       <c r="A183" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="B183" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D183" s="11" t="s">
         <v>443</v>
-      </c>
-      <c r="B183" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D183" s="11" t="s">
-        <v>445</v>
       </c>
       <c r="E183" s="17"/>
       <c r="F183" s="17"/>
@@ -7173,16 +7173,16 @@
     </row>
     <row r="184" spans="1:12" ht="30" customHeight="1">
       <c r="A184" s="20" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B184" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E184" s="17"/>
       <c r="F184" s="17"/>
@@ -7195,16 +7195,16 @@
     </row>
     <row r="185" spans="1:12" ht="30" customHeight="1">
       <c r="A185" s="20" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B185" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E185" s="17"/>
       <c r="F185" s="17"/>
@@ -7217,16 +7217,16 @@
     </row>
     <row r="186" spans="1:12" ht="30" customHeight="1">
       <c r="A186" s="20" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B186" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E186" s="17"/>
       <c r="F186" s="17"/>
@@ -7239,16 +7239,16 @@
     </row>
     <row r="187" spans="1:12" ht="30" customHeight="1">
       <c r="A187" s="20" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B187" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E187" s="17"/>
       <c r="F187" s="17"/>
@@ -7261,16 +7261,16 @@
     </row>
     <row r="188" spans="1:12" ht="30" customHeight="1">
       <c r="A188" s="20" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B188" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E188" s="17"/>
       <c r="F188" s="17"/>
@@ -7283,16 +7283,16 @@
     </row>
     <row r="189" spans="1:12" ht="30" customHeight="1">
       <c r="A189" s="20" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B189" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E189" s="17"/>
       <c r="F189" s="17"/>
@@ -7305,16 +7305,16 @@
     </row>
     <row r="190" spans="1:12" ht="30" customHeight="1">
       <c r="A190" s="20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B190" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E190" s="17"/>
       <c r="F190" s="17"/>
@@ -7327,16 +7327,16 @@
     </row>
     <row r="191" spans="1:12" ht="30" customHeight="1">
       <c r="A191" s="20" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B191" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E191" s="17"/>
       <c r="F191" s="17"/>
@@ -7349,16 +7349,16 @@
     </row>
     <row r="192" spans="1:12" ht="30" customHeight="1">
       <c r="A192" s="20" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B192" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E192" s="17"/>
       <c r="F192" s="17"/>
@@ -7371,16 +7371,16 @@
     </row>
     <row r="193" spans="1:12" ht="30" customHeight="1">
       <c r="A193" s="20" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B193" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E193" s="17"/>
       <c r="F193" s="17"/>
@@ -7393,16 +7393,16 @@
     </row>
     <row r="194" spans="1:12" ht="30" customHeight="1">
       <c r="A194" s="20" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B194" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E194" s="17"/>
       <c r="F194" s="17"/>
@@ -7415,16 +7415,16 @@
     </row>
     <row r="195" spans="1:12" ht="30" customHeight="1">
       <c r="A195" s="20" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B195" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E195" s="17"/>
       <c r="F195" s="17"/>
@@ -7437,16 +7437,16 @@
     </row>
     <row r="196" spans="1:12" ht="30" customHeight="1">
       <c r="A196" s="20" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B196" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E196" s="17"/>
       <c r="F196" s="17"/>
@@ -7459,16 +7459,16 @@
     </row>
     <row r="197" spans="1:12" ht="30" customHeight="1">
       <c r="A197" s="20" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B197" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E197" s="17"/>
       <c r="F197" s="17"/>
@@ -7481,16 +7481,16 @@
     </row>
     <row r="198" spans="1:12" ht="30" customHeight="1">
       <c r="A198" s="20" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B198" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E198" s="17"/>
       <c r="F198" s="17"/>
@@ -7503,13 +7503,13 @@
     </row>
     <row r="199" spans="1:12" ht="30" customHeight="1">
       <c r="A199" s="20" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D199" s="11"/>
       <c r="E199" s="17"/>
@@ -7523,16 +7523,16 @@
     </row>
     <row r="200" spans="1:12" ht="30" customHeight="1">
       <c r="A200" s="20" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B200" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E200" s="17"/>
       <c r="F200" s="17"/>
@@ -7545,16 +7545,16 @@
     </row>
     <row r="201" spans="1:12" ht="30" customHeight="1">
       <c r="A201" s="20" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B201" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E201" s="17"/>
       <c r="F201" s="17"/>
@@ -7567,16 +7567,16 @@
     </row>
     <row r="202" spans="1:12" ht="30" customHeight="1">
       <c r="A202" s="20" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B202" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E202" s="17"/>
       <c r="F202" s="17"/>
@@ -7589,16 +7589,16 @@
     </row>
     <row r="203" spans="1:12" ht="30" customHeight="1">
       <c r="A203" s="20" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B203" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E203" s="17"/>
       <c r="F203" s="17"/>
@@ -7611,16 +7611,16 @@
     </row>
     <row r="204" spans="1:12" ht="30" customHeight="1">
       <c r="A204" s="20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B204" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E204" s="17"/>
       <c r="F204" s="17"/>
@@ -7633,16 +7633,16 @@
     </row>
     <row r="205" spans="1:12" ht="30" customHeight="1">
       <c r="A205" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B205" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E205" s="17"/>
       <c r="F205" s="17"/>
@@ -7655,16 +7655,16 @@
     </row>
     <row r="206" spans="1:12" ht="30" customHeight="1">
       <c r="A206" s="20" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B206" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D206" s="11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E206" s="17"/>
       <c r="F206" s="17"/>
@@ -7677,16 +7677,16 @@
     </row>
     <row r="207" spans="1:12" ht="30" customHeight="1">
       <c r="A207" s="20" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E207" s="17"/>
       <c r="F207" s="17"/>
@@ -7699,16 +7699,16 @@
     </row>
     <row r="208" spans="1:12" ht="30" customHeight="1">
       <c r="A208" s="20" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B208" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E208" s="17"/>
       <c r="F208" s="17"/>
@@ -7721,16 +7721,16 @@
     </row>
     <row r="209" spans="1:12" ht="30" customHeight="1">
       <c r="A209" s="20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B209" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E209" s="17"/>
       <c r="F209" s="17"/>
@@ -7743,16 +7743,16 @@
     </row>
     <row r="210" spans="1:12" ht="30" customHeight="1">
       <c r="A210" s="20" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B210" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E210" s="17"/>
       <c r="F210" s="17"/>
@@ -7765,16 +7765,16 @@
     </row>
     <row r="211" spans="1:12" ht="30" customHeight="1">
       <c r="A211" s="20" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D211" s="11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E211" s="17"/>
       <c r="F211" s="17"/>
@@ -7787,16 +7787,16 @@
     </row>
     <row r="212" spans="1:12" ht="30" customHeight="1">
       <c r="A212" s="20" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B212" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E212" s="17"/>
       <c r="F212" s="17"/>
@@ -7809,16 +7809,16 @@
     </row>
     <row r="213" spans="1:12" ht="30" customHeight="1">
       <c r="A213" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E213" s="17"/>
       <c r="F213" s="17"/>
@@ -7831,16 +7831,16 @@
     </row>
     <row r="214" spans="1:12" ht="30" customHeight="1">
       <c r="A214" s="20" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B214" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E214" s="17"/>
       <c r="F214" s="17"/>
@@ -7853,16 +7853,16 @@
     </row>
     <row r="215" spans="1:12" ht="30" customHeight="1">
       <c r="A215" s="20" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B215" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E215" s="17"/>
       <c r="F215" s="17"/>
@@ -7875,16 +7875,16 @@
     </row>
     <row r="216" spans="1:12" ht="30" customHeight="1">
       <c r="A216" s="20" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B216" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D216" s="11" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E216" s="17"/>
       <c r="F216" s="17"/>
@@ -7897,16 +7897,16 @@
     </row>
     <row r="217" spans="1:12" ht="30" customHeight="1">
       <c r="A217" s="20" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B217" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E217" s="17"/>
       <c r="F217" s="17"/>
@@ -7919,16 +7919,16 @@
     </row>
     <row r="218" spans="1:12" ht="30" customHeight="1">
       <c r="A218" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="B218" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C218" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D218" s="11" t="s">
         <v>523</v>
-      </c>
-      <c r="B218" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C218" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D218" s="11" t="s">
-        <v>525</v>
       </c>
       <c r="E218" s="17"/>
       <c r="F218" s="17"/>
@@ -7941,16 +7941,16 @@
     </row>
     <row r="219" spans="1:12" ht="30" customHeight="1">
       <c r="A219" s="20" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D219" s="11" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E219" s="17"/>
       <c r="F219" s="17"/>
@@ -7963,16 +7963,16 @@
     </row>
     <row r="220" spans="1:12" ht="30" customHeight="1">
       <c r="A220" s="20" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C220" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E220" s="17"/>
       <c r="F220" s="17"/>
@@ -7985,16 +7985,16 @@
     </row>
     <row r="221" spans="1:12" ht="30" customHeight="1">
       <c r="A221" s="20" t="s">
+        <v>528</v>
+      </c>
+      <c r="B221" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C221" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="D221" s="11" t="s">
         <v>530</v>
-      </c>
-      <c r="B221" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C221" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="D221" s="11" t="s">
-        <v>532</v>
       </c>
       <c r="E221" s="17"/>
       <c r="F221" s="17"/>
@@ -8007,16 +8007,16 @@
     </row>
     <row r="222" spans="1:12" ht="30" customHeight="1">
       <c r="A222" s="20" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D222" s="11" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E222" s="17"/>
       <c r="F222" s="17"/>
@@ -8029,16 +8029,16 @@
     </row>
     <row r="223" spans="1:12" ht="30" customHeight="1">
       <c r="A223" s="20" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B223" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D223" s="11" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E223" s="17"/>
       <c r="F223" s="17"/>
@@ -8051,16 +8051,16 @@
     </row>
     <row r="224" spans="1:12" ht="30" customHeight="1">
       <c r="A224" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="B224" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C224" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="D224" s="11" t="s">
         <v>537</v>
-      </c>
-      <c r="B224" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C224" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="D224" s="11" t="s">
-        <v>539</v>
       </c>
       <c r="E224" s="17"/>
       <c r="F224" s="17"/>
@@ -8073,16 +8073,16 @@
     </row>
     <row r="225" spans="1:12" ht="30" customHeight="1">
       <c r="A225" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="B225" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C225" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="D225" s="11" t="s">
         <v>540</v>
-      </c>
-      <c r="B225" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C225" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="D225" s="11" t="s">
-        <v>542</v>
       </c>
       <c r="E225" s="17"/>
       <c r="F225" s="17"/>
@@ -8095,16 +8095,16 @@
     </row>
     <row r="226" spans="1:12" ht="30" customHeight="1">
       <c r="A226" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="B226" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C226" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="D226" s="11" t="s">
         <v>543</v>
-      </c>
-      <c r="B226" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C226" s="8" t="s">
-        <v>544</v>
-      </c>
-      <c r="D226" s="11" t="s">
-        <v>545</v>
       </c>
       <c r="E226" s="17"/>
       <c r="F226" s="17"/>
@@ -8117,16 +8117,16 @@
     </row>
     <row r="227" spans="1:12" ht="30" customHeight="1">
       <c r="A227" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="B227" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C227" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="D227" s="11" t="s">
         <v>546</v>
-      </c>
-      <c r="B227" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C227" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="D227" s="11" t="s">
-        <v>548</v>
       </c>
       <c r="E227" s="17"/>
       <c r="F227" s="17"/>
@@ -8139,16 +8139,16 @@
     </row>
     <row r="228" spans="1:12" ht="30" customHeight="1">
       <c r="A228" s="20" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B228" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E228" s="17"/>
       <c r="F228" s="17"/>
@@ -8161,16 +8161,16 @@
     </row>
     <row r="229" spans="1:12" ht="30" customHeight="1">
       <c r="A229" s="20" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B229" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D229" s="11" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E229" s="17"/>
       <c r="F229" s="17"/>
@@ -8183,16 +8183,16 @@
     </row>
     <row r="230" spans="1:12" ht="30" customHeight="1">
       <c r="A230" s="20" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D230" s="11" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E230" s="17"/>
       <c r="F230" s="17"/>
@@ -8205,16 +8205,16 @@
     </row>
     <row r="231" spans="1:12" ht="30" customHeight="1">
       <c r="A231" s="20" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B231" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D231" s="11" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E231" s="17"/>
       <c r="F231" s="17"/>
@@ -8227,16 +8227,16 @@
     </row>
     <row r="232" spans="1:12" ht="30" customHeight="1">
       <c r="A232" s="20" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B232" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D232" s="11" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E232" s="17"/>
       <c r="F232" s="17"/>
@@ -8249,16 +8249,16 @@
     </row>
     <row r="233" spans="1:12" ht="30" customHeight="1">
       <c r="A233" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="B233" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C233" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="D233" s="11" t="s">
         <v>557</v>
-      </c>
-      <c r="B233" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C233" s="8" t="s">
-        <v>558</v>
-      </c>
-      <c r="D233" s="11" t="s">
-        <v>559</v>
       </c>
       <c r="E233" s="17"/>
       <c r="F233" s="17"/>
@@ -8271,16 +8271,16 @@
     </row>
     <row r="234" spans="1:12" ht="30" customHeight="1">
       <c r="A234" s="20" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B234" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D234" s="11" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E234" s="17"/>
       <c r="F234" s="17"/>
@@ -8293,16 +8293,16 @@
     </row>
     <row r="235" spans="1:12" ht="30" customHeight="1">
       <c r="A235" s="20" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B235" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E235" s="17"/>
       <c r="F235" s="17"/>
@@ -8315,16 +8315,16 @@
     </row>
     <row r="236" spans="1:12" ht="30" customHeight="1">
       <c r="A236" s="20" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D236" s="11" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E236" s="17"/>
       <c r="F236" s="17"/>
@@ -8337,16 +8337,16 @@
     </row>
     <row r="237" spans="1:12" ht="30" customHeight="1">
       <c r="A237" s="20" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B237" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C237" s="8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D237" s="11" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E237" s="17"/>
       <c r="F237" s="17"/>
@@ -8359,16 +8359,16 @@
     </row>
     <row r="238" spans="1:12" ht="30" customHeight="1">
       <c r="A238" s="20" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B238" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D238" s="11" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E238" s="17"/>
       <c r="F238" s="17"/>
@@ -8381,16 +8381,16 @@
     </row>
     <row r="239" spans="1:12" ht="30" customHeight="1">
       <c r="A239" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="B239" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C239" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="D239" s="11" t="s">
         <v>570</v>
-      </c>
-      <c r="B239" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C239" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="D239" s="11" t="s">
-        <v>572</v>
       </c>
       <c r="E239" s="17"/>
       <c r="F239" s="17"/>
@@ -8403,16 +8403,16 @@
     </row>
     <row r="240" spans="1:12" ht="30" customHeight="1">
       <c r="A240" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="B240" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C240" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="D240" s="11" t="s">
         <v>573</v>
-      </c>
-      <c r="B240" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C240" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="D240" s="11" t="s">
-        <v>575</v>
       </c>
       <c r="E240" s="17"/>
       <c r="F240" s="17"/>
@@ -8425,16 +8425,16 @@
     </row>
     <row r="241" spans="1:12" ht="30" customHeight="1">
       <c r="A241" s="20" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B241" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D241" s="11" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E241" s="17"/>
       <c r="F241" s="17"/>
@@ -8447,16 +8447,16 @@
     </row>
     <row r="242" spans="1:12" ht="30" customHeight="1">
       <c r="A242" s="20" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B242" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D242" s="11" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E242" s="17"/>
       <c r="F242" s="17"/>
@@ -8469,16 +8469,16 @@
     </row>
     <row r="243" spans="1:12" ht="30" customHeight="1">
       <c r="A243" s="20" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B243" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C243" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D243" s="11" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E243" s="17"/>
       <c r="F243" s="17"/>
@@ -8491,16 +8491,16 @@
     </row>
     <row r="244" spans="1:12" ht="30" customHeight="1">
       <c r="A244" s="20" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B244" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C244" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E244" s="17"/>
       <c r="F244" s="17"/>
@@ -8513,16 +8513,16 @@
     </row>
     <row r="245" spans="1:12" ht="30" customHeight="1">
       <c r="A245" s="20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B245" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D245" s="11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E245" s="17"/>
       <c r="F245" s="17"/>
@@ -8535,16 +8535,16 @@
     </row>
     <row r="246" spans="1:12" ht="30" customHeight="1">
       <c r="A246" s="20" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B246" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C246" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D246" s="11" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E246" s="17"/>
       <c r="F246" s="17"/>
@@ -8557,16 +8557,16 @@
     </row>
     <row r="247" spans="1:12" ht="30" customHeight="1">
       <c r="A247" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="B247" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C247" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="D247" s="11" t="s">
         <v>588</v>
-      </c>
-      <c r="B247" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C247" s="8" t="s">
-        <v>589</v>
-      </c>
-      <c r="D247" s="11" t="s">
-        <v>590</v>
       </c>
       <c r="E247" s="17"/>
       <c r="F247" s="17"/>
@@ -8579,16 +8579,16 @@
     </row>
     <row r="248" spans="1:12" ht="30" customHeight="1">
       <c r="A248" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="B248" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C248" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="D248" s="11" t="s">
         <v>591</v>
-      </c>
-      <c r="B248" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C248" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="D248" s="11" t="s">
-        <v>593</v>
       </c>
       <c r="E248" s="17"/>
       <c r="F248" s="17"/>
@@ -8601,16 +8601,16 @@
     </row>
     <row r="249" spans="1:12" ht="30" customHeight="1">
       <c r="A249" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="B249" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C249" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="D249" s="11" t="s">
         <v>594</v>
-      </c>
-      <c r="B249" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C249" s="8" t="s">
-        <v>595</v>
-      </c>
-      <c r="D249" s="11" t="s">
-        <v>596</v>
       </c>
       <c r="E249" s="17"/>
       <c r="F249" s="17"/>
@@ -8623,16 +8623,16 @@
     </row>
     <row r="250" spans="1:12" ht="30" customHeight="1">
       <c r="A250" s="20" t="s">
+        <v>595</v>
+      </c>
+      <c r="B250" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C250" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D250" s="11" t="s">
         <v>597</v>
-      </c>
-      <c r="B250" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C250" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="D250" s="11" t="s">
-        <v>599</v>
       </c>
       <c r="E250" s="17"/>
       <c r="F250" s="17"/>
@@ -8645,16 +8645,16 @@
     </row>
     <row r="251" spans="1:12" ht="30" customHeight="1">
       <c r="A251" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="B251" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C251" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="D251" s="11" t="s">
         <v>600</v>
-      </c>
-      <c r="B251" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C251" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="D251" s="11" t="s">
-        <v>602</v>
       </c>
       <c r="E251" s="17"/>
       <c r="F251" s="17"/>
@@ -8667,16 +8667,16 @@
     </row>
     <row r="252" spans="1:12" ht="30" customHeight="1">
       <c r="A252" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="B252" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C252" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="D252" s="11" t="s">
         <v>603</v>
-      </c>
-      <c r="B252" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C252" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="D252" s="11" t="s">
-        <v>605</v>
       </c>
       <c r="E252" s="17"/>
       <c r="F252" s="17"/>
@@ -8689,16 +8689,16 @@
     </row>
     <row r="253" spans="1:12" ht="30" customHeight="1">
       <c r="A253" s="20" t="s">
+        <v>604</v>
+      </c>
+      <c r="B253" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C253" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="D253" s="11" t="s">
         <v>606</v>
-      </c>
-      <c r="B253" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C253" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="D253" s="11" t="s">
-        <v>608</v>
       </c>
       <c r="E253" s="17"/>
       <c r="F253" s="17"/>
@@ -8711,16 +8711,16 @@
     </row>
     <row r="254" spans="1:12" ht="30" customHeight="1">
       <c r="A254" s="20" t="s">
+        <v>607</v>
+      </c>
+      <c r="B254" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C254" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="D254" s="11" t="s">
         <v>609</v>
-      </c>
-      <c r="B254" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C254" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="D254" s="11" t="s">
-        <v>611</v>
       </c>
       <c r="E254" s="17"/>
       <c r="F254" s="17"/>
@@ -8733,16 +8733,16 @@
     </row>
     <row r="255" spans="1:12" ht="30" customHeight="1">
       <c r="A255" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="B255" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C255" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="D255" s="11" t="s">
         <v>612</v>
-      </c>
-      <c r="B255" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C255" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="D255" s="11" t="s">
-        <v>614</v>
       </c>
       <c r="E255" s="17"/>
       <c r="F255" s="17"/>
@@ -8755,16 +8755,16 @@
     </row>
     <row r="256" spans="1:12" ht="30" customHeight="1">
       <c r="A256" s="20" t="s">
+        <v>613</v>
+      </c>
+      <c r="B256" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C256" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="D256" s="11" t="s">
         <v>615</v>
-      </c>
-      <c r="B256" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C256" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="D256" s="11" t="s">
-        <v>617</v>
       </c>
       <c r="E256" s="17"/>
       <c r="F256" s="17"/>
@@ -8777,16 +8777,16 @@
     </row>
     <row r="257" spans="1:12" ht="30" customHeight="1">
       <c r="A257" s="20" t="s">
+        <v>616</v>
+      </c>
+      <c r="B257" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C257" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D257" s="11" t="s">
         <v>618</v>
-      </c>
-      <c r="B257" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C257" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="D257" s="11" t="s">
-        <v>620</v>
       </c>
       <c r="E257" s="17"/>
       <c r="F257" s="17"/>
@@ -8799,16 +8799,16 @@
     </row>
     <row r="258" spans="1:12" ht="30" customHeight="1">
       <c r="A258" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="B258" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="C258" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="B258" s="14" t="s">
+      <c r="D258" s="11" t="s">
         <v>622</v>
-      </c>
-      <c r="C258" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="D258" s="11" t="s">
-        <v>624</v>
       </c>
       <c r="E258" s="17"/>
       <c r="F258" s="17"/>
@@ -8821,16 +8821,16 @@
     </row>
     <row r="259" spans="1:12" ht="30" customHeight="1">
       <c r="A259" s="20" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B259" s="14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D259" s="11" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E259" s="17"/>
       <c r="F259" s="17"/>
@@ -8843,16 +8843,16 @@
     </row>
     <row r="260" spans="1:12" ht="30" customHeight="1">
       <c r="A260" s="20" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D260" s="11" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E260" s="17"/>
       <c r="F260" s="17"/>
@@ -8865,16 +8865,16 @@
     </row>
     <row r="261" spans="1:12" ht="30" customHeight="1">
       <c r="A261" s="20" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B261" s="14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D261" s="11" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E261" s="17"/>
       <c r="F261" s="17"/>
@@ -8887,16 +8887,16 @@
     </row>
     <row r="262" spans="1:12" ht="30" customHeight="1">
       <c r="A262" s="20" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B262" s="14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D262" s="11" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E262" s="17"/>
       <c r="F262" s="17"/>
@@ -8909,16 +8909,16 @@
     </row>
     <row r="263" spans="1:12" ht="30" customHeight="1">
       <c r="A263" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="B263" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="C263" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="D263" s="11" t="s">
         <v>631</v>
-      </c>
-      <c r="B263" s="14" t="s">
-        <v>622</v>
-      </c>
-      <c r="C263" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="D263" s="11" t="s">
-        <v>633</v>
       </c>
       <c r="E263" s="17"/>
       <c r="F263" s="17"/>
@@ -8931,16 +8931,16 @@
     </row>
     <row r="264" spans="1:12" ht="30" customHeight="1">
       <c r="A264" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="B264" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C264" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="B264" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C264" s="8" t="s">
-        <v>636</v>
-      </c>
       <c r="D264" s="11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E264" s="17"/>
       <c r="F264" s="17"/>
@@ -8953,16 +8953,16 @@
     </row>
     <row r="265" spans="1:12" ht="30" customHeight="1">
       <c r="A265" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="B265" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C265" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="D265" s="11" t="s">
         <v>637</v>
-      </c>
-      <c r="B265" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C265" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="D265" s="11" t="s">
-        <v>639</v>
       </c>
       <c r="E265" s="17"/>
       <c r="F265" s="17"/>
@@ -8975,16 +8975,16 @@
     </row>
     <row r="266" spans="1:12" ht="30" customHeight="1">
       <c r="A266" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="B266" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C266" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="D266" s="11" t="s">
         <v>640</v>
-      </c>
-      <c r="B266" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C266" s="8" t="s">
-        <v>641</v>
-      </c>
-      <c r="D266" s="11" t="s">
-        <v>642</v>
       </c>
       <c r="E266" s="17"/>
       <c r="F266" s="17"/>
@@ -8997,16 +8997,16 @@
     </row>
     <row r="267" spans="1:12" ht="30" customHeight="1">
       <c r="A267" s="20" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B267" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C267" s="8" t="s">
         <v>60</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E267" s="17"/>
       <c r="F267" s="17"/>
@@ -9019,16 +9019,16 @@
     </row>
     <row r="268" spans="1:12" ht="30" customHeight="1">
       <c r="A268" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="B268" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C268" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D268" s="11" t="s">
         <v>644</v>
-      </c>
-      <c r="B268" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C268" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="D268" s="11" t="s">
-        <v>646</v>
       </c>
       <c r="E268" s="17"/>
       <c r="F268" s="17"/>
@@ -9041,16 +9041,16 @@
     </row>
     <row r="269" spans="1:12" ht="30" customHeight="1">
       <c r="A269" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="B269" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C269" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="D269" s="11" t="s">
         <v>647</v>
-      </c>
-      <c r="B269" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C269" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="D269" s="11" t="s">
-        <v>649</v>
       </c>
       <c r="E269" s="17"/>
       <c r="F269" s="17"/>
@@ -9063,16 +9063,16 @@
     </row>
     <row r="270" spans="1:12" ht="30" customHeight="1">
       <c r="A270" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="B270" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C270" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="D270" s="11" t="s">
         <v>650</v>
-      </c>
-      <c r="B270" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C270" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="D270" s="11" t="s">
-        <v>652</v>
       </c>
       <c r="E270" s="17"/>
       <c r="F270" s="17"/>
@@ -9085,16 +9085,16 @@
     </row>
     <row r="271" spans="1:12" ht="30" customHeight="1">
       <c r="A271" s="20" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B271" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C271" s="8" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E271" s="17"/>
       <c r="F271" s="17"/>
@@ -9107,16 +9107,16 @@
     </row>
     <row r="272" spans="1:12" ht="30" customHeight="1">
       <c r="A272" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="B272" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C272" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="D272" s="11" t="s">
         <v>655</v>
-      </c>
-      <c r="B272" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C272" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="D272" s="11" t="s">
-        <v>657</v>
       </c>
       <c r="E272" s="17"/>
       <c r="F272" s="17"/>
@@ -9129,16 +9129,16 @@
     </row>
     <row r="273" spans="1:12" ht="30" customHeight="1">
       <c r="A273" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="B273" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="C273" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D273" s="11" t="s">
         <v>658</v>
-      </c>
-      <c r="B273" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="C273" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D273" s="11" t="s">
-        <v>660</v>
       </c>
       <c r="E273" s="17"/>
       <c r="F273" s="17"/>
@@ -9151,16 +9151,16 @@
     </row>
     <row r="274" spans="1:12" ht="30" customHeight="1">
       <c r="A274" s="20" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B274" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E274" s="17"/>
       <c r="F274" s="17"/>
@@ -9173,16 +9173,16 @@
     </row>
     <row r="275" spans="1:12" ht="30" customHeight="1">
       <c r="A275" s="20" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B275" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D275" s="11" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E275" s="17"/>
       <c r="F275" s="17"/>
@@ -9195,16 +9195,16 @@
     </row>
     <row r="276" spans="1:12" ht="30" customHeight="1">
       <c r="A276" s="20" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B276" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E276" s="17"/>
       <c r="F276" s="17"/>
@@ -9217,16 +9217,16 @@
     </row>
     <row r="277" spans="1:12" ht="30" customHeight="1">
       <c r="A277" s="20" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B277" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E277" s="17"/>
       <c r="F277" s="17"/>
@@ -9239,16 +9239,16 @@
     </row>
     <row r="278" spans="1:12" ht="30" customHeight="1">
       <c r="A278" s="20" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B278" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D278" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E278" s="17"/>
       <c r="F278" s="17"/>
@@ -9261,16 +9261,16 @@
     </row>
     <row r="279" spans="1:12" ht="30" customHeight="1">
       <c r="A279" s="20" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B279" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D279" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E279" s="17"/>
       <c r="F279" s="17"/>
@@ -9283,16 +9283,16 @@
     </row>
     <row r="280" spans="1:12" ht="30" customHeight="1">
       <c r="A280" s="20" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B280" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E280" s="17"/>
       <c r="F280" s="17"/>
@@ -9305,16 +9305,16 @@
     </row>
     <row r="281" spans="1:12" ht="30" customHeight="1">
       <c r="A281" s="20" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B281" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D281" s="11" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E281" s="17"/>
       <c r="F281" s="17"/>
@@ -9327,16 +9327,16 @@
     </row>
     <row r="282" spans="1:12" ht="30" customHeight="1">
       <c r="A282" s="20" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B282" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E282" s="17"/>
       <c r="F282" s="17"/>
@@ -9349,16 +9349,16 @@
     </row>
     <row r="283" spans="1:12" ht="30" customHeight="1">
       <c r="A283" s="20" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B283" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D283" s="11" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E283" s="17"/>
       <c r="F283" s="17"/>
@@ -9371,16 +9371,16 @@
     </row>
     <row r="284" spans="1:12" ht="30" customHeight="1">
       <c r="A284" s="20" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B284" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E284" s="17"/>
       <c r="F284" s="17"/>
@@ -9393,16 +9393,16 @@
     </row>
     <row r="285" spans="1:12" ht="30" customHeight="1">
       <c r="A285" s="20" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B285" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D285" s="11" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E285" s="17"/>
       <c r="F285" s="17"/>
@@ -9415,16 +9415,16 @@
     </row>
     <row r="286" spans="1:12" ht="30" customHeight="1">
       <c r="A286" s="20" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B286" s="14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E286" s="17"/>
       <c r="F286" s="17"/>
@@ -9437,16 +9437,16 @@
     </row>
     <row r="287" spans="1:12" ht="30" customHeight="1">
       <c r="A287" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="B287" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="C287" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="B287" s="14" t="s">
+      <c r="D287" s="11" t="s">
         <v>688</v>
-      </c>
-      <c r="C287" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="D287" s="11" t="s">
-        <v>690</v>
       </c>
       <c r="E287" s="17"/>
       <c r="F287" s="17"/>
@@ -9459,16 +9459,16 @@
     </row>
     <row r="288" spans="1:12" ht="30" customHeight="1">
       <c r="A288" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="B288" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="C288" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="D288" s="11" t="s">
         <v>691</v>
-      </c>
-      <c r="B288" s="14" t="s">
-        <v>688</v>
-      </c>
-      <c r="C288" s="8" t="s">
-        <v>692</v>
-      </c>
-      <c r="D288" s="11" t="s">
-        <v>693</v>
       </c>
       <c r="E288" s="17"/>
       <c r="F288" s="17"/>
@@ -9481,16 +9481,16 @@
     </row>
     <row r="289" spans="1:12" ht="30" customHeight="1">
       <c r="A289" s="20" t="s">
+        <v>692</v>
+      </c>
+      <c r="B289" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="C289" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="D289" s="11" t="s">
         <v>694</v>
-      </c>
-      <c r="B289" s="14" t="s">
-        <v>688</v>
-      </c>
-      <c r="C289" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="D289" s="11" t="s">
-        <v>696</v>
       </c>
       <c r="E289" s="17"/>
       <c r="F289" s="17"/>
@@ -9503,16 +9503,16 @@
     </row>
     <row r="290" spans="1:12" ht="30" customHeight="1">
       <c r="A290" s="20" t="s">
+        <v>695</v>
+      </c>
+      <c r="B290" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="C290" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="D290" s="11" t="s">
         <v>697</v>
-      </c>
-      <c r="B290" s="14" t="s">
-        <v>688</v>
-      </c>
-      <c r="C290" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="D290" s="11" t="s">
-        <v>699</v>
       </c>
       <c r="E290" s="17"/>
       <c r="F290" s="17"/>
@@ -9525,16 +9525,16 @@
     </row>
     <row r="291" spans="1:12" ht="30" customHeight="1">
       <c r="A291" s="20" t="s">
+        <v>698</v>
+      </c>
+      <c r="B291" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="C291" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="D291" s="11" t="s">
         <v>700</v>
-      </c>
-      <c r="B291" s="14" t="s">
-        <v>688</v>
-      </c>
-      <c r="C291" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="D291" s="11" t="s">
-        <v>702</v>
       </c>
       <c r="E291" s="17"/>
       <c r="F291" s="17"/>
@@ -9547,16 +9547,16 @@
     </row>
     <row r="292" spans="1:12" ht="30" customHeight="1">
       <c r="A292" s="20" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B292" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="C292" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="D292" s="11" t="s">
         <v>688</v>
-      </c>
-      <c r="C292" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="D292" s="11" t="s">
-        <v>690</v>
       </c>
       <c r="E292" s="17"/>
       <c r="F292" s="17"/>
@@ -9569,16 +9569,16 @@
     </row>
     <row r="293" spans="1:12" ht="30" customHeight="1">
       <c r="A293" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="B293" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="C293" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="D293" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="B293" s="14" t="s">
-        <v>688</v>
-      </c>
-      <c r="C293" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="D293" s="11" t="s">
-        <v>707</v>
       </c>
       <c r="E293" s="17"/>
       <c r="F293" s="17"/>
@@ -9591,16 +9591,16 @@
     </row>
     <row r="294" spans="1:12" ht="30" customHeight="1">
       <c r="A294" s="20" t="s">
+        <v>706</v>
+      </c>
+      <c r="B294" s="14" t="s">
+        <v>707</v>
+      </c>
+      <c r="C294" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="B294" s="14" t="s">
+      <c r="D294" s="11" t="s">
         <v>709</v>
-      </c>
-      <c r="C294" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="D294" s="11" t="s">
-        <v>711</v>
       </c>
       <c r="E294" s="17"/>
       <c r="F294" s="17"/>
@@ -9613,16 +9613,16 @@
     </row>
     <row r="295" spans="1:12" ht="30" customHeight="1">
       <c r="A295" s="20" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B295" s="14" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D295" s="11" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E295" s="17"/>
       <c r="F295" s="17"/>
@@ -9635,16 +9635,16 @@
     </row>
     <row r="296" spans="1:12" ht="30" customHeight="1">
       <c r="A296" s="20" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B296" s="14" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C296" s="8" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D296" s="11" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E296" s="17"/>
       <c r="F296" s="17"/>
@@ -9657,16 +9657,16 @@
     </row>
     <row r="297" spans="1:12" ht="30" customHeight="1">
       <c r="A297" s="20" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B297" s="14" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C297" s="8" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D297" s="11" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E297" s="17"/>
       <c r="F297" s="17"/>
@@ -9679,16 +9679,16 @@
     </row>
     <row r="298" spans="1:12" ht="30" customHeight="1">
       <c r="A298" s="20" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B298" s="14" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C298" s="8" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D298" s="11" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E298" s="17"/>
       <c r="F298" s="17"/>
@@ -9701,16 +9701,16 @@
     </row>
     <row r="299" spans="1:12" ht="30" customHeight="1">
       <c r="A299" s="20" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B299" s="14" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C299" s="8" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D299" s="11" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E299" s="17"/>
       <c r="F299" s="17"/>
@@ -9723,16 +9723,16 @@
     </row>
     <row r="300" spans="1:12" ht="30" customHeight="1">
       <c r="A300" s="20" t="s">
+        <v>720</v>
+      </c>
+      <c r="B300" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="C300" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="D300" s="11" t="s">
         <v>722</v>
-      </c>
-      <c r="B300" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="C300" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="D300" s="11" t="s">
-        <v>724</v>
       </c>
       <c r="E300" s="17"/>
       <c r="F300" s="17"/>
@@ -9745,16 +9745,16 @@
     </row>
     <row r="301" spans="1:12" ht="30" customHeight="1">
       <c r="A301" s="20" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B301" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D301" s="11" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E301" s="17"/>
       <c r="F301" s="17"/>
@@ -9767,16 +9767,16 @@
     </row>
     <row r="302" spans="1:12" ht="30" customHeight="1">
       <c r="A302" s="20" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B302" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C302" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E302" s="17"/>
       <c r="F302" s="17"/>
@@ -9789,16 +9789,16 @@
     </row>
     <row r="303" spans="1:12" ht="30" customHeight="1">
       <c r="A303" s="20" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B303" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C303" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D303" s="11" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E303" s="17"/>
       <c r="F303" s="17"/>
@@ -9811,16 +9811,16 @@
     </row>
     <row r="304" spans="1:12" ht="30" customHeight="1">
       <c r="A304" s="20" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B304" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C304" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D304" s="11" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E304" s="17"/>
       <c r="F304" s="17"/>
@@ -9833,16 +9833,16 @@
     </row>
     <row r="305" spans="1:12" ht="30" customHeight="1">
       <c r="A305" s="20" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B305" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C305" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D305" s="11" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E305" s="17"/>
       <c r="F305" s="17"/>
@@ -9855,16 +9855,16 @@
     </row>
     <row r="306" spans="1:12" ht="30" customHeight="1">
       <c r="A306" s="20" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B306" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C306" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D306" s="11" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E306" s="17"/>
       <c r="F306" s="17"/>
@@ -9877,16 +9877,16 @@
     </row>
     <row r="307" spans="1:12" ht="30" customHeight="1">
       <c r="A307" s="20" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B307" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C307" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D307" s="11" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E307" s="17"/>
       <c r="F307" s="17"/>
@@ -9899,16 +9899,16 @@
     </row>
     <row r="308" spans="1:12" ht="30" customHeight="1">
       <c r="A308" s="20" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B308" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C308" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D308" s="11" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E308" s="17"/>
       <c r="F308" s="17"/>
@@ -9921,16 +9921,16 @@
     </row>
     <row r="309" spans="1:12" ht="30" customHeight="1">
       <c r="A309" s="20" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B309" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C309" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D309" s="11" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E309" s="17"/>
       <c r="F309" s="17"/>
@@ -9943,16 +9943,16 @@
     </row>
     <row r="310" spans="1:12" ht="30" customHeight="1">
       <c r="A310" s="20" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B310" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C310" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D310" s="11" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E310" s="17"/>
       <c r="F310" s="17"/>
@@ -9965,16 +9965,16 @@
     </row>
     <row r="311" spans="1:12" ht="30" customHeight="1">
       <c r="A311" s="20" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B311" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C311" s="8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D311" s="11" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E311" s="17"/>
       <c r="F311" s="17"/>
@@ -9987,16 +9987,16 @@
     </row>
     <row r="312" spans="1:12" ht="30" customHeight="1">
       <c r="A312" s="20" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B312" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C312" s="8" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D312" s="11" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="E312" s="17"/>
       <c r="F312" s="17"/>
@@ -10009,16 +10009,16 @@
     </row>
     <row r="313" spans="1:12" ht="30" customHeight="1">
       <c r="A313" s="20" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B313" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C313" s="8" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D313" s="11" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E313" s="17"/>
       <c r="F313" s="17"/>
@@ -10031,13 +10031,13 @@
     </row>
     <row r="314" spans="1:12" ht="30" customHeight="1">
       <c r="A314" s="20" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B314" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C314" s="8" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D314" s="11" t="s">
         <v>76</v>
@@ -10053,16 +10053,16 @@
     </row>
     <row r="315" spans="1:12" ht="30" customHeight="1">
       <c r="A315" s="20" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B315" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C315" s="8" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E315" s="17"/>
       <c r="F315" s="17"/>
@@ -10075,16 +10075,16 @@
     </row>
     <row r="316" spans="1:12" ht="30" customHeight="1">
       <c r="A316" s="20" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B316" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C316" s="8" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E316" s="17"/>
       <c r="F316" s="17"/>
@@ -10097,16 +10097,16 @@
     </row>
     <row r="317" spans="1:12" ht="30" customHeight="1">
       <c r="A317" s="20" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B317" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C317" s="8" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E317" s="17"/>
       <c r="F317" s="17"/>
@@ -10119,16 +10119,16 @@
     </row>
     <row r="318" spans="1:12" ht="30" customHeight="1">
       <c r="A318" s="20" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B318" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E318" s="17"/>
       <c r="F318" s="17"/>
@@ -10141,16 +10141,16 @@
     </row>
     <row r="319" spans="1:12" ht="30" customHeight="1">
       <c r="A319" s="20" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B319" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C319" s="8" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D319" s="11" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E319" s="17"/>
       <c r="F319" s="17"/>
@@ -10163,16 +10163,16 @@
     </row>
     <row r="320" spans="1:12" ht="30" customHeight="1">
       <c r="A320" s="20" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B320" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C320" s="8" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D320" s="11" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E320" s="17"/>
       <c r="F320" s="17"/>
@@ -10185,16 +10185,16 @@
     </row>
     <row r="321" spans="1:12" ht="30" customHeight="1">
       <c r="A321" s="20" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B321" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C321" s="8" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D321" s="11" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E321" s="17"/>
       <c r="F321" s="17"/>
@@ -10207,16 +10207,16 @@
     </row>
     <row r="322" spans="1:12" ht="30" customHeight="1">
       <c r="A322" s="20" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B322" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C322" s="8" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D322" s="11" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E322" s="17"/>
       <c r="F322" s="17"/>
@@ -10229,16 +10229,16 @@
     </row>
     <row r="323" spans="1:12" ht="30" customHeight="1">
       <c r="A323" s="20" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B323" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C323" s="8" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D323" s="11" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E323" s="17"/>
       <c r="F323" s="17"/>
@@ -10251,16 +10251,16 @@
     </row>
     <row r="324" spans="1:12" ht="30" customHeight="1">
       <c r="A324" s="20" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B324" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C324" s="8" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D324" s="11" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E324" s="17"/>
       <c r="F324" s="17"/>
@@ -10273,16 +10273,16 @@
     </row>
     <row r="325" spans="1:12" ht="30" customHeight="1">
       <c r="A325" s="20" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B325" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C325" s="8" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D325" s="11" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E325" s="17"/>
       <c r="F325" s="17"/>
@@ -10295,16 +10295,16 @@
     </row>
     <row r="326" spans="1:12" ht="30" customHeight="1">
       <c r="A326" s="20" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B326" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C326" s="8" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D326" s="11" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E326" s="17"/>
       <c r="F326" s="17"/>
@@ -10317,16 +10317,16 @@
     </row>
     <row r="327" spans="1:12" ht="30" customHeight="1">
       <c r="A327" s="20" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B327" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C327" s="8" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D327" s="11" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="E327" s="17"/>
       <c r="F327" s="17"/>
@@ -10339,16 +10339,16 @@
     </row>
     <row r="328" spans="1:12" ht="30" customHeight="1">
       <c r="A328" s="20" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B328" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D328" s="11" t="s">
-        <v>792</v>
+        <v>828</v>
       </c>
       <c r="E328" s="17"/>
       <c r="F328" s="17"/>
@@ -10361,16 +10361,16 @@
     </row>
     <row r="329" spans="1:12" ht="30" customHeight="1">
       <c r="A329" s="20" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B329" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D329" s="11" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="E329" s="17"/>
       <c r="F329" s="17"/>
@@ -10383,16 +10383,16 @@
     </row>
     <row r="330" spans="1:12" ht="30" customHeight="1">
       <c r="A330" s="20" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B330" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C330" s="8" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D330" s="11" t="s">
-        <v>798</v>
+        <v>826</v>
       </c>
       <c r="E330" s="17"/>
       <c r="F330" s="17"/>
@@ -10405,16 +10405,16 @@
     </row>
     <row r="331" spans="1:12" ht="30" customHeight="1">
       <c r="A331" s="21" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B331" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C331" s="9" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D331" s="12" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E331" s="18"/>
       <c r="F331" s="18"/>
@@ -10427,16 +10427,16 @@
     </row>
     <row r="332" spans="1:12" ht="15">
       <c r="A332" s="23" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B332" s="24" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C332" s="25" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D332" s="26" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E332" s="22"/>
       <c r="F332" s="22"/>
@@ -10449,16 +10449,16 @@
     </row>
     <row r="333" spans="1:12" ht="15">
       <c r="A333" s="23" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B333" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C333" s="28" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="D333" s="29" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E333" s="22"/>
       <c r="F333" s="22"/>
@@ -10471,16 +10471,16 @@
     </row>
     <row r="334" spans="1:12" ht="15">
       <c r="A334" s="23" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B334" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C334" s="25" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="D334" s="26" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="E334" s="22"/>
       <c r="F334" s="22"/>
@@ -10493,16 +10493,16 @@
     </row>
     <row r="335" spans="1:12" ht="15">
       <c r="A335" s="23" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B335" s="27" t="s">
         <v>50</v>
       </c>
       <c r="C335" s="28" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="D335" s="29" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="E335" s="22"/>
       <c r="F335" s="22"/>
@@ -10515,16 +10515,16 @@
     </row>
     <row r="336" spans="1:12" ht="15">
       <c r="A336" s="23" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B336" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C336" s="25" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="D336" s="26" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="E336" s="22"/>
       <c r="F336" s="22"/>
@@ -10537,16 +10537,16 @@
     </row>
     <row r="337" spans="1:12" ht="15">
       <c r="A337" s="23" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B337" s="27" t="s">
         <v>50</v>
       </c>
       <c r="C337" s="28" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="D337" s="29" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="E337" s="22"/>
       <c r="F337" s="22"/>
@@ -10559,16 +10559,16 @@
     </row>
     <row r="338" spans="1:12" ht="15">
       <c r="A338" s="23" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B338" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C338" s="25" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="D338" s="26" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="E338" s="22"/>
       <c r="F338" s="22"/>
@@ -10581,16 +10581,16 @@
     </row>
     <row r="339" spans="1:12" ht="15">
       <c r="A339" s="23" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B339" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C339" s="28" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="D339" s="29" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="E339" s="22"/>
       <c r="F339" s="22"/>
@@ -10743,16 +10743,16 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="B350" t="s">
         <v>54</v>
       </c>
       <c r="C350" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D350" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
     </row>
   </sheetData>

--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WebDev\stark-electronic-base\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C10BD9-DC3C-4247-95CC-AE9D54868666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E89D56-3A33-4818-BCDB-BA17BE875A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WebDev\stark-electronic-base\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E89D56-3A33-4818-BCDB-BA17BE875A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212F39DF-EA9A-49B8-81EB-CDFFEF07ECCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -658,9 +658,6 @@
     <t>demo.step.summary-preview.title</t>
   </si>
   <si>
-    <t>Проверьте краткую сводку в чате</t>
-  </si>
-  <si>
     <t>demo.step.summary-preview.description</t>
   </si>
   <si>
@@ -727,9 +724,6 @@
     <t>demo.step.visits-table.title</t>
   </si>
   <si>
-    <t>Отдельная таблица хранит историю визитов</t>
-  </si>
-  <si>
     <t>demo.step.visits-table.description</t>
   </si>
   <si>
@@ -1282,9 +1276,6 @@
     <t>benefits.voice.description</t>
   </si>
   <si>
-    <t>Надиктуйте информацию сразу после приёма.</t>
-  </si>
-  <si>
     <t>benefits.structure.title</t>
   </si>
   <si>
@@ -1318,9 +1309,6 @@
     <t>benefits.history.description</t>
   </si>
   <si>
-    <t>Процедуры, советы и фото связаны с клиентом.</t>
-  </si>
-  <si>
     <t>benefits.search.title</t>
   </si>
   <si>
@@ -1330,18 +1318,12 @@
     <t>benefits.search.description</t>
   </si>
   <si>
-    <t>Получите сводку по имени или цифрам телефона.</t>
-  </si>
-  <si>
     <t>benefits.profession.title</t>
   </si>
   <si>
     <t>benefits.profession.description</t>
   </si>
   <si>
-    <t>Структура таблицы адаптируется под вашу работу.</t>
-  </si>
-  <si>
     <t>benefits.connection_time</t>
   </si>
   <si>
@@ -2503,19 +2485,37 @@
     <t>В любой момент вы можете запросить сводку по конктеному посещению или по всей истории клиента</t>
   </si>
   <si>
-    <t>После приёма надиктовываю всё за 2 минуты — раньше на записи и таблицы уходило 15–20. Теперь в конце дня остаются силы на себя.</t>
-  </si>
-  <si>
     <t>Клиент пришёл спустя полгода, а я за минуту подняла всю историю: с чем обращался, что делали и какие были рекомендации. Очень удобно.</t>
   </si>
   <si>
-    <t>У меня несколько клиентов подряд, и после рабочего дня уже сложно вспомнить детали каждого. Теперь фиксирую всё сразу и вечером ничего восстанавливать не приходится.</t>
-  </si>
-  <si>
     <t>психолог</t>
   </si>
   <si>
     <t>стоматолог</t>
+  </si>
+  <si>
+    <t>После приёма надиктовываю всё за 2 минуты — раньше на записи и таблицы уходило 15–20 минут. Теперь в конце дня остаются силы на себя.</t>
+  </si>
+  <si>
+    <t>У меня несколько клиентов подряд, и после рабочего дня уже сложно вспомнить детали про каждого. Теперь фиксирую всё сразу и вечером ничего восстанавливать не приходится.</t>
+  </si>
+  <si>
+    <t>Ассисиетент анализирует все данные, структурирует их и присылает на итоговую проверку</t>
+  </si>
+  <si>
+    <t>Все данные сохраняются в таблице</t>
+  </si>
+  <si>
+    <t>Понятный и удобный формат диалога</t>
+  </si>
+  <si>
+    <t>Вся информация по всем клиентам в одном месте</t>
+  </si>
+  <si>
+    <t>Получите сводку о клиенте по имени и фамилии.</t>
+  </si>
+  <si>
+    <t>Помощник и таблица адаптируются под вас и вашу специфику</t>
   </si>
 </sst>
 </file>
@@ -3734,7 +3734,7 @@
         <v>107</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
@@ -3778,7 +3778,7 @@
         <v>112</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -4676,7 +4676,7 @@
         <v>207</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>210</v>
+        <v>824</v>
       </c>
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
@@ -4689,7 +4689,7 @@
     </row>
     <row r="71" spans="1:12" ht="30" customHeight="1">
       <c r="A71" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>178</v>
@@ -4698,7 +4698,7 @@
         <v>207</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E71" s="17"/>
       <c r="F71" s="17"/>
@@ -4711,13 +4711,13 @@
     </row>
     <row r="72" spans="1:12" ht="30" customHeight="1">
       <c r="A72" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>214</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>207</v>
@@ -4733,16 +4733,16 @@
     </row>
     <row r="73" spans="1:12" ht="30" customHeight="1">
       <c r="A73" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D73" s="11" t="s">
         <v>215</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>216</v>
       </c>
       <c r="E73" s="17"/>
       <c r="F73" s="17"/>
@@ -4755,13 +4755,13 @@
     </row>
     <row r="74" spans="1:12" ht="30" customHeight="1">
       <c r="A74" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B74" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="17"/>
@@ -4775,16 +4775,16 @@
     </row>
     <row r="75" spans="1:12" ht="30" customHeight="1">
       <c r="A75" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C75" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="B75" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>219</v>
-      </c>
       <c r="D75" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E75" s="17"/>
       <c r="F75" s="17"/>
@@ -4797,16 +4797,16 @@
     </row>
     <row r="76" spans="1:12" ht="30" customHeight="1">
       <c r="A76" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D76" s="11" t="s">
         <v>220</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>221</v>
       </c>
       <c r="E76" s="17"/>
       <c r="F76" s="17"/>
@@ -4819,16 +4819,16 @@
     </row>
     <row r="77" spans="1:12" ht="30" customHeight="1">
       <c r="A77" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D77" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="E77" s="17"/>
       <c r="F77" s="17"/>
@@ -4841,16 +4841,16 @@
     </row>
     <row r="78" spans="1:12" ht="30" customHeight="1">
       <c r="A78" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B78" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>225</v>
-      </c>
       <c r="D78" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E78" s="17"/>
       <c r="F78" s="17"/>
@@ -4863,16 +4863,16 @@
     </row>
     <row r="79" spans="1:12" ht="30" customHeight="1">
       <c r="A79" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D79" s="11" t="s">
         <v>226</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>227</v>
       </c>
       <c r="E79" s="17"/>
       <c r="F79" s="17"/>
@@ -4885,16 +4885,16 @@
     </row>
     <row r="80" spans="1:12" ht="30" customHeight="1">
       <c r="A80" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D80" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D80" s="11" t="s">
-        <v>229</v>
       </c>
       <c r="E80" s="17"/>
       <c r="F80" s="17"/>
@@ -4907,16 +4907,16 @@
     </row>
     <row r="81" spans="1:12" ht="30" customHeight="1">
       <c r="A81" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="B81" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>231</v>
-      </c>
       <c r="D81" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E81" s="17"/>
       <c r="F81" s="17"/>
@@ -4929,16 +4929,16 @@
     </row>
     <row r="82" spans="1:12" ht="30" customHeight="1">
       <c r="A82" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>233</v>
+        <v>825</v>
       </c>
       <c r="E82" s="17"/>
       <c r="F82" s="17"/>
@@ -4951,16 +4951,16 @@
     </row>
     <row r="83" spans="1:12" ht="30" customHeight="1">
       <c r="A83" s="20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E83" s="17"/>
       <c r="F83" s="17"/>
@@ -4973,16 +4973,16 @@
     </row>
     <row r="84" spans="1:12" ht="30" customHeight="1">
       <c r="A84" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E84" s="17"/>
       <c r="F84" s="17"/>
@@ -4995,16 +4995,16 @@
     </row>
     <row r="85" spans="1:12" ht="30" customHeight="1">
       <c r="A85" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="E85" s="17"/>
       <c r="F85" s="17"/>
@@ -5017,16 +5017,16 @@
     </row>
     <row r="86" spans="1:12" ht="30" customHeight="1">
       <c r="A86" s="20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E86" s="17"/>
       <c r="F86" s="17"/>
@@ -5039,16 +5039,16 @@
     </row>
     <row r="87" spans="1:12" ht="30" customHeight="1">
       <c r="A87" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D87" s="11" t="s">
         <v>241</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="E87" s="17"/>
       <c r="F87" s="17"/>
@@ -5061,16 +5061,16 @@
     </row>
     <row r="88" spans="1:12" ht="30" customHeight="1">
       <c r="A88" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E88" s="17"/>
       <c r="F88" s="17"/>
@@ -5083,16 +5083,16 @@
     </row>
     <row r="89" spans="1:12" ht="30" customHeight="1">
       <c r="A89" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E89" s="17"/>
       <c r="F89" s="17"/>
@@ -5105,16 +5105,16 @@
     </row>
     <row r="90" spans="1:12" ht="30" customHeight="1">
       <c r="A90" s="20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B90" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E90" s="17"/>
       <c r="F90" s="17"/>
@@ -5127,16 +5127,16 @@
     </row>
     <row r="91" spans="1:12" ht="30" customHeight="1">
       <c r="A91" s="20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E91" s="17"/>
       <c r="F91" s="17"/>
@@ -5149,16 +5149,16 @@
     </row>
     <row r="92" spans="1:12" ht="30" customHeight="1">
       <c r="A92" s="20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B92" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E92" s="17"/>
       <c r="F92" s="17"/>
@@ -5171,16 +5171,16 @@
     </row>
     <row r="93" spans="1:12" ht="30" customHeight="1">
       <c r="A93" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E93" s="17"/>
       <c r="F93" s="17"/>
@@ -5193,16 +5193,16 @@
     </row>
     <row r="94" spans="1:12" ht="30" customHeight="1">
       <c r="A94" s="20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B94" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E94" s="17"/>
       <c r="F94" s="17"/>
@@ -5215,16 +5215,16 @@
     </row>
     <row r="95" spans="1:12" ht="30" customHeight="1">
       <c r="A95" s="20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B95" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E95" s="17"/>
       <c r="F95" s="17"/>
@@ -5237,16 +5237,16 @@
     </row>
     <row r="96" spans="1:12" ht="30" customHeight="1">
       <c r="A96" s="20" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E96" s="17"/>
       <c r="F96" s="17"/>
@@ -5259,16 +5259,16 @@
     </row>
     <row r="97" spans="1:12" ht="30" customHeight="1">
       <c r="A97" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E97" s="17"/>
       <c r="F97" s="17"/>
@@ -5281,16 +5281,16 @@
     </row>
     <row r="98" spans="1:12" ht="30" customHeight="1">
       <c r="A98" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D98" s="11" t="s">
         <v>264</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>266</v>
       </c>
       <c r="E98" s="17"/>
       <c r="F98" s="17"/>
@@ -5303,16 +5303,16 @@
     </row>
     <row r="99" spans="1:12" ht="30" customHeight="1">
       <c r="A99" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D99" s="11" t="s">
         <v>267</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>269</v>
       </c>
       <c r="E99" s="17"/>
       <c r="F99" s="17"/>
@@ -5325,16 +5325,16 @@
     </row>
     <row r="100" spans="1:12" ht="30" customHeight="1">
       <c r="A100" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E100" s="17"/>
       <c r="F100" s="17"/>
@@ -5347,16 +5347,16 @@
     </row>
     <row r="101" spans="1:12" ht="30" customHeight="1">
       <c r="A101" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B101" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E101" s="17"/>
       <c r="F101" s="17"/>
@@ -5369,16 +5369,16 @@
     </row>
     <row r="102" spans="1:12" ht="30" customHeight="1">
       <c r="A102" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B102" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E102" s="17"/>
       <c r="F102" s="17"/>
@@ -5391,16 +5391,16 @@
     </row>
     <row r="103" spans="1:12" ht="30" customHeight="1">
       <c r="A103" s="20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E103" s="17"/>
       <c r="F103" s="17"/>
@@ -5413,16 +5413,16 @@
     </row>
     <row r="104" spans="1:12" ht="30" customHeight="1">
       <c r="A104" s="20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
@@ -5435,16 +5435,16 @@
     </row>
     <row r="105" spans="1:12" ht="30" customHeight="1">
       <c r="A105" s="20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E105" s="17"/>
       <c r="F105" s="17"/>
@@ -5457,16 +5457,16 @@
     </row>
     <row r="106" spans="1:12" ht="30" customHeight="1">
       <c r="A106" s="20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E106" s="17"/>
       <c r="F106" s="17"/>
@@ -5479,16 +5479,16 @@
     </row>
     <row r="107" spans="1:12" ht="30" customHeight="1">
       <c r="A107" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B107" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E107" s="17"/>
       <c r="F107" s="17"/>
@@ -5501,16 +5501,16 @@
     </row>
     <row r="108" spans="1:12" ht="30" customHeight="1">
       <c r="A108" s="20" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B108" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E108" s="17"/>
       <c r="F108" s="17"/>
@@ -5523,16 +5523,16 @@
     </row>
     <row r="109" spans="1:12" ht="30" customHeight="1">
       <c r="A109" s="20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E109" s="17"/>
       <c r="F109" s="17"/>
@@ -5545,16 +5545,16 @@
     </row>
     <row r="110" spans="1:12" ht="30" customHeight="1">
       <c r="A110" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B110" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E110" s="17"/>
       <c r="F110" s="17"/>
@@ -5567,16 +5567,16 @@
     </row>
     <row r="111" spans="1:12" ht="30" customHeight="1">
       <c r="A111" s="20" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B111" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E111" s="17"/>
       <c r="F111" s="17"/>
@@ -5589,16 +5589,16 @@
     </row>
     <row r="112" spans="1:12" ht="30" customHeight="1">
       <c r="A112" s="20" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B112" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E112" s="17"/>
       <c r="F112" s="17"/>
@@ -5611,16 +5611,16 @@
     </row>
     <row r="113" spans="1:12" ht="30" customHeight="1">
       <c r="A113" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D113" s="11" t="s">
         <v>296</v>
-      </c>
-      <c r="B113" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="E113" s="17"/>
       <c r="F113" s="17"/>
@@ -5633,16 +5633,16 @@
     </row>
     <row r="114" spans="1:12" ht="30" customHeight="1">
       <c r="A114" s="20" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B114" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E114" s="17"/>
       <c r="F114" s="17"/>
@@ -5655,16 +5655,16 @@
     </row>
     <row r="115" spans="1:12" ht="30" customHeight="1">
       <c r="A115" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B115" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E115" s="17"/>
       <c r="F115" s="17"/>
@@ -5677,16 +5677,16 @@
     </row>
     <row r="116" spans="1:12" ht="30" customHeight="1">
       <c r="A116" s="20" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B116" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E116" s="17"/>
       <c r="F116" s="17"/>
@@ -5699,16 +5699,16 @@
     </row>
     <row r="117" spans="1:12" ht="30" customHeight="1">
       <c r="A117" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E117" s="17"/>
       <c r="F117" s="17"/>
@@ -5721,16 +5721,16 @@
     </row>
     <row r="118" spans="1:12" ht="30" customHeight="1">
       <c r="A118" s="20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E118" s="17"/>
       <c r="F118" s="17"/>
@@ -5743,16 +5743,16 @@
     </row>
     <row r="119" spans="1:12" ht="30" customHeight="1">
       <c r="A119" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E119" s="17"/>
       <c r="F119" s="17"/>
@@ -5765,16 +5765,16 @@
     </row>
     <row r="120" spans="1:12" ht="30" customHeight="1">
       <c r="A120" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E120" s="17"/>
       <c r="F120" s="17"/>
@@ -5787,16 +5787,16 @@
     </row>
     <row r="121" spans="1:12" ht="30" customHeight="1">
       <c r="A121" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B121" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E121" s="17"/>
       <c r="F121" s="17"/>
@@ -5809,16 +5809,16 @@
     </row>
     <row r="122" spans="1:12" ht="30" customHeight="1">
       <c r="A122" s="20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B122" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E122" s="17"/>
       <c r="F122" s="17"/>
@@ -5831,16 +5831,16 @@
     </row>
     <row r="123" spans="1:12" ht="30" customHeight="1">
       <c r="A123" s="20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E123" s="17"/>
       <c r="F123" s="17"/>
@@ -5853,16 +5853,16 @@
     </row>
     <row r="124" spans="1:12" ht="30" customHeight="1">
       <c r="A124" s="20" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B124" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E124" s="17"/>
       <c r="F124" s="17"/>
@@ -5875,16 +5875,16 @@
     </row>
     <row r="125" spans="1:12" ht="30" customHeight="1">
       <c r="A125" s="20" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B125" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E125" s="17"/>
       <c r="F125" s="17"/>
@@ -5897,16 +5897,16 @@
     </row>
     <row r="126" spans="1:12" ht="30" customHeight="1">
       <c r="A126" s="20" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B126" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E126" s="17"/>
       <c r="F126" s="17"/>
@@ -5919,16 +5919,16 @@
     </row>
     <row r="127" spans="1:12" ht="30" customHeight="1">
       <c r="A127" s="20" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B127" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E127" s="17"/>
       <c r="F127" s="17"/>
@@ -5941,16 +5941,16 @@
     </row>
     <row r="128" spans="1:12" ht="30" customHeight="1">
       <c r="A128" s="20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B128" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E128" s="17"/>
       <c r="F128" s="17"/>
@@ -5963,16 +5963,16 @@
     </row>
     <row r="129" spans="1:12" ht="30" customHeight="1">
       <c r="A129" s="20" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B129" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E129" s="17"/>
       <c r="F129" s="17"/>
@@ -5985,16 +5985,16 @@
     </row>
     <row r="130" spans="1:12" ht="30" customHeight="1">
       <c r="A130" s="20" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E130" s="17"/>
       <c r="F130" s="17"/>
@@ -6007,16 +6007,16 @@
     </row>
     <row r="131" spans="1:12" ht="30" customHeight="1">
       <c r="A131" s="20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B131" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E131" s="17"/>
       <c r="F131" s="17"/>
@@ -6029,16 +6029,16 @@
     </row>
     <row r="132" spans="1:12" ht="30" customHeight="1">
       <c r="A132" s="20" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B132" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E132" s="17"/>
       <c r="F132" s="17"/>
@@ -6051,16 +6051,16 @@
     </row>
     <row r="133" spans="1:12" ht="30" customHeight="1">
       <c r="A133" s="20" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B133" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E133" s="17"/>
       <c r="F133" s="17"/>
@@ -6073,16 +6073,16 @@
     </row>
     <row r="134" spans="1:12" ht="30" customHeight="1">
       <c r="A134" s="20" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B134" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E134" s="17"/>
       <c r="F134" s="17"/>
@@ -6095,16 +6095,16 @@
     </row>
     <row r="135" spans="1:12" ht="30" customHeight="1">
       <c r="A135" s="20" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B135" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E135" s="17"/>
       <c r="F135" s="17"/>
@@ -6117,16 +6117,16 @@
     </row>
     <row r="136" spans="1:12" ht="30" customHeight="1">
       <c r="A136" s="20" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B136" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E136" s="17"/>
       <c r="F136" s="17"/>
@@ -6139,16 +6139,16 @@
     </row>
     <row r="137" spans="1:12" ht="30" customHeight="1">
       <c r="A137" s="20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E137" s="17"/>
       <c r="F137" s="17"/>
@@ -6161,16 +6161,16 @@
     </row>
     <row r="138" spans="1:12" ht="30" customHeight="1">
       <c r="A138" s="20" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B138" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E138" s="17"/>
       <c r="F138" s="17"/>
@@ -6183,16 +6183,16 @@
     </row>
     <row r="139" spans="1:12" ht="30" customHeight="1">
       <c r="A139" s="20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B139" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E139" s="17"/>
       <c r="F139" s="17"/>
@@ -6205,16 +6205,16 @@
     </row>
     <row r="140" spans="1:12" ht="30" customHeight="1">
       <c r="A140" s="20" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B140" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E140" s="17"/>
       <c r="F140" s="17"/>
@@ -6227,16 +6227,16 @@
     </row>
     <row r="141" spans="1:12" ht="30" customHeight="1">
       <c r="A141" s="20" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B141" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E141" s="17"/>
       <c r="F141" s="17"/>
@@ -6249,16 +6249,16 @@
     </row>
     <row r="142" spans="1:12" ht="30" customHeight="1">
       <c r="A142" s="20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B142" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E142" s="17"/>
       <c r="F142" s="17"/>
@@ -6271,16 +6271,16 @@
     </row>
     <row r="143" spans="1:12" ht="30" customHeight="1">
       <c r="A143" s="20" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B143" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E143" s="17"/>
       <c r="F143" s="17"/>
@@ -6293,16 +6293,16 @@
     </row>
     <row r="144" spans="1:12" ht="30" customHeight="1">
       <c r="A144" s="20" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B144" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E144" s="17"/>
       <c r="F144" s="17"/>
@@ -6315,16 +6315,16 @@
     </row>
     <row r="145" spans="1:12" ht="30" customHeight="1">
       <c r="A145" s="20" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B145" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E145" s="17"/>
       <c r="F145" s="17"/>
@@ -6337,16 +6337,16 @@
     </row>
     <row r="146" spans="1:12" ht="30" customHeight="1">
       <c r="A146" s="20" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B146" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E146" s="17"/>
       <c r="F146" s="17"/>
@@ -6359,16 +6359,16 @@
     </row>
     <row r="147" spans="1:12" ht="30" customHeight="1">
       <c r="A147" s="20" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B147" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E147" s="17"/>
       <c r="F147" s="17"/>
@@ -6381,16 +6381,16 @@
     </row>
     <row r="148" spans="1:12" ht="30" customHeight="1">
       <c r="A148" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B148" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="D148" s="11" t="s">
         <v>367</v>
-      </c>
-      <c r="B148" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D148" s="11" t="s">
-        <v>369</v>
       </c>
       <c r="E148" s="17"/>
       <c r="F148" s="17"/>
@@ -6403,16 +6403,16 @@
     </row>
     <row r="149" spans="1:12" ht="30" customHeight="1">
       <c r="A149" s="20" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B149" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E149" s="17"/>
       <c r="F149" s="17"/>
@@ -6425,16 +6425,16 @@
     </row>
     <row r="150" spans="1:12" ht="30" customHeight="1">
       <c r="A150" s="20" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B150" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E150" s="17"/>
       <c r="F150" s="17"/>
@@ -6447,16 +6447,16 @@
     </row>
     <row r="151" spans="1:12" ht="30" customHeight="1">
       <c r="A151" s="20" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B151" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E151" s="17"/>
       <c r="F151" s="17"/>
@@ -6469,16 +6469,16 @@
     </row>
     <row r="152" spans="1:12" ht="30" customHeight="1">
       <c r="A152" s="20" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B152" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E152" s="17"/>
       <c r="F152" s="17"/>
@@ -6491,16 +6491,16 @@
     </row>
     <row r="153" spans="1:12" ht="30" customHeight="1">
       <c r="A153" s="20" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B153" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E153" s="17"/>
       <c r="F153" s="17"/>
@@ -6513,16 +6513,16 @@
     </row>
     <row r="154" spans="1:12" ht="30" customHeight="1">
       <c r="A154" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="B154" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="D154" s="11" t="s">
         <v>380</v>
-      </c>
-      <c r="B154" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="D154" s="11" t="s">
-        <v>382</v>
       </c>
       <c r="E154" s="17"/>
       <c r="F154" s="17"/>
@@ -6535,16 +6535,16 @@
     </row>
     <row r="155" spans="1:12" ht="30" customHeight="1">
       <c r="A155" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B155" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E155" s="17"/>
       <c r="F155" s="17"/>
@@ -6557,16 +6557,16 @@
     </row>
     <row r="156" spans="1:12" ht="30" customHeight="1">
       <c r="A156" s="20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B156" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E156" s="17"/>
       <c r="F156" s="17"/>
@@ -6579,16 +6579,16 @@
     </row>
     <row r="157" spans="1:12" ht="30" customHeight="1">
       <c r="A157" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B157" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E157" s="17"/>
       <c r="F157" s="17"/>
@@ -6601,16 +6601,16 @@
     </row>
     <row r="158" spans="1:12" ht="30" customHeight="1">
       <c r="A158" s="20" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B158" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E158" s="17"/>
       <c r="F158" s="17"/>
@@ -6623,16 +6623,16 @@
     </row>
     <row r="159" spans="1:12" ht="30" customHeight="1">
       <c r="A159" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B159" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E159" s="17"/>
       <c r="F159" s="17"/>
@@ -6645,16 +6645,16 @@
     </row>
     <row r="160" spans="1:12" ht="30" customHeight="1">
       <c r="A160" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B160" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E160" s="17"/>
       <c r="F160" s="17"/>
@@ -6667,16 +6667,16 @@
     </row>
     <row r="161" spans="1:12" ht="30" customHeight="1">
       <c r="A161" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B161" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E161" s="17"/>
       <c r="F161" s="17"/>
@@ -6689,16 +6689,16 @@
     </row>
     <row r="162" spans="1:12" ht="30" customHeight="1">
       <c r="A162" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B162" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E162" s="17"/>
       <c r="F162" s="17"/>
@@ -6711,16 +6711,16 @@
     </row>
     <row r="163" spans="1:12" ht="30" customHeight="1">
       <c r="A163" s="20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B163" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E163" s="17"/>
       <c r="F163" s="17"/>
@@ -6733,16 +6733,16 @@
     </row>
     <row r="164" spans="1:12" ht="30" customHeight="1">
       <c r="A164" s="20" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B164" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E164" s="17"/>
       <c r="F164" s="17"/>
@@ -6755,16 +6755,16 @@
     </row>
     <row r="165" spans="1:12" ht="30" customHeight="1">
       <c r="A165" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B165" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E165" s="17"/>
       <c r="F165" s="17"/>
@@ -6777,16 +6777,16 @@
     </row>
     <row r="166" spans="1:12" ht="30" customHeight="1">
       <c r="A166" s="20" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B166" s="14" t="s">
         <v>178</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E166" s="17"/>
       <c r="F166" s="17"/>
@@ -6799,16 +6799,16 @@
     </row>
     <row r="167" spans="1:12" ht="30" customHeight="1">
       <c r="A167" s="20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B167" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>115</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E167" s="17"/>
       <c r="F167" s="17"/>
@@ -6821,16 +6821,16 @@
     </row>
     <row r="168" spans="1:12" ht="30" customHeight="1">
       <c r="A168" s="20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>118</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E168" s="17"/>
       <c r="F168" s="17"/>
@@ -6843,16 +6843,16 @@
     </row>
     <row r="169" spans="1:12" ht="30" customHeight="1">
       <c r="A169" s="20" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>121</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E169" s="17"/>
       <c r="F169" s="17"/>
@@ -6865,16 +6865,16 @@
     </row>
     <row r="170" spans="1:12" ht="30" customHeight="1">
       <c r="A170" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="B170" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="D170" s="11" t="s">
         <v>414</v>
-      </c>
-      <c r="B170" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="D170" s="11" t="s">
-        <v>416</v>
       </c>
       <c r="E170" s="17"/>
       <c r="F170" s="17"/>
@@ -6887,16 +6887,16 @@
     </row>
     <row r="171" spans="1:12" ht="30" customHeight="1">
       <c r="A171" s="20" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>418</v>
+        <v>826</v>
       </c>
       <c r="E171" s="17"/>
       <c r="F171" s="17"/>
@@ -6909,16 +6909,16 @@
     </row>
     <row r="172" spans="1:12" ht="30" customHeight="1">
       <c r="A172" s="20" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E172" s="17"/>
       <c r="F172" s="17"/>
@@ -6931,16 +6931,16 @@
     </row>
     <row r="173" spans="1:12" ht="30" customHeight="1">
       <c r="A173" s="20" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E173" s="17"/>
       <c r="F173" s="17"/>
@@ -6953,16 +6953,16 @@
     </row>
     <row r="174" spans="1:12" ht="30" customHeight="1">
       <c r="A174" s="20" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E174" s="17"/>
       <c r="F174" s="17"/>
@@ -6975,16 +6975,16 @@
     </row>
     <row r="175" spans="1:12" ht="30" customHeight="1">
       <c r="A175" s="20" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E175" s="17"/>
       <c r="F175" s="17"/>
@@ -6997,16 +6997,16 @@
     </row>
     <row r="176" spans="1:12" ht="30" customHeight="1">
       <c r="A176" s="20" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B176" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E176" s="17"/>
       <c r="F176" s="17"/>
@@ -7019,16 +7019,16 @@
     </row>
     <row r="177" spans="1:12" ht="30" customHeight="1">
       <c r="A177" s="20" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>430</v>
+        <v>827</v>
       </c>
       <c r="E177" s="17"/>
       <c r="F177" s="17"/>
@@ -7041,16 +7041,16 @@
     </row>
     <row r="178" spans="1:12" ht="30" customHeight="1">
       <c r="A178" s="20" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E178" s="17"/>
       <c r="F178" s="17"/>
@@ -7063,16 +7063,16 @@
     </row>
     <row r="179" spans="1:12" ht="30" customHeight="1">
       <c r="A179" s="20" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B179" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>434</v>
+        <v>828</v>
       </c>
       <c r="E179" s="17"/>
       <c r="F179" s="17"/>
@@ -7085,13 +7085,13 @@
     </row>
     <row r="180" spans="1:12" ht="30" customHeight="1">
       <c r="A180" s="20" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D180" s="11" t="s">
         <v>84</v>
@@ -7107,16 +7107,16 @@
     </row>
     <row r="181" spans="1:12" ht="30" customHeight="1">
       <c r="A181" s="20" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B181" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>437</v>
+        <v>829</v>
       </c>
       <c r="E181" s="17"/>
       <c r="F181" s="17"/>
@@ -7129,16 +7129,16 @@
     </row>
     <row r="182" spans="1:12" ht="30" customHeight="1">
       <c r="A182" s="20" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="E182" s="17"/>
       <c r="F182" s="17"/>
@@ -7151,16 +7151,16 @@
     </row>
     <row r="183" spans="1:12" ht="30" customHeight="1">
       <c r="A183" s="20" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B183" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E183" s="17"/>
       <c r="F183" s="17"/>
@@ -7173,7 +7173,7 @@
     </row>
     <row r="184" spans="1:12" ht="30" customHeight="1">
       <c r="A184" s="20" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B184" s="14" t="s">
         <v>54</v>
@@ -7182,7 +7182,7 @@
         <v>115</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E184" s="17"/>
       <c r="F184" s="17"/>
@@ -7195,7 +7195,7 @@
     </row>
     <row r="185" spans="1:12" ht="30" customHeight="1">
       <c r="A185" s="20" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B185" s="14" t="s">
         <v>54</v>
@@ -7204,7 +7204,7 @@
         <v>118</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E185" s="17"/>
       <c r="F185" s="17"/>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="186" spans="1:12" ht="30" customHeight="1">
       <c r="A186" s="20" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B186" s="14" t="s">
         <v>54</v>
@@ -7226,7 +7226,7 @@
         <v>121</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E186" s="17"/>
       <c r="F186" s="17"/>
@@ -7239,16 +7239,16 @@
     </row>
     <row r="187" spans="1:12" ht="30" customHeight="1">
       <c r="A187" s="20" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B187" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E187" s="17"/>
       <c r="F187" s="17"/>
@@ -7261,16 +7261,16 @@
     </row>
     <row r="188" spans="1:12" ht="30" customHeight="1">
       <c r="A188" s="20" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B188" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E188" s="17"/>
       <c r="F188" s="17"/>
@@ -7283,16 +7283,16 @@
     </row>
     <row r="189" spans="1:12" ht="30" customHeight="1">
       <c r="A189" s="20" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B189" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="E189" s="17"/>
       <c r="F189" s="17"/>
@@ -7305,16 +7305,16 @@
     </row>
     <row r="190" spans="1:12" ht="30" customHeight="1">
       <c r="A190" s="20" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B190" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E190" s="17"/>
       <c r="F190" s="17"/>
@@ -7327,16 +7327,16 @@
     </row>
     <row r="191" spans="1:12" ht="30" customHeight="1">
       <c r="A191" s="20" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B191" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="E191" s="17"/>
       <c r="F191" s="17"/>
@@ -7349,16 +7349,16 @@
     </row>
     <row r="192" spans="1:12" ht="30" customHeight="1">
       <c r="A192" s="20" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B192" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E192" s="17"/>
       <c r="F192" s="17"/>
@@ -7371,16 +7371,16 @@
     </row>
     <row r="193" spans="1:12" ht="30" customHeight="1">
       <c r="A193" s="20" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B193" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="E193" s="17"/>
       <c r="F193" s="17"/>
@@ -7393,16 +7393,16 @@
     </row>
     <row r="194" spans="1:12" ht="30" customHeight="1">
       <c r="A194" s="20" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B194" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E194" s="17"/>
       <c r="F194" s="17"/>
@@ -7415,16 +7415,16 @@
     </row>
     <row r="195" spans="1:12" ht="30" customHeight="1">
       <c r="A195" s="20" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B195" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E195" s="17"/>
       <c r="F195" s="17"/>
@@ -7437,16 +7437,16 @@
     </row>
     <row r="196" spans="1:12" ht="30" customHeight="1">
       <c r="A196" s="20" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B196" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E196" s="17"/>
       <c r="F196" s="17"/>
@@ -7459,16 +7459,16 @@
     </row>
     <row r="197" spans="1:12" ht="30" customHeight="1">
       <c r="A197" s="20" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B197" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E197" s="17"/>
       <c r="F197" s="17"/>
@@ -7481,16 +7481,16 @@
     </row>
     <row r="198" spans="1:12" ht="30" customHeight="1">
       <c r="A198" s="20" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B198" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E198" s="17"/>
       <c r="F198" s="17"/>
@@ -7503,13 +7503,13 @@
     </row>
     <row r="199" spans="1:12" ht="30" customHeight="1">
       <c r="A199" s="20" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D199" s="11"/>
       <c r="E199" s="17"/>
@@ -7523,16 +7523,16 @@
     </row>
     <row r="200" spans="1:12" ht="30" customHeight="1">
       <c r="A200" s="20" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B200" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C200" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="D200" s="11" t="s">
         <v>473</v>
-      </c>
-      <c r="D200" s="11" t="s">
-        <v>479</v>
       </c>
       <c r="E200" s="17"/>
       <c r="F200" s="17"/>
@@ -7545,16 +7545,16 @@
     </row>
     <row r="201" spans="1:12" ht="30" customHeight="1">
       <c r="A201" s="20" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B201" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E201" s="17"/>
       <c r="F201" s="17"/>
@@ -7567,16 +7567,16 @@
     </row>
     <row r="202" spans="1:12" ht="30" customHeight="1">
       <c r="A202" s="20" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B202" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E202" s="17"/>
       <c r="F202" s="17"/>
@@ -7589,16 +7589,16 @@
     </row>
     <row r="203" spans="1:12" ht="30" customHeight="1">
       <c r="A203" s="20" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B203" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E203" s="17"/>
       <c r="F203" s="17"/>
@@ -7611,16 +7611,16 @@
     </row>
     <row r="204" spans="1:12" ht="30" customHeight="1">
       <c r="A204" s="20" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B204" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="E204" s="17"/>
       <c r="F204" s="17"/>
@@ -7633,16 +7633,16 @@
     </row>
     <row r="205" spans="1:12" ht="30" customHeight="1">
       <c r="A205" s="20" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B205" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="E205" s="17"/>
       <c r="F205" s="17"/>
@@ -7655,16 +7655,16 @@
     </row>
     <row r="206" spans="1:12" ht="30" customHeight="1">
       <c r="A206" s="20" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B206" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D206" s="11" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="E206" s="17"/>
       <c r="F206" s="17"/>
@@ -7677,16 +7677,16 @@
     </row>
     <row r="207" spans="1:12" ht="30" customHeight="1">
       <c r="A207" s="20" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="E207" s="17"/>
       <c r="F207" s="17"/>
@@ -7699,16 +7699,16 @@
     </row>
     <row r="208" spans="1:12" ht="30" customHeight="1">
       <c r="A208" s="20" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B208" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="E208" s="17"/>
       <c r="F208" s="17"/>
@@ -7721,16 +7721,16 @@
     </row>
     <row r="209" spans="1:12" ht="30" customHeight="1">
       <c r="A209" s="20" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B209" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E209" s="17"/>
       <c r="F209" s="17"/>
@@ -7743,16 +7743,16 @@
     </row>
     <row r="210" spans="1:12" ht="30" customHeight="1">
       <c r="A210" s="20" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B210" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E210" s="17"/>
       <c r="F210" s="17"/>
@@ -7765,16 +7765,16 @@
     </row>
     <row r="211" spans="1:12" ht="30" customHeight="1">
       <c r="A211" s="20" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D211" s="11" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E211" s="17"/>
       <c r="F211" s="17"/>
@@ -7787,16 +7787,16 @@
     </row>
     <row r="212" spans="1:12" ht="30" customHeight="1">
       <c r="A212" s="20" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B212" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E212" s="17"/>
       <c r="F212" s="17"/>
@@ -7809,16 +7809,16 @@
     </row>
     <row r="213" spans="1:12" ht="30" customHeight="1">
       <c r="A213" s="20" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="E213" s="17"/>
       <c r="F213" s="17"/>
@@ -7831,16 +7831,16 @@
     </row>
     <row r="214" spans="1:12" ht="30" customHeight="1">
       <c r="A214" s="20" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B214" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E214" s="17"/>
       <c r="F214" s="17"/>
@@ -7853,16 +7853,16 @@
     </row>
     <row r="215" spans="1:12" ht="30" customHeight="1">
       <c r="A215" s="20" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B215" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E215" s="17"/>
       <c r="F215" s="17"/>
@@ -7875,16 +7875,16 @@
     </row>
     <row r="216" spans="1:12" ht="30" customHeight="1">
       <c r="A216" s="20" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B216" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D216" s="11" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E216" s="17"/>
       <c r="F216" s="17"/>
@@ -7897,16 +7897,16 @@
     </row>
     <row r="217" spans="1:12" ht="30" customHeight="1">
       <c r="A217" s="20" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B217" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E217" s="17"/>
       <c r="F217" s="17"/>
@@ -7919,16 +7919,16 @@
     </row>
     <row r="218" spans="1:12" ht="30" customHeight="1">
       <c r="A218" s="20" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B218" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C218" s="8" t="s">
         <v>115</v>
       </c>
       <c r="D218" s="11" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="E218" s="17"/>
       <c r="F218" s="17"/>
@@ -7941,16 +7941,16 @@
     </row>
     <row r="219" spans="1:12" ht="30" customHeight="1">
       <c r="A219" s="20" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C219" s="8" t="s">
         <v>118</v>
       </c>
       <c r="D219" s="11" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="E219" s="17"/>
       <c r="F219" s="17"/>
@@ -7963,16 +7963,16 @@
     </row>
     <row r="220" spans="1:12" ht="30" customHeight="1">
       <c r="A220" s="20" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C220" s="8" t="s">
         <v>121</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="E220" s="17"/>
       <c r="F220" s="17"/>
@@ -7985,16 +7985,16 @@
     </row>
     <row r="221" spans="1:12" ht="30" customHeight="1">
       <c r="A221" s="20" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D221" s="11" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E221" s="17"/>
       <c r="F221" s="17"/>
@@ -8007,16 +8007,16 @@
     </row>
     <row r="222" spans="1:12" ht="30" customHeight="1">
       <c r="A222" s="20" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D222" s="11" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E222" s="17"/>
       <c r="F222" s="17"/>
@@ -8029,16 +8029,16 @@
     </row>
     <row r="223" spans="1:12" ht="30" customHeight="1">
       <c r="A223" s="20" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B223" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D223" s="11" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="E223" s="17"/>
       <c r="F223" s="17"/>
@@ -8051,16 +8051,16 @@
     </row>
     <row r="224" spans="1:12" ht="30" customHeight="1">
       <c r="A224" s="20" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B224" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="E224" s="17"/>
       <c r="F224" s="17"/>
@@ -8073,16 +8073,16 @@
     </row>
     <row r="225" spans="1:12" ht="30" customHeight="1">
       <c r="A225" s="20" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B225" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="E225" s="17"/>
       <c r="F225" s="17"/>
@@ -8095,16 +8095,16 @@
     </row>
     <row r="226" spans="1:12" ht="30" customHeight="1">
       <c r="A226" s="20" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B226" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="D226" s="11" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="E226" s="17"/>
       <c r="F226" s="17"/>
@@ -8117,16 +8117,16 @@
     </row>
     <row r="227" spans="1:12" ht="30" customHeight="1">
       <c r="A227" s="20" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B227" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D227" s="11" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E227" s="17"/>
       <c r="F227" s="17"/>
@@ -8139,16 +8139,16 @@
     </row>
     <row r="228" spans="1:12" ht="30" customHeight="1">
       <c r="A228" s="20" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B228" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E228" s="17"/>
       <c r="F228" s="17"/>
@@ -8161,16 +8161,16 @@
     </row>
     <row r="229" spans="1:12" ht="30" customHeight="1">
       <c r="A229" s="20" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B229" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D229" s="11" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E229" s="17"/>
       <c r="F229" s="17"/>
@@ -8183,16 +8183,16 @@
     </row>
     <row r="230" spans="1:12" ht="30" customHeight="1">
       <c r="A230" s="20" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B230" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D230" s="11" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E230" s="17"/>
       <c r="F230" s="17"/>
@@ -8205,16 +8205,16 @@
     </row>
     <row r="231" spans="1:12" ht="30" customHeight="1">
       <c r="A231" s="20" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B231" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D231" s="11" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E231" s="17"/>
       <c r="F231" s="17"/>
@@ -8227,16 +8227,16 @@
     </row>
     <row r="232" spans="1:12" ht="30" customHeight="1">
       <c r="A232" s="20" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B232" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D232" s="11" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="E232" s="17"/>
       <c r="F232" s="17"/>
@@ -8249,16 +8249,16 @@
     </row>
     <row r="233" spans="1:12" ht="30" customHeight="1">
       <c r="A233" s="20" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B233" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D233" s="11" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="E233" s="17"/>
       <c r="F233" s="17"/>
@@ -8271,16 +8271,16 @@
     </row>
     <row r="234" spans="1:12" ht="30" customHeight="1">
       <c r="A234" s="20" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B234" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D234" s="11" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="E234" s="17"/>
       <c r="F234" s="17"/>
@@ -8293,16 +8293,16 @@
     </row>
     <row r="235" spans="1:12" ht="30" customHeight="1">
       <c r="A235" s="20" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="B235" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="E235" s="17"/>
       <c r="F235" s="17"/>
@@ -8315,16 +8315,16 @@
     </row>
     <row r="236" spans="1:12" ht="30" customHeight="1">
       <c r="A236" s="20" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D236" s="11" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E236" s="17"/>
       <c r="F236" s="17"/>
@@ -8337,16 +8337,16 @@
     </row>
     <row r="237" spans="1:12" ht="30" customHeight="1">
       <c r="A237" s="20" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B237" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C237" s="8" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D237" s="11" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="E237" s="17"/>
       <c r="F237" s="17"/>
@@ -8359,16 +8359,16 @@
     </row>
     <row r="238" spans="1:12" ht="30" customHeight="1">
       <c r="A238" s="20" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B238" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D238" s="11" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="E238" s="17"/>
       <c r="F238" s="17"/>
@@ -8381,16 +8381,16 @@
     </row>
     <row r="239" spans="1:12" ht="30" customHeight="1">
       <c r="A239" s="20" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B239" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C239" s="8" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D239" s="11" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E239" s="17"/>
       <c r="F239" s="17"/>
@@ -8403,16 +8403,16 @@
     </row>
     <row r="240" spans="1:12" ht="30" customHeight="1">
       <c r="A240" s="20" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B240" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D240" s="11" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="E240" s="17"/>
       <c r="F240" s="17"/>
@@ -8425,16 +8425,16 @@
     </row>
     <row r="241" spans="1:12" ht="30" customHeight="1">
       <c r="A241" s="20" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="B241" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D241" s="11" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E241" s="17"/>
       <c r="F241" s="17"/>
@@ -8447,16 +8447,16 @@
     </row>
     <row r="242" spans="1:12" ht="30" customHeight="1">
       <c r="A242" s="20" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B242" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C242" s="8" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D242" s="11" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="E242" s="17"/>
       <c r="F242" s="17"/>
@@ -8469,16 +8469,16 @@
     </row>
     <row r="243" spans="1:12" ht="30" customHeight="1">
       <c r="A243" s="20" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B243" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C243" s="8" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D243" s="11" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="E243" s="17"/>
       <c r="F243" s="17"/>
@@ -8491,16 +8491,16 @@
     </row>
     <row r="244" spans="1:12" ht="30" customHeight="1">
       <c r="A244" s="20" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B244" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C244" s="8" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E244" s="17"/>
       <c r="F244" s="17"/>
@@ -8513,16 +8513,16 @@
     </row>
     <row r="245" spans="1:12" ht="30" customHeight="1">
       <c r="A245" s="20" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="B245" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D245" s="11" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="E245" s="17"/>
       <c r="F245" s="17"/>
@@ -8535,16 +8535,16 @@
     </row>
     <row r="246" spans="1:12" ht="30" customHeight="1">
       <c r="A246" s="20" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B246" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C246" s="8" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D246" s="11" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E246" s="17"/>
       <c r="F246" s="17"/>
@@ -8557,16 +8557,16 @@
     </row>
     <row r="247" spans="1:12" ht="30" customHeight="1">
       <c r="A247" s="20" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="B247" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C247" s="8" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D247" s="11" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="E247" s="17"/>
       <c r="F247" s="17"/>
@@ -8579,16 +8579,16 @@
     </row>
     <row r="248" spans="1:12" ht="30" customHeight="1">
       <c r="A248" s="20" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B248" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C248" s="8" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D248" s="11" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E248" s="17"/>
       <c r="F248" s="17"/>
@@ -8601,16 +8601,16 @@
     </row>
     <row r="249" spans="1:12" ht="30" customHeight="1">
       <c r="A249" s="20" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B249" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C249" s="8" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D249" s="11" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E249" s="17"/>
       <c r="F249" s="17"/>
@@ -8623,16 +8623,16 @@
     </row>
     <row r="250" spans="1:12" ht="30" customHeight="1">
       <c r="A250" s="20" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B250" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D250" s="11" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="E250" s="17"/>
       <c r="F250" s="17"/>
@@ -8645,16 +8645,16 @@
     </row>
     <row r="251" spans="1:12" ht="30" customHeight="1">
       <c r="A251" s="20" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="B251" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D251" s="11" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="E251" s="17"/>
       <c r="F251" s="17"/>
@@ -8667,16 +8667,16 @@
     </row>
     <row r="252" spans="1:12" ht="30" customHeight="1">
       <c r="A252" s="20" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B252" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D252" s="11" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="E252" s="17"/>
       <c r="F252" s="17"/>
@@ -8689,16 +8689,16 @@
     </row>
     <row r="253" spans="1:12" ht="30" customHeight="1">
       <c r="A253" s="20" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="B253" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="D253" s="11" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="E253" s="17"/>
       <c r="F253" s="17"/>
@@ -8711,16 +8711,16 @@
     </row>
     <row r="254" spans="1:12" ht="30" customHeight="1">
       <c r="A254" s="20" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B254" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C254" s="8" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D254" s="11" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="E254" s="17"/>
       <c r="F254" s="17"/>
@@ -8733,16 +8733,16 @@
     </row>
     <row r="255" spans="1:12" ht="30" customHeight="1">
       <c r="A255" s="20" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C255" s="8" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D255" s="11" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="E255" s="17"/>
       <c r="F255" s="17"/>
@@ -8755,16 +8755,16 @@
     </row>
     <row r="256" spans="1:12" ht="30" customHeight="1">
       <c r="A256" s="20" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B256" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="D256" s="11" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="E256" s="17"/>
       <c r="F256" s="17"/>
@@ -8777,16 +8777,16 @@
     </row>
     <row r="257" spans="1:12" ht="30" customHeight="1">
       <c r="A257" s="20" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B257" s="14" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C257" s="8" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D257" s="11" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="E257" s="17"/>
       <c r="F257" s="17"/>
@@ -8799,16 +8799,16 @@
     </row>
     <row r="258" spans="1:12" ht="30" customHeight="1">
       <c r="A258" s="20" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B258" s="14" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C258" s="8" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D258" s="11" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="E258" s="17"/>
       <c r="F258" s="17"/>
@@ -8821,16 +8821,16 @@
     </row>
     <row r="259" spans="1:12" ht="30" customHeight="1">
       <c r="A259" s="20" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B259" s="14" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D259" s="11" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E259" s="17"/>
       <c r="F259" s="17"/>
@@ -8843,16 +8843,16 @@
     </row>
     <row r="260" spans="1:12" ht="30" customHeight="1">
       <c r="A260" s="20" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D260" s="11" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E260" s="17"/>
       <c r="F260" s="17"/>
@@ -8865,16 +8865,16 @@
     </row>
     <row r="261" spans="1:12" ht="30" customHeight="1">
       <c r="A261" s="20" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="B261" s="14" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D261" s="11" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="E261" s="17"/>
       <c r="F261" s="17"/>
@@ -8887,16 +8887,16 @@
     </row>
     <row r="262" spans="1:12" ht="30" customHeight="1">
       <c r="A262" s="20" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B262" s="14" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D262" s="11" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E262" s="17"/>
       <c r="F262" s="17"/>
@@ -8909,16 +8909,16 @@
     </row>
     <row r="263" spans="1:12" ht="30" customHeight="1">
       <c r="A263" s="20" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B263" s="14" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="D263" s="11" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="E263" s="17"/>
       <c r="F263" s="17"/>
@@ -8931,16 +8931,16 @@
     </row>
     <row r="264" spans="1:12" ht="30" customHeight="1">
       <c r="A264" s="20" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B264" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C264" s="8" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E264" s="17"/>
       <c r="F264" s="17"/>
@@ -8953,16 +8953,16 @@
     </row>
     <row r="265" spans="1:12" ht="30" customHeight="1">
       <c r="A265" s="20" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="B265" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D265" s="11" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="E265" s="17"/>
       <c r="F265" s="17"/>
@@ -8975,16 +8975,16 @@
     </row>
     <row r="266" spans="1:12" ht="30" customHeight="1">
       <c r="A266" s="20" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B266" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="C266" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="C266" s="8" t="s">
-        <v>639</v>
-      </c>
       <c r="D266" s="11" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E266" s="17"/>
       <c r="F266" s="17"/>
@@ -8997,16 +8997,16 @@
     </row>
     <row r="267" spans="1:12" ht="30" customHeight="1">
       <c r="A267" s="20" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B267" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C267" s="8" t="s">
         <v>60</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E267" s="17"/>
       <c r="F267" s="17"/>
@@ -9019,16 +9019,16 @@
     </row>
     <row r="268" spans="1:12" ht="30" customHeight="1">
       <c r="A268" s="20" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B268" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C268" s="8" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="E268" s="17"/>
       <c r="F268" s="17"/>
@@ -9041,16 +9041,16 @@
     </row>
     <row r="269" spans="1:12" ht="30" customHeight="1">
       <c r="A269" s="20" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="B269" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D269" s="11" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="E269" s="17"/>
       <c r="F269" s="17"/>
@@ -9063,16 +9063,16 @@
     </row>
     <row r="270" spans="1:12" ht="30" customHeight="1">
       <c r="A270" s="20" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B270" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C270" s="8" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="E270" s="17"/>
       <c r="F270" s="17"/>
@@ -9085,16 +9085,16 @@
     </row>
     <row r="271" spans="1:12" ht="30" customHeight="1">
       <c r="A271" s="20" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B271" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C271" s="8" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="E271" s="17"/>
       <c r="F271" s="17"/>
@@ -9107,16 +9107,16 @@
     </row>
     <row r="272" spans="1:12" ht="30" customHeight="1">
       <c r="A272" s="20" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B272" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C272" s="8" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="E272" s="17"/>
       <c r="F272" s="17"/>
@@ -9129,16 +9129,16 @@
     </row>
     <row r="273" spans="1:12" ht="30" customHeight="1">
       <c r="A273" s="20" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="B273" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E273" s="17"/>
       <c r="F273" s="17"/>
@@ -9151,16 +9151,16 @@
     </row>
     <row r="274" spans="1:12" ht="30" customHeight="1">
       <c r="A274" s="20" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B274" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="E274" s="17"/>
       <c r="F274" s="17"/>
@@ -9173,16 +9173,16 @@
     </row>
     <row r="275" spans="1:12" ht="30" customHeight="1">
       <c r="A275" s="20" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B275" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D275" s="11" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="E275" s="17"/>
       <c r="F275" s="17"/>
@@ -9195,16 +9195,16 @@
     </row>
     <row r="276" spans="1:12" ht="30" customHeight="1">
       <c r="A276" s="20" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B276" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E276" s="17"/>
       <c r="F276" s="17"/>
@@ -9217,16 +9217,16 @@
     </row>
     <row r="277" spans="1:12" ht="30" customHeight="1">
       <c r="A277" s="20" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B277" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E277" s="17"/>
       <c r="F277" s="17"/>
@@ -9239,16 +9239,16 @@
     </row>
     <row r="278" spans="1:12" ht="30" customHeight="1">
       <c r="A278" s="20" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B278" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D278" s="11" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E278" s="17"/>
       <c r="F278" s="17"/>
@@ -9261,16 +9261,16 @@
     </row>
     <row r="279" spans="1:12" ht="30" customHeight="1">
       <c r="A279" s="20" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="B279" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C279" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D279" s="11" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="E279" s="17"/>
       <c r="F279" s="17"/>
@@ -9283,16 +9283,16 @@
     </row>
     <row r="280" spans="1:12" ht="30" customHeight="1">
       <c r="A280" s="20" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B280" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="E280" s="17"/>
       <c r="F280" s="17"/>
@@ -9305,16 +9305,16 @@
     </row>
     <row r="281" spans="1:12" ht="30" customHeight="1">
       <c r="A281" s="20" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B281" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C281" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D281" s="11" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="E281" s="17"/>
       <c r="F281" s="17"/>
@@ -9327,16 +9327,16 @@
     </row>
     <row r="282" spans="1:12" ht="30" customHeight="1">
       <c r="A282" s="20" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="B282" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E282" s="17"/>
       <c r="F282" s="17"/>
@@ -9349,16 +9349,16 @@
     </row>
     <row r="283" spans="1:12" ht="30" customHeight="1">
       <c r="A283" s="20" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B283" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D283" s="11" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E283" s="17"/>
       <c r="F283" s="17"/>
@@ -9371,16 +9371,16 @@
     </row>
     <row r="284" spans="1:12" ht="30" customHeight="1">
       <c r="A284" s="20" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B284" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="E284" s="17"/>
       <c r="F284" s="17"/>
@@ -9393,16 +9393,16 @@
     </row>
     <row r="285" spans="1:12" ht="30" customHeight="1">
       <c r="A285" s="20" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B285" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C285" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D285" s="11" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="E285" s="17"/>
       <c r="F285" s="17"/>
@@ -9415,16 +9415,16 @@
     </row>
     <row r="286" spans="1:12" ht="30" customHeight="1">
       <c r="A286" s="20" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B286" s="14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E286" s="17"/>
       <c r="F286" s="17"/>
@@ -9437,16 +9437,16 @@
     </row>
     <row r="287" spans="1:12" ht="30" customHeight="1">
       <c r="A287" s="20" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B287" s="14" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D287" s="11" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="E287" s="17"/>
       <c r="F287" s="17"/>
@@ -9459,16 +9459,16 @@
     </row>
     <row r="288" spans="1:12" ht="30" customHeight="1">
       <c r="A288" s="20" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B288" s="14" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="E288" s="17"/>
       <c r="F288" s="17"/>
@@ -9481,16 +9481,16 @@
     </row>
     <row r="289" spans="1:12" ht="30" customHeight="1">
       <c r="A289" s="20" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="B289" s="14" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="D289" s="11" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E289" s="17"/>
       <c r="F289" s="17"/>
@@ -9503,16 +9503,16 @@
     </row>
     <row r="290" spans="1:12" ht="30" customHeight="1">
       <c r="A290" s="20" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="B290" s="14" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C290" s="8" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D290" s="11" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="E290" s="17"/>
       <c r="F290" s="17"/>
@@ -9525,16 +9525,16 @@
     </row>
     <row r="291" spans="1:12" ht="30" customHeight="1">
       <c r="A291" s="20" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="B291" s="14" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C291" s="8" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D291" s="11" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="E291" s="17"/>
       <c r="F291" s="17"/>
@@ -9547,16 +9547,16 @@
     </row>
     <row r="292" spans="1:12" ht="30" customHeight="1">
       <c r="A292" s="20" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B292" s="14" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D292" s="11" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="E292" s="17"/>
       <c r="F292" s="17"/>
@@ -9569,16 +9569,16 @@
     </row>
     <row r="293" spans="1:12" ht="30" customHeight="1">
       <c r="A293" s="20" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B293" s="14" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D293" s="11" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="E293" s="17"/>
       <c r="F293" s="17"/>
@@ -9591,16 +9591,16 @@
     </row>
     <row r="294" spans="1:12" ht="30" customHeight="1">
       <c r="A294" s="20" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="B294" s="14" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C294" s="8" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D294" s="11" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="E294" s="17"/>
       <c r="F294" s="17"/>
@@ -9613,16 +9613,16 @@
     </row>
     <row r="295" spans="1:12" ht="30" customHeight="1">
       <c r="A295" s="20" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="B295" s="14" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D295" s="11" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="E295" s="17"/>
       <c r="F295" s="17"/>
@@ -9635,16 +9635,16 @@
     </row>
     <row r="296" spans="1:12" ht="30" customHeight="1">
       <c r="A296" s="20" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B296" s="14" t="s">
+        <v>701</v>
+      </c>
+      <c r="C296" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="D296" s="11" t="s">
         <v>707</v>
-      </c>
-      <c r="C296" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="D296" s="11" t="s">
-        <v>713</v>
       </c>
       <c r="E296" s="17"/>
       <c r="F296" s="17"/>
@@ -9657,16 +9657,16 @@
     </row>
     <row r="297" spans="1:12" ht="30" customHeight="1">
       <c r="A297" s="20" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="B297" s="14" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C297" s="8" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D297" s="11" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="E297" s="17"/>
       <c r="F297" s="17"/>
@@ -9679,16 +9679,16 @@
     </row>
     <row r="298" spans="1:12" ht="30" customHeight="1">
       <c r="A298" s="20" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="B298" s="14" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C298" s="8" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D298" s="11" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="E298" s="17"/>
       <c r="F298" s="17"/>
@@ -9701,16 +9701,16 @@
     </row>
     <row r="299" spans="1:12" ht="30" customHeight="1">
       <c r="A299" s="20" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="B299" s="14" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C299" s="8" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D299" s="11" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="E299" s="17"/>
       <c r="F299" s="17"/>
@@ -9723,16 +9723,16 @@
     </row>
     <row r="300" spans="1:12" ht="30" customHeight="1">
       <c r="A300" s="20" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="B300" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C300" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D300" s="11" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E300" s="17"/>
       <c r="F300" s="17"/>
@@ -9745,16 +9745,16 @@
     </row>
     <row r="301" spans="1:12" ht="30" customHeight="1">
       <c r="A301" s="20" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="B301" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C301" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D301" s="11" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="E301" s="17"/>
       <c r="F301" s="17"/>
@@ -9767,16 +9767,16 @@
     </row>
     <row r="302" spans="1:12" ht="30" customHeight="1">
       <c r="A302" s="20" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B302" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C302" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E302" s="17"/>
       <c r="F302" s="17"/>
@@ -9789,16 +9789,16 @@
     </row>
     <row r="303" spans="1:12" ht="30" customHeight="1">
       <c r="A303" s="20" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="B303" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C303" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D303" s="11" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E303" s="17"/>
       <c r="F303" s="17"/>
@@ -9811,16 +9811,16 @@
     </row>
     <row r="304" spans="1:12" ht="30" customHeight="1">
       <c r="A304" s="20" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="B304" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C304" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D304" s="11" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E304" s="17"/>
       <c r="F304" s="17"/>
@@ -9833,16 +9833,16 @@
     </row>
     <row r="305" spans="1:12" ht="30" customHeight="1">
       <c r="A305" s="20" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="B305" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C305" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D305" s="11" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E305" s="17"/>
       <c r="F305" s="17"/>
@@ -9855,16 +9855,16 @@
     </row>
     <row r="306" spans="1:12" ht="30" customHeight="1">
       <c r="A306" s="20" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="B306" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C306" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D306" s="11" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="E306" s="17"/>
       <c r="F306" s="17"/>
@@ -9877,16 +9877,16 @@
     </row>
     <row r="307" spans="1:12" ht="30" customHeight="1">
       <c r="A307" s="20" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B307" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C307" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D307" s="11" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="E307" s="17"/>
       <c r="F307" s="17"/>
@@ -9899,16 +9899,16 @@
     </row>
     <row r="308" spans="1:12" ht="30" customHeight="1">
       <c r="A308" s="20" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B308" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C308" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D308" s="11" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="E308" s="17"/>
       <c r="F308" s="17"/>
@@ -9921,16 +9921,16 @@
     </row>
     <row r="309" spans="1:12" ht="30" customHeight="1">
       <c r="A309" s="20" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B309" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C309" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D309" s="11" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="E309" s="17"/>
       <c r="F309" s="17"/>
@@ -9943,16 +9943,16 @@
     </row>
     <row r="310" spans="1:12" ht="30" customHeight="1">
       <c r="A310" s="20" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="B310" s="14" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C310" s="8" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D310" s="11" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="E310" s="17"/>
       <c r="F310" s="17"/>
@@ -9965,16 +9965,16 @@
     </row>
     <row r="311" spans="1:12" ht="30" customHeight="1">
       <c r="A311" s="20" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="B311" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C311" s="8" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D311" s="11" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="E311" s="17"/>
       <c r="F311" s="17"/>
@@ -9987,16 +9987,16 @@
     </row>
     <row r="312" spans="1:12" ht="30" customHeight="1">
       <c r="A312" s="20" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B312" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C312" s="8" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="D312" s="11" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="E312" s="17"/>
       <c r="F312" s="17"/>
@@ -10009,16 +10009,16 @@
     </row>
     <row r="313" spans="1:12" ht="30" customHeight="1">
       <c r="A313" s="20" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="B313" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C313" s="8" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="D313" s="11" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E313" s="17"/>
       <c r="F313" s="17"/>
@@ -10031,13 +10031,13 @@
     </row>
     <row r="314" spans="1:12" ht="30" customHeight="1">
       <c r="A314" s="20" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="B314" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C314" s="8" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D314" s="11" t="s">
         <v>76</v>
@@ -10053,16 +10053,16 @@
     </row>
     <row r="315" spans="1:12" ht="30" customHeight="1">
       <c r="A315" s="20" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="B315" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C315" s="8" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E315" s="17"/>
       <c r="F315" s="17"/>
@@ -10075,16 +10075,16 @@
     </row>
     <row r="316" spans="1:12" ht="30" customHeight="1">
       <c r="A316" s="20" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="B316" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C316" s="8" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="E316" s="17"/>
       <c r="F316" s="17"/>
@@ -10097,16 +10097,16 @@
     </row>
     <row r="317" spans="1:12" ht="30" customHeight="1">
       <c r="A317" s="20" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B317" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C317" s="8" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E317" s="17"/>
       <c r="F317" s="17"/>
@@ -10119,16 +10119,16 @@
     </row>
     <row r="318" spans="1:12" ht="30" customHeight="1">
       <c r="A318" s="20" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="B318" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E318" s="17"/>
       <c r="F318" s="17"/>
@@ -10141,16 +10141,16 @@
     </row>
     <row r="319" spans="1:12" ht="30" customHeight="1">
       <c r="A319" s="20" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B319" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C319" s="8" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="D319" s="11" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="E319" s="17"/>
       <c r="F319" s="17"/>
@@ -10163,16 +10163,16 @@
     </row>
     <row r="320" spans="1:12" ht="30" customHeight="1">
       <c r="A320" s="20" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="B320" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C320" s="8" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="D320" s="11" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="E320" s="17"/>
       <c r="F320" s="17"/>
@@ -10185,16 +10185,16 @@
     </row>
     <row r="321" spans="1:12" ht="30" customHeight="1">
       <c r="A321" s="20" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="B321" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C321" s="8" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="D321" s="11" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="E321" s="17"/>
       <c r="F321" s="17"/>
@@ -10207,16 +10207,16 @@
     </row>
     <row r="322" spans="1:12" ht="30" customHeight="1">
       <c r="A322" s="20" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="B322" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C322" s="8" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="D322" s="11" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="E322" s="17"/>
       <c r="F322" s="17"/>
@@ -10229,16 +10229,16 @@
     </row>
     <row r="323" spans="1:12" ht="30" customHeight="1">
       <c r="A323" s="20" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B323" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C323" s="8" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="D323" s="11" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="E323" s="17"/>
       <c r="F323" s="17"/>
@@ -10251,16 +10251,16 @@
     </row>
     <row r="324" spans="1:12" ht="30" customHeight="1">
       <c r="A324" s="20" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="B324" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C324" s="8" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="D324" s="11" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="E324" s="17"/>
       <c r="F324" s="17"/>
@@ -10273,16 +10273,16 @@
     </row>
     <row r="325" spans="1:12" ht="30" customHeight="1">
       <c r="A325" s="20" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B325" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C325" s="8" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="D325" s="11" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="E325" s="17"/>
       <c r="F325" s="17"/>
@@ -10295,16 +10295,16 @@
     </row>
     <row r="326" spans="1:12" ht="30" customHeight="1">
       <c r="A326" s="20" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="B326" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C326" s="8" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="D326" s="11" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="E326" s="17"/>
       <c r="F326" s="17"/>
@@ -10317,16 +10317,16 @@
     </row>
     <row r="327" spans="1:12" ht="30" customHeight="1">
       <c r="A327" s="20" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="B327" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C327" s="8" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="D327" s="11" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="E327" s="17"/>
       <c r="F327" s="17"/>
@@ -10339,16 +10339,16 @@
     </row>
     <row r="328" spans="1:12" ht="30" customHeight="1">
       <c r="A328" s="20" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="B328" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C328" s="8" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="D328" s="11" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="E328" s="17"/>
       <c r="F328" s="17"/>
@@ -10361,16 +10361,16 @@
     </row>
     <row r="329" spans="1:12" ht="30" customHeight="1">
       <c r="A329" s="20" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="B329" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="D329" s="11" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="E329" s="17"/>
       <c r="F329" s="17"/>
@@ -10383,16 +10383,16 @@
     </row>
     <row r="330" spans="1:12" ht="30" customHeight="1">
       <c r="A330" s="20" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="B330" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C330" s="8" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="D330" s="11" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="E330" s="17"/>
       <c r="F330" s="17"/>
@@ -10405,16 +10405,16 @@
     </row>
     <row r="331" spans="1:12" ht="30" customHeight="1">
       <c r="A331" s="21" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="B331" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C331" s="9" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="D331" s="12" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="E331" s="18"/>
       <c r="F331" s="18"/>
@@ -10427,16 +10427,16 @@
     </row>
     <row r="332" spans="1:12" ht="15">
       <c r="A332" s="23" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="B332" s="24" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C332" s="25" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="D332" s="26" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="E332" s="22"/>
       <c r="F332" s="22"/>
@@ -10449,16 +10449,16 @@
     </row>
     <row r="333" spans="1:12" ht="15">
       <c r="A333" s="23" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="B333" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C333" s="28" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D333" s="29" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="E333" s="22"/>
       <c r="F333" s="22"/>
@@ -10471,16 +10471,16 @@
     </row>
     <row r="334" spans="1:12" ht="15">
       <c r="A334" s="23" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="B334" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C334" s="25" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="D334" s="26" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="E334" s="22"/>
       <c r="F334" s="22"/>
@@ -10493,16 +10493,16 @@
     </row>
     <row r="335" spans="1:12" ht="15">
       <c r="A335" s="23" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="B335" s="27" t="s">
         <v>50</v>
       </c>
       <c r="C335" s="28" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="D335" s="29" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E335" s="22"/>
       <c r="F335" s="22"/>
@@ -10515,16 +10515,16 @@
     </row>
     <row r="336" spans="1:12" ht="15">
       <c r="A336" s="23" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B336" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C336" s="25" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="D336" s="26" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="E336" s="22"/>
       <c r="F336" s="22"/>
@@ -10537,16 +10537,16 @@
     </row>
     <row r="337" spans="1:12" ht="15">
       <c r="A337" s="23" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="B337" s="27" t="s">
         <v>50</v>
       </c>
       <c r="C337" s="28" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="D337" s="29" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="E337" s="22"/>
       <c r="F337" s="22"/>
@@ -10559,16 +10559,16 @@
     </row>
     <row r="338" spans="1:12" ht="15">
       <c r="A338" s="23" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="B338" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C338" s="25" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="D338" s="26" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="E338" s="22"/>
       <c r="F338" s="22"/>
@@ -10581,16 +10581,16 @@
     </row>
     <row r="339" spans="1:12" ht="15">
       <c r="A339" s="23" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="B339" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C339" s="28" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="D339" s="29" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="E339" s="22"/>
       <c r="F339" s="22"/>
@@ -10743,16 +10743,16 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="B350" t="s">
         <v>54</v>
       </c>
       <c r="C350" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="D350" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>

--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WebDev\stark-electronic-base\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212F39DF-EA9A-49B8-81EB-CDFFEF07ECCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9B711F-BDE4-43A2-805B-9444152935CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="Rc0a97a4d5efa4caa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R42e108231cd14450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R46d744df8bc84354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R4207886ca99643d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10679,6 +10679,72 @@
         <x:v>826</x:v>
       </x:c>
     </x:row>
+    <x:row r="351">
+      <x:c r="A351" t="str">
+        <x:v>hero.review_4_text</x:v>
+      </x:c>
+      <x:c r="B351" t="str">
+        <x:v>hero</x:v>
+      </x:c>
+      <x:c r="C351" t="str">
+        <x:v>Четвёртый отзыв</x:v>
+      </x:c>
+      <x:c r="D351" t="str">
+        <x:v>Я вообще не люблю CRM и сложные программы. Здесь просто пишу или говорю обычным языком — система сама сохраняет информацию куда нужно.</x:v>
+      </x:c>
+      <x:c r="E351"/>
+      <x:c r="F351"/>
+      <x:c r="G351"/>
+      <x:c r="H351"/>
+      <x:c r="I351"/>
+      <x:c r="J351"/>
+      <x:c r="K351"/>
+      <x:c r="L351"/>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352" t="str">
+        <x:v>hero.review_4_name</x:v>
+      </x:c>
+      <x:c r="B352" t="str">
+        <x:v>hero</x:v>
+      </x:c>
+      <x:c r="C352" t="str">
+        <x:v>Имя автора четвёртого отзыва</x:v>
+      </x:c>
+      <x:c r="D352" t="str">
+        <x:v>Алина</x:v>
+      </x:c>
+      <x:c r="E352"/>
+      <x:c r="F352"/>
+      <x:c r="G352"/>
+      <x:c r="H352"/>
+      <x:c r="I352"/>
+      <x:c r="J352"/>
+      <x:c r="K352"/>
+      <x:c r="L352"/>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353" t="str">
+        <x:v>hero.review_4_role</x:v>
+      </x:c>
+      <x:c r="B353" t="str">
+        <x:v>hero</x:v>
+      </x:c>
+      <x:c r="C353" t="str">
+        <x:v>Профессия автора четвёртого отзыва</x:v>
+      </x:c>
+      <x:c r="D353" t="str">
+        <x:v>ветеринар</x:v>
+      </x:c>
+      <x:c r="E353"/>
+      <x:c r="F353"/>
+      <x:c r="G353"/>
+      <x:c r="H353"/>
+      <x:c r="I353"/>
+      <x:c r="J353"/>
+      <x:c r="K353"/>
+      <x:c r="L353"/>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="K2:K331">
@@ -10690,7 +10756,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa079023d8bb40a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8db9dda7026f4ac9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R46d744df8bc84354"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R4207886ca99643d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R1d47d72800e24af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="Re116f7254be64e2e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1472,15 +1472,9 @@
     <x:t xml:space="preserve">pricing.plan.online.feature_4</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Устранение</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">pricing.plan.online.feature_5</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Проверка</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">pricing.addons_title</x:t>
   </x:si>
   <x:si>
@@ -2321,16 +2315,10 @@
     <x:t xml:space="preserve">Пункт онлайн-поддержки 6</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Помощь</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">pricing.plan.online.feature_7</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Пункт онлайн-поддержки 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Поддержка</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">pricing.plan.online.note_1</x:t>
@@ -7500,7 +7488,7 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="D202" s="11" t="str">
-        <x:v>Корректировка, исправление и устранение ошибок</x:v>
+        <x:v>Корректировка и улучшение промптов для ИИ</x:v>
       </x:c>
       <x:c r="E202" s="17"/>
       <x:c r="F202" s="17"/>
@@ -7522,7 +7510,7 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="D203" s="11" t="str">
-        <x:v>Помощь и поддержка</x:v>
+        <x:v>Исправление накопительных ошибок в работе ИИ</x:v>
       </x:c>
       <x:c r="E203" s="17"/>
       <x:c r="F203" s="17"/>
@@ -7543,8 +7531,8 @@
       <x:c r="C204" s="8" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="D204" s="11" t="s">
-        <x:v>487</x:v>
+      <x:c r="D204" s="11" t="str">
+        <x:v>Устранение повторяющихся неточностей в распознавании и структурировании данных</x:v>
       </x:c>
       <x:c r="E204" s="17"/>
       <x:c r="F204" s="17"/>
@@ -7557,7 +7545,7 @@
     </x:row>
     <x:row r="205" ht="30" customHeight="1">
       <x:c r="A205" s="20" t="s">
-        <x:v>488</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B205" s="14" t="s">
         <x:v>54</x:v>
@@ -7565,8 +7553,8 @@
       <x:c r="C205" s="8" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="D205" s="11" t="s">
-        <x:v>489</x:v>
+      <x:c r="D205" s="11" t="str">
+        <x:v>Проверка работоспособности всех подключённых интеграций</x:v>
       </x:c>
       <x:c r="E205" s="17"/>
       <x:c r="F205" s="17"/>
@@ -7579,16 +7567,16 @@
     </x:row>
     <x:row r="206" ht="30" customHeight="1">
       <x:c r="A206" s="20" t="s">
-        <x:v>490</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B206" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C206" s="8" t="s">
-        <x:v>491</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D206" s="11" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="E206" s="17"/>
       <x:c r="F206" s="17"/>
@@ -7601,16 +7589,16 @@
     </x:row>
     <x:row r="207" ht="30" customHeight="1">
       <x:c r="A207" s="20" t="s">
-        <x:v>493</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B207" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C207" s="8" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D207" s="11" t="s">
-        <x:v>495</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E207" s="17"/>
       <x:c r="F207" s="17"/>
@@ -7623,16 +7611,16 @@
     </x:row>
     <x:row r="208" ht="30" customHeight="1">
       <x:c r="A208" s="20" t="s">
-        <x:v>496</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B208" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C208" s="8" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="D208" s="11" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="E208" s="17"/>
       <x:c r="F208" s="17"/>
@@ -7645,16 +7633,16 @@
     </x:row>
     <x:row r="209" ht="30" customHeight="1">
       <x:c r="A209" s="20" t="s">
-        <x:v>499</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B209" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C209" s="8" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="D209" s="11" t="s">
-        <x:v>500</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="E209" s="17"/>
       <x:c r="F209" s="17"/>
@@ -7667,16 +7655,16 @@
     </x:row>
     <x:row r="210" ht="30" customHeight="1">
       <x:c r="A210" s="20" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B210" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C210" s="8" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="D210" s="11" t="s">
-        <x:v>502</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="E210" s="17"/>
       <x:c r="F210" s="17"/>
@@ -7689,16 +7677,16 @@
     </x:row>
     <x:row r="211" ht="30" customHeight="1">
       <x:c r="A211" s="20" t="s">
-        <x:v>503</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B211" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C211" s="8" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D211" s="11" t="s">
-        <x:v>505</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="E211" s="17"/>
       <x:c r="F211" s="17"/>
@@ -7711,16 +7699,16 @@
     </x:row>
     <x:row r="212" ht="30" customHeight="1">
       <x:c r="A212" s="20" t="s">
-        <x:v>506</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B212" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C212" s="8" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D212" s="11" t="s">
-        <x:v>507</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="E212" s="17"/>
       <x:c r="F212" s="17"/>
@@ -7733,16 +7721,16 @@
     </x:row>
     <x:row r="213" ht="30" customHeight="1">
       <x:c r="A213" s="20" t="s">
-        <x:v>508</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B213" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C213" s="8" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D213" s="11" t="s">
-        <x:v>509</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="E213" s="17"/>
       <x:c r="F213" s="17"/>
@@ -7755,16 +7743,16 @@
     </x:row>
     <x:row r="214" ht="30" customHeight="1">
       <x:c r="A214" s="20" t="s">
-        <x:v>510</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B214" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C214" s="8" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D214" s="11" t="s">
-        <x:v>511</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="E214" s="17"/>
       <x:c r="F214" s="17"/>
@@ -7777,16 +7765,16 @@
     </x:row>
     <x:row r="215" ht="30" customHeight="1">
       <x:c r="A215" s="20" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B215" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C215" s="8" t="s">
-        <x:v>513</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="D215" s="11" t="s">
-        <x:v>514</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="E215" s="17"/>
       <x:c r="F215" s="17"/>
@@ -7799,16 +7787,16 @@
     </x:row>
     <x:row r="216" ht="30" customHeight="1">
       <x:c r="A216" s="20" t="s">
-        <x:v>515</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B216" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C216" s="8" t="s">
-        <x:v>516</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D216" s="11" t="s">
-        <x:v>517</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="E216" s="17"/>
       <x:c r="F216" s="17"/>
@@ -7821,16 +7809,16 @@
     </x:row>
     <x:row r="217" ht="30" customHeight="1">
       <x:c r="A217" s="20" t="s">
-        <x:v>518</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B217" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C217" s="8" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D217" s="11" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E217" s="17"/>
       <x:c r="F217" s="17"/>
@@ -7843,16 +7831,16 @@
     </x:row>
     <x:row r="218" ht="30" customHeight="1">
       <x:c r="A218" s="20" t="s">
-        <x:v>521</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B218" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C218" s="8" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="D218" s="11" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="E218" s="17"/>
       <x:c r="F218" s="17"/>
@@ -7865,16 +7853,16 @@
     </x:row>
     <x:row r="219" ht="30" customHeight="1">
       <x:c r="A219" s="20" t="s">
-        <x:v>524</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B219" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C219" s="8" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="D219" s="11" t="s">
-        <x:v>525</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="E219" s="17"/>
       <x:c r="F219" s="17"/>
@@ -7887,16 +7875,16 @@
     </x:row>
     <x:row r="220" ht="30" customHeight="1">
       <x:c r="A220" s="20" t="s">
-        <x:v>526</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B220" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C220" s="8" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="D220" s="11" t="s">
-        <x:v>527</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="E220" s="17"/>
       <x:c r="F220" s="17"/>
@@ -7909,16 +7897,16 @@
     </x:row>
     <x:row r="221" ht="30" customHeight="1">
       <x:c r="A221" s="20" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B221" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C221" s="8" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="D221" s="11" t="s">
         <x:v>528</x:v>
-      </x:c>
-      <x:c r="B221" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C221" s="8" t="s">
-        <x:v>529</x:v>
-      </x:c>
-      <x:c r="D221" s="11" t="s">
-        <x:v>530</x:v>
       </x:c>
       <x:c r="E221" s="17"/>
       <x:c r="F221" s="17"/>
@@ -7931,16 +7919,16 @@
     </x:row>
     <x:row r="222" ht="30" customHeight="1">
       <x:c r="A222" s="20" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B222" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C222" s="8" t="s">
-        <x:v>529</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D222" s="11" t="s">
-        <x:v>532</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="E222" s="17"/>
       <x:c r="F222" s="17"/>
@@ -7953,16 +7941,16 @@
     </x:row>
     <x:row r="223" ht="30" customHeight="1">
       <x:c r="A223" s="20" t="s">
-        <x:v>533</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B223" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C223" s="8" t="s">
-        <x:v>529</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D223" s="11" t="s">
-        <x:v>534</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="E223" s="17"/>
       <x:c r="F223" s="17"/>
@@ -7975,16 +7963,16 @@
     </x:row>
     <x:row r="224" ht="30" customHeight="1">
       <x:c r="A224" s="20" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B224" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C224" s="8" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="D224" s="11" t="s">
         <x:v>535</x:v>
-      </x:c>
-      <x:c r="B224" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C224" s="8" t="s">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c r="D224" s="11" t="s">
-        <x:v>537</x:v>
       </x:c>
       <x:c r="E224" s="17"/>
       <x:c r="F224" s="17"/>
@@ -7997,16 +7985,16 @@
     </x:row>
     <x:row r="225" ht="30" customHeight="1">
       <x:c r="A225" s="20" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B225" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C225" s="8" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="D225" s="11" t="s">
         <x:v>538</x:v>
-      </x:c>
-      <x:c r="B225" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C225" s="8" t="s">
-        <x:v>539</x:v>
-      </x:c>
-      <x:c r="D225" s="11" t="s">
-        <x:v>540</x:v>
       </x:c>
       <x:c r="E225" s="17"/>
       <x:c r="F225" s="17"/>
@@ -8019,16 +8007,16 @@
     </x:row>
     <x:row r="226" ht="30" customHeight="1">
       <x:c r="A226" s="20" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B226" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C226" s="8" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="D226" s="11" t="s">
         <x:v>541</x:v>
-      </x:c>
-      <x:c r="B226" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C226" s="8" t="s">
-        <x:v>542</x:v>
-      </x:c>
-      <x:c r="D226" s="11" t="s">
-        <x:v>543</x:v>
       </x:c>
       <x:c r="E226" s="17"/>
       <x:c r="F226" s="17"/>
@@ -8041,16 +8029,16 @@
     </x:row>
     <x:row r="227" ht="30" customHeight="1">
       <x:c r="A227" s="20" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B227" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C227" s="8" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="D227" s="11" t="s">
         <x:v>544</x:v>
-      </x:c>
-      <x:c r="B227" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C227" s="8" t="s">
-        <x:v>545</x:v>
-      </x:c>
-      <x:c r="D227" s="11" t="s">
-        <x:v>546</x:v>
       </x:c>
       <x:c r="E227" s="17"/>
       <x:c r="F227" s="17"/>
@@ -8063,16 +8051,16 @@
     </x:row>
     <x:row r="228" ht="30" customHeight="1">
       <x:c r="A228" s="20" t="s">
-        <x:v>547</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B228" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C228" s="8" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="D228" s="11" t="s">
-        <x:v>548</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="E228" s="17"/>
       <x:c r="F228" s="17"/>
@@ -8085,16 +8073,16 @@
     </x:row>
     <x:row r="229" ht="30" customHeight="1">
       <x:c r="A229" s="20" t="s">
-        <x:v>549</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B229" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C229" s="8" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="D229" s="11" t="s">
-        <x:v>550</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="E229" s="17"/>
       <x:c r="F229" s="17"/>
@@ -8107,16 +8095,16 @@
     </x:row>
     <x:row r="230" ht="30" customHeight="1">
       <x:c r="A230" s="20" t="s">
-        <x:v>551</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B230" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C230" s="8" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="D230" s="11" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="E230" s="17"/>
       <x:c r="F230" s="17"/>
@@ -8129,16 +8117,16 @@
     </x:row>
     <x:row r="231" ht="30" customHeight="1">
       <x:c r="A231" s="20" t="s">
-        <x:v>552</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B231" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C231" s="8" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="D231" s="11" t="s">
-        <x:v>532</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="E231" s="17"/>
       <x:c r="F231" s="17"/>
@@ -8151,16 +8139,16 @@
     </x:row>
     <x:row r="232" ht="30" customHeight="1">
       <x:c r="A232" s="20" t="s">
-        <x:v>553</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B232" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C232" s="8" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="D232" s="11" t="s">
-        <x:v>554</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="E232" s="17"/>
       <x:c r="F232" s="17"/>
@@ -8173,16 +8161,16 @@
     </x:row>
     <x:row r="233" ht="30" customHeight="1">
       <x:c r="A233" s="20" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B233" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C233" s="8" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="D233" s="11" t="s">
         <x:v>555</x:v>
-      </x:c>
-      <x:c r="B233" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C233" s="8" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="D233" s="11" t="s">
-        <x:v>557</x:v>
       </x:c>
       <x:c r="E233" s="17"/>
       <x:c r="F233" s="17"/>
@@ -8195,16 +8183,16 @@
     </x:row>
     <x:row r="234" ht="30" customHeight="1">
       <x:c r="A234" s="20" t="s">
-        <x:v>558</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B234" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C234" s="8" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="D234" s="11" t="s">
-        <x:v>559</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="E234" s="17"/>
       <x:c r="F234" s="17"/>
@@ -8217,16 +8205,16 @@
     </x:row>
     <x:row r="235" ht="30" customHeight="1">
       <x:c r="A235" s="20" t="s">
-        <x:v>560</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B235" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C235" s="8" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="D235" s="11" t="s">
-        <x:v>561</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="E235" s="17"/>
       <x:c r="F235" s="17"/>
@@ -8239,16 +8227,16 @@
     </x:row>
     <x:row r="236" ht="30" customHeight="1">
       <x:c r="A236" s="20" t="s">
-        <x:v>562</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B236" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C236" s="8" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="D236" s="11" t="s">
-        <x:v>563</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="E236" s="17"/>
       <x:c r="F236" s="17"/>
@@ -8261,16 +8249,16 @@
     </x:row>
     <x:row r="237" ht="30" customHeight="1">
       <x:c r="A237" s="20" t="s">
-        <x:v>564</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B237" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C237" s="8" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="D237" s="11" t="s">
-        <x:v>565</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="E237" s="17"/>
       <x:c r="F237" s="17"/>
@@ -8283,16 +8271,16 @@
     </x:row>
     <x:row r="238" ht="30" customHeight="1">
       <x:c r="A238" s="20" t="s">
-        <x:v>566</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B238" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C238" s="8" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="D238" s="11" t="s">
-        <x:v>567</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="E238" s="17"/>
       <x:c r="F238" s="17"/>
@@ -8305,16 +8293,16 @@
     </x:row>
     <x:row r="239" ht="30" customHeight="1">
       <x:c r="A239" s="20" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B239" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C239" s="8" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="D239" s="11" t="s">
         <x:v>568</x:v>
-      </x:c>
-      <x:c r="B239" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C239" s="8" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="D239" s="11" t="s">
-        <x:v>570</x:v>
       </x:c>
       <x:c r="E239" s="17"/>
       <x:c r="F239" s="17"/>
@@ -8327,16 +8315,16 @@
     </x:row>
     <x:row r="240" ht="30" customHeight="1">
       <x:c r="A240" s="20" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B240" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C240" s="8" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="D240" s="11" t="s">
         <x:v>571</x:v>
-      </x:c>
-      <x:c r="B240" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C240" s="8" t="s">
-        <x:v>572</x:v>
-      </x:c>
-      <x:c r="D240" s="11" t="s">
-        <x:v>573</x:v>
       </x:c>
       <x:c r="E240" s="17"/>
       <x:c r="F240" s="17"/>
@@ -8349,16 +8337,16 @@
     </x:row>
     <x:row r="241" ht="30" customHeight="1">
       <x:c r="A241" s="20" t="s">
-        <x:v>574</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B241" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C241" s="8" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D241" s="11" t="s">
-        <x:v>575</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="E241" s="17"/>
       <x:c r="F241" s="17"/>
@@ -8371,16 +8359,16 @@
     </x:row>
     <x:row r="242" ht="30" customHeight="1">
       <x:c r="A242" s="20" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B242" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C242" s="8" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D242" s="11" t="s">
-        <x:v>577</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="E242" s="17"/>
       <x:c r="F242" s="17"/>
@@ -8393,16 +8381,16 @@
     </x:row>
     <x:row r="243" ht="30" customHeight="1">
       <x:c r="A243" s="20" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B243" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C243" s="8" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D243" s="11" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="E243" s="17"/>
       <x:c r="F243" s="17"/>
@@ -8415,16 +8403,16 @@
     </x:row>
     <x:row r="244" ht="30" customHeight="1">
       <x:c r="A244" s="20" t="s">
-        <x:v>580</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B244" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C244" s="8" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D244" s="11" t="s">
-        <x:v>581</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="E244" s="17"/>
       <x:c r="F244" s="17"/>
@@ -8437,16 +8425,16 @@
     </x:row>
     <x:row r="245" ht="30" customHeight="1">
       <x:c r="A245" s="20" t="s">
-        <x:v>582</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B245" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C245" s="8" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D245" s="11" t="s">
-        <x:v>583</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="E245" s="17"/>
       <x:c r="F245" s="17"/>
@@ -8459,16 +8447,16 @@
     </x:row>
     <x:row r="246" ht="30" customHeight="1">
       <x:c r="A246" s="20" t="s">
-        <x:v>584</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B246" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C246" s="8" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D246" s="11" t="s">
-        <x:v>585</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="E246" s="17"/>
       <x:c r="F246" s="17"/>
@@ -8481,16 +8469,16 @@
     </x:row>
     <x:row r="247" ht="30" customHeight="1">
       <x:c r="A247" s="20" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B247" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C247" s="8" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="D247" s="11" t="s">
         <x:v>586</x:v>
-      </x:c>
-      <x:c r="B247" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C247" s="8" t="s">
-        <x:v>587</x:v>
-      </x:c>
-      <x:c r="D247" s="11" t="s">
-        <x:v>588</x:v>
       </x:c>
       <x:c r="E247" s="17"/>
       <x:c r="F247" s="17"/>
@@ -8503,16 +8491,16 @@
     </x:row>
     <x:row r="248" ht="30" customHeight="1">
       <x:c r="A248" s="20" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B248" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C248" s="8" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="D248" s="11" t="s">
         <x:v>589</x:v>
-      </x:c>
-      <x:c r="B248" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C248" s="8" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="D248" s="11" t="s">
-        <x:v>591</x:v>
       </x:c>
       <x:c r="E248" s="17"/>
       <x:c r="F248" s="17"/>
@@ -8525,16 +8513,16 @@
     </x:row>
     <x:row r="249" ht="30" customHeight="1">
       <x:c r="A249" s="20" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B249" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C249" s="8" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="D249" s="11" t="s">
         <x:v>592</x:v>
-      </x:c>
-      <x:c r="B249" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C249" s="8" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="D249" s="11" t="s">
-        <x:v>594</x:v>
       </x:c>
       <x:c r="E249" s="17"/>
       <x:c r="F249" s="17"/>
@@ -8547,16 +8535,16 @@
     </x:row>
     <x:row r="250" ht="30" customHeight="1">
       <x:c r="A250" s="20" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B250" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C250" s="8" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="D250" s="11" t="s">
         <x:v>595</x:v>
-      </x:c>
-      <x:c r="B250" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C250" s="8" t="s">
-        <x:v>596</x:v>
-      </x:c>
-      <x:c r="D250" s="11" t="s">
-        <x:v>597</x:v>
       </x:c>
       <x:c r="E250" s="17"/>
       <x:c r="F250" s="17"/>
@@ -8569,16 +8557,16 @@
     </x:row>
     <x:row r="251" ht="30" customHeight="1">
       <x:c r="A251" s="20" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B251" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C251" s="8" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="D251" s="11" t="s">
         <x:v>598</x:v>
-      </x:c>
-      <x:c r="B251" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C251" s="8" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="D251" s="11" t="s">
-        <x:v>600</x:v>
       </x:c>
       <x:c r="E251" s="17"/>
       <x:c r="F251" s="17"/>
@@ -8591,16 +8579,16 @@
     </x:row>
     <x:row r="252" ht="30" customHeight="1">
       <x:c r="A252" s="20" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B252" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C252" s="8" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D252" s="11" t="s">
         <x:v>601</x:v>
-      </x:c>
-      <x:c r="B252" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C252" s="8" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="D252" s="11" t="s">
-        <x:v>603</x:v>
       </x:c>
       <x:c r="E252" s="17"/>
       <x:c r="F252" s="17"/>
@@ -8613,16 +8601,16 @@
     </x:row>
     <x:row r="253" ht="30" customHeight="1">
       <x:c r="A253" s="20" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B253" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C253" s="8" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="D253" s="11" t="s">
         <x:v>604</x:v>
-      </x:c>
-      <x:c r="B253" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C253" s="8" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="D253" s="11" t="s">
-        <x:v>606</x:v>
       </x:c>
       <x:c r="E253" s="17"/>
       <x:c r="F253" s="17"/>
@@ -8635,16 +8623,16 @@
     </x:row>
     <x:row r="254" ht="30" customHeight="1">
       <x:c r="A254" s="20" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B254" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C254" s="8" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="D254" s="11" t="s">
         <x:v>607</x:v>
-      </x:c>
-      <x:c r="B254" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C254" s="8" t="s">
-        <x:v>608</x:v>
-      </x:c>
-      <x:c r="D254" s="11" t="s">
-        <x:v>609</x:v>
       </x:c>
       <x:c r="E254" s="17"/>
       <x:c r="F254" s="17"/>
@@ -8657,16 +8645,16 @@
     </x:row>
     <x:row r="255" ht="30" customHeight="1">
       <x:c r="A255" s="20" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B255" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C255" s="8" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="D255" s="11" t="s">
         <x:v>610</x:v>
-      </x:c>
-      <x:c r="B255" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C255" s="8" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="D255" s="11" t="s">
-        <x:v>612</x:v>
       </x:c>
       <x:c r="E255" s="17"/>
       <x:c r="F255" s="17"/>
@@ -8679,16 +8667,16 @@
     </x:row>
     <x:row r="256" ht="30" customHeight="1">
       <x:c r="A256" s="20" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B256" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C256" s="8" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="D256" s="11" t="s">
         <x:v>613</x:v>
-      </x:c>
-      <x:c r="B256" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C256" s="8" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="D256" s="11" t="s">
-        <x:v>615</x:v>
       </x:c>
       <x:c r="E256" s="17"/>
       <x:c r="F256" s="17"/>
@@ -8701,16 +8689,16 @@
     </x:row>
     <x:row r="257" ht="30" customHeight="1">
       <x:c r="A257" s="20" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="B257" s="14" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C257" s="8" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="D257" s="11" t="s">
         <x:v>616</x:v>
-      </x:c>
-      <x:c r="B257" s="14" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="C257" s="8" t="s">
-        <x:v>617</x:v>
-      </x:c>
-      <x:c r="D257" s="11" t="s">
-        <x:v>618</x:v>
       </x:c>
       <x:c r="E257" s="17"/>
       <x:c r="F257" s="17"/>
@@ -8723,16 +8711,16 @@
     </x:row>
     <x:row r="258" ht="30" customHeight="1">
       <x:c r="A258" s="20" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="B258" s="14" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="C258" s="8" t="s">
         <x:v>619</x:v>
       </x:c>
-      <x:c r="B258" s="14" t="s">
+      <x:c r="D258" s="11" t="s">
         <x:v>620</x:v>
-      </x:c>
-      <x:c r="C258" s="8" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="D258" s="11" t="s">
-        <x:v>622</x:v>
       </x:c>
       <x:c r="E258" s="17"/>
       <x:c r="F258" s="17"/>
@@ -8745,16 +8733,16 @@
     </x:row>
     <x:row r="259" ht="30" customHeight="1">
       <x:c r="A259" s="20" t="s">
-        <x:v>623</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="B259" s="14" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="C259" s="8" t="s">
-        <x:v>624</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="D259" s="11" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="E259" s="17"/>
       <x:c r="F259" s="17"/>
@@ -8767,16 +8755,16 @@
     </x:row>
     <x:row r="260" ht="30" customHeight="1">
       <x:c r="A260" s="20" t="s">
-        <x:v>625</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="B260" s="14" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="C260" s="8" t="s">
-        <x:v>624</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="D260" s="11" t="s">
-        <x:v>532</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="E260" s="17"/>
       <x:c r="F260" s="17"/>
@@ -8789,16 +8777,16 @@
     </x:row>
     <x:row r="261" ht="30" customHeight="1">
       <x:c r="A261" s="20" t="s">
-        <x:v>626</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B261" s="14" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="C261" s="8" t="s">
-        <x:v>624</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="D261" s="11" t="s">
-        <x:v>534</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="E261" s="17"/>
       <x:c r="F261" s="17"/>
@@ -8811,16 +8799,16 @@
     </x:row>
     <x:row r="262" ht="30" customHeight="1">
       <x:c r="A262" s="20" t="s">
-        <x:v>627</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="B262" s="14" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="C262" s="8" t="s">
-        <x:v>624</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="D262" s="11" t="s">
-        <x:v>628</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="E262" s="17"/>
       <x:c r="F262" s="17"/>
@@ -8833,16 +8821,16 @@
     </x:row>
     <x:row r="263" ht="30" customHeight="1">
       <x:c r="A263" s="20" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B263" s="14" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="C263" s="8" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="D263" s="11" t="s">
         <x:v>629</x:v>
-      </x:c>
-      <x:c r="B263" s="14" t="s">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="C263" s="8" t="s">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="D263" s="11" t="s">
-        <x:v>631</x:v>
       </x:c>
       <x:c r="E263" s="17"/>
       <x:c r="F263" s="17"/>
@@ -8855,16 +8843,16 @@
     </x:row>
     <x:row r="264" ht="30" customHeight="1">
       <x:c r="A264" s="20" t="s">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="B264" s="14" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C264" s="8" t="s">
         <x:v>632</x:v>
       </x:c>
-      <x:c r="B264" s="14" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="C264" s="8" t="s">
-        <x:v>634</x:v>
-      </x:c>
       <x:c r="D264" s="11" t="s">
-        <x:v>591</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="E264" s="17"/>
       <x:c r="F264" s="17"/>
@@ -8877,16 +8865,16 @@
     </x:row>
     <x:row r="265" ht="30" customHeight="1">
       <x:c r="A265" s="20" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="B265" s="14" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C265" s="8" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="D265" s="11" t="s">
         <x:v>635</x:v>
-      </x:c>
-      <x:c r="B265" s="14" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="C265" s="8" t="s">
-        <x:v>636</x:v>
-      </x:c>
-      <x:c r="D265" s="11" t="s">
-        <x:v>637</x:v>
       </x:c>
       <x:c r="E265" s="17"/>
       <x:c r="F265" s="17"/>
@@ -8899,16 +8887,16 @@
     </x:row>
     <x:row r="266" ht="30" customHeight="1">
       <x:c r="A266" s="20" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="B266" s="14" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C266" s="8" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="D266" s="11" t="s">
         <x:v>638</x:v>
-      </x:c>
-      <x:c r="B266" s="14" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="C266" s="8" t="s">
-        <x:v>639</x:v>
-      </x:c>
-      <x:c r="D266" s="11" t="s">
-        <x:v>640</x:v>
       </x:c>
       <x:c r="E266" s="17"/>
       <x:c r="F266" s="17"/>
@@ -8921,16 +8909,16 @@
     </x:row>
     <x:row r="267" ht="30" customHeight="1">
       <x:c r="A267" s="20" t="s">
-        <x:v>641</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="B267" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C267" s="8" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D267" s="11" t="s">
-        <x:v>591</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="E267" s="17"/>
       <x:c r="F267" s="17"/>
@@ -8943,16 +8931,16 @@
     </x:row>
     <x:row r="268" ht="30" customHeight="1">
       <x:c r="A268" s="20" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="B268" s="14" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C268" s="8" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="D268" s="11" t="s">
         <x:v>642</x:v>
-      </x:c>
-      <x:c r="B268" s="14" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="C268" s="8" t="s">
-        <x:v>643</x:v>
-      </x:c>
-      <x:c r="D268" s="11" t="s">
-        <x:v>644</x:v>
       </x:c>
       <x:c r="E268" s="17"/>
       <x:c r="F268" s="17"/>
@@ -8965,16 +8953,16 @@
     </x:row>
     <x:row r="269" ht="30" customHeight="1">
       <x:c r="A269" s="20" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="B269" s="14" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C269" s="8" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="D269" s="11" t="s">
         <x:v>645</x:v>
-      </x:c>
-      <x:c r="B269" s="14" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="C269" s="8" t="s">
-        <x:v>646</x:v>
-      </x:c>
-      <x:c r="D269" s="11" t="s">
-        <x:v>647</x:v>
       </x:c>
       <x:c r="E269" s="17"/>
       <x:c r="F269" s="17"/>
@@ -8987,16 +8975,16 @@
     </x:row>
     <x:row r="270" ht="30" customHeight="1">
       <x:c r="A270" s="20" t="s">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="B270" s="14" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C270" s="8" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="D270" s="11" t="s">
         <x:v>648</x:v>
-      </x:c>
-      <x:c r="B270" s="14" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="C270" s="8" t="s">
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="D270" s="11" t="s">
-        <x:v>650</x:v>
       </x:c>
       <x:c r="E270" s="17"/>
       <x:c r="F270" s="17"/>
@@ -9009,16 +8997,16 @@
     </x:row>
     <x:row r="271" ht="30" customHeight="1">
       <x:c r="A271" s="20" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="B271" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C271" s="8" t="s">
-        <x:v>649</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D271" s="11" t="s">
-        <x:v>652</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="E271" s="17"/>
       <x:c r="F271" s="17"/>
@@ -9031,16 +9019,16 @@
     </x:row>
     <x:row r="272" ht="30" customHeight="1">
       <x:c r="A272" s="20" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="B272" s="14" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C272" s="8" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="D272" s="11" t="s">
         <x:v>653</x:v>
-      </x:c>
-      <x:c r="B272" s="14" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="C272" s="8" t="s">
-        <x:v>654</x:v>
-      </x:c>
-      <x:c r="D272" s="11" t="s">
-        <x:v>655</x:v>
       </x:c>
       <x:c r="E272" s="17"/>
       <x:c r="F272" s="17"/>
@@ -9053,16 +9041,16 @@
     </x:row>
     <x:row r="273" ht="30" customHeight="1">
       <x:c r="A273" s="20" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="B273" s="14" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C273" s="8" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="D273" s="11" t="s">
         <x:v>656</x:v>
-      </x:c>
-      <x:c r="B273" s="14" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="C273" s="8" t="s">
-        <x:v>657</x:v>
-      </x:c>
-      <x:c r="D273" s="11" t="s">
-        <x:v>658</x:v>
       </x:c>
       <x:c r="E273" s="17"/>
       <x:c r="F273" s="17"/>
@@ -9075,16 +9063,16 @@
     </x:row>
     <x:row r="274" ht="30" customHeight="1">
       <x:c r="A274" s="20" t="s">
-        <x:v>659</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="B274" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C274" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D274" s="11" t="s">
-        <x:v>660</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="E274" s="17"/>
       <x:c r="F274" s="17"/>
@@ -9097,16 +9085,16 @@
     </x:row>
     <x:row r="275" ht="30" customHeight="1">
       <x:c r="A275" s="20" t="s">
-        <x:v>661</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="B275" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C275" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D275" s="11" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="E275" s="17"/>
       <x:c r="F275" s="17"/>
@@ -9119,16 +9107,16 @@
     </x:row>
     <x:row r="276" ht="30" customHeight="1">
       <x:c r="A276" s="20" t="s">
-        <x:v>663</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="B276" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C276" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D276" s="11" t="s">
-        <x:v>664</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="E276" s="17"/>
       <x:c r="F276" s="17"/>
@@ -9141,16 +9129,16 @@
     </x:row>
     <x:row r="277" ht="30" customHeight="1">
       <x:c r="A277" s="20" t="s">
-        <x:v>665</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="B277" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C277" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D277" s="11" t="s">
-        <x:v>666</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="E277" s="17"/>
       <x:c r="F277" s="17"/>
@@ -9163,16 +9151,16 @@
     </x:row>
     <x:row r="278" ht="30" customHeight="1">
       <x:c r="A278" s="20" t="s">
-        <x:v>667</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="B278" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C278" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D278" s="11" t="s">
-        <x:v>668</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E278" s="17"/>
       <x:c r="F278" s="17"/>
@@ -9185,16 +9173,16 @@
     </x:row>
     <x:row r="279" ht="30" customHeight="1">
       <x:c r="A279" s="20" t="s">
-        <x:v>669</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="B279" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C279" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D279" s="11" t="s">
-        <x:v>670</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="E279" s="17"/>
       <x:c r="F279" s="17"/>
@@ -9207,16 +9195,16 @@
     </x:row>
     <x:row r="280" ht="30" customHeight="1">
       <x:c r="A280" s="20" t="s">
-        <x:v>671</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="B280" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C280" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D280" s="11" t="s">
-        <x:v>672</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="E280" s="17"/>
       <x:c r="F280" s="17"/>
@@ -9229,16 +9217,16 @@
     </x:row>
     <x:row r="281" ht="30" customHeight="1">
       <x:c r="A281" s="20" t="s">
-        <x:v>673</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="B281" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C281" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D281" s="11" t="s">
-        <x:v>674</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E281" s="17"/>
       <x:c r="F281" s="17"/>
@@ -9251,16 +9239,16 @@
     </x:row>
     <x:row r="282" ht="30" customHeight="1">
       <x:c r="A282" s="20" t="s">
-        <x:v>675</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="B282" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C282" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D282" s="11" t="s">
-        <x:v>676</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="E282" s="17"/>
       <x:c r="F282" s="17"/>
@@ -9273,16 +9261,16 @@
     </x:row>
     <x:row r="283" ht="30" customHeight="1">
       <x:c r="A283" s="20" t="s">
-        <x:v>677</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B283" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C283" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D283" s="11" t="s">
-        <x:v>678</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="E283" s="17"/>
       <x:c r="F283" s="17"/>
@@ -9295,16 +9283,16 @@
     </x:row>
     <x:row r="284" ht="30" customHeight="1">
       <x:c r="A284" s="20" t="s">
-        <x:v>679</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="B284" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C284" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D284" s="11" t="s">
-        <x:v>680</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E284" s="17"/>
       <x:c r="F284" s="17"/>
@@ -9317,16 +9305,16 @@
     </x:row>
     <x:row r="285" ht="30" customHeight="1">
       <x:c r="A285" s="20" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="B285" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C285" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D285" s="11" t="s">
-        <x:v>682</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="E285" s="17"/>
       <x:c r="F285" s="17"/>
@@ -9339,16 +9327,16 @@
     </x:row>
     <x:row r="286" ht="30" customHeight="1">
       <x:c r="A286" s="20" t="s">
-        <x:v>683</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="B286" s="14" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C286" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D286" s="11" t="s">
-        <x:v>684</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="E286" s="17"/>
       <x:c r="F286" s="17"/>
@@ -9361,16 +9349,16 @@
     </x:row>
     <x:row r="287" ht="30" customHeight="1">
       <x:c r="A287" s="20" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="B287" s="14" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="C287" s="8" t="s">
         <x:v>685</x:v>
       </x:c>
-      <x:c r="B287" s="14" t="s">
+      <x:c r="D287" s="11" t="s">
         <x:v>686</x:v>
-      </x:c>
-      <x:c r="C287" s="8" t="s">
-        <x:v>687</x:v>
-      </x:c>
-      <x:c r="D287" s="11" t="s">
-        <x:v>688</x:v>
       </x:c>
       <x:c r="E287" s="17"/>
       <x:c r="F287" s="17"/>
@@ -9383,16 +9371,16 @@
     </x:row>
     <x:row r="288" ht="30" customHeight="1">
       <x:c r="A288" s="20" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="B288" s="14" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="C288" s="8" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="D288" s="11" t="s">
         <x:v>689</x:v>
-      </x:c>
-      <x:c r="B288" s="14" t="s">
-        <x:v>686</x:v>
-      </x:c>
-      <x:c r="C288" s="8" t="s">
-        <x:v>690</x:v>
-      </x:c>
-      <x:c r="D288" s="11" t="s">
-        <x:v>691</x:v>
       </x:c>
       <x:c r="E288" s="17"/>
       <x:c r="F288" s="17"/>
@@ -9405,16 +9393,16 @@
     </x:row>
     <x:row r="289" ht="30" customHeight="1">
       <x:c r="A289" s="20" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="B289" s="14" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="C289" s="8" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="D289" s="11" t="s">
         <x:v>692</x:v>
-      </x:c>
-      <x:c r="B289" s="14" t="s">
-        <x:v>686</x:v>
-      </x:c>
-      <x:c r="C289" s="8" t="s">
-        <x:v>693</x:v>
-      </x:c>
-      <x:c r="D289" s="11" t="s">
-        <x:v>694</x:v>
       </x:c>
       <x:c r="E289" s="17"/>
       <x:c r="F289" s="17"/>
@@ -9427,16 +9415,16 @@
     </x:row>
     <x:row r="290" ht="30" customHeight="1">
       <x:c r="A290" s="20" t="s">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="B290" s="14" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="C290" s="8" t="s">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="D290" s="11" t="s">
         <x:v>695</x:v>
-      </x:c>
-      <x:c r="B290" s="14" t="s">
-        <x:v>686</x:v>
-      </x:c>
-      <x:c r="C290" s="8" t="s">
-        <x:v>696</x:v>
-      </x:c>
-      <x:c r="D290" s="11" t="s">
-        <x:v>697</x:v>
       </x:c>
       <x:c r="E290" s="17"/>
       <x:c r="F290" s="17"/>
@@ -9449,16 +9437,16 @@
     </x:row>
     <x:row r="291" ht="30" customHeight="1">
       <x:c r="A291" s="20" t="s">
+        <x:v>696</x:v>
+      </x:c>
+      <x:c r="B291" s="14" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="C291" s="8" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="D291" s="11" t="s">
         <x:v>698</x:v>
-      </x:c>
-      <x:c r="B291" s="14" t="s">
-        <x:v>686</x:v>
-      </x:c>
-      <x:c r="C291" s="8" t="s">
-        <x:v>699</x:v>
-      </x:c>
-      <x:c r="D291" s="11" t="s">
-        <x:v>700</x:v>
       </x:c>
       <x:c r="E291" s="17"/>
       <x:c r="F291" s="17"/>
@@ -9471,16 +9459,16 @@
     </x:row>
     <x:row r="292" ht="30" customHeight="1">
       <x:c r="A292" s="20" t="s">
-        <x:v>701</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="B292" s="14" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="C292" s="8" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="D292" s="11" t="s">
         <x:v>686</x:v>
-      </x:c>
-      <x:c r="C292" s="8" t="s">
-        <x:v>702</x:v>
-      </x:c>
-      <x:c r="D292" s="11" t="s">
-        <x:v>688</x:v>
       </x:c>
       <x:c r="E292" s="17"/>
       <x:c r="F292" s="17"/>
@@ -9493,16 +9481,16 @@
     </x:row>
     <x:row r="293" ht="30" customHeight="1">
       <x:c r="A293" s="20" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="B293" s="14" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="C293" s="8" t="s">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="D293" s="11" t="s">
         <x:v>703</x:v>
-      </x:c>
-      <x:c r="B293" s="14" t="s">
-        <x:v>686</x:v>
-      </x:c>
-      <x:c r="C293" s="8" t="s">
-        <x:v>704</x:v>
-      </x:c>
-      <x:c r="D293" s="11" t="s">
-        <x:v>705</x:v>
       </x:c>
       <x:c r="E293" s="17"/>
       <x:c r="F293" s="17"/>
@@ -9515,16 +9503,16 @@
     </x:row>
     <x:row r="294" ht="30" customHeight="1">
       <x:c r="A294" s="20" t="s">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="B294" s="14" t="s">
+        <x:v>705</x:v>
+      </x:c>
+      <x:c r="C294" s="8" t="s">
         <x:v>706</x:v>
       </x:c>
-      <x:c r="B294" s="14" t="s">
+      <x:c r="D294" s="11" t="s">
         <x:v>707</x:v>
-      </x:c>
-      <x:c r="C294" s="8" t="s">
-        <x:v>708</x:v>
-      </x:c>
-      <x:c r="D294" s="11" t="s">
-        <x:v>709</x:v>
       </x:c>
       <x:c r="E294" s="17"/>
       <x:c r="F294" s="17"/>
@@ -9537,16 +9525,16 @@
     </x:row>
     <x:row r="295" ht="30" customHeight="1">
       <x:c r="A295" s="20" t="s">
-        <x:v>710</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B295" s="14" t="s">
-        <x:v>707</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="C295" s="8" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="D295" s="11" t="s">
-        <x:v>711</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="E295" s="17"/>
       <x:c r="F295" s="17"/>
@@ -9559,16 +9547,16 @@
     </x:row>
     <x:row r="296" ht="30" customHeight="1">
       <x:c r="A296" s="20" t="s">
-        <x:v>712</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B296" s="14" t="s">
-        <x:v>707</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="C296" s="8" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="D296" s="11" t="s">
-        <x:v>713</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="E296" s="17"/>
       <x:c r="F296" s="17"/>
@@ -9581,16 +9569,16 @@
     </x:row>
     <x:row r="297" ht="30" customHeight="1">
       <x:c r="A297" s="20" t="s">
-        <x:v>714</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B297" s="14" t="s">
-        <x:v>707</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="C297" s="8" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="D297" s="11" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="E297" s="17"/>
       <x:c r="F297" s="17"/>
@@ -9603,16 +9591,16 @@
     </x:row>
     <x:row r="298" ht="30" customHeight="1">
       <x:c r="A298" s="20" t="s">
-        <x:v>716</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="B298" s="14" t="s">
-        <x:v>707</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="C298" s="8" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="D298" s="11" t="s">
-        <x:v>717</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="E298" s="17"/>
       <x:c r="F298" s="17"/>
@@ -9625,16 +9613,16 @@
     </x:row>
     <x:row r="299" ht="30" customHeight="1">
       <x:c r="A299" s="20" t="s">
-        <x:v>718</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="B299" s="14" t="s">
-        <x:v>707</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="C299" s="8" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="D299" s="11" t="s">
-        <x:v>719</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="E299" s="17"/>
       <x:c r="F299" s="17"/>
@@ -9647,16 +9635,16 @@
     </x:row>
     <x:row r="300" ht="30" customHeight="1">
       <x:c r="A300" s="20" t="s">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c r="B300" s="14" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="C300" s="8" t="s">
+        <x:v>719</x:v>
+      </x:c>
+      <x:c r="D300" s="11" t="s">
         <x:v>720</x:v>
-      </x:c>
-      <x:c r="B300" s="14" t="s">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="C300" s="8" t="s">
-        <x:v>721</x:v>
-      </x:c>
-      <x:c r="D300" s="11" t="s">
-        <x:v>722</x:v>
       </x:c>
       <x:c r="E300" s="17"/>
       <x:c r="F300" s="17"/>
@@ -9669,16 +9657,16 @@
     </x:row>
     <x:row r="301" ht="30" customHeight="1">
       <x:c r="A301" s="20" t="s">
-        <x:v>723</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="B301" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C301" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D301" s="11" t="s">
-        <x:v>724</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="E301" s="17"/>
       <x:c r="F301" s="17"/>
@@ -9691,16 +9679,16 @@
     </x:row>
     <x:row r="302" ht="30" customHeight="1">
       <x:c r="A302" s="20" t="s">
-        <x:v>725</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="B302" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C302" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D302" s="11" t="s">
-        <x:v>726</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="E302" s="17"/>
       <x:c r="F302" s="17"/>
@@ -9713,16 +9701,16 @@
     </x:row>
     <x:row r="303" ht="30" customHeight="1">
       <x:c r="A303" s="20" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B303" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C303" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D303" s="11" t="s">
-        <x:v>728</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="E303" s="17"/>
       <x:c r="F303" s="17"/>
@@ -9735,16 +9723,16 @@
     </x:row>
     <x:row r="304" ht="30" customHeight="1">
       <x:c r="A304" s="20" t="s">
-        <x:v>729</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="B304" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C304" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D304" s="11" t="s">
-        <x:v>730</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E304" s="17"/>
       <x:c r="F304" s="17"/>
@@ -9757,16 +9745,16 @@
     </x:row>
     <x:row r="305" ht="30" customHeight="1">
       <x:c r="A305" s="20" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="B305" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C305" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D305" s="11" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="E305" s="17"/>
       <x:c r="F305" s="17"/>
@@ -9779,16 +9767,16 @@
     </x:row>
     <x:row r="306" ht="30" customHeight="1">
       <x:c r="A306" s="20" t="s">
-        <x:v>733</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="B306" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C306" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D306" s="11" t="s">
-        <x:v>734</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="E306" s="17"/>
       <x:c r="F306" s="17"/>
@@ -9801,16 +9789,16 @@
     </x:row>
     <x:row r="307" ht="30" customHeight="1">
       <x:c r="A307" s="20" t="s">
-        <x:v>735</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="B307" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C307" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D307" s="11" t="s">
-        <x:v>736</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="E307" s="17"/>
       <x:c r="F307" s="17"/>
@@ -9823,16 +9811,16 @@
     </x:row>
     <x:row r="308" ht="30" customHeight="1">
       <x:c r="A308" s="20" t="s">
-        <x:v>737</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B308" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C308" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D308" s="11" t="s">
-        <x:v>738</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="E308" s="17"/>
       <x:c r="F308" s="17"/>
@@ -9845,16 +9833,16 @@
     </x:row>
     <x:row r="309" ht="30" customHeight="1">
       <x:c r="A309" s="20" t="s">
-        <x:v>739</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="B309" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C309" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D309" s="11" t="s">
-        <x:v>740</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="E309" s="17"/>
       <x:c r="F309" s="17"/>
@@ -9867,16 +9855,16 @@
     </x:row>
     <x:row r="310" ht="30" customHeight="1">
       <x:c r="A310" s="20" t="s">
-        <x:v>741</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="B310" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C310" s="8" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="D310" s="11" t="s">
-        <x:v>742</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="E310" s="17"/>
       <x:c r="F310" s="17"/>
@@ -9889,16 +9877,16 @@
     </x:row>
     <x:row r="311" ht="30" customHeight="1">
       <x:c r="A311" s="20" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="B311" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C311" s="8" t="s">
-        <x:v>744</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="D311" s="11" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="E311" s="17"/>
       <x:c r="F311" s="17"/>
@@ -9911,16 +9899,16 @@
     </x:row>
     <x:row r="312" ht="30" customHeight="1">
       <x:c r="A312" s="20" t="s">
-        <x:v>746</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="B312" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C312" s="8" t="s">
-        <x:v>747</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="D312" s="11" t="s">
-        <x:v>748</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="E312" s="17"/>
       <x:c r="F312" s="17"/>
@@ -9933,16 +9921,16 @@
     </x:row>
     <x:row r="313" ht="30" customHeight="1">
       <x:c r="A313" s="20" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="B313" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C313" s="8" t="s">
-        <x:v>750</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="D313" s="11" t="s">
-        <x:v>751</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="E313" s="17"/>
       <x:c r="F313" s="17"/>
@@ -9955,13 +9943,13 @@
     </x:row>
     <x:row r="314" ht="30" customHeight="1">
       <x:c r="A314" s="20" t="s">
-        <x:v>752</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B314" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C314" s="8" t="s">
-        <x:v>753</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="D314" s="11" t="s">
         <x:v>76</x:v>
@@ -9977,13 +9965,13 @@
     </x:row>
     <x:row r="315" ht="30" customHeight="1">
       <x:c r="A315" s="20" t="s">
-        <x:v>754</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="B315" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C315" s="8" t="s">
-        <x:v>755</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="D315" s="11" t="s">
         <x:v>466</x:v>
@@ -9999,13 +9987,13 @@
     </x:row>
     <x:row r="316" ht="30" customHeight="1">
       <x:c r="A316" s="20" t="s">
-        <x:v>756</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B316" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C316" s="8" t="s">
-        <x:v>757</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="D316" s="11" t="s">
         <x:v>468</x:v>
@@ -10021,13 +10009,13 @@
     </x:row>
     <x:row r="317" ht="30" customHeight="1">
       <x:c r="A317" s="20" t="s">
-        <x:v>758</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="B317" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C317" s="8" t="s">
-        <x:v>759</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="D317" s="11" t="s">
         <x:v>470</x:v>
@@ -10043,13 +10031,13 @@
     </x:row>
     <x:row r="318" ht="30" customHeight="1">
       <x:c r="A318" s="20" t="s">
-        <x:v>760</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="B318" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C318" s="8" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="D318" s="11" t="s">
         <x:v>472</x:v>
@@ -10065,16 +10053,16 @@
     </x:row>
     <x:row r="319" ht="30" customHeight="1">
       <x:c r="A319" s="20" t="s">
-        <x:v>762</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B319" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C319" s="8" t="s">
-        <x:v>763</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="D319" s="11" t="s">
-        <x:v>764</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="E319" s="17"/>
       <x:c r="F319" s="17"/>
@@ -10087,16 +10075,16 @@
     </x:row>
     <x:row r="320" ht="30" customHeight="1">
       <x:c r="A320" s="20" t="s">
-        <x:v>765</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B320" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C320" s="8" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="D320" s="11" t="s">
-        <x:v>767</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="E320" s="17"/>
       <x:c r="F320" s="17"/>
@@ -10109,16 +10097,16 @@
     </x:row>
     <x:row r="321" ht="30" customHeight="1">
       <x:c r="A321" s="20" t="s">
-        <x:v>768</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B321" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C321" s="8" t="s">
-        <x:v>769</x:v>
-      </x:c>
-      <x:c r="D321" s="11" t="s">
-        <x:v>770</x:v>
+        <x:v>767</x:v>
+      </x:c>
+      <x:c r="D321" s="11" t="str">
+        <x:v>Помощь, консультации и контроль качества работы системы</x:v>
       </x:c>
       <x:c r="E321" s="17"/>
       <x:c r="F321" s="17"/>
@@ -10131,16 +10119,16 @@
     </x:row>
     <x:row r="322" ht="30" customHeight="1">
       <x:c r="A322" s="20" t="s">
-        <x:v>771</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B322" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C322" s="8" t="s">
-        <x:v>772</x:v>
-      </x:c>
-      <x:c r="D322" s="11" t="s">
-        <x:v>773</x:v>
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="D322" s="11" t="str">
+        <x:v>Онлайн-поддержка</x:v>
       </x:c>
       <x:c r="E322" s="17"/>
       <x:c r="F322" s="17"/>
@@ -10153,16 +10141,16 @@
     </x:row>
     <x:row r="323" ht="30" customHeight="1">
       <x:c r="A323" s="20" t="s">
-        <x:v>774</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B323" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C323" s="8" t="s">
-        <x:v>775</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="D323" s="11" t="s">
-        <x:v>776</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="E323" s="17"/>
       <x:c r="F323" s="17"/>
@@ -10175,16 +10163,16 @@
     </x:row>
     <x:row r="324" ht="30" customHeight="1">
       <x:c r="A324" s="20" t="s">
-        <x:v>777</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="B324" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C324" s="8" t="s">
-        <x:v>778</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="D324" s="11" t="s">
-        <x:v>779</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="E324" s="17"/>
       <x:c r="F324" s="17"/>
@@ -10197,16 +10185,16 @@
     </x:row>
     <x:row r="325" ht="30" customHeight="1">
       <x:c r="A325" s="20" t="s">
-        <x:v>780</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B325" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C325" s="8" t="s">
-        <x:v>781</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="D325" s="11" t="s">
-        <x:v>782</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="E325" s="17"/>
       <x:c r="F325" s="17"/>
@@ -10219,16 +10207,16 @@
     </x:row>
     <x:row r="326" ht="30" customHeight="1">
       <x:c r="A326" s="20" t="s">
-        <x:v>783</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="B326" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C326" s="8" t="s">
-        <x:v>784</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="D326" s="11" t="s">
-        <x:v>785</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="E326" s="17"/>
       <x:c r="F326" s="17"/>
@@ -10241,16 +10229,16 @@
     </x:row>
     <x:row r="327" ht="30" customHeight="1">
       <x:c r="A327" s="20" t="s">
-        <x:v>786</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="B327" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C327" s="8" t="s">
-        <x:v>787</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="D327" s="11" t="s">
-        <x:v>788</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="E327" s="17"/>
       <x:c r="F327" s="17"/>
@@ -10263,16 +10251,16 @@
     </x:row>
     <x:row r="328" ht="30" customHeight="1">
       <x:c r="A328" s="20" t="s">
-        <x:v>789</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="B328" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C328" s="8" t="s">
-        <x:v>790</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="D328" s="11" t="s">
-        <x:v>791</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="E328" s="17"/>
       <x:c r="F328" s="17"/>
@@ -10285,16 +10273,16 @@
     </x:row>
     <x:row r="329" ht="30" customHeight="1">
       <x:c r="A329" s="20" t="s">
-        <x:v>792</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B329" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C329" s="8" t="s">
-        <x:v>793</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="D329" s="11" t="s">
-        <x:v>794</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="E329" s="17"/>
       <x:c r="F329" s="17"/>
@@ -10307,16 +10295,16 @@
     </x:row>
     <x:row r="330" ht="30" customHeight="1">
       <x:c r="A330" s="20" t="s">
-        <x:v>795</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="B330" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C330" s="8" t="s">
-        <x:v>796</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="D330" s="11" t="s">
-        <x:v>797</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="E330" s="17"/>
       <x:c r="F330" s="17"/>
@@ -10329,16 +10317,16 @@
     </x:row>
     <x:row r="331" ht="30" customHeight="1">
       <x:c r="A331" s="21" t="s">
-        <x:v>798</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="B331" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C331" s="9" t="s">
-        <x:v>799</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="D331" s="12" t="s">
-        <x:v>800</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="E331" s="18"/>
       <x:c r="F331" s="18"/>
@@ -10351,16 +10339,16 @@
     </x:row>
     <x:row r="332" ht="15">
       <x:c r="A332" s="23" t="s">
-        <x:v>801</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B332" s="24" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C332" s="25" t="s">
-        <x:v>802</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="D332" s="26" t="s">
-        <x:v>803</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="E332" s="22"/>
       <x:c r="F332" s="22"/>
@@ -10373,16 +10361,16 @@
     </x:row>
     <x:row r="333" ht="15">
       <x:c r="A333" s="23" t="s">
-        <x:v>804</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B333" s="27" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C333" s="28" t="s">
-        <x:v>805</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="D333" s="29" t="s">
-        <x:v>806</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="E333" s="22"/>
       <x:c r="F333" s="22"/>
@@ -10395,16 +10383,16 @@
     </x:row>
     <x:row r="334" ht="15">
       <x:c r="A334" s="23" t="s">
-        <x:v>807</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B334" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C334" s="25" t="s">
-        <x:v>808</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="D334" s="26" t="s">
-        <x:v>809</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="E334" s="22"/>
       <x:c r="F334" s="22"/>
@@ -10417,16 +10405,16 @@
     </x:row>
     <x:row r="335" ht="15">
       <x:c r="A335" s="23" t="s">
-        <x:v>810</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B335" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C335" s="28" t="s">
-        <x:v>811</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="D335" s="29" t="s">
-        <x:v>812</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="E335" s="22"/>
       <x:c r="F335" s="22"/>
@@ -10439,16 +10427,16 @@
     </x:row>
     <x:row r="336" ht="15">
       <x:c r="A336" s="23" t="s">
-        <x:v>813</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="B336" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C336" s="25" t="s">
-        <x:v>814</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="D336" s="26" t="s">
-        <x:v>815</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="E336" s="22"/>
       <x:c r="F336" s="22"/>
@@ -10461,16 +10449,16 @@
     </x:row>
     <x:row r="337" ht="15">
       <x:c r="A337" s="23" t="s">
-        <x:v>816</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B337" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C337" s="28" t="s">
-        <x:v>817</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="D337" s="29" t="s">
-        <x:v>818</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="E337" s="22"/>
       <x:c r="F337" s="22"/>
@@ -10483,16 +10471,16 @@
     </x:row>
     <x:row r="338" ht="15">
       <x:c r="A338" s="23" t="s">
-        <x:v>819</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="B338" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C338" s="25" t="s">
-        <x:v>820</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="D338" s="26" t="s">
-        <x:v>821</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="E338" s="22"/>
       <x:c r="F338" s="22"/>
@@ -10505,16 +10493,16 @@
     </x:row>
     <x:row r="339" ht="15">
       <x:c r="A339" s="23" t="s">
-        <x:v>822</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="B339" s="27" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C339" s="28" t="s">
-        <x:v>823</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="D339" s="29" t="s">
-        <x:v>824</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="E339" s="22"/>
       <x:c r="F339" s="22"/>
@@ -10667,16 +10655,16 @@
     </x:row>
     <x:row r="350">
       <x:c r="A350" t="s">
-        <x:v>825</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="B350" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C350" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="D350" t="s">
-        <x:v>826</x:v>
+        <x:v>822</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -10756,7 +10744,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8db9dda7026f4ac9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d9da988733e4a2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R1d47d72800e24af0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="Re116f7254be64e2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R30a68264af8b481d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R449dcade0fac4099"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -500,18 +500,12 @@
     <x:t xml:space="preserve">Второй абзац</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Тогда она предложила: "А можно сделать так, чтобы я говорила AI ассистенту информацию о клиенте, а это сохранялось в какую-то базу, от куда это можно будет также получить через ассистента."</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">story.quote</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Цитата</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Она предложила идею, а я превратил её в инструмент. И придумал простое решение, которое не требует больших затрат, при этом сохраняя безопастность данных</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">story.before_label</x:t>
   </x:si>
   <x:si>
@@ -614,9 +608,6 @@
     <x:t xml:space="preserve">demo.step.transcription.title</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Система распознаёт сообщение и показывает результат до отправки.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">demo.step.transcription.description</x:t>
   </x:si>
   <x:si>
@@ -629,9 +620,6 @@
     <x:t xml:space="preserve">demo.step.attachments.title</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Фотографии до и после прикрепляюся к конкретному посещению</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">demo.step.attachments.description</x:t>
   </x:si>
   <x:si>
@@ -647,9 +635,6 @@
     <x:t xml:space="preserve">demo.step.summary-preview.title</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Ассисиетент анализирует все данные, структурирует их и присылает на итоговую проверку</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">demo.step.summary-preview.description</x:t>
   </x:si>
   <x:si>
@@ -665,9 +650,6 @@
     <x:t xml:space="preserve">demo.step.confirmation.title</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Вы контролируете итог и подстверждаете сохранение</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">demo.step.confirmation.description</x:t>
   </x:si>
   <x:si>
@@ -734,9 +716,6 @@
     <x:t xml:space="preserve">demo.step.visit-details.title</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">В любой момент вы можете запросить сводку по конктеному посещению или по всей истории клиента</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">demo.step.visit-details.description</x:t>
   </x:si>
   <x:si>
@@ -903,9 +882,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">demo.template.last_visit_query</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Покажи последний визит {shortName}, телефон заканчивается на {phoneLastDigits}.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">demo.ui.assistant_default_status</x:t>
@@ -4107,8 +4083,8 @@
       <x:c r="C48" s="8" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="D48" s="11" t="s">
-        <x:v>163</x:v>
+      <x:c r="D48" s="11" t="str">
+        <x:v>Тогда она предложила: «А можно сделать так, чтобы я сообщала ИИ-ассистенту информацию о клиенте, а она сохранялась в какую-то базу, откуда её также можно было бы получить через ассистента?»</x:v>
       </x:c>
       <x:c r="E48" s="17"/>
       <x:c r="F48" s="17"/>
@@ -4121,16 +4097,16 @@
     </x:row>
     <x:row r="49" ht="30" customHeight="1">
       <x:c r="A49" s="20" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B49" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C49" s="8" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D49" s="11" t="s">
-        <x:v>166</x:v>
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="str">
+        <x:v>Она предложила идею, а я превратил её в инструмент. Я придумал простое решение, которое не требует больших затрат и при этом обеспечивает безопасность данных.</x:v>
       </x:c>
       <x:c r="E49" s="17"/>
       <x:c r="F49" s="17"/>
@@ -4143,16 +4119,16 @@
     </x:row>
     <x:row r="50" ht="30" customHeight="1">
       <x:c r="A50" s="20" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B50" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C50" s="8" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D50" s="11" t="s">
-        <x:v>169</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E50" s="17"/>
       <x:c r="F50" s="17"/>
@@ -4165,16 +4141,16 @@
     </x:row>
     <x:row r="51" ht="30" customHeight="1">
       <x:c r="A51" s="20" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B51" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C51" s="8" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D51" s="11" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E51" s="17"/>
       <x:c r="F51" s="17"/>
@@ -4187,16 +4163,16 @@
     </x:row>
     <x:row r="52" ht="30" customHeight="1">
       <x:c r="A52" s="20" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B52" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C52" s="8" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D52" s="11" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E52" s="17"/>
       <x:c r="F52" s="17"/>
@@ -4209,16 +4185,16 @@
     </x:row>
     <x:row r="53" ht="30" customHeight="1">
       <x:c r="A53" s="20" t="s">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B53" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C53" s="8" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D53" s="11" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E53" s="17"/>
       <x:c r="F53" s="17"/>
@@ -4231,16 +4207,16 @@
     </x:row>
     <x:row r="54" ht="30" customHeight="1">
       <x:c r="A54" s="20" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B54" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C54" s="8" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="D54" s="11" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E54" s="17"/>
       <x:c r="F54" s="17"/>
@@ -4253,16 +4229,16 @@
     </x:row>
     <x:row r="55" ht="30" customHeight="1">
       <x:c r="A55" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B55" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C55" s="8" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="D55" s="11" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E55" s="17"/>
       <x:c r="F55" s="17"/>
@@ -4275,16 +4251,16 @@
     </x:row>
     <x:row r="56" ht="30" customHeight="1">
       <x:c r="A56" s="20" t="s">
-        <x:v>184</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B56" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C56" s="8" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="D56" s="11" t="s">
-        <x:v>185</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E56" s="17"/>
       <x:c r="F56" s="17"/>
@@ -4297,16 +4273,16 @@
     </x:row>
     <x:row r="57" ht="30" customHeight="1">
       <x:c r="A57" s="20" t="s">
-        <x:v>186</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B57" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C57" s="8" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D57" s="11" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E57" s="17"/>
       <x:c r="F57" s="17"/>
@@ -4319,16 +4295,16 @@
     </x:row>
     <x:row r="58" ht="30" customHeight="1">
       <x:c r="A58" s="20" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B58" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C58" s="8" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D58" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="D58" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="E58" s="17"/>
       <x:c r="F58" s="17"/>
@@ -4341,16 +4317,16 @@
     </x:row>
     <x:row r="59" ht="30" customHeight="1">
       <x:c r="A59" s="20" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B59" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C59" s="8" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D59" s="11" t="s">
-        <x:v>191</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E59" s="17"/>
       <x:c r="F59" s="17"/>
@@ -4363,16 +4339,16 @@
     </x:row>
     <x:row r="60" ht="30" customHeight="1">
       <x:c r="A60" s="20" t="s">
-        <x:v>192</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B60" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C60" s="8" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D60" s="11" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E60" s="17"/>
       <x:c r="F60" s="17"/>
@@ -4385,16 +4361,16 @@
     </x:row>
     <x:row r="61" ht="30" customHeight="1">
       <x:c r="A61" s="20" t="s">
-        <x:v>194</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B61" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C61" s="8" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="D61" s="11" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="E61" s="17"/>
       <x:c r="F61" s="17"/>
@@ -4407,16 +4383,16 @@
     </x:row>
     <x:row r="62" ht="30" customHeight="1">
       <x:c r="A62" s="20" t="s">
-        <x:v>196</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B62" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C62" s="8" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D62" s="11" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E62" s="17"/>
       <x:c r="F62" s="17"/>
@@ -4429,16 +4405,16 @@
     </x:row>
     <x:row r="63" ht="30" customHeight="1">
       <x:c r="A63" s="20" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B63" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C63" s="8" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D63" s="11" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E63" s="17"/>
       <x:c r="F63" s="17"/>
@@ -4451,16 +4427,16 @@
     </x:row>
     <x:row r="64" ht="30" customHeight="1">
       <x:c r="A64" s="20" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B64" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C64" s="8" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="D64" s="11" t="s">
-        <x:v>201</x:v>
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D64" s="11" t="str">
+        <x:v>Система распознаёт сообщение и показывает результат до отправки</x:v>
       </x:c>
       <x:c r="E64" s="17"/>
       <x:c r="F64" s="17"/>
@@ -4473,13 +4449,13 @@
     </x:row>
     <x:row r="65" ht="30" customHeight="1">
       <x:c r="A65" s="20" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B65" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C65" s="8" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D65" s="11"/>
       <x:c r="E65" s="17"/>
@@ -4493,16 +4469,16 @@
     </x:row>
     <x:row r="66" ht="30" customHeight="1">
       <x:c r="A66" s="20" t="s">
-        <x:v>203</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B66" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C66" s="8" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D66" s="11" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E66" s="17"/>
       <x:c r="F66" s="17"/>
@@ -4515,16 +4491,16 @@
     </x:row>
     <x:row r="67" ht="30" customHeight="1">
       <x:c r="A67" s="20" t="s">
-        <x:v>205</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B67" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C67" s="8" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D67" s="11" t="s">
-        <x:v>206</x:v>
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="str">
+        <x:v>Фотографии до и после прикрепляются к конкретному посещению</x:v>
       </x:c>
       <x:c r="E67" s="17"/>
       <x:c r="F67" s="17"/>
@@ -4537,13 +4513,13 @@
     </x:row>
     <x:row r="68" ht="30" customHeight="1">
       <x:c r="A68" s="20" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B68" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C68" s="8" t="s">
-        <x:v>204</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D68" s="11"/>
       <x:c r="E68" s="17"/>
@@ -4557,16 +4533,16 @@
     </x:row>
     <x:row r="69" ht="30" customHeight="1">
       <x:c r="A69" s="20" t="s">
-        <x:v>208</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B69" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C69" s="8" t="s">
-        <x:v>209</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D69" s="11" t="s">
-        <x:v>210</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E69" s="17"/>
       <x:c r="F69" s="17"/>
@@ -4579,16 +4555,16 @@
     </x:row>
     <x:row r="70" ht="30" customHeight="1">
       <x:c r="A70" s="20" t="s">
-        <x:v>211</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B70" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C70" s="8" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D70" s="11" t="s">
-        <x:v>212</x:v>
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D70" s="11" t="str">
+        <x:v>Ассистент анализирует все данные, структурирует их и присылает на итоговую проверку</x:v>
       </x:c>
       <x:c r="E70" s="17"/>
       <x:c r="F70" s="17"/>
@@ -4601,16 +4577,16 @@
     </x:row>
     <x:row r="71" ht="30" customHeight="1">
       <x:c r="A71" s="20" t="s">
-        <x:v>213</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B71" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C71" s="8" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="D71" s="11" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="E71" s="17"/>
       <x:c r="F71" s="17"/>
@@ -4623,16 +4599,16 @@
     </x:row>
     <x:row r="72" ht="30" customHeight="1">
       <x:c r="A72" s="20" t="s">
-        <x:v>215</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B72" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C72" s="8" t="s">
-        <x:v>216</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D72" s="11" t="s">
-        <x:v>209</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E72" s="17"/>
       <x:c r="F72" s="17"/>
@@ -4645,16 +4621,16 @@
     </x:row>
     <x:row r="73" ht="30" customHeight="1">
       <x:c r="A73" s="20" t="s">
-        <x:v>217</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B73" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C73" s="8" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D73" s="11" t="s">
-        <x:v>218</x:v>
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="str">
+        <x:v>Вы контролируете итог и подтверждаете сохранение</x:v>
       </x:c>
       <x:c r="E73" s="17"/>
       <x:c r="F73" s="17"/>
@@ -4667,13 +4643,13 @@
     </x:row>
     <x:row r="74" ht="30" customHeight="1">
       <x:c r="A74" s="20" t="s">
-        <x:v>219</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B74" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C74" s="8" t="s">
-        <x:v>216</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D74" s="11"/>
       <x:c r="E74" s="17"/>
@@ -4687,16 +4663,16 @@
     </x:row>
     <x:row r="75" ht="30" customHeight="1">
       <x:c r="A75" s="20" t="s">
-        <x:v>220</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B75" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C75" s="8" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D75" s="11" t="s">
-        <x:v>216</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E75" s="17"/>
       <x:c r="F75" s="17"/>
@@ -4709,16 +4685,16 @@
     </x:row>
     <x:row r="76" ht="30" customHeight="1">
       <x:c r="A76" s="20" t="s">
-        <x:v>222</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B76" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C76" s="8" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D76" s="11" t="s">
-        <x:v>223</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E76" s="17"/>
       <x:c r="F76" s="17"/>
@@ -4731,16 +4707,16 @@
     </x:row>
     <x:row r="77" ht="30" customHeight="1">
       <x:c r="A77" s="20" t="s">
-        <x:v>224</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B77" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C77" s="8" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D77" s="11" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E77" s="17"/>
       <x:c r="F77" s="17"/>
@@ -4753,16 +4729,16 @@
     </x:row>
     <x:row r="78" ht="30" customHeight="1">
       <x:c r="A78" s="20" t="s">
-        <x:v>226</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B78" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C78" s="8" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D78" s="11" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E78" s="17"/>
       <x:c r="F78" s="17"/>
@@ -4775,16 +4751,16 @@
     </x:row>
     <x:row r="79" ht="30" customHeight="1">
       <x:c r="A79" s="20" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B79" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C79" s="8" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D79" s="11" t="s">
-        <x:v>229</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E79" s="17"/>
       <x:c r="F79" s="17"/>
@@ -4797,16 +4773,16 @@
     </x:row>
     <x:row r="80" ht="30" customHeight="1">
       <x:c r="A80" s="20" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B80" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C80" s="8" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D80" s="11" t="s">
-        <x:v>231</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E80" s="17"/>
       <x:c r="F80" s="17"/>
@@ -4819,16 +4795,16 @@
     </x:row>
     <x:row r="81" ht="30" customHeight="1">
       <x:c r="A81" s="20" t="s">
-        <x:v>232</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B81" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C81" s="8" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D81" s="11" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E81" s="17"/>
       <x:c r="F81" s="17"/>
@@ -4841,16 +4817,16 @@
     </x:row>
     <x:row r="82" ht="30" customHeight="1">
       <x:c r="A82" s="20" t="s">
-        <x:v>234</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B82" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C82" s="8" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D82" s="11" t="s">
-        <x:v>235</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E82" s="17"/>
       <x:c r="F82" s="17"/>
@@ -4863,16 +4839,16 @@
     </x:row>
     <x:row r="83" ht="30" customHeight="1">
       <x:c r="A83" s="20" t="s">
-        <x:v>236</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B83" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C83" s="8" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="D83" s="11" t="s">
-        <x:v>237</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E83" s="17"/>
       <x:c r="F83" s="17"/>
@@ -4885,16 +4861,16 @@
     </x:row>
     <x:row r="84" ht="30" customHeight="1">
       <x:c r="A84" s="20" t="s">
-        <x:v>238</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B84" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C84" s="8" t="s">
-        <x:v>239</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="D84" s="11" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E84" s="17"/>
       <x:c r="F84" s="17"/>
@@ -4907,16 +4883,16 @@
     </x:row>
     <x:row r="85" ht="30" customHeight="1">
       <x:c r="A85" s="20" t="s">
-        <x:v>240</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B85" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C85" s="8" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D85" s="11" t="s">
-        <x:v>241</x:v>
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="str">
+        <x:v>В любой момент вы можете запросить сводку по конкретному посещению или по всей истории клиента</x:v>
       </x:c>
       <x:c r="E85" s="17"/>
       <x:c r="F85" s="17"/>
@@ -4929,16 +4905,16 @@
     </x:row>
     <x:row r="86" ht="30" customHeight="1">
       <x:c r="A86" s="20" t="s">
-        <x:v>242</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B86" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C86" s="8" t="s">
-        <x:v>239</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="D86" s="11" t="s">
-        <x:v>243</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E86" s="17"/>
       <x:c r="F86" s="17"/>
@@ -4951,16 +4927,16 @@
     </x:row>
     <x:row r="87" ht="30" customHeight="1">
       <x:c r="A87" s="20" t="s">
-        <x:v>244</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B87" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C87" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D87" s="11" t="s">
-        <x:v>246</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E87" s="17"/>
       <x:c r="F87" s="17"/>
@@ -4973,16 +4949,16 @@
     </x:row>
     <x:row r="88" ht="30" customHeight="1">
       <x:c r="A88" s="20" t="s">
-        <x:v>247</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B88" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C88" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D88" s="11" t="s">
-        <x:v>248</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E88" s="17"/>
       <x:c r="F88" s="17"/>
@@ -4995,16 +4971,16 @@
     </x:row>
     <x:row r="89" ht="30" customHeight="1">
       <x:c r="A89" s="20" t="s">
-        <x:v>249</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B89" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C89" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D89" s="11" t="s">
-        <x:v>250</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E89" s="17"/>
       <x:c r="F89" s="17"/>
@@ -5017,16 +4993,16 @@
     </x:row>
     <x:row r="90" ht="30" customHeight="1">
       <x:c r="A90" s="20" t="s">
-        <x:v>251</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B90" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C90" s="8" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D90" s="11" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="D90" s="11" t="s">
-        <x:v>252</x:v>
       </x:c>
       <x:c r="E90" s="17"/>
       <x:c r="F90" s="17"/>
@@ -5039,16 +5015,16 @@
     </x:row>
     <x:row r="91" ht="30" customHeight="1">
       <x:c r="A91" s="20" t="s">
-        <x:v>253</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B91" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C91" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D91" s="11" t="s">
-        <x:v>254</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E91" s="17"/>
       <x:c r="F91" s="17"/>
@@ -5061,16 +5037,16 @@
     </x:row>
     <x:row r="92" ht="30" customHeight="1">
       <x:c r="A92" s="20" t="s">
-        <x:v>255</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B92" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C92" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D92" s="11" t="s">
-        <x:v>256</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E92" s="17"/>
       <x:c r="F92" s="17"/>
@@ -5083,16 +5059,16 @@
     </x:row>
     <x:row r="93" ht="30" customHeight="1">
       <x:c r="A93" s="20" t="s">
-        <x:v>257</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B93" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C93" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D93" s="11" t="s">
-        <x:v>258</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E93" s="17"/>
       <x:c r="F93" s="17"/>
@@ -5105,16 +5081,16 @@
     </x:row>
     <x:row r="94" ht="30" customHeight="1">
       <x:c r="A94" s="20" t="s">
-        <x:v>259</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B94" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C94" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D94" s="11" t="s">
-        <x:v>260</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E94" s="17"/>
       <x:c r="F94" s="17"/>
@@ -5127,16 +5103,16 @@
     </x:row>
     <x:row r="95" ht="30" customHeight="1">
       <x:c r="A95" s="20" t="s">
-        <x:v>261</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B95" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C95" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D95" s="11" t="s">
-        <x:v>262</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="E95" s="17"/>
       <x:c r="F95" s="17"/>
@@ -5149,16 +5125,16 @@
     </x:row>
     <x:row r="96" ht="30" customHeight="1">
       <x:c r="A96" s="20" t="s">
-        <x:v>263</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B96" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C96" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D96" s="11" t="s">
-        <x:v>264</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E96" s="17"/>
       <x:c r="F96" s="17"/>
@@ -5171,16 +5147,16 @@
     </x:row>
     <x:row r="97" ht="30" customHeight="1">
       <x:c r="A97" s="20" t="s">
-        <x:v>265</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B97" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C97" s="8" t="s">
-        <x:v>245</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D97" s="11" t="s">
-        <x:v>266</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E97" s="17"/>
       <x:c r="F97" s="17"/>
@@ -5193,16 +5169,16 @@
     </x:row>
     <x:row r="98" ht="30" customHeight="1">
       <x:c r="A98" s="20" t="s">
-        <x:v>267</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B98" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C98" s="8" t="s">
-        <x:v>268</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D98" s="11" t="s">
-        <x:v>269</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E98" s="17"/>
       <x:c r="F98" s="17"/>
@@ -5215,16 +5191,16 @@
     </x:row>
     <x:row r="99" ht="30" customHeight="1">
       <x:c r="A99" s="20" t="s">
-        <x:v>270</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B99" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C99" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D99" s="11" t="s">
-        <x:v>272</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E99" s="17"/>
       <x:c r="F99" s="17"/>
@@ -5237,16 +5213,16 @@
     </x:row>
     <x:row r="100" ht="30" customHeight="1">
       <x:c r="A100" s="20" t="s">
-        <x:v>273</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B100" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C100" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D100" s="11" t="s">
-        <x:v>274</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E100" s="17"/>
       <x:c r="F100" s="17"/>
@@ -5259,16 +5235,16 @@
     </x:row>
     <x:row r="101" ht="30" customHeight="1">
       <x:c r="A101" s="20" t="s">
-        <x:v>275</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B101" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C101" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D101" s="11" t="s">
-        <x:v>276</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E101" s="17"/>
       <x:c r="F101" s="17"/>
@@ -5281,16 +5257,16 @@
     </x:row>
     <x:row r="102" ht="30" customHeight="1">
       <x:c r="A102" s="20" t="s">
-        <x:v>277</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B102" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C102" s="8" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D102" s="11" t="s">
         <x:v>271</x:v>
-      </x:c>
-      <x:c r="D102" s="11" t="s">
-        <x:v>278</x:v>
       </x:c>
       <x:c r="E102" s="17"/>
       <x:c r="F102" s="17"/>
@@ -5303,16 +5279,16 @@
     </x:row>
     <x:row r="103" ht="30" customHeight="1">
       <x:c r="A103" s="20" t="s">
-        <x:v>279</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B103" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C103" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D103" s="11" t="s">
-        <x:v>280</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E103" s="17"/>
       <x:c r="F103" s="17"/>
@@ -5325,16 +5301,16 @@
     </x:row>
     <x:row r="104" ht="30" customHeight="1">
       <x:c r="A104" s="20" t="s">
-        <x:v>281</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B104" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C104" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D104" s="11" t="s">
-        <x:v>282</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E104" s="17"/>
       <x:c r="F104" s="17"/>
@@ -5347,16 +5323,16 @@
     </x:row>
     <x:row r="105" ht="30" customHeight="1">
       <x:c r="A105" s="20" t="s">
-        <x:v>283</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B105" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C105" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D105" s="11" t="s">
-        <x:v>284</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E105" s="17"/>
       <x:c r="F105" s="17"/>
@@ -5369,16 +5345,16 @@
     </x:row>
     <x:row r="106" ht="30" customHeight="1">
       <x:c r="A106" s="20" t="s">
-        <x:v>285</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B106" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C106" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D106" s="11" t="s">
-        <x:v>286</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="E106" s="17"/>
       <x:c r="F106" s="17"/>
@@ -5391,16 +5367,16 @@
     </x:row>
     <x:row r="107" ht="30" customHeight="1">
       <x:c r="A107" s="20" t="s">
-        <x:v>287</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B107" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C107" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D107" s="11" t="s">
-        <x:v>288</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E107" s="17"/>
       <x:c r="F107" s="17"/>
@@ -5413,16 +5389,16 @@
     </x:row>
     <x:row r="108" ht="30" customHeight="1">
       <x:c r="A108" s="20" t="s">
-        <x:v>289</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B108" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C108" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D108" s="11" t="s">
-        <x:v>290</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E108" s="17"/>
       <x:c r="F108" s="17"/>
@@ -5435,16 +5411,16 @@
     </x:row>
     <x:row r="109" ht="30" customHeight="1">
       <x:c r="A109" s="20" t="s">
-        <x:v>291</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B109" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C109" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D109" s="11" t="s">
-        <x:v>292</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="E109" s="17"/>
       <x:c r="F109" s="17"/>
@@ -5457,16 +5433,16 @@
     </x:row>
     <x:row r="110" ht="30" customHeight="1">
       <x:c r="A110" s="20" t="s">
-        <x:v>293</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B110" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C110" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D110" s="11" t="s">
-        <x:v>294</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E110" s="17"/>
       <x:c r="F110" s="17"/>
@@ -5479,16 +5455,16 @@
     </x:row>
     <x:row r="111" ht="30" customHeight="1">
       <x:c r="A111" s="20" t="s">
-        <x:v>295</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B111" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C111" s="8" t="s">
-        <x:v>271</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D111" s="11" t="s">
-        <x:v>296</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E111" s="17"/>
       <x:c r="F111" s="17"/>
@@ -5501,16 +5477,16 @@
     </x:row>
     <x:row r="112" ht="30" customHeight="1">
       <x:c r="A112" s="20" t="s">
-        <x:v>297</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B112" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C112" s="8" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="D112" s="11" t="s">
-        <x:v>298</x:v>
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D112" s="11" t="str">
+        <x:v>Покажи данные о последнем визите клиента: {shortName}. Телефон заканчивается на {phoneLastDigits}.</x:v>
       </x:c>
       <x:c r="E112" s="17"/>
       <x:c r="F112" s="17"/>
@@ -5523,16 +5499,16 @@
     </x:row>
     <x:row r="113" ht="30" customHeight="1">
       <x:c r="A113" s="20" t="s">
-        <x:v>299</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B113" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C113" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D113" s="11" t="s">
-        <x:v>301</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E113" s="17"/>
       <x:c r="F113" s="17"/>
@@ -5545,16 +5521,16 @@
     </x:row>
     <x:row r="114" ht="30" customHeight="1">
       <x:c r="A114" s="20" t="s">
-        <x:v>302</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B114" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C114" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D114" s="11" t="s">
-        <x:v>303</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E114" s="17"/>
       <x:c r="F114" s="17"/>
@@ -5567,16 +5543,16 @@
     </x:row>
     <x:row r="115" ht="30" customHeight="1">
       <x:c r="A115" s="20" t="s">
-        <x:v>304</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B115" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C115" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D115" s="11" t="s">
-        <x:v>305</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E115" s="17"/>
       <x:c r="F115" s="17"/>
@@ -5589,16 +5565,16 @@
     </x:row>
     <x:row r="116" ht="30" customHeight="1">
       <x:c r="A116" s="20" t="s">
-        <x:v>306</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B116" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C116" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D116" s="11" t="s">
-        <x:v>307</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E116" s="17"/>
       <x:c r="F116" s="17"/>
@@ -5611,16 +5587,16 @@
     </x:row>
     <x:row r="117" ht="30" customHeight="1">
       <x:c r="A117" s="20" t="s">
-        <x:v>308</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B117" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C117" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D117" s="11" t="s">
-        <x:v>309</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E117" s="17"/>
       <x:c r="F117" s="17"/>
@@ -5633,16 +5609,16 @@
     </x:row>
     <x:row r="118" ht="30" customHeight="1">
       <x:c r="A118" s="20" t="s">
-        <x:v>310</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B118" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C118" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D118" s="11" t="s">
-        <x:v>311</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="E118" s="17"/>
       <x:c r="F118" s="17"/>
@@ -5655,16 +5631,16 @@
     </x:row>
     <x:row r="119" ht="30" customHeight="1">
       <x:c r="A119" s="20" t="s">
-        <x:v>312</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B119" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C119" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D119" s="11" t="s">
-        <x:v>313</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="E119" s="17"/>
       <x:c r="F119" s="17"/>
@@ -5677,16 +5653,16 @@
     </x:row>
     <x:row r="120" ht="30" customHeight="1">
       <x:c r="A120" s="20" t="s">
-        <x:v>314</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B120" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C120" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D120" s="11" t="s">
-        <x:v>315</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E120" s="17"/>
       <x:c r="F120" s="17"/>
@@ -5699,16 +5675,16 @@
     </x:row>
     <x:row r="121" ht="30" customHeight="1">
       <x:c r="A121" s="20" t="s">
-        <x:v>316</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B121" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C121" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D121" s="11" t="s">
-        <x:v>317</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="E121" s="17"/>
       <x:c r="F121" s="17"/>
@@ -5721,16 +5697,16 @@
     </x:row>
     <x:row r="122" ht="30" customHeight="1">
       <x:c r="A122" s="20" t="s">
-        <x:v>318</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B122" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C122" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D122" s="11" t="s">
-        <x:v>319</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E122" s="17"/>
       <x:c r="F122" s="17"/>
@@ -5743,16 +5719,16 @@
     </x:row>
     <x:row r="123" ht="30" customHeight="1">
       <x:c r="A123" s="20" t="s">
-        <x:v>320</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B123" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C123" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D123" s="11" t="s">
-        <x:v>321</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="E123" s="17"/>
       <x:c r="F123" s="17"/>
@@ -5765,16 +5741,16 @@
     </x:row>
     <x:row r="124" ht="30" customHeight="1">
       <x:c r="A124" s="20" t="s">
-        <x:v>322</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B124" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C124" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D124" s="11" t="s">
-        <x:v>323</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="E124" s="17"/>
       <x:c r="F124" s="17"/>
@@ -5787,16 +5763,16 @@
     </x:row>
     <x:row r="125" ht="30" customHeight="1">
       <x:c r="A125" s="20" t="s">
-        <x:v>324</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B125" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C125" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D125" s="11" t="s">
-        <x:v>325</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="E125" s="17"/>
       <x:c r="F125" s="17"/>
@@ -5809,16 +5785,16 @@
     </x:row>
     <x:row r="126" ht="30" customHeight="1">
       <x:c r="A126" s="20" t="s">
-        <x:v>326</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B126" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C126" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D126" s="11" t="s">
-        <x:v>327</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="E126" s="17"/>
       <x:c r="F126" s="17"/>
@@ -5831,16 +5807,16 @@
     </x:row>
     <x:row r="127" ht="30" customHeight="1">
       <x:c r="A127" s="20" t="s">
-        <x:v>328</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B127" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C127" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D127" s="11" t="s">
-        <x:v>329</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E127" s="17"/>
       <x:c r="F127" s="17"/>
@@ -5853,16 +5829,16 @@
     </x:row>
     <x:row r="128" ht="30" customHeight="1">
       <x:c r="A128" s="20" t="s">
-        <x:v>330</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B128" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C128" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D128" s="11" t="s">
-        <x:v>331</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E128" s="17"/>
       <x:c r="F128" s="17"/>
@@ -5875,16 +5851,16 @@
     </x:row>
     <x:row r="129" ht="30" customHeight="1">
       <x:c r="A129" s="20" t="s">
-        <x:v>332</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B129" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C129" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D129" s="11" t="s">
-        <x:v>333</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="E129" s="17"/>
       <x:c r="F129" s="17"/>
@@ -5897,16 +5873,16 @@
     </x:row>
     <x:row r="130" ht="30" customHeight="1">
       <x:c r="A130" s="20" t="s">
-        <x:v>334</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B130" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C130" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D130" s="11" t="s">
-        <x:v>335</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E130" s="17"/>
       <x:c r="F130" s="17"/>
@@ -5919,16 +5895,16 @@
     </x:row>
     <x:row r="131" ht="30" customHeight="1">
       <x:c r="A131" s="20" t="s">
-        <x:v>336</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B131" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C131" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D131" s="11" t="s">
-        <x:v>337</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="E131" s="17"/>
       <x:c r="F131" s="17"/>
@@ -5941,16 +5917,16 @@
     </x:row>
     <x:row r="132" ht="30" customHeight="1">
       <x:c r="A132" s="20" t="s">
-        <x:v>338</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B132" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C132" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D132" s="11" t="s">
-        <x:v>339</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="E132" s="17"/>
       <x:c r="F132" s="17"/>
@@ -5963,16 +5939,16 @@
     </x:row>
     <x:row r="133" ht="30" customHeight="1">
       <x:c r="A133" s="20" t="s">
-        <x:v>340</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B133" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C133" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D133" s="11" t="s">
-        <x:v>341</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="E133" s="17"/>
       <x:c r="F133" s="17"/>
@@ -5985,16 +5961,16 @@
     </x:row>
     <x:row r="134" ht="30" customHeight="1">
       <x:c r="A134" s="20" t="s">
-        <x:v>342</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B134" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C134" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D134" s="11" t="s">
-        <x:v>343</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E134" s="17"/>
       <x:c r="F134" s="17"/>
@@ -6007,16 +5983,16 @@
     </x:row>
     <x:row r="135" ht="30" customHeight="1">
       <x:c r="A135" s="20" t="s">
-        <x:v>344</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B135" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C135" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D135" s="11" t="s">
-        <x:v>345</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="E135" s="17"/>
       <x:c r="F135" s="17"/>
@@ -6029,16 +6005,16 @@
     </x:row>
     <x:row r="136" ht="30" customHeight="1">
       <x:c r="A136" s="20" t="s">
-        <x:v>346</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B136" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C136" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D136" s="11" t="s">
-        <x:v>347</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="E136" s="17"/>
       <x:c r="F136" s="17"/>
@@ -6051,16 +6027,16 @@
     </x:row>
     <x:row r="137" ht="30" customHeight="1">
       <x:c r="A137" s="20" t="s">
-        <x:v>348</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B137" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C137" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D137" s="11" t="s">
-        <x:v>349</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="E137" s="17"/>
       <x:c r="F137" s="17"/>
@@ -6073,16 +6049,16 @@
     </x:row>
     <x:row r="138" ht="30" customHeight="1">
       <x:c r="A138" s="20" t="s">
-        <x:v>350</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B138" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C138" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D138" s="11" t="s">
-        <x:v>351</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="E138" s="17"/>
       <x:c r="F138" s="17"/>
@@ -6095,16 +6071,16 @@
     </x:row>
     <x:row r="139" ht="30" customHeight="1">
       <x:c r="A139" s="20" t="s">
-        <x:v>352</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B139" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C139" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D139" s="11" t="s">
-        <x:v>353</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E139" s="17"/>
       <x:c r="F139" s="17"/>
@@ -6117,16 +6093,16 @@
     </x:row>
     <x:row r="140" ht="30" customHeight="1">
       <x:c r="A140" s="20" t="s">
-        <x:v>354</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B140" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C140" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D140" s="11" t="s">
-        <x:v>355</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="E140" s="17"/>
       <x:c r="F140" s="17"/>
@@ -6139,16 +6115,16 @@
     </x:row>
     <x:row r="141" ht="30" customHeight="1">
       <x:c r="A141" s="20" t="s">
-        <x:v>356</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B141" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C141" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D141" s="11" t="s">
-        <x:v>357</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E141" s="17"/>
       <x:c r="F141" s="17"/>
@@ -6161,16 +6137,16 @@
     </x:row>
     <x:row r="142" ht="30" customHeight="1">
       <x:c r="A142" s="20" t="s">
-        <x:v>358</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B142" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C142" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D142" s="11" t="s">
-        <x:v>359</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E142" s="17"/>
       <x:c r="F142" s="17"/>
@@ -6183,16 +6159,16 @@
     </x:row>
     <x:row r="143" ht="30" customHeight="1">
       <x:c r="A143" s="20" t="s">
-        <x:v>360</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B143" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C143" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D143" s="11" t="s">
-        <x:v>361</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="E143" s="17"/>
       <x:c r="F143" s="17"/>
@@ -6205,16 +6181,16 @@
     </x:row>
     <x:row r="144" ht="30" customHeight="1">
       <x:c r="A144" s="20" t="s">
-        <x:v>362</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B144" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C144" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D144" s="11" t="s">
-        <x:v>363</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E144" s="17"/>
       <x:c r="F144" s="17"/>
@@ -6227,16 +6203,16 @@
     </x:row>
     <x:row r="145" ht="30" customHeight="1">
       <x:c r="A145" s="20" t="s">
-        <x:v>364</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B145" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C145" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D145" s="11" t="s">
-        <x:v>365</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E145" s="17"/>
       <x:c r="F145" s="17"/>
@@ -6249,16 +6225,16 @@
     </x:row>
     <x:row r="146" ht="30" customHeight="1">
       <x:c r="A146" s="20" t="s">
-        <x:v>366</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B146" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C146" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D146" s="11" t="s">
-        <x:v>367</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="E146" s="17"/>
       <x:c r="F146" s="17"/>
@@ -6271,16 +6247,16 @@
     </x:row>
     <x:row r="147" ht="30" customHeight="1">
       <x:c r="A147" s="20" t="s">
-        <x:v>368</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B147" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C147" s="8" t="s">
-        <x:v>300</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D147" s="11" t="s">
-        <x:v>369</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E147" s="17"/>
       <x:c r="F147" s="17"/>
@@ -6293,16 +6269,16 @@
     </x:row>
     <x:row r="148" ht="30" customHeight="1">
       <x:c r="A148" s="20" t="s">
-        <x:v>370</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B148" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C148" s="8" t="s">
-        <x:v>371</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D148" s="11" t="s">
-        <x:v>372</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="E148" s="17"/>
       <x:c r="F148" s="17"/>
@@ -6315,16 +6291,16 @@
     </x:row>
     <x:row r="149" ht="30" customHeight="1">
       <x:c r="A149" s="20" t="s">
-        <x:v>373</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B149" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C149" s="8" t="s">
-        <x:v>371</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D149" s="11" t="s">
-        <x:v>374</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="E149" s="17"/>
       <x:c r="F149" s="17"/>
@@ -6337,16 +6313,16 @@
     </x:row>
     <x:row r="150" ht="30" customHeight="1">
       <x:c r="A150" s="20" t="s">
-        <x:v>375</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B150" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C150" s="8" t="s">
-        <x:v>371</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D150" s="11" t="s">
-        <x:v>376</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="E150" s="17"/>
       <x:c r="F150" s="17"/>
@@ -6359,16 +6335,16 @@
     </x:row>
     <x:row r="151" ht="30" customHeight="1">
       <x:c r="A151" s="20" t="s">
-        <x:v>377</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B151" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C151" s="8" t="s">
-        <x:v>371</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D151" s="11" t="s">
-        <x:v>378</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="E151" s="17"/>
       <x:c r="F151" s="17"/>
@@ -6381,16 +6357,16 @@
     </x:row>
     <x:row r="152" ht="30" customHeight="1">
       <x:c r="A152" s="20" t="s">
-        <x:v>379</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B152" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C152" s="8" t="s">
-        <x:v>371</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D152" s="11" t="s">
-        <x:v>380</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E152" s="17"/>
       <x:c r="F152" s="17"/>
@@ -6403,16 +6379,16 @@
     </x:row>
     <x:row r="153" ht="30" customHeight="1">
       <x:c r="A153" s="20" t="s">
-        <x:v>381</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B153" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C153" s="8" t="s">
-        <x:v>371</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D153" s="11" t="s">
-        <x:v>382</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="E153" s="17"/>
       <x:c r="F153" s="17"/>
@@ -6425,16 +6401,16 @@
     </x:row>
     <x:row r="154" ht="30" customHeight="1">
       <x:c r="A154" s="20" t="s">
-        <x:v>383</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B154" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C154" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D154" s="11" t="s">
-        <x:v>385</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="E154" s="17"/>
       <x:c r="F154" s="17"/>
@@ -6447,16 +6423,16 @@
     </x:row>
     <x:row r="155" ht="30" customHeight="1">
       <x:c r="A155" s="20" t="s">
-        <x:v>386</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B155" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C155" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D155" s="11" t="s">
-        <x:v>387</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="E155" s="17"/>
       <x:c r="F155" s="17"/>
@@ -6469,16 +6445,16 @@
     </x:row>
     <x:row r="156" ht="30" customHeight="1">
       <x:c r="A156" s="20" t="s">
-        <x:v>388</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B156" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C156" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D156" s="11" t="s">
-        <x:v>389</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="E156" s="17"/>
       <x:c r="F156" s="17"/>
@@ -6491,16 +6467,16 @@
     </x:row>
     <x:row r="157" ht="30" customHeight="1">
       <x:c r="A157" s="20" t="s">
-        <x:v>390</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B157" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C157" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D157" s="11" t="s">
-        <x:v>391</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E157" s="17"/>
       <x:c r="F157" s="17"/>
@@ -6513,16 +6489,16 @@
     </x:row>
     <x:row r="158" ht="30" customHeight="1">
       <x:c r="A158" s="20" t="s">
-        <x:v>392</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B158" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C158" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D158" s="11" t="s">
-        <x:v>393</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="E158" s="17"/>
       <x:c r="F158" s="17"/>
@@ -6535,16 +6511,16 @@
     </x:row>
     <x:row r="159" ht="30" customHeight="1">
       <x:c r="A159" s="20" t="s">
-        <x:v>394</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B159" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C159" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D159" s="11" t="s">
-        <x:v>395</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="E159" s="17"/>
       <x:c r="F159" s="17"/>
@@ -6557,16 +6533,16 @@
     </x:row>
     <x:row r="160" ht="30" customHeight="1">
       <x:c r="A160" s="20" t="s">
-        <x:v>396</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B160" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C160" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D160" s="11" t="s">
-        <x:v>397</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E160" s="17"/>
       <x:c r="F160" s="17"/>
@@ -6579,16 +6555,16 @@
     </x:row>
     <x:row r="161" ht="30" customHeight="1">
       <x:c r="A161" s="20" t="s">
-        <x:v>398</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B161" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C161" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D161" s="11" t="s">
-        <x:v>399</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="E161" s="17"/>
       <x:c r="F161" s="17"/>
@@ -6601,16 +6577,16 @@
     </x:row>
     <x:row r="162" ht="30" customHeight="1">
       <x:c r="A162" s="20" t="s">
-        <x:v>400</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B162" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C162" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D162" s="11" t="s">
-        <x:v>401</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="E162" s="17"/>
       <x:c r="F162" s="17"/>
@@ -6623,16 +6599,16 @@
     </x:row>
     <x:row r="163" ht="30" customHeight="1">
       <x:c r="A163" s="20" t="s">
-        <x:v>402</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B163" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C163" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D163" s="11" t="s">
-        <x:v>403</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E163" s="17"/>
       <x:c r="F163" s="17"/>
@@ -6645,16 +6621,16 @@
     </x:row>
     <x:row r="164" ht="30" customHeight="1">
       <x:c r="A164" s="20" t="s">
-        <x:v>404</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B164" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C164" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D164" s="11" t="s">
-        <x:v>405</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="E164" s="17"/>
       <x:c r="F164" s="17"/>
@@ -6667,16 +6643,16 @@
     </x:row>
     <x:row r="165" ht="30" customHeight="1">
       <x:c r="A165" s="20" t="s">
-        <x:v>406</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B165" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C165" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D165" s="11" t="s">
-        <x:v>407</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E165" s="17"/>
       <x:c r="F165" s="17"/>
@@ -6689,16 +6665,16 @@
     </x:row>
     <x:row r="166" ht="30" customHeight="1">
       <x:c r="A166" s="20" t="s">
-        <x:v>408</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B166" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C166" s="8" t="s">
-        <x:v>384</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D166" s="11" t="s">
-        <x:v>409</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E166" s="17"/>
       <x:c r="F166" s="17"/>
@@ -6711,16 +6687,16 @@
     </x:row>
     <x:row r="167" ht="30" customHeight="1">
       <x:c r="A167" s="20" t="s">
-        <x:v>410</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B167" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C167" s="8" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="D167" s="11" t="s">
-        <x:v>412</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E167" s="17"/>
       <x:c r="F167" s="17"/>
@@ -6733,16 +6709,16 @@
     </x:row>
     <x:row r="168" ht="30" customHeight="1">
       <x:c r="A168" s="20" t="s">
-        <x:v>413</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B168" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C168" s="8" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="D168" s="11" t="s">
-        <x:v>414</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="E168" s="17"/>
       <x:c r="F168" s="17"/>
@@ -6755,16 +6731,16 @@
     </x:row>
     <x:row r="169" ht="30" customHeight="1">
       <x:c r="A169" s="20" t="s">
-        <x:v>415</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B169" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C169" s="8" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="D169" s="11" t="s">
-        <x:v>416</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="E169" s="17"/>
       <x:c r="F169" s="17"/>
@@ -6777,16 +6753,16 @@
     </x:row>
     <x:row r="170" ht="30" customHeight="1">
       <x:c r="A170" s="20" t="s">
-        <x:v>417</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B170" s="14" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="C170" s="8" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="D170" s="11" t="s">
         <x:v>411</x:v>
-      </x:c>
-      <x:c r="C170" s="8" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="D170" s="11" t="s">
-        <x:v>419</x:v>
       </x:c>
       <x:c r="E170" s="17"/>
       <x:c r="F170" s="17"/>
@@ -6799,16 +6775,16 @@
     </x:row>
     <x:row r="171" ht="30" customHeight="1">
       <x:c r="A171" s="20" t="s">
-        <x:v>420</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B171" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C171" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D171" s="11" t="s">
-        <x:v>421</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E171" s="17"/>
       <x:c r="F171" s="17"/>
@@ -6821,16 +6797,16 @@
     </x:row>
     <x:row r="172" ht="30" customHeight="1">
       <x:c r="A172" s="20" t="s">
-        <x:v>422</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B172" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C172" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D172" s="11" t="s">
-        <x:v>423</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="E172" s="17"/>
       <x:c r="F172" s="17"/>
@@ -6843,16 +6819,16 @@
     </x:row>
     <x:row r="173" ht="30" customHeight="1">
       <x:c r="A173" s="20" t="s">
-        <x:v>424</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B173" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C173" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D173" s="11" t="s">
-        <x:v>425</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="E173" s="17"/>
       <x:c r="F173" s="17"/>
@@ -6865,16 +6841,16 @@
     </x:row>
     <x:row r="174" ht="30" customHeight="1">
       <x:c r="A174" s="20" t="s">
-        <x:v>426</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B174" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C174" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D174" s="11" t="s">
-        <x:v>427</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E174" s="17"/>
       <x:c r="F174" s="17"/>
@@ -6887,16 +6863,16 @@
     </x:row>
     <x:row r="175" ht="30" customHeight="1">
       <x:c r="A175" s="20" t="s">
-        <x:v>428</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B175" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C175" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D175" s="11" t="s">
-        <x:v>429</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="E175" s="17"/>
       <x:c r="F175" s="17"/>
@@ -6909,16 +6885,16 @@
     </x:row>
     <x:row r="176" ht="30" customHeight="1">
       <x:c r="A176" s="20" t="s">
-        <x:v>430</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B176" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C176" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D176" s="11" t="s">
-        <x:v>431</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="E176" s="17"/>
       <x:c r="F176" s="17"/>
@@ -6931,16 +6907,16 @@
     </x:row>
     <x:row r="177" ht="30" customHeight="1">
       <x:c r="A177" s="20" t="s">
-        <x:v>432</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B177" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C177" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D177" s="11" t="s">
-        <x:v>433</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="E177" s="17"/>
       <x:c r="F177" s="17"/>
@@ -6953,16 +6929,16 @@
     </x:row>
     <x:row r="178" ht="30" customHeight="1">
       <x:c r="A178" s="20" t="s">
-        <x:v>434</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B178" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C178" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D178" s="11" t="s">
-        <x:v>435</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E178" s="17"/>
       <x:c r="F178" s="17"/>
@@ -6975,16 +6951,16 @@
     </x:row>
     <x:row r="179" ht="30" customHeight="1">
       <x:c r="A179" s="20" t="s">
-        <x:v>436</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B179" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C179" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D179" s="11" t="s">
-        <x:v>437</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="E179" s="17"/>
       <x:c r="F179" s="17"/>
@@ -6997,13 +6973,13 @@
     </x:row>
     <x:row r="180" ht="30" customHeight="1">
       <x:c r="A180" s="20" t="s">
-        <x:v>438</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B180" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C180" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D180" s="11" t="s">
         <x:v>84</x:v>
@@ -7019,16 +6995,16 @@
     </x:row>
     <x:row r="181" ht="30" customHeight="1">
       <x:c r="A181" s="20" t="s">
-        <x:v>439</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B181" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C181" s="8" t="s">
-        <x:v>418</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="D181" s="11" t="s">
-        <x:v>440</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E181" s="17"/>
       <x:c r="F181" s="17"/>
@@ -7041,16 +7017,16 @@
     </x:row>
     <x:row r="182" ht="30" customHeight="1">
       <x:c r="A182" s="20" t="s">
-        <x:v>441</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B182" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C182" s="8" t="s">
-        <x:v>442</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D182" s="11" t="s">
-        <x:v>443</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E182" s="17"/>
       <x:c r="F182" s="17"/>
@@ -7063,16 +7039,16 @@
     </x:row>
     <x:row r="183" ht="30" customHeight="1">
       <x:c r="A183" s="20" t="s">
-        <x:v>444</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B183" s="14" t="s">
-        <x:v>411</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C183" s="8" t="s">
-        <x:v>445</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="D183" s="11" t="s">
-        <x:v>446</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E183" s="17"/>
       <x:c r="F183" s="17"/>
@@ -7085,7 +7061,7 @@
     </x:row>
     <x:row r="184" ht="30" customHeight="1">
       <x:c r="A184" s="20" t="s">
-        <x:v>447</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B184" s="14" t="s">
         <x:v>54</x:v>
@@ -7094,7 +7070,7 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="D184" s="11" t="s">
-        <x:v>448</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="E184" s="17"/>
       <x:c r="F184" s="17"/>
@@ -7107,7 +7083,7 @@
     </x:row>
     <x:row r="185" ht="30" customHeight="1">
       <x:c r="A185" s="20" t="s">
-        <x:v>449</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B185" s="14" t="s">
         <x:v>54</x:v>
@@ -7116,7 +7092,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="D185" s="11" t="s">
-        <x:v>450</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="E185" s="17"/>
       <x:c r="F185" s="17"/>
@@ -7129,7 +7105,7 @@
     </x:row>
     <x:row r="186" ht="30" customHeight="1">
       <x:c r="A186" s="20" t="s">
-        <x:v>451</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B186" s="14" t="s">
         <x:v>54</x:v>
@@ -7138,7 +7114,7 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="D186" s="11" t="s">
-        <x:v>452</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="E186" s="17"/>
       <x:c r="F186" s="17"/>
@@ -7151,16 +7127,16 @@
     </x:row>
     <x:row r="187" ht="30" customHeight="1">
       <x:c r="A187" s="20" t="s">
-        <x:v>453</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B187" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C187" s="8" t="s">
-        <x:v>454</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="D187" s="11" t="s">
-        <x:v>455</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="E187" s="17"/>
       <x:c r="F187" s="17"/>
@@ -7173,16 +7149,16 @@
     </x:row>
     <x:row r="188" ht="30" customHeight="1">
       <x:c r="A188" s="20" t="s">
-        <x:v>456</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B188" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C188" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D188" s="11" t="s">
-        <x:v>458</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="E188" s="17"/>
       <x:c r="F188" s="17"/>
@@ -7195,16 +7171,16 @@
     </x:row>
     <x:row r="189" ht="30" customHeight="1">
       <x:c r="A189" s="20" t="s">
-        <x:v>459</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B189" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C189" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D189" s="11" t="s">
-        <x:v>460</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="E189" s="17"/>
       <x:c r="F189" s="17"/>
@@ -7217,16 +7193,16 @@
     </x:row>
     <x:row r="190" ht="30" customHeight="1">
       <x:c r="A190" s="20" t="s">
-        <x:v>461</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B190" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C190" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D190" s="11" t="s">
-        <x:v>462</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E190" s="17"/>
       <x:c r="F190" s="17"/>
@@ -7239,16 +7215,16 @@
     </x:row>
     <x:row r="191" ht="30" customHeight="1">
       <x:c r="A191" s="20" t="s">
-        <x:v>463</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B191" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C191" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D191" s="11" t="s">
-        <x:v>464</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E191" s="17"/>
       <x:c r="F191" s="17"/>
@@ -7261,16 +7237,16 @@
     </x:row>
     <x:row r="192" ht="30" customHeight="1">
       <x:c r="A192" s="20" t="s">
-        <x:v>465</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B192" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C192" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D192" s="11" t="s">
-        <x:v>466</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="E192" s="17"/>
       <x:c r="F192" s="17"/>
@@ -7283,16 +7259,16 @@
     </x:row>
     <x:row r="193" ht="30" customHeight="1">
       <x:c r="A193" s="20" t="s">
-        <x:v>467</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B193" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C193" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D193" s="11" t="s">
-        <x:v>468</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="E193" s="17"/>
       <x:c r="F193" s="17"/>
@@ -7305,16 +7281,16 @@
     </x:row>
     <x:row r="194" ht="30" customHeight="1">
       <x:c r="A194" s="20" t="s">
-        <x:v>469</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B194" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C194" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D194" s="11" t="s">
-        <x:v>470</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E194" s="17"/>
       <x:c r="F194" s="17"/>
@@ -7327,16 +7303,16 @@
     </x:row>
     <x:row r="195" ht="30" customHeight="1">
       <x:c r="A195" s="20" t="s">
-        <x:v>471</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B195" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C195" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D195" s="11" t="s">
-        <x:v>472</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="E195" s="17"/>
       <x:c r="F195" s="17"/>
@@ -7349,16 +7325,16 @@
     </x:row>
     <x:row r="196" ht="30" customHeight="1">
       <x:c r="A196" s="20" t="s">
-        <x:v>473</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B196" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C196" s="8" t="s">
-        <x:v>457</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D196" s="11" t="s">
-        <x:v>474</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E196" s="17"/>
       <x:c r="F196" s="17"/>
@@ -7371,16 +7347,16 @@
     </x:row>
     <x:row r="197" ht="30" customHeight="1">
       <x:c r="A197" s="20" t="s">
-        <x:v>475</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B197" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C197" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D197" s="11" t="s">
-        <x:v>477</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E197" s="17"/>
       <x:c r="F197" s="17"/>
@@ -7393,16 +7369,16 @@
     </x:row>
     <x:row r="198" ht="30" customHeight="1">
       <x:c r="A198" s="20" t="s">
-        <x:v>478</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B198" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C198" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D198" s="11" t="s">
-        <x:v>479</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="E198" s="17"/>
       <x:c r="F198" s="17"/>
@@ -7415,13 +7391,13 @@
     </x:row>
     <x:row r="199" ht="30" customHeight="1">
       <x:c r="A199" s="20" t="s">
-        <x:v>480</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B199" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C199" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D199" s="11"/>
       <x:c r="E199" s="17"/>
@@ -7435,16 +7411,16 @@
     </x:row>
     <x:row r="200" ht="30" customHeight="1">
       <x:c r="A200" s="20" t="s">
-        <x:v>481</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B200" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C200" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D200" s="11" t="s">
-        <x:v>482</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="E200" s="17"/>
       <x:c r="F200" s="17"/>
@@ -7457,13 +7433,13 @@
     </x:row>
     <x:row r="201" ht="30" customHeight="1">
       <x:c r="A201" s="20" t="s">
-        <x:v>483</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B201" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C201" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D201" s="11" t="str">
         <x:v>Проверка работоспособности всей системы</x:v>
@@ -7479,13 +7455,13 @@
     </x:row>
     <x:row r="202" ht="30" customHeight="1">
       <x:c r="A202" s="20" t="s">
-        <x:v>484</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B202" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C202" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D202" s="11" t="str">
         <x:v>Корректировка и улучшение промптов для ИИ</x:v>
@@ -7501,13 +7477,13 @@
     </x:row>
     <x:row r="203" ht="30" customHeight="1">
       <x:c r="A203" s="20" t="s">
-        <x:v>485</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B203" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C203" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D203" s="11" t="str">
         <x:v>Исправление накопительных ошибок в работе ИИ</x:v>
@@ -7523,13 +7499,13 @@
     </x:row>
     <x:row r="204" ht="30" customHeight="1">
       <x:c r="A204" s="20" t="s">
-        <x:v>486</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B204" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C204" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D204" s="11" t="str">
         <x:v>Устранение повторяющихся неточностей в распознавании и структурировании данных</x:v>
@@ -7545,13 +7521,13 @@
     </x:row>
     <x:row r="205" ht="30" customHeight="1">
       <x:c r="A205" s="20" t="s">
-        <x:v>487</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B205" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C205" s="8" t="s">
-        <x:v>476</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D205" s="11" t="str">
         <x:v>Проверка работоспособности всех подключённых интеграций</x:v>
@@ -7567,16 +7543,16 @@
     </x:row>
     <x:row r="206" ht="30" customHeight="1">
       <x:c r="A206" s="20" t="s">
-        <x:v>488</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B206" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C206" s="8" t="s">
-        <x:v>489</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D206" s="11" t="s">
-        <x:v>490</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="E206" s="17"/>
       <x:c r="F206" s="17"/>
@@ -7589,16 +7565,16 @@
     </x:row>
     <x:row r="207" ht="30" customHeight="1">
       <x:c r="A207" s="20" t="s">
-        <x:v>491</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B207" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C207" s="8" t="s">
-        <x:v>492</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="D207" s="11" t="s">
-        <x:v>493</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E207" s="17"/>
       <x:c r="F207" s="17"/>
@@ -7611,16 +7587,16 @@
     </x:row>
     <x:row r="208" ht="30" customHeight="1">
       <x:c r="A208" s="20" t="s">
-        <x:v>494</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B208" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C208" s="8" t="s">
-        <x:v>495</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="D208" s="11" t="s">
-        <x:v>496</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E208" s="17"/>
       <x:c r="F208" s="17"/>
@@ -7633,16 +7609,16 @@
     </x:row>
     <x:row r="209" ht="30" customHeight="1">
       <x:c r="A209" s="20" t="s">
-        <x:v>497</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B209" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C209" s="8" t="s">
-        <x:v>495</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="D209" s="11" t="s">
-        <x:v>498</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="E209" s="17"/>
       <x:c r="F209" s="17"/>
@@ -7655,16 +7631,16 @@
     </x:row>
     <x:row r="210" ht="30" customHeight="1">
       <x:c r="A210" s="20" t="s">
-        <x:v>499</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B210" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C210" s="8" t="s">
-        <x:v>495</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="D210" s="11" t="s">
-        <x:v>500</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E210" s="17"/>
       <x:c r="F210" s="17"/>
@@ -7677,16 +7653,16 @@
     </x:row>
     <x:row r="211" ht="30" customHeight="1">
       <x:c r="A211" s="20" t="s">
-        <x:v>501</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B211" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C211" s="8" t="s">
-        <x:v>502</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="D211" s="11" t="s">
-        <x:v>503</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E211" s="17"/>
       <x:c r="F211" s="17"/>
@@ -7699,16 +7675,16 @@
     </x:row>
     <x:row r="212" ht="30" customHeight="1">
       <x:c r="A212" s="20" t="s">
-        <x:v>504</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B212" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C212" s="8" t="s">
-        <x:v>502</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="D212" s="11" t="s">
-        <x:v>505</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="E212" s="17"/>
       <x:c r="F212" s="17"/>
@@ -7721,16 +7697,16 @@
     </x:row>
     <x:row r="213" ht="30" customHeight="1">
       <x:c r="A213" s="20" t="s">
-        <x:v>506</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B213" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C213" s="8" t="s">
-        <x:v>502</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="D213" s="11" t="s">
-        <x:v>507</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E213" s="17"/>
       <x:c r="F213" s="17"/>
@@ -7743,16 +7719,16 @@
     </x:row>
     <x:row r="214" ht="30" customHeight="1">
       <x:c r="A214" s="20" t="s">
-        <x:v>508</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B214" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C214" s="8" t="s">
-        <x:v>502</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="D214" s="11" t="s">
-        <x:v>509</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="E214" s="17"/>
       <x:c r="F214" s="17"/>
@@ -7765,16 +7741,16 @@
     </x:row>
     <x:row r="215" ht="30" customHeight="1">
       <x:c r="A215" s="20" t="s">
-        <x:v>510</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B215" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C215" s="8" t="s">
-        <x:v>511</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D215" s="11" t="s">
-        <x:v>512</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="E215" s="17"/>
       <x:c r="F215" s="17"/>
@@ -7787,16 +7763,16 @@
     </x:row>
     <x:row r="216" ht="30" customHeight="1">
       <x:c r="A216" s="20" t="s">
-        <x:v>513</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B216" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C216" s="8" t="s">
-        <x:v>514</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="D216" s="11" t="s">
-        <x:v>515</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="E216" s="17"/>
       <x:c r="F216" s="17"/>
@@ -7809,16 +7785,16 @@
     </x:row>
     <x:row r="217" ht="30" customHeight="1">
       <x:c r="A217" s="20" t="s">
-        <x:v>516</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B217" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C217" s="8" t="s">
-        <x:v>517</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="D217" s="11" t="s">
-        <x:v>518</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="E217" s="17"/>
       <x:c r="F217" s="17"/>
@@ -7831,16 +7807,16 @@
     </x:row>
     <x:row r="218" ht="30" customHeight="1">
       <x:c r="A218" s="20" t="s">
-        <x:v>519</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B218" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C218" s="8" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="D218" s="11" t="s">
-        <x:v>521</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="E218" s="17"/>
       <x:c r="F218" s="17"/>
@@ -7853,16 +7829,16 @@
     </x:row>
     <x:row r="219" ht="30" customHeight="1">
       <x:c r="A219" s="20" t="s">
-        <x:v>522</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B219" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C219" s="8" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="D219" s="11" t="s">
-        <x:v>523</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="E219" s="17"/>
       <x:c r="F219" s="17"/>
@@ -7875,16 +7851,16 @@
     </x:row>
     <x:row r="220" ht="30" customHeight="1">
       <x:c r="A220" s="20" t="s">
-        <x:v>524</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B220" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C220" s="8" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="D220" s="11" t="s">
-        <x:v>525</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="E220" s="17"/>
       <x:c r="F220" s="17"/>
@@ -7897,16 +7873,16 @@
     </x:row>
     <x:row r="221" ht="30" customHeight="1">
       <x:c r="A221" s="20" t="s">
-        <x:v>526</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B221" s="14" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="C221" s="8" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="D221" s="11" t="s">
         <x:v>520</x:v>
-      </x:c>
-      <x:c r="C221" s="8" t="s">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="D221" s="11" t="s">
-        <x:v>528</x:v>
       </x:c>
       <x:c r="E221" s="17"/>
       <x:c r="F221" s="17"/>
@@ -7919,16 +7895,16 @@
     </x:row>
     <x:row r="222" ht="30" customHeight="1">
       <x:c r="A222" s="20" t="s">
-        <x:v>529</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B222" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C222" s="8" t="s">
-        <x:v>527</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D222" s="11" t="s">
-        <x:v>530</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="E222" s="17"/>
       <x:c r="F222" s="17"/>
@@ -7941,16 +7917,16 @@
     </x:row>
     <x:row r="223" ht="30" customHeight="1">
       <x:c r="A223" s="20" t="s">
-        <x:v>531</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B223" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C223" s="8" t="s">
-        <x:v>527</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="D223" s="11" t="s">
-        <x:v>532</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E223" s="17"/>
       <x:c r="F223" s="17"/>
@@ -7963,16 +7939,16 @@
     </x:row>
     <x:row r="224" ht="30" customHeight="1">
       <x:c r="A224" s="20" t="s">
-        <x:v>533</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B224" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C224" s="8" t="s">
-        <x:v>534</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="D224" s="11" t="s">
-        <x:v>535</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="E224" s="17"/>
       <x:c r="F224" s="17"/>
@@ -7985,16 +7961,16 @@
     </x:row>
     <x:row r="225" ht="30" customHeight="1">
       <x:c r="A225" s="20" t="s">
-        <x:v>536</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B225" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C225" s="8" t="s">
-        <x:v>537</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="D225" s="11" t="s">
-        <x:v>538</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="E225" s="17"/>
       <x:c r="F225" s="17"/>
@@ -8007,16 +7983,16 @@
     </x:row>
     <x:row r="226" ht="30" customHeight="1">
       <x:c r="A226" s="20" t="s">
-        <x:v>539</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B226" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C226" s="8" t="s">
-        <x:v>540</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="D226" s="11" t="s">
-        <x:v>541</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="E226" s="17"/>
       <x:c r="F226" s="17"/>
@@ -8029,16 +8005,16 @@
     </x:row>
     <x:row r="227" ht="30" customHeight="1">
       <x:c r="A227" s="20" t="s">
-        <x:v>542</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B227" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C227" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D227" s="11" t="s">
-        <x:v>544</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="E227" s="17"/>
       <x:c r="F227" s="17"/>
@@ -8051,16 +8027,16 @@
     </x:row>
     <x:row r="228" ht="30" customHeight="1">
       <x:c r="A228" s="20" t="s">
-        <x:v>545</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B228" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C228" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D228" s="11" t="s">
-        <x:v>546</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E228" s="17"/>
       <x:c r="F228" s="17"/>
@@ -8073,16 +8049,16 @@
     </x:row>
     <x:row r="229" ht="30" customHeight="1">
       <x:c r="A229" s="20" t="s">
-        <x:v>547</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B229" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C229" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D229" s="11" t="s">
-        <x:v>548</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="E229" s="17"/>
       <x:c r="F229" s="17"/>
@@ -8095,16 +8071,16 @@
     </x:row>
     <x:row r="230" ht="30" customHeight="1">
       <x:c r="A230" s="20" t="s">
-        <x:v>549</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B230" s="14" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="C230" s="8" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="D230" s="11" t="s">
         <x:v>520</x:v>
-      </x:c>
-      <x:c r="C230" s="8" t="s">
-        <x:v>543</x:v>
-      </x:c>
-      <x:c r="D230" s="11" t="s">
-        <x:v>528</x:v>
       </x:c>
       <x:c r="E230" s="17"/>
       <x:c r="F230" s="17"/>
@@ -8117,16 +8093,16 @@
     </x:row>
     <x:row r="231" ht="30" customHeight="1">
       <x:c r="A231" s="20" t="s">
-        <x:v>550</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B231" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C231" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D231" s="11" t="s">
-        <x:v>530</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="E231" s="17"/>
       <x:c r="F231" s="17"/>
@@ -8139,16 +8115,16 @@
     </x:row>
     <x:row r="232" ht="30" customHeight="1">
       <x:c r="A232" s="20" t="s">
-        <x:v>551</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B232" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C232" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D232" s="11" t="s">
-        <x:v>552</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="E232" s="17"/>
       <x:c r="F232" s="17"/>
@@ -8161,16 +8137,16 @@
     </x:row>
     <x:row r="233" ht="30" customHeight="1">
       <x:c r="A233" s="20" t="s">
-        <x:v>553</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B233" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C233" s="8" t="s">
-        <x:v>554</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="D233" s="11" t="s">
-        <x:v>555</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="E233" s="17"/>
       <x:c r="F233" s="17"/>
@@ -8183,16 +8159,16 @@
     </x:row>
     <x:row r="234" ht="30" customHeight="1">
       <x:c r="A234" s="20" t="s">
-        <x:v>556</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B234" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C234" s="8" t="s">
-        <x:v>554</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="D234" s="11" t="s">
-        <x:v>557</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="E234" s="17"/>
       <x:c r="F234" s="17"/>
@@ -8205,16 +8181,16 @@
     </x:row>
     <x:row r="235" ht="30" customHeight="1">
       <x:c r="A235" s="20" t="s">
-        <x:v>558</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B235" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C235" s="8" t="s">
-        <x:v>554</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="D235" s="11" t="s">
-        <x:v>559</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="E235" s="17"/>
       <x:c r="F235" s="17"/>
@@ -8227,16 +8203,16 @@
     </x:row>
     <x:row r="236" ht="30" customHeight="1">
       <x:c r="A236" s="20" t="s">
-        <x:v>560</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B236" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C236" s="8" t="s">
-        <x:v>554</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="D236" s="11" t="s">
-        <x:v>561</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="E236" s="17"/>
       <x:c r="F236" s="17"/>
@@ -8249,16 +8225,16 @@
     </x:row>
     <x:row r="237" ht="30" customHeight="1">
       <x:c r="A237" s="20" t="s">
-        <x:v>562</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B237" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C237" s="8" t="s">
-        <x:v>554</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="D237" s="11" t="s">
-        <x:v>563</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="E237" s="17"/>
       <x:c r="F237" s="17"/>
@@ -8271,16 +8247,16 @@
     </x:row>
     <x:row r="238" ht="30" customHeight="1">
       <x:c r="A238" s="20" t="s">
-        <x:v>564</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B238" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C238" s="8" t="s">
-        <x:v>554</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="D238" s="11" t="s">
-        <x:v>565</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="E238" s="17"/>
       <x:c r="F238" s="17"/>
@@ -8293,16 +8269,16 @@
     </x:row>
     <x:row r="239" ht="30" customHeight="1">
       <x:c r="A239" s="20" t="s">
-        <x:v>566</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B239" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C239" s="8" t="s">
-        <x:v>567</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="D239" s="11" t="s">
-        <x:v>568</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="E239" s="17"/>
       <x:c r="F239" s="17"/>
@@ -8315,16 +8291,16 @@
     </x:row>
     <x:row r="240" ht="30" customHeight="1">
       <x:c r="A240" s="20" t="s">
-        <x:v>569</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B240" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C240" s="8" t="s">
-        <x:v>570</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="D240" s="11" t="s">
-        <x:v>571</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="E240" s="17"/>
       <x:c r="F240" s="17"/>
@@ -8337,16 +8313,16 @@
     </x:row>
     <x:row r="241" ht="30" customHeight="1">
       <x:c r="A241" s="20" t="s">
-        <x:v>572</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B241" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C241" s="8" t="s">
-        <x:v>570</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="D241" s="11" t="s">
-        <x:v>573</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="E241" s="17"/>
       <x:c r="F241" s="17"/>
@@ -8359,16 +8335,16 @@
     </x:row>
     <x:row r="242" ht="30" customHeight="1">
       <x:c r="A242" s="20" t="s">
-        <x:v>574</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B242" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C242" s="8" t="s">
-        <x:v>570</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="D242" s="11" t="s">
-        <x:v>575</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="E242" s="17"/>
       <x:c r="F242" s="17"/>
@@ -8381,16 +8357,16 @@
     </x:row>
     <x:row r="243" ht="30" customHeight="1">
       <x:c r="A243" s="20" t="s">
-        <x:v>576</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B243" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C243" s="8" t="s">
-        <x:v>570</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="D243" s="11" t="s">
-        <x:v>577</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="E243" s="17"/>
       <x:c r="F243" s="17"/>
@@ -8403,16 +8379,16 @@
     </x:row>
     <x:row r="244" ht="30" customHeight="1">
       <x:c r="A244" s="20" t="s">
-        <x:v>578</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B244" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C244" s="8" t="s">
-        <x:v>570</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="D244" s="11" t="s">
-        <x:v>579</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="E244" s="17"/>
       <x:c r="F244" s="17"/>
@@ -8425,16 +8401,16 @@
     </x:row>
     <x:row r="245" ht="30" customHeight="1">
       <x:c r="A245" s="20" t="s">
-        <x:v>580</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B245" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C245" s="8" t="s">
-        <x:v>570</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="D245" s="11" t="s">
-        <x:v>581</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="E245" s="17"/>
       <x:c r="F245" s="17"/>
@@ -8447,16 +8423,16 @@
     </x:row>
     <x:row r="246" ht="30" customHeight="1">
       <x:c r="A246" s="20" t="s">
-        <x:v>582</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B246" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C246" s="8" t="s">
-        <x:v>570</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="D246" s="11" t="s">
-        <x:v>583</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="E246" s="17"/>
       <x:c r="F246" s="17"/>
@@ -8469,16 +8445,16 @@
     </x:row>
     <x:row r="247" ht="30" customHeight="1">
       <x:c r="A247" s="20" t="s">
-        <x:v>584</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B247" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C247" s="8" t="s">
-        <x:v>585</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="D247" s="11" t="s">
-        <x:v>586</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="E247" s="17"/>
       <x:c r="F247" s="17"/>
@@ -8491,16 +8467,16 @@
     </x:row>
     <x:row r="248" ht="30" customHeight="1">
       <x:c r="A248" s="20" t="s">
-        <x:v>587</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B248" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C248" s="8" t="s">
-        <x:v>588</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="D248" s="11" t="s">
-        <x:v>589</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="E248" s="17"/>
       <x:c r="F248" s="17"/>
@@ -8513,16 +8489,16 @@
     </x:row>
     <x:row r="249" ht="30" customHeight="1">
       <x:c r="A249" s="20" t="s">
-        <x:v>590</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B249" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C249" s="8" t="s">
-        <x:v>591</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="D249" s="11" t="s">
-        <x:v>592</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="E249" s="17"/>
       <x:c r="F249" s="17"/>
@@ -8535,16 +8511,16 @@
     </x:row>
     <x:row r="250" ht="30" customHeight="1">
       <x:c r="A250" s="20" t="s">
-        <x:v>593</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B250" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C250" s="8" t="s">
-        <x:v>594</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="D250" s="11" t="s">
-        <x:v>595</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="E250" s="17"/>
       <x:c r="F250" s="17"/>
@@ -8557,16 +8533,16 @@
     </x:row>
     <x:row r="251" ht="30" customHeight="1">
       <x:c r="A251" s="20" t="s">
-        <x:v>596</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B251" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C251" s="8" t="s">
-        <x:v>597</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D251" s="11" t="s">
-        <x:v>598</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E251" s="17"/>
       <x:c r="F251" s="17"/>
@@ -8579,16 +8555,16 @@
     </x:row>
     <x:row r="252" ht="30" customHeight="1">
       <x:c r="A252" s="20" t="s">
-        <x:v>599</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B252" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C252" s="8" t="s">
-        <x:v>600</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D252" s="11" t="s">
-        <x:v>601</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E252" s="17"/>
       <x:c r="F252" s="17"/>
@@ -8601,16 +8577,16 @@
     </x:row>
     <x:row r="253" ht="30" customHeight="1">
       <x:c r="A253" s="20" t="s">
-        <x:v>602</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B253" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C253" s="8" t="s">
-        <x:v>603</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="D253" s="11" t="s">
-        <x:v>604</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="E253" s="17"/>
       <x:c r="F253" s="17"/>
@@ -8623,16 +8599,16 @@
     </x:row>
     <x:row r="254" ht="30" customHeight="1">
       <x:c r="A254" s="20" t="s">
-        <x:v>605</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B254" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C254" s="8" t="s">
-        <x:v>606</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="D254" s="11" t="s">
-        <x:v>607</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="E254" s="17"/>
       <x:c r="F254" s="17"/>
@@ -8645,16 +8621,16 @@
     </x:row>
     <x:row r="255" ht="30" customHeight="1">
       <x:c r="A255" s="20" t="s">
-        <x:v>608</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B255" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C255" s="8" t="s">
-        <x:v>609</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="D255" s="11" t="s">
-        <x:v>610</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="E255" s="17"/>
       <x:c r="F255" s="17"/>
@@ -8667,16 +8643,16 @@
     </x:row>
     <x:row r="256" ht="30" customHeight="1">
       <x:c r="A256" s="20" t="s">
-        <x:v>611</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B256" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C256" s="8" t="s">
-        <x:v>612</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="D256" s="11" t="s">
-        <x:v>613</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="E256" s="17"/>
       <x:c r="F256" s="17"/>
@@ -8689,16 +8665,16 @@
     </x:row>
     <x:row r="257" ht="30" customHeight="1">
       <x:c r="A257" s="20" t="s">
-        <x:v>614</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B257" s="14" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C257" s="8" t="s">
-        <x:v>615</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="D257" s="11" t="s">
-        <x:v>616</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="E257" s="17"/>
       <x:c r="F257" s="17"/>
@@ -8711,16 +8687,16 @@
     </x:row>
     <x:row r="258" ht="30" customHeight="1">
       <x:c r="A258" s="20" t="s">
-        <x:v>617</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B258" s="14" t="s">
-        <x:v>618</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="C258" s="8" t="s">
-        <x:v>619</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D258" s="11" t="s">
-        <x:v>620</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="E258" s="17"/>
       <x:c r="F258" s="17"/>
@@ -8733,16 +8709,16 @@
     </x:row>
     <x:row r="259" ht="30" customHeight="1">
       <x:c r="A259" s="20" t="s">
-        <x:v>621</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B259" s="14" t="s">
-        <x:v>618</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="C259" s="8" t="s">
-        <x:v>622</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D259" s="11" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="E259" s="17"/>
       <x:c r="F259" s="17"/>
@@ -8755,16 +8731,16 @@
     </x:row>
     <x:row r="260" ht="30" customHeight="1">
       <x:c r="A260" s="20" t="s">
-        <x:v>623</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="B260" s="14" t="s">
-        <x:v>618</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="C260" s="8" t="s">
-        <x:v>622</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D260" s="11" t="s">
-        <x:v>530</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="E260" s="17"/>
       <x:c r="F260" s="17"/>
@@ -8777,16 +8753,16 @@
     </x:row>
     <x:row r="261" ht="30" customHeight="1">
       <x:c r="A261" s="20" t="s">
-        <x:v>624</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="B261" s="14" t="s">
-        <x:v>618</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="C261" s="8" t="s">
-        <x:v>622</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D261" s="11" t="s">
-        <x:v>532</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E261" s="17"/>
       <x:c r="F261" s="17"/>
@@ -8799,16 +8775,16 @@
     </x:row>
     <x:row r="262" ht="30" customHeight="1">
       <x:c r="A262" s="20" t="s">
-        <x:v>625</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="B262" s="14" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="C262" s="8" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="D262" s="11" t="s">
         <x:v>618</x:v>
-      </x:c>
-      <x:c r="C262" s="8" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="D262" s="11" t="s">
-        <x:v>626</x:v>
       </x:c>
       <x:c r="E262" s="17"/>
       <x:c r="F262" s="17"/>
@@ -8821,16 +8797,16 @@
     </x:row>
     <x:row r="263" ht="30" customHeight="1">
       <x:c r="A263" s="20" t="s">
-        <x:v>627</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="B263" s="14" t="s">
-        <x:v>618</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="C263" s="8" t="s">
-        <x:v>628</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="D263" s="11" t="s">
-        <x:v>629</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="E263" s="17"/>
       <x:c r="F263" s="17"/>
@@ -8843,16 +8819,16 @@
     </x:row>
     <x:row r="264" ht="30" customHeight="1">
       <x:c r="A264" s="20" t="s">
-        <x:v>630</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="B264" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C264" s="8" t="s">
-        <x:v>632</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="D264" s="11" t="s">
-        <x:v>589</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="E264" s="17"/>
       <x:c r="F264" s="17"/>
@@ -8865,16 +8841,16 @@
     </x:row>
     <x:row r="265" ht="30" customHeight="1">
       <x:c r="A265" s="20" t="s">
-        <x:v>633</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="B265" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C265" s="8" t="s">
-        <x:v>634</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="D265" s="11" t="s">
-        <x:v>635</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="E265" s="17"/>
       <x:c r="F265" s="17"/>
@@ -8887,16 +8863,16 @@
     </x:row>
     <x:row r="266" ht="30" customHeight="1">
       <x:c r="A266" s="20" t="s">
-        <x:v>636</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="B266" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C266" s="8" t="s">
-        <x:v>637</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="D266" s="11" t="s">
-        <x:v>638</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E266" s="17"/>
       <x:c r="F266" s="17"/>
@@ -8909,16 +8885,16 @@
     </x:row>
     <x:row r="267" ht="30" customHeight="1">
       <x:c r="A267" s="20" t="s">
-        <x:v>639</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="B267" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C267" s="8" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D267" s="11" t="s">
-        <x:v>589</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="E267" s="17"/>
       <x:c r="F267" s="17"/>
@@ -8931,16 +8907,16 @@
     </x:row>
     <x:row r="268" ht="30" customHeight="1">
       <x:c r="A268" s="20" t="s">
-        <x:v>640</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="B268" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C268" s="8" t="s">
-        <x:v>641</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="D268" s="11" t="s">
-        <x:v>642</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="E268" s="17"/>
       <x:c r="F268" s="17"/>
@@ -8953,16 +8929,16 @@
     </x:row>
     <x:row r="269" ht="30" customHeight="1">
       <x:c r="A269" s="20" t="s">
-        <x:v>643</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="B269" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C269" s="8" t="s">
-        <x:v>644</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="D269" s="11" t="s">
-        <x:v>645</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="E269" s="17"/>
       <x:c r="F269" s="17"/>
@@ -8975,16 +8951,16 @@
     </x:row>
     <x:row r="270" ht="30" customHeight="1">
       <x:c r="A270" s="20" t="s">
-        <x:v>646</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="B270" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C270" s="8" t="s">
-        <x:v>647</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="D270" s="11" t="s">
-        <x:v>648</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="E270" s="17"/>
       <x:c r="F270" s="17"/>
@@ -8997,16 +8973,16 @@
     </x:row>
     <x:row r="271" ht="30" customHeight="1">
       <x:c r="A271" s="20" t="s">
-        <x:v>649</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="B271" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C271" s="8" t="s">
-        <x:v>647</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="D271" s="11" t="s">
-        <x:v>650</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E271" s="17"/>
       <x:c r="F271" s="17"/>
@@ -9019,16 +8995,16 @@
     </x:row>
     <x:row r="272" ht="30" customHeight="1">
       <x:c r="A272" s="20" t="s">
-        <x:v>651</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="B272" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C272" s="8" t="s">
-        <x:v>652</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="D272" s="11" t="s">
-        <x:v>653</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="E272" s="17"/>
       <x:c r="F272" s="17"/>
@@ -9041,16 +9017,16 @@
     </x:row>
     <x:row r="273" ht="30" customHeight="1">
       <x:c r="A273" s="20" t="s">
-        <x:v>654</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="B273" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C273" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D273" s="11" t="s">
-        <x:v>656</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E273" s="17"/>
       <x:c r="F273" s="17"/>
@@ -9063,16 +9039,16 @@
     </x:row>
     <x:row r="274" ht="30" customHeight="1">
       <x:c r="A274" s="20" t="s">
-        <x:v>657</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="B274" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C274" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D274" s="11" t="s">
-        <x:v>658</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="E274" s="17"/>
       <x:c r="F274" s="17"/>
@@ -9085,16 +9061,16 @@
     </x:row>
     <x:row r="275" ht="30" customHeight="1">
       <x:c r="A275" s="20" t="s">
-        <x:v>659</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B275" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C275" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D275" s="11" t="s">
-        <x:v>660</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="E275" s="17"/>
       <x:c r="F275" s="17"/>
@@ -9107,16 +9083,16 @@
     </x:row>
     <x:row r="276" ht="30" customHeight="1">
       <x:c r="A276" s="20" t="s">
-        <x:v>661</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="B276" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C276" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D276" s="11" t="s">
-        <x:v>662</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="E276" s="17"/>
       <x:c r="F276" s="17"/>
@@ -9129,16 +9105,16 @@
     </x:row>
     <x:row r="277" ht="30" customHeight="1">
       <x:c r="A277" s="20" t="s">
-        <x:v>663</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="B277" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C277" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D277" s="11" t="s">
-        <x:v>664</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="E277" s="17"/>
       <x:c r="F277" s="17"/>
@@ -9151,16 +9127,16 @@
     </x:row>
     <x:row r="278" ht="30" customHeight="1">
       <x:c r="A278" s="20" t="s">
-        <x:v>665</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="B278" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C278" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D278" s="11" t="s">
-        <x:v>666</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="E278" s="17"/>
       <x:c r="F278" s="17"/>
@@ -9173,16 +9149,16 @@
     </x:row>
     <x:row r="279" ht="30" customHeight="1">
       <x:c r="A279" s="20" t="s">
-        <x:v>667</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="B279" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C279" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D279" s="11" t="s">
-        <x:v>668</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="E279" s="17"/>
       <x:c r="F279" s="17"/>
@@ -9195,16 +9171,16 @@
     </x:row>
     <x:row r="280" ht="30" customHeight="1">
       <x:c r="A280" s="20" t="s">
-        <x:v>669</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="B280" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C280" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D280" s="11" t="s">
-        <x:v>670</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="E280" s="17"/>
       <x:c r="F280" s="17"/>
@@ -9217,16 +9193,16 @@
     </x:row>
     <x:row r="281" ht="30" customHeight="1">
       <x:c r="A281" s="20" t="s">
-        <x:v>671</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="B281" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C281" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D281" s="11" t="s">
-        <x:v>672</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="E281" s="17"/>
       <x:c r="F281" s="17"/>
@@ -9239,16 +9215,16 @@
     </x:row>
     <x:row r="282" ht="30" customHeight="1">
       <x:c r="A282" s="20" t="s">
-        <x:v>673</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="B282" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C282" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D282" s="11" t="s">
-        <x:v>674</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="E282" s="17"/>
       <x:c r="F282" s="17"/>
@@ -9261,16 +9237,16 @@
     </x:row>
     <x:row r="283" ht="30" customHeight="1">
       <x:c r="A283" s="20" t="s">
-        <x:v>675</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="B283" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C283" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D283" s="11" t="s">
-        <x:v>676</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="E283" s="17"/>
       <x:c r="F283" s="17"/>
@@ -9283,16 +9259,16 @@
     </x:row>
     <x:row r="284" ht="30" customHeight="1">
       <x:c r="A284" s="20" t="s">
-        <x:v>677</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="B284" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C284" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D284" s="11" t="s">
-        <x:v>678</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="E284" s="17"/>
       <x:c r="F284" s="17"/>
@@ -9305,16 +9281,16 @@
     </x:row>
     <x:row r="285" ht="30" customHeight="1">
       <x:c r="A285" s="20" t="s">
-        <x:v>679</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="B285" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C285" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D285" s="11" t="s">
-        <x:v>680</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="E285" s="17"/>
       <x:c r="F285" s="17"/>
@@ -9327,16 +9303,16 @@
     </x:row>
     <x:row r="286" ht="30" customHeight="1">
       <x:c r="A286" s="20" t="s">
-        <x:v>681</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="B286" s="14" t="s">
-        <x:v>631</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C286" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D286" s="11" t="s">
-        <x:v>682</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="E286" s="17"/>
       <x:c r="F286" s="17"/>
@@ -9349,16 +9325,16 @@
     </x:row>
     <x:row r="287" ht="30" customHeight="1">
       <x:c r="A287" s="20" t="s">
-        <x:v>683</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B287" s="14" t="s">
-        <x:v>684</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C287" s="8" t="s">
-        <x:v>685</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="D287" s="11" t="s">
-        <x:v>686</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E287" s="17"/>
       <x:c r="F287" s="17"/>
@@ -9371,16 +9347,16 @@
     </x:row>
     <x:row r="288" ht="30" customHeight="1">
       <x:c r="A288" s="20" t="s">
-        <x:v>687</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="B288" s="14" t="s">
-        <x:v>684</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C288" s="8" t="s">
-        <x:v>688</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="D288" s="11" t="s">
-        <x:v>689</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E288" s="17"/>
       <x:c r="F288" s="17"/>
@@ -9393,16 +9369,16 @@
     </x:row>
     <x:row r="289" ht="30" customHeight="1">
       <x:c r="A289" s="20" t="s">
-        <x:v>690</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="B289" s="14" t="s">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="C289" s="8" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="D289" s="11" t="s">
         <x:v>684</x:v>
-      </x:c>
-      <x:c r="C289" s="8" t="s">
-        <x:v>691</x:v>
-      </x:c>
-      <x:c r="D289" s="11" t="s">
-        <x:v>692</x:v>
       </x:c>
       <x:c r="E289" s="17"/>
       <x:c r="F289" s="17"/>
@@ -9415,16 +9391,16 @@
     </x:row>
     <x:row r="290" ht="30" customHeight="1">
       <x:c r="A290" s="20" t="s">
-        <x:v>693</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="B290" s="14" t="s">
-        <x:v>684</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C290" s="8" t="s">
-        <x:v>694</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="D290" s="11" t="s">
-        <x:v>695</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="E290" s="17"/>
       <x:c r="F290" s="17"/>
@@ -9437,16 +9413,16 @@
     </x:row>
     <x:row r="291" ht="30" customHeight="1">
       <x:c r="A291" s="20" t="s">
-        <x:v>696</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="B291" s="14" t="s">
-        <x:v>684</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C291" s="8" t="s">
-        <x:v>697</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D291" s="11" t="s">
-        <x:v>698</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="E291" s="17"/>
       <x:c r="F291" s="17"/>
@@ -9459,16 +9435,16 @@
     </x:row>
     <x:row r="292" ht="30" customHeight="1">
       <x:c r="A292" s="20" t="s">
-        <x:v>699</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="B292" s="14" t="s">
-        <x:v>684</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C292" s="8" t="s">
-        <x:v>700</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="D292" s="11" t="s">
-        <x:v>686</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E292" s="17"/>
       <x:c r="F292" s="17"/>
@@ -9481,16 +9457,16 @@
     </x:row>
     <x:row r="293" ht="30" customHeight="1">
       <x:c r="A293" s="20" t="s">
-        <x:v>701</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="B293" s="14" t="s">
-        <x:v>684</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C293" s="8" t="s">
-        <x:v>702</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="D293" s="11" t="s">
-        <x:v>703</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="E293" s="17"/>
       <x:c r="F293" s="17"/>
@@ -9503,16 +9479,16 @@
     </x:row>
     <x:row r="294" ht="30" customHeight="1">
       <x:c r="A294" s="20" t="s">
-        <x:v>704</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="B294" s="14" t="s">
-        <x:v>705</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C294" s="8" t="s">
-        <x:v>706</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D294" s="11" t="s">
-        <x:v>707</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="E294" s="17"/>
       <x:c r="F294" s="17"/>
@@ -9525,16 +9501,16 @@
     </x:row>
     <x:row r="295" ht="30" customHeight="1">
       <x:c r="A295" s="20" t="s">
-        <x:v>708</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B295" s="14" t="s">
-        <x:v>705</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C295" s="8" t="s">
-        <x:v>706</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D295" s="11" t="s">
-        <x:v>709</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="E295" s="17"/>
       <x:c r="F295" s="17"/>
@@ -9547,16 +9523,16 @@
     </x:row>
     <x:row r="296" ht="30" customHeight="1">
       <x:c r="A296" s="20" t="s">
-        <x:v>710</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="B296" s="14" t="s">
-        <x:v>705</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C296" s="8" t="s">
-        <x:v>706</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D296" s="11" t="s">
-        <x:v>711</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E296" s="17"/>
       <x:c r="F296" s="17"/>
@@ -9569,16 +9545,16 @@
     </x:row>
     <x:row r="297" ht="30" customHeight="1">
       <x:c r="A297" s="20" t="s">
-        <x:v>712</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="B297" s="14" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="C297" s="8" t="s">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="D297" s="11" t="s">
         <x:v>705</x:v>
-      </x:c>
-      <x:c r="C297" s="8" t="s">
-        <x:v>706</x:v>
-      </x:c>
-      <x:c r="D297" s="11" t="s">
-        <x:v>713</x:v>
       </x:c>
       <x:c r="E297" s="17"/>
       <x:c r="F297" s="17"/>
@@ -9591,16 +9567,16 @@
     </x:row>
     <x:row r="298" ht="30" customHeight="1">
       <x:c r="A298" s="20" t="s">
-        <x:v>714</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="B298" s="14" t="s">
-        <x:v>705</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C298" s="8" t="s">
-        <x:v>706</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D298" s="11" t="s">
-        <x:v>715</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="E298" s="17"/>
       <x:c r="F298" s="17"/>
@@ -9613,16 +9589,16 @@
     </x:row>
     <x:row r="299" ht="30" customHeight="1">
       <x:c r="A299" s="20" t="s">
-        <x:v>716</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B299" s="14" t="s">
-        <x:v>705</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C299" s="8" t="s">
-        <x:v>706</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D299" s="11" t="s">
-        <x:v>717</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="E299" s="17"/>
       <x:c r="F299" s="17"/>
@@ -9635,16 +9611,16 @@
     </x:row>
     <x:row r="300" ht="30" customHeight="1">
       <x:c r="A300" s="20" t="s">
-        <x:v>718</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B300" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C300" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D300" s="11" t="s">
-        <x:v>720</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="E300" s="17"/>
       <x:c r="F300" s="17"/>
@@ -9657,16 +9633,16 @@
     </x:row>
     <x:row r="301" ht="30" customHeight="1">
       <x:c r="A301" s="20" t="s">
-        <x:v>721</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B301" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C301" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D301" s="11" t="s">
-        <x:v>722</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="E301" s="17"/>
       <x:c r="F301" s="17"/>
@@ -9679,16 +9655,16 @@
     </x:row>
     <x:row r="302" ht="30" customHeight="1">
       <x:c r="A302" s="20" t="s">
-        <x:v>723</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B302" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C302" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D302" s="11" t="s">
-        <x:v>724</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="E302" s="17"/>
       <x:c r="F302" s="17"/>
@@ -9701,16 +9677,16 @@
     </x:row>
     <x:row r="303" ht="30" customHeight="1">
       <x:c r="A303" s="20" t="s">
-        <x:v>725</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="B303" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C303" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D303" s="11" t="s">
-        <x:v>726</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="E303" s="17"/>
       <x:c r="F303" s="17"/>
@@ -9723,16 +9699,16 @@
     </x:row>
     <x:row r="304" ht="30" customHeight="1">
       <x:c r="A304" s="20" t="s">
-        <x:v>727</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B304" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C304" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D304" s="11" t="s">
-        <x:v>728</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="E304" s="17"/>
       <x:c r="F304" s="17"/>
@@ -9745,16 +9721,16 @@
     </x:row>
     <x:row r="305" ht="30" customHeight="1">
       <x:c r="A305" s="20" t="s">
-        <x:v>729</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="B305" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C305" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D305" s="11" t="s">
-        <x:v>730</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="E305" s="17"/>
       <x:c r="F305" s="17"/>
@@ -9767,16 +9743,16 @@
     </x:row>
     <x:row r="306" ht="30" customHeight="1">
       <x:c r="A306" s="20" t="s">
-        <x:v>731</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="B306" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C306" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D306" s="11" t="s">
-        <x:v>732</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="E306" s="17"/>
       <x:c r="F306" s="17"/>
@@ -9789,16 +9765,16 @@
     </x:row>
     <x:row r="307" ht="30" customHeight="1">
       <x:c r="A307" s="20" t="s">
-        <x:v>733</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B307" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C307" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D307" s="11" t="s">
-        <x:v>734</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="E307" s="17"/>
       <x:c r="F307" s="17"/>
@@ -9811,16 +9787,16 @@
     </x:row>
     <x:row r="308" ht="30" customHeight="1">
       <x:c r="A308" s="20" t="s">
-        <x:v>735</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="B308" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C308" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D308" s="11" t="s">
-        <x:v>736</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="E308" s="17"/>
       <x:c r="F308" s="17"/>
@@ -9833,16 +9809,16 @@
     </x:row>
     <x:row r="309" ht="30" customHeight="1">
       <x:c r="A309" s="20" t="s">
-        <x:v>737</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="B309" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C309" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D309" s="11" t="s">
-        <x:v>738</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="E309" s="17"/>
       <x:c r="F309" s="17"/>
@@ -9855,16 +9831,16 @@
     </x:row>
     <x:row r="310" ht="30" customHeight="1">
       <x:c r="A310" s="20" t="s">
-        <x:v>739</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="B310" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C310" s="8" t="s">
-        <x:v>719</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D310" s="11" t="s">
-        <x:v>740</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="E310" s="17"/>
       <x:c r="F310" s="17"/>
@@ -9877,16 +9853,16 @@
     </x:row>
     <x:row r="311" ht="30" customHeight="1">
       <x:c r="A311" s="20" t="s">
-        <x:v>741</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="B311" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C311" s="8" t="s">
-        <x:v>742</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="D311" s="11" t="s">
-        <x:v>743</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="E311" s="17"/>
       <x:c r="F311" s="17"/>
@@ -9899,16 +9875,16 @@
     </x:row>
     <x:row r="312" ht="30" customHeight="1">
       <x:c r="A312" s="20" t="s">
-        <x:v>744</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B312" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C312" s="8" t="s">
-        <x:v>745</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="D312" s="11" t="s">
-        <x:v>746</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="E312" s="17"/>
       <x:c r="F312" s="17"/>
@@ -9921,16 +9897,16 @@
     </x:row>
     <x:row r="313" ht="30" customHeight="1">
       <x:c r="A313" s="20" t="s">
-        <x:v>747</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="B313" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C313" s="8" t="s">
-        <x:v>748</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="D313" s="11" t="s">
-        <x:v>749</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="E313" s="17"/>
       <x:c r="F313" s="17"/>
@@ -9943,13 +9919,13 @@
     </x:row>
     <x:row r="314" ht="30" customHeight="1">
       <x:c r="A314" s="20" t="s">
-        <x:v>750</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B314" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C314" s="8" t="s">
-        <x:v>751</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="D314" s="11" t="s">
         <x:v>76</x:v>
@@ -9965,16 +9941,16 @@
     </x:row>
     <x:row r="315" ht="30" customHeight="1">
       <x:c r="A315" s="20" t="s">
-        <x:v>752</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="B315" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C315" s="8" t="s">
-        <x:v>753</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="D315" s="11" t="s">
-        <x:v>466</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="E315" s="17"/>
       <x:c r="F315" s="17"/>
@@ -9987,16 +9963,16 @@
     </x:row>
     <x:row r="316" ht="30" customHeight="1">
       <x:c r="A316" s="20" t="s">
-        <x:v>754</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="B316" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C316" s="8" t="s">
-        <x:v>755</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="D316" s="11" t="s">
-        <x:v>468</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="E316" s="17"/>
       <x:c r="F316" s="17"/>
@@ -10009,16 +9985,16 @@
     </x:row>
     <x:row r="317" ht="30" customHeight="1">
       <x:c r="A317" s="20" t="s">
-        <x:v>756</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="B317" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C317" s="8" t="s">
-        <x:v>757</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="D317" s="11" t="s">
-        <x:v>470</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E317" s="17"/>
       <x:c r="F317" s="17"/>
@@ -10031,16 +10007,16 @@
     </x:row>
     <x:row r="318" ht="30" customHeight="1">
       <x:c r="A318" s="20" t="s">
-        <x:v>758</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B318" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C318" s="8" t="s">
-        <x:v>759</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="D318" s="11" t="s">
-        <x:v>472</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="E318" s="17"/>
       <x:c r="F318" s="17"/>
@@ -10053,16 +10029,16 @@
     </x:row>
     <x:row r="319" ht="30" customHeight="1">
       <x:c r="A319" s="20" t="s">
-        <x:v>760</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="B319" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C319" s="8" t="s">
-        <x:v>761</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="D319" s="11" t="s">
-        <x:v>762</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="E319" s="17"/>
       <x:c r="F319" s="17"/>
@@ -10075,16 +10051,16 @@
     </x:row>
     <x:row r="320" ht="30" customHeight="1">
       <x:c r="A320" s="20" t="s">
-        <x:v>763</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="B320" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C320" s="8" t="s">
-        <x:v>764</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="D320" s="11" t="s">
-        <x:v>765</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="E320" s="17"/>
       <x:c r="F320" s="17"/>
@@ -10097,13 +10073,13 @@
     </x:row>
     <x:row r="321" ht="30" customHeight="1">
       <x:c r="A321" s="20" t="s">
-        <x:v>766</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="B321" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C321" s="8" t="s">
-        <x:v>767</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="D321" s="11" t="str">
         <x:v>Помощь, консультации и контроль качества работы системы</x:v>
@@ -10119,13 +10095,13 @@
     </x:row>
     <x:row r="322" ht="30" customHeight="1">
       <x:c r="A322" s="20" t="s">
-        <x:v>768</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B322" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C322" s="8" t="s">
-        <x:v>769</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="D322" s="11" t="str">
         <x:v>Онлайн-поддержка</x:v>
@@ -10141,16 +10117,16 @@
     </x:row>
     <x:row r="323" ht="30" customHeight="1">
       <x:c r="A323" s="20" t="s">
-        <x:v>770</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="B323" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C323" s="8" t="s">
-        <x:v>771</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="D323" s="11" t="s">
-        <x:v>772</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="E323" s="17"/>
       <x:c r="F323" s="17"/>
@@ -10163,16 +10139,16 @@
     </x:row>
     <x:row r="324" ht="30" customHeight="1">
       <x:c r="A324" s="20" t="s">
-        <x:v>773</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B324" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C324" s="8" t="s">
-        <x:v>774</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="D324" s="11" t="s">
-        <x:v>775</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="E324" s="17"/>
       <x:c r="F324" s="17"/>
@@ -10185,16 +10161,16 @@
     </x:row>
     <x:row r="325" ht="30" customHeight="1">
       <x:c r="A325" s="20" t="s">
-        <x:v>776</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B325" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C325" s="8" t="s">
-        <x:v>777</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="D325" s="11" t="s">
-        <x:v>778</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="E325" s="17"/>
       <x:c r="F325" s="17"/>
@@ -10207,16 +10183,16 @@
     </x:row>
     <x:row r="326" ht="30" customHeight="1">
       <x:c r="A326" s="20" t="s">
-        <x:v>779</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="B326" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C326" s="8" t="s">
-        <x:v>780</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="D326" s="11" t="s">
-        <x:v>781</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="E326" s="17"/>
       <x:c r="F326" s="17"/>
@@ -10229,16 +10205,16 @@
     </x:row>
     <x:row r="327" ht="30" customHeight="1">
       <x:c r="A327" s="20" t="s">
-        <x:v>782</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="B327" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C327" s="8" t="s">
-        <x:v>783</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="D327" s="11" t="s">
-        <x:v>784</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="E327" s="17"/>
       <x:c r="F327" s="17"/>
@@ -10251,16 +10227,16 @@
     </x:row>
     <x:row r="328" ht="30" customHeight="1">
       <x:c r="A328" s="20" t="s">
-        <x:v>785</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B328" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C328" s="8" t="s">
-        <x:v>786</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="D328" s="11" t="s">
-        <x:v>787</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="E328" s="17"/>
       <x:c r="F328" s="17"/>
@@ -10273,16 +10249,16 @@
     </x:row>
     <x:row r="329" ht="30" customHeight="1">
       <x:c r="A329" s="20" t="s">
-        <x:v>788</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="B329" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C329" s="8" t="s">
-        <x:v>789</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="D329" s="11" t="s">
-        <x:v>790</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="E329" s="17"/>
       <x:c r="F329" s="17"/>
@@ -10295,16 +10271,16 @@
     </x:row>
     <x:row r="330" ht="30" customHeight="1">
       <x:c r="A330" s="20" t="s">
-        <x:v>791</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="B330" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C330" s="8" t="s">
-        <x:v>792</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="D330" s="11" t="s">
-        <x:v>793</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="E330" s="17"/>
       <x:c r="F330" s="17"/>
@@ -10317,16 +10293,16 @@
     </x:row>
     <x:row r="331" ht="30" customHeight="1">
       <x:c r="A331" s="21" t="s">
-        <x:v>794</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B331" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C331" s="9" t="s">
-        <x:v>795</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="D331" s="12" t="s">
-        <x:v>796</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="E331" s="18"/>
       <x:c r="F331" s="18"/>
@@ -10339,16 +10315,16 @@
     </x:row>
     <x:row r="332" ht="15">
       <x:c r="A332" s="23" t="s">
-        <x:v>797</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B332" s="24" t="s">
-        <x:v>520</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C332" s="25" t="s">
-        <x:v>798</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="D332" s="26" t="s">
-        <x:v>799</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="E332" s="22"/>
       <x:c r="F332" s="22"/>
@@ -10361,16 +10337,16 @@
     </x:row>
     <x:row r="333" ht="15">
       <x:c r="A333" s="23" t="s">
-        <x:v>800</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="B333" s="27" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C333" s="28" t="s">
-        <x:v>801</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="D333" s="29" t="s">
-        <x:v>802</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="E333" s="22"/>
       <x:c r="F333" s="22"/>
@@ -10383,16 +10359,16 @@
     </x:row>
     <x:row r="334" ht="15">
       <x:c r="A334" s="23" t="s">
-        <x:v>803</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B334" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C334" s="25" t="s">
-        <x:v>804</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="D334" s="26" t="s">
-        <x:v>805</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="E334" s="22"/>
       <x:c r="F334" s="22"/>
@@ -10405,16 +10381,16 @@
     </x:row>
     <x:row r="335" ht="15">
       <x:c r="A335" s="23" t="s">
-        <x:v>806</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="B335" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C335" s="28" t="s">
-        <x:v>807</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="D335" s="29" t="s">
-        <x:v>808</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="E335" s="22"/>
       <x:c r="F335" s="22"/>
@@ -10427,16 +10403,16 @@
     </x:row>
     <x:row r="336" ht="15">
       <x:c r="A336" s="23" t="s">
-        <x:v>809</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B336" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C336" s="25" t="s">
-        <x:v>810</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="D336" s="26" t="s">
-        <x:v>811</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="E336" s="22"/>
       <x:c r="F336" s="22"/>
@@ -10449,16 +10425,16 @@
     </x:row>
     <x:row r="337" ht="15">
       <x:c r="A337" s="23" t="s">
-        <x:v>812</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="B337" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C337" s="28" t="s">
-        <x:v>813</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="D337" s="29" t="s">
-        <x:v>814</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="E337" s="22"/>
       <x:c r="F337" s="22"/>
@@ -10471,16 +10447,16 @@
     </x:row>
     <x:row r="338" ht="15">
       <x:c r="A338" s="23" t="s">
-        <x:v>815</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="B338" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C338" s="25" t="s">
-        <x:v>816</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="D338" s="26" t="s">
-        <x:v>817</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="E338" s="22"/>
       <x:c r="F338" s="22"/>
@@ -10493,16 +10469,16 @@
     </x:row>
     <x:row r="339" ht="15">
       <x:c r="A339" s="23" t="s">
-        <x:v>818</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="B339" s="27" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C339" s="28" t="s">
-        <x:v>819</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="D339" s="29" t="s">
-        <x:v>820</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="E339" s="22"/>
       <x:c r="F339" s="22"/>
@@ -10655,16 +10631,16 @@
     </x:row>
     <x:row r="350">
       <x:c r="A350" t="s">
-        <x:v>821</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B350" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C350" t="s">
-        <x:v>764</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="D350" t="s">
-        <x:v>822</x:v>
+        <x:v>814</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -10678,7 +10654,7 @@
         <x:v>Четвёртый отзыв</x:v>
       </x:c>
       <x:c r="D351" t="str">
-        <x:v>Я вообще не люблю CRM и сложные программы. Здесь просто пишу или говорю обычным языком — система сама сохраняет информацию куда нужно.</x:v>
+        <x:v>Я вообще не люблю CRM и сложные программы. Здесь просто пишу или говорю обычным языком — система сама сохраняет информацию туда, куда нужно.</x:v>
       </x:c>
       <x:c r="E351"/>
       <x:c r="F351"/>
@@ -10744,7 +10720,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d9da988733e4a2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0c987386db24766"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R30a68264af8b481d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R449dcade0fac4099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R7d374794cdb5408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="Ra42f5e3b19e04ddb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10709,6 +10709,50 @@
       <x:c r="K353"/>
       <x:c r="L353"/>
     </x:row>
+    <x:row r="354">
+      <x:c r="A354" t="str">
+        <x:v>benefits.recommendations.title</x:v>
+      </x:c>
+      <x:c r="B354" t="str">
+        <x:v>Возможности</x:v>
+      </x:c>
+      <x:c r="C354" t="str">
+        <x:v>Карточка возможности</x:v>
+      </x:c>
+      <x:c r="D354" t="str">
+        <x:v>Фиксация рекомендаций</x:v>
+      </x:c>
+      <x:c r="E354"/>
+      <x:c r="F354"/>
+      <x:c r="G354"/>
+      <x:c r="H354"/>
+      <x:c r="I354"/>
+      <x:c r="J354"/>
+      <x:c r="K354"/>
+      <x:c r="L354"/>
+    </x:row>
+    <x:row r="355">
+      <x:c r="A355" t="str">
+        <x:v>benefits.recommendations.description</x:v>
+      </x:c>
+      <x:c r="B355" t="str">
+        <x:v>Возможности</x:v>
+      </x:c>
+      <x:c r="C355" t="str">
+        <x:v>Карточка возможности</x:v>
+      </x:c>
+      <x:c r="D355" t="str">
+        <x:v>Специалист всегда видит, что рекомендовал клиенту делать дома, — без противоречий и повторных вопросов.</x:v>
+      </x:c>
+      <x:c r="E355"/>
+      <x:c r="F355"/>
+      <x:c r="G355"/>
+      <x:c r="H355"/>
+      <x:c r="I355"/>
+      <x:c r="J355"/>
+      <x:c r="K355"/>
+      <x:c r="L355"/>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="K2:K331">
@@ -10720,7 +10764,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0c987386db24766"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e21e42147bb4bd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R7d374794cdb5408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="Ra42f5e3b19e04ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R40d363dae5ff4eb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R611013302dda46cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2385,42 +2385,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Другое — указать свой вариант</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">hero.review_3_metric</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Выгода третьего отзыва</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">без вечерней рутины</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">story.meaning_idea</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Смысловая плашка 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Её идея</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">story.meaning_tool</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Смысловая плашка 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Мой инструмент</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">story.meaning_savings</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Смысловая плашка 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Нет лишних затрат</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">story.meaning_speed</x:t>
@@ -2707,7 +2671,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SiteContent" displayName="SiteContent" ref="A1:L332" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SiteContent" displayName="SiteContent" ref="A1:L336" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="key"/>
     <x:tableColumn id="2" name="section"/>
@@ -10336,17 +10300,17 @@
       <x:c r="L332" s="22"/>
     </x:row>
     <x:row r="333" ht="15">
-      <x:c r="A333" s="23" t="s">
-        <x:v>792</x:v>
-      </x:c>
-      <x:c r="B333" s="27" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C333" s="28" t="s">
-        <x:v>793</x:v>
-      </x:c>
-      <x:c r="D333" s="29" t="s">
-        <x:v>794</x:v>
+      <x:c r="A333" s="23" t="str">
+        <x:v>hero.review_3_metric</x:v>
+      </x:c>
+      <x:c r="B333" s="27" t="str">
+        <x:v>Hero</x:v>
+      </x:c>
+      <x:c r="C333" s="28" t="str">
+        <x:v>Выгода третьего отзыва</x:v>
+      </x:c>
+      <x:c r="D333" s="29" t="str">
+        <x:v>без вечерней рутины</x:v>
       </x:c>
       <x:c r="E333" s="22"/>
       <x:c r="F333" s="22"/>
@@ -10358,17 +10322,17 @@
       <x:c r="L333" s="22"/>
     </x:row>
     <x:row r="334" ht="15">
-      <x:c r="A334" s="23" t="s">
-        <x:v>795</x:v>
-      </x:c>
-      <x:c r="B334" s="24" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C334" s="25" t="s">
-        <x:v>796</x:v>
-      </x:c>
-      <x:c r="D334" s="26" t="s">
-        <x:v>797</x:v>
+      <x:c r="A334" s="23" t="str">
+        <x:v>story.meaning_idea</x:v>
+      </x:c>
+      <x:c r="B334" s="24" t="str">
+        <x:v>История</x:v>
+      </x:c>
+      <x:c r="C334" s="25" t="str">
+        <x:v>Смысловая плашка 1</x:v>
+      </x:c>
+      <x:c r="D334" s="26" t="str">
+        <x:v>Её идея</x:v>
       </x:c>
       <x:c r="E334" s="22"/>
       <x:c r="F334" s="22"/>
@@ -10380,17 +10344,17 @@
       <x:c r="L334" s="22"/>
     </x:row>
     <x:row r="335" ht="15">
-      <x:c r="A335" s="23" t="s">
-        <x:v>798</x:v>
-      </x:c>
-      <x:c r="B335" s="27" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C335" s="28" t="s">
-        <x:v>799</x:v>
-      </x:c>
-      <x:c r="D335" s="29" t="s">
-        <x:v>800</x:v>
+      <x:c r="A335" s="23" t="str">
+        <x:v>story.meaning_tool</x:v>
+      </x:c>
+      <x:c r="B335" s="27" t="str">
+        <x:v>История</x:v>
+      </x:c>
+      <x:c r="C335" s="28" t="str">
+        <x:v>Смысловая плашка 2</x:v>
+      </x:c>
+      <x:c r="D335" s="29" t="str">
+        <x:v>Мой инструмент</x:v>
       </x:c>
       <x:c r="E335" s="22"/>
       <x:c r="F335" s="22"/>
@@ -10402,17 +10366,17 @@
       <x:c r="L335" s="22"/>
     </x:row>
     <x:row r="336" ht="15">
-      <x:c r="A336" s="23" t="s">
-        <x:v>801</x:v>
-      </x:c>
-      <x:c r="B336" s="24" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C336" s="25" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="D336" s="26" t="s">
-        <x:v>803</x:v>
+      <x:c r="A336" s="23" t="str">
+        <x:v>story.meaning_savings</x:v>
+      </x:c>
+      <x:c r="B336" s="24" t="str">
+        <x:v>История</x:v>
+      </x:c>
+      <x:c r="C336" s="25" t="str">
+        <x:v>Смысловая плашка 3</x:v>
+      </x:c>
+      <x:c r="D336" s="26" t="str">
+        <x:v>Нет лишних затрат</x:v>
       </x:c>
       <x:c r="E336" s="22"/>
       <x:c r="F336" s="22"/>
@@ -10425,16 +10389,16 @@
     </x:row>
     <x:row r="337" ht="15">
       <x:c r="A337" s="23" t="s">
-        <x:v>804</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="B337" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C337" s="28" t="s">
-        <x:v>805</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="D337" s="29" t="s">
-        <x:v>806</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="E337" s="22"/>
       <x:c r="F337" s="22"/>
@@ -10447,16 +10411,16 @@
     </x:row>
     <x:row r="338" ht="15">
       <x:c r="A338" s="23" t="s">
-        <x:v>807</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B338" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C338" s="25" t="s">
-        <x:v>808</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="D338" s="26" t="s">
-        <x:v>809</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="E338" s="22"/>
       <x:c r="F338" s="22"/>
@@ -10469,16 +10433,16 @@
     </x:row>
     <x:row r="339" ht="15">
       <x:c r="A339" s="23" t="s">
-        <x:v>810</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="B339" s="27" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C339" s="28" t="s">
-        <x:v>811</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="D339" s="29" t="s">
-        <x:v>812</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="E339" s="22"/>
       <x:c r="F339" s="22"/>
@@ -10490,10 +10454,18 @@
       <x:c r="L339" s="22"/>
     </x:row>
     <x:row r="340" ht="15">
-      <x:c r="A340" s="23"/>
-      <x:c r="B340" s="24"/>
-      <x:c r="C340" s="25"/>
-      <x:c r="D340" s="26"/>
+      <x:c r="A340" s="23" t="str">
+        <x:v>pricing.chatgpt_plus.title</x:v>
+      </x:c>
+      <x:c r="B340" s="24" t="str">
+        <x:v>Стоимость</x:v>
+      </x:c>
+      <x:c r="C340" s="25" t="str">
+        <x:v>Заголовок блока о подписке ChatGPT Plus</x:v>
+      </x:c>
+      <x:c r="D340" s="26" t="str">
+        <x:v>Для работы сервиса нужен ChatGPT Plus</x:v>
+      </x:c>
       <x:c r="E340" s="22"/>
       <x:c r="F340" s="22"/>
       <x:c r="G340" s="22"/>
@@ -10504,10 +10476,18 @@
       <x:c r="L340" s="22"/>
     </x:row>
     <x:row r="341" ht="15">
-      <x:c r="A341" s="23"/>
-      <x:c r="B341" s="27"/>
-      <x:c r="C341" s="28"/>
-      <x:c r="D341" s="29"/>
+      <x:c r="A341" s="23" t="str">
+        <x:v>pricing.chatgpt_plus.requirement</x:v>
+      </x:c>
+      <x:c r="B341" s="27" t="str">
+        <x:v>Стоимость</x:v>
+      </x:c>
+      <x:c r="C341" s="28" t="str">
+        <x:v>Требование к подписке ChatGPT</x:v>
+      </x:c>
+      <x:c r="D341" s="29" t="str">
+        <x:v>Сервис работает на базе ChatGPT, поэтому для его использования необходима подписка ChatGPT Plus или выше.</x:v>
+      </x:c>
       <x:c r="E341" s="22"/>
       <x:c r="F341" s="22"/>
       <x:c r="G341" s="22"/>
@@ -10518,10 +10498,18 @@
       <x:c r="L341" s="22"/>
     </x:row>
     <x:row r="342" ht="15">
-      <x:c r="A342" s="23"/>
-      <x:c r="B342" s="24"/>
-      <x:c r="C342" s="25"/>
-      <x:c r="D342" s="26"/>
+      <x:c r="A342" s="23" t="str">
+        <x:v>pricing.chatgpt_plus.options</x:v>
+      </x:c>
+      <x:c r="B342" s="24" t="str">
+        <x:v>Стоимость</x:v>
+      </x:c>
+      <x:c r="C342" s="25" t="str">
+        <x:v>Варианты подключения подписки ChatGPT</x:v>
+      </x:c>
+      <x:c r="D342" s="26" t="str">
+        <x:v>Если у вас уже есть подписка - ничего дополнительно подключать не нужно. Если подписки пока нет, вы можете оформить её самостоятельно или воспользоваться нашей помощью.</x:v>
+      </x:c>
       <x:c r="E342" s="22"/>
       <x:c r="F342" s="22"/>
       <x:c r="G342" s="22"/>
@@ -10532,10 +10520,18 @@
       <x:c r="L342" s="22"/>
     </x:row>
     <x:row r="343" ht="15">
-      <x:c r="A343" s="23"/>
-      <x:c r="B343" s="27"/>
-      <x:c r="C343" s="28"/>
-      <x:c r="D343" s="29"/>
+      <x:c r="A343" s="23" t="str">
+        <x:v>pricing.chatgpt_plus.help</x:v>
+      </x:c>
+      <x:c r="B343" s="27" t="str">
+        <x:v>Стоимость</x:v>
+      </x:c>
+      <x:c r="C343" s="28" t="str">
+        <x:v>Помощь с аккаунтом и оплатой ChatGPT</x:v>
+      </x:c>
+      <x:c r="D343" s="29" t="str">
+        <x:v>Мы поможем создать аккаунт ChatGPT, подключить подписку и провести оплату, чтобы вам не пришлось разбираться с этим самостоятельно. Необходимый уровень подписки стоит от 20$ в месяц.</x:v>
+      </x:c>
       <x:c r="E343" s="22"/>
       <x:c r="F343" s="22"/>
       <x:c r="G343" s="22"/>
@@ -10631,7 +10627,7 @@
     </x:row>
     <x:row r="350">
       <x:c r="A350" t="s">
-        <x:v>813</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B350" t="s">
         <x:v>54</x:v>
@@ -10640,7 +10636,7 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="D350" t="s">
-        <x:v>814</x:v>
+        <x:v>802</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -10764,7 +10760,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e21e42147bb4bd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d51145395fd4544"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WebDev\stark-electronic-base\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDBB455-3AC0-48E4-B16A-CA0DAE496A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461D7993-10A4-4506-A403-2C706202B64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="Re67b77bba7954a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R99493972252e41da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R99cdb97935704258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты" sheetId="2" r:id="R6b70f02a480a4e40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1514,9 +1514,6 @@
     <x:t xml:space="preserve">pricing.addon.database-backup.price</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">2 000 ₽</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">pricing.addon.database-backup.description</x:t>
   </x:si>
   <x:si>
@@ -1533,9 +1530,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">pricing.addon.employee-account.price</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 000 ₽</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">pricing.addon.employee-account.price_note</x:t>
@@ -7294,7 +7288,7 @@
         <x:v>457</x:v>
       </x:c>
       <x:c r="D189" s="11" t="str">
-        <x:v>10 000 ₽ · разовая оплата</x:v>
+        <x:v>360 Br · разовая оплата</x:v>
       </x:c>
       <x:c r="E189" s="17"/>
       <x:c r="F189" s="17"/>
@@ -7492,7 +7486,7 @@
         <x:v>475</x:v>
       </x:c>
       <x:c r="D198" s="11" t="str">
-        <x:v>4 000 ₽ · оплата не чаще, чем раз в месяц</x:v>
+        <x:v>140 Br · оплата не чаще, чем раз в месяц</x:v>
       </x:c>
       <x:c r="E198" s="17"/>
       <x:c r="F198" s="17"/>
@@ -7731,8 +7725,8 @@
       <x:c r="C209" s="8" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="D209" s="11" t="s">
-        <x:v>501</x:v>
+      <x:c r="D209" s="11" t="str">
+        <x:v>70 Br</x:v>
       </x:c>
       <x:c r="E209" s="17"/>
       <x:c r="F209" s="17"/>
@@ -7745,7 +7739,7 @@
     </x:row>
     <x:row r="210" ht="30" customHeight="1">
       <x:c r="A210" s="20" t="s">
-        <x:v>502</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B210" s="14" t="s">
         <x:v>54</x:v>
@@ -7754,7 +7748,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="D210" s="11" t="s">
-        <x:v>503</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="E210" s="17"/>
       <x:c r="F210" s="17"/>
@@ -7767,16 +7761,16 @@
     </x:row>
     <x:row r="211" ht="30" customHeight="1">
       <x:c r="A211" s="20" t="s">
-        <x:v>504</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B211" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C211" s="8" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="D211" s="11" t="s">
         <x:v>505</x:v>
-      </x:c>
-      <x:c r="D211" s="11" t="s">
-        <x:v>506</x:v>
       </x:c>
       <x:c r="E211" s="17"/>
       <x:c r="F211" s="17"/>
@@ -7789,16 +7783,16 @@
     </x:row>
     <x:row r="212" ht="30" customHeight="1">
       <x:c r="A212" s="20" t="s">
-        <x:v>507</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B212" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C212" s="8" t="s">
-        <x:v>505</x:v>
-      </x:c>
-      <x:c r="D212" s="11" t="s">
-        <x:v>508</x:v>
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="D212" s="11" t="str">
+        <x:v>40 Br</x:v>
       </x:c>
       <x:c r="E212" s="17"/>
       <x:c r="F212" s="17"/>
@@ -7811,16 +7805,16 @@
     </x:row>
     <x:row r="213" ht="30" customHeight="1">
       <x:c r="A213" s="20" t="s">
-        <x:v>509</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B213" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C213" s="8" t="s">
-        <x:v>505</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="D213" s="11" t="s">
-        <x:v>510</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="E213" s="17"/>
       <x:c r="F213" s="17"/>
@@ -7833,16 +7827,16 @@
     </x:row>
     <x:row r="214" ht="30" customHeight="1">
       <x:c r="A214" s="20" t="s">
-        <x:v>511</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B214" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C214" s="8" t="s">
-        <x:v>505</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="D214" s="11" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="E214" s="17"/>
       <x:c r="F214" s="17"/>
@@ -7855,16 +7849,16 @@
     </x:row>
     <x:row r="215" ht="30" customHeight="1">
       <x:c r="A215" s="20" t="s">
-        <x:v>513</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B215" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C215" s="8" t="s">
-        <x:v>514</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D215" s="11" t="s">
-        <x:v>515</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="E215" s="17"/>
       <x:c r="F215" s="17"/>
@@ -7877,16 +7871,16 @@
     </x:row>
     <x:row r="216" ht="30" customHeight="1">
       <x:c r="A216" s="20" t="s">
-        <x:v>516</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B216" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C216" s="8" t="s">
-        <x:v>517</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D216" s="11" t="s">
-        <x:v>518</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="E216" s="17"/>
       <x:c r="F216" s="17"/>
@@ -7899,16 +7893,16 @@
     </x:row>
     <x:row r="217" ht="30" customHeight="1">
       <x:c r="A217" s="20" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B217" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C217" s="8" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="D217" s="11" t="s">
-        <x:v>521</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="E217" s="17"/>
       <x:c r="F217" s="17"/>
@@ -7921,16 +7915,16 @@
     </x:row>
     <x:row r="218" ht="30" customHeight="1">
       <x:c r="A218" s="20" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B218" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C218" s="8" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="D218" s="11" t="s">
-        <x:v>524</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="E218" s="17"/>
       <x:c r="F218" s="17"/>
@@ -7943,16 +7937,16 @@
     </x:row>
     <x:row r="219" ht="30" customHeight="1">
       <x:c r="A219" s="20" t="s">
-        <x:v>525</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B219" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C219" s="8" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="D219" s="11" t="s">
-        <x:v>526</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E219" s="17"/>
       <x:c r="F219" s="17"/>
@@ -7965,16 +7959,16 @@
     </x:row>
     <x:row r="220" ht="30" customHeight="1">
       <x:c r="A220" s="20" t="s">
-        <x:v>527</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B220" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C220" s="8" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="D220" s="11" t="s">
-        <x:v>528</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="E220" s="17"/>
       <x:c r="F220" s="17"/>
@@ -7987,16 +7981,16 @@
     </x:row>
     <x:row r="221" ht="30" customHeight="1">
       <x:c r="A221" s="20" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B221" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C221" s="8" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="D221" s="11" t="s">
         <x:v>529</x:v>
-      </x:c>
-      <x:c r="B221" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C221" s="8" t="s">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="D221" s="11" t="s">
-        <x:v>531</x:v>
       </x:c>
       <x:c r="E221" s="17"/>
       <x:c r="F221" s="17"/>
@@ -8009,16 +8003,16 @@
     </x:row>
     <x:row r="222" ht="30" customHeight="1">
       <x:c r="A222" s="20" t="s">
-        <x:v>532</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B222" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C222" s="8" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D222" s="11" t="s">
-        <x:v>533</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="E222" s="17"/>
       <x:c r="F222" s="17"/>
@@ -8031,16 +8025,16 @@
     </x:row>
     <x:row r="223" ht="30" customHeight="1">
       <x:c r="A223" s="20" t="s">
-        <x:v>534</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B223" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C223" s="8" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="D223" s="11" t="s">
-        <x:v>535</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="E223" s="17"/>
       <x:c r="F223" s="17"/>
@@ -8053,16 +8047,16 @@
     </x:row>
     <x:row r="224" ht="30" customHeight="1">
       <x:c r="A224" s="20" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B224" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C224" s="8" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="D224" s="11" t="s">
         <x:v>536</x:v>
-      </x:c>
-      <x:c r="B224" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C224" s="8" t="s">
-        <x:v>537</x:v>
-      </x:c>
-      <x:c r="D224" s="11" t="s">
-        <x:v>538</x:v>
       </x:c>
       <x:c r="E224" s="17"/>
       <x:c r="F224" s="17"/>
@@ -8075,16 +8069,16 @@
     </x:row>
     <x:row r="225" ht="30" customHeight="1">
       <x:c r="A225" s="20" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="B225" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C225" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="D225" s="11" t="s">
         <x:v>539</x:v>
-      </x:c>
-      <x:c r="B225" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C225" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="D225" s="11" t="s">
-        <x:v>541</x:v>
       </x:c>
       <x:c r="E225" s="17"/>
       <x:c r="F225" s="17"/>
@@ -8097,16 +8091,16 @@
     </x:row>
     <x:row r="226" ht="30" customHeight="1">
       <x:c r="A226" s="20" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B226" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C226" s="8" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="D226" s="11" t="s">
         <x:v>542</x:v>
-      </x:c>
-      <x:c r="B226" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C226" s="8" t="s">
-        <x:v>543</x:v>
-      </x:c>
-      <x:c r="D226" s="11" t="s">
-        <x:v>544</x:v>
       </x:c>
       <x:c r="E226" s="17"/>
       <x:c r="F226" s="17"/>
@@ -8119,16 +8113,16 @@
     </x:row>
     <x:row r="227" ht="30" customHeight="1">
       <x:c r="A227" s="20" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B227" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C227" s="8" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="D227" s="11" t="s">
         <x:v>545</x:v>
-      </x:c>
-      <x:c r="B227" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C227" s="8" t="s">
-        <x:v>546</x:v>
-      </x:c>
-      <x:c r="D227" s="11" t="s">
-        <x:v>547</x:v>
       </x:c>
       <x:c r="E227" s="17"/>
       <x:c r="F227" s="17"/>
@@ -8141,16 +8135,16 @@
     </x:row>
     <x:row r="228" ht="30" customHeight="1">
       <x:c r="A228" s="20" t="s">
-        <x:v>548</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B228" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C228" s="8" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D228" s="11" t="s">
-        <x:v>549</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="E228" s="17"/>
       <x:c r="F228" s="17"/>
@@ -8163,16 +8157,16 @@
     </x:row>
     <x:row r="229" ht="30" customHeight="1">
       <x:c r="A229" s="20" t="s">
-        <x:v>550</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B229" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C229" s="8" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D229" s="11" t="s">
-        <x:v>551</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="E229" s="17"/>
       <x:c r="F229" s="17"/>
@@ -8185,16 +8179,16 @@
     </x:row>
     <x:row r="230" ht="30" customHeight="1">
       <x:c r="A230" s="20" t="s">
-        <x:v>552</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B230" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C230" s="8" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D230" s="11" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="E230" s="17"/>
       <x:c r="F230" s="17"/>
@@ -8207,16 +8201,16 @@
     </x:row>
     <x:row r="231" ht="30" customHeight="1">
       <x:c r="A231" s="20" t="s">
-        <x:v>553</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B231" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C231" s="8" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D231" s="11" t="s">
-        <x:v>533</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="E231" s="17"/>
       <x:c r="F231" s="17"/>
@@ -8229,16 +8223,16 @@
     </x:row>
     <x:row r="232" ht="30" customHeight="1">
       <x:c r="A232" s="20" t="s">
-        <x:v>554</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B232" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C232" s="8" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D232" s="11" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="E232" s="17"/>
       <x:c r="F232" s="17"/>
@@ -8251,16 +8245,16 @@
     </x:row>
     <x:row r="233" ht="30" customHeight="1">
       <x:c r="A233" s="20" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B233" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C233" s="8" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="D233" s="11" t="s">
         <x:v>556</x:v>
-      </x:c>
-      <x:c r="B233" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C233" s="8" t="s">
-        <x:v>557</x:v>
-      </x:c>
-      <x:c r="D233" s="11" t="s">
-        <x:v>558</x:v>
       </x:c>
       <x:c r="E233" s="17"/>
       <x:c r="F233" s="17"/>
@@ -8273,16 +8267,16 @@
     </x:row>
     <x:row r="234" ht="30" customHeight="1">
       <x:c r="A234" s="20" t="s">
-        <x:v>559</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B234" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C234" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D234" s="11" t="s">
-        <x:v>560</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="E234" s="17"/>
       <x:c r="F234" s="17"/>
@@ -8295,16 +8289,16 @@
     </x:row>
     <x:row r="235" ht="30" customHeight="1">
       <x:c r="A235" s="20" t="s">
-        <x:v>561</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B235" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C235" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D235" s="11" t="s">
-        <x:v>562</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="E235" s="17"/>
       <x:c r="F235" s="17"/>
@@ -8317,16 +8311,16 @@
     </x:row>
     <x:row r="236" ht="30" customHeight="1">
       <x:c r="A236" s="20" t="s">
-        <x:v>563</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B236" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C236" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D236" s="11" t="s">
-        <x:v>564</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="E236" s="17"/>
       <x:c r="F236" s="17"/>
@@ -8339,16 +8333,16 @@
     </x:row>
     <x:row r="237" ht="30" customHeight="1">
       <x:c r="A237" s="20" t="s">
-        <x:v>565</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B237" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C237" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D237" s="11" t="s">
-        <x:v>566</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="E237" s="17"/>
       <x:c r="F237" s="17"/>
@@ -8361,16 +8355,16 @@
     </x:row>
     <x:row r="238" ht="30" customHeight="1">
       <x:c r="A238" s="20" t="s">
-        <x:v>567</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B238" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C238" s="8" t="s">
-        <x:v>557</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D238" s="11" t="s">
-        <x:v>568</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="E238" s="17"/>
       <x:c r="F238" s="17"/>
@@ -8383,16 +8377,16 @@
     </x:row>
     <x:row r="239" ht="30" customHeight="1">
       <x:c r="A239" s="20" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B239" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C239" s="8" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="D239" s="11" t="s">
         <x:v>569</x:v>
-      </x:c>
-      <x:c r="B239" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C239" s="8" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="D239" s="11" t="s">
-        <x:v>571</x:v>
       </x:c>
       <x:c r="E239" s="17"/>
       <x:c r="F239" s="17"/>
@@ -8405,16 +8399,16 @@
     </x:row>
     <x:row r="240" ht="30" customHeight="1">
       <x:c r="A240" s="20" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B240" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C240" s="8" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="D240" s="11" t="s">
         <x:v>572</x:v>
-      </x:c>
-      <x:c r="B240" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C240" s="8" t="s">
-        <x:v>573</x:v>
-      </x:c>
-      <x:c r="D240" s="11" t="s">
-        <x:v>574</x:v>
       </x:c>
       <x:c r="E240" s="17"/>
       <x:c r="F240" s="17"/>
@@ -8427,16 +8421,16 @@
     </x:row>
     <x:row r="241" ht="30" customHeight="1">
       <x:c r="A241" s="20" t="s">
-        <x:v>575</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B241" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C241" s="8" t="s">
-        <x:v>573</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D241" s="11" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="E241" s="17"/>
       <x:c r="F241" s="17"/>
@@ -8449,16 +8443,16 @@
     </x:row>
     <x:row r="242" ht="30" customHeight="1">
       <x:c r="A242" s="20" t="s">
-        <x:v>577</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B242" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C242" s="8" t="s">
-        <x:v>573</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D242" s="11" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="E242" s="17"/>
       <x:c r="F242" s="17"/>
@@ -8471,16 +8465,16 @@
     </x:row>
     <x:row r="243" ht="30" customHeight="1">
       <x:c r="A243" s="20" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B243" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C243" s="8" t="s">
-        <x:v>573</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D243" s="11" t="s">
-        <x:v>580</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="E243" s="17"/>
       <x:c r="F243" s="17"/>
@@ -8493,16 +8487,16 @@
     </x:row>
     <x:row r="244" ht="30" customHeight="1">
       <x:c r="A244" s="20" t="s">
-        <x:v>581</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B244" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C244" s="8" t="s">
-        <x:v>573</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D244" s="11" t="s">
-        <x:v>582</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="E244" s="17"/>
       <x:c r="F244" s="17"/>
@@ -8515,16 +8509,16 @@
     </x:row>
     <x:row r="245" ht="30" customHeight="1">
       <x:c r="A245" s="20" t="s">
-        <x:v>583</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B245" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C245" s="8" t="s">
-        <x:v>573</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D245" s="11" t="s">
-        <x:v>584</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="E245" s="17"/>
       <x:c r="F245" s="17"/>
@@ -8537,16 +8531,16 @@
     </x:row>
     <x:row r="246" ht="30" customHeight="1">
       <x:c r="A246" s="20" t="s">
-        <x:v>585</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B246" s="14" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C246" s="8" t="s">
-        <x:v>573</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="D246" s="11" t="s">
-        <x:v>586</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="E246" s="17"/>
       <x:c r="F246" s="17"/>
@@ -8559,16 +8553,16 @@
     </x:row>
     <x:row r="247" ht="30" customHeight="1">
       <x:c r="A247" s="20" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B247" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C247" s="8" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="D247" s="11" t="s">
         <x:v>587</x:v>
-      </x:c>
-      <x:c r="B247" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C247" s="8" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="D247" s="11" t="s">
-        <x:v>589</x:v>
       </x:c>
       <x:c r="E247" s="17"/>
       <x:c r="F247" s="17"/>
@@ -8581,16 +8575,16 @@
     </x:row>
     <x:row r="248" ht="30" customHeight="1">
       <x:c r="A248" s="20" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B248" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C248" s="8" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="D248" s="11" t="s">
         <x:v>590</x:v>
-      </x:c>
-      <x:c r="B248" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C248" s="8" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="D248" s="11" t="s">
-        <x:v>592</x:v>
       </x:c>
       <x:c r="E248" s="17"/>
       <x:c r="F248" s="17"/>
@@ -8603,16 +8597,16 @@
     </x:row>
     <x:row r="249" ht="30" customHeight="1">
       <x:c r="A249" s="20" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B249" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C249" s="8" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="D249" s="11" t="s">
         <x:v>593</x:v>
-      </x:c>
-      <x:c r="B249" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C249" s="8" t="s">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="D249" s="11" t="s">
-        <x:v>595</x:v>
       </x:c>
       <x:c r="E249" s="17"/>
       <x:c r="F249" s="17"/>
@@ -8625,16 +8619,16 @@
     </x:row>
     <x:row r="250" ht="30" customHeight="1">
       <x:c r="A250" s="20" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B250" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C250" s="8" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="D250" s="11" t="s">
         <x:v>596</x:v>
-      </x:c>
-      <x:c r="B250" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C250" s="8" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="D250" s="11" t="s">
-        <x:v>598</x:v>
       </x:c>
       <x:c r="E250" s="17"/>
       <x:c r="F250" s="17"/>
@@ -8647,16 +8641,16 @@
     </x:row>
     <x:row r="251" ht="30" customHeight="1">
       <x:c r="A251" s="20" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B251" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C251" s="8" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="D251" s="11" t="s">
         <x:v>599</x:v>
-      </x:c>
-      <x:c r="B251" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C251" s="8" t="s">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="D251" s="11" t="s">
-        <x:v>601</x:v>
       </x:c>
       <x:c r="E251" s="17"/>
       <x:c r="F251" s="17"/>
@@ -8669,16 +8663,16 @@
     </x:row>
     <x:row r="252" ht="30" customHeight="1">
       <x:c r="A252" s="20" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B252" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C252" s="8" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="D252" s="11" t="s">
         <x:v>602</x:v>
-      </x:c>
-      <x:c r="B252" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C252" s="8" t="s">
-        <x:v>603</x:v>
-      </x:c>
-      <x:c r="D252" s="11" t="s">
-        <x:v>604</x:v>
       </x:c>
       <x:c r="E252" s="17"/>
       <x:c r="F252" s="17"/>
@@ -8691,16 +8685,16 @@
     </x:row>
     <x:row r="253" ht="30" customHeight="1">
       <x:c r="A253" s="20" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B253" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C253" s="8" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="D253" s="11" t="s">
         <x:v>605</x:v>
-      </x:c>
-      <x:c r="B253" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C253" s="8" t="s">
-        <x:v>606</x:v>
-      </x:c>
-      <x:c r="D253" s="11" t="s">
-        <x:v>607</x:v>
       </x:c>
       <x:c r="E253" s="17"/>
       <x:c r="F253" s="17"/>
@@ -8713,16 +8707,16 @@
     </x:row>
     <x:row r="254" ht="30" customHeight="1">
       <x:c r="A254" s="20" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B254" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C254" s="8" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="D254" s="11" t="s">
         <x:v>608</x:v>
-      </x:c>
-      <x:c r="B254" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C254" s="8" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="D254" s="11" t="s">
-        <x:v>610</x:v>
       </x:c>
       <x:c r="E254" s="17"/>
       <x:c r="F254" s="17"/>
@@ -8735,16 +8729,16 @@
     </x:row>
     <x:row r="255" ht="30" customHeight="1">
       <x:c r="A255" s="20" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B255" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C255" s="8" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="D255" s="11" t="s">
         <x:v>611</x:v>
-      </x:c>
-      <x:c r="B255" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C255" s="8" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="D255" s="11" t="s">
-        <x:v>613</x:v>
       </x:c>
       <x:c r="E255" s="17"/>
       <x:c r="F255" s="17"/>
@@ -8757,16 +8751,16 @@
     </x:row>
     <x:row r="256" ht="30" customHeight="1">
       <x:c r="A256" s="20" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B256" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C256" s="8" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="D256" s="11" t="s">
         <x:v>614</x:v>
-      </x:c>
-      <x:c r="B256" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C256" s="8" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="D256" s="11" t="s">
-        <x:v>616</x:v>
       </x:c>
       <x:c r="E256" s="17"/>
       <x:c r="F256" s="17"/>
@@ -8779,16 +8773,16 @@
     </x:row>
     <x:row r="257" ht="30" customHeight="1">
       <x:c r="A257" s="20" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B257" s="14" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C257" s="8" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="D257" s="11" t="s">
         <x:v>617</x:v>
-      </x:c>
-      <x:c r="B257" s="14" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C257" s="8" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="D257" s="11" t="s">
-        <x:v>619</x:v>
       </x:c>
       <x:c r="E257" s="17"/>
       <x:c r="F257" s="17"/>
@@ -8801,16 +8795,16 @@
     </x:row>
     <x:row r="258" ht="30" customHeight="1">
       <x:c r="A258" s="20" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B258" s="14" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="C258" s="8" t="s">
         <x:v>620</x:v>
       </x:c>
-      <x:c r="B258" s="14" t="s">
+      <x:c r="D258" s="11" t="s">
         <x:v>621</x:v>
-      </x:c>
-      <x:c r="C258" s="8" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="D258" s="11" t="s">
-        <x:v>623</x:v>
       </x:c>
       <x:c r="E258" s="17"/>
       <x:c r="F258" s="17"/>
@@ -8823,16 +8817,16 @@
     </x:row>
     <x:row r="259" ht="30" customHeight="1">
       <x:c r="A259" s="20" t="s">
-        <x:v>624</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="B259" s="14" t="s">
-        <x:v>621</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="C259" s="8" t="s">
-        <x:v>625</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D259" s="11" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="E259" s="17"/>
       <x:c r="F259" s="17"/>
@@ -8845,16 +8839,16 @@
     </x:row>
     <x:row r="260" ht="30" customHeight="1">
       <x:c r="A260" s="20" t="s">
-        <x:v>626</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B260" s="14" t="s">
-        <x:v>621</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="C260" s="8" t="s">
-        <x:v>625</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D260" s="11" t="s">
-        <x:v>533</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="E260" s="17"/>
       <x:c r="F260" s="17"/>
@@ -8867,16 +8861,16 @@
     </x:row>
     <x:row r="261" ht="30" customHeight="1">
       <x:c r="A261" s="20" t="s">
-        <x:v>627</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="B261" s="14" t="s">
-        <x:v>621</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="C261" s="8" t="s">
-        <x:v>625</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D261" s="11" t="s">
-        <x:v>535</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="E261" s="17"/>
       <x:c r="F261" s="17"/>
@@ -8889,16 +8883,16 @@
     </x:row>
     <x:row r="262" ht="30" customHeight="1">
       <x:c r="A262" s="20" t="s">
-        <x:v>628</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="B262" s="14" t="s">
-        <x:v>621</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="C262" s="8" t="s">
-        <x:v>625</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D262" s="11" t="s">
-        <x:v>629</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="E262" s="17"/>
       <x:c r="F262" s="17"/>
@@ -8911,16 +8905,16 @@
     </x:row>
     <x:row r="263" ht="30" customHeight="1">
       <x:c r="A263" s="20" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="B263" s="14" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="C263" s="8" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="D263" s="11" t="s">
         <x:v>630</x:v>
-      </x:c>
-      <x:c r="B263" s="14" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="C263" s="8" t="s">
-        <x:v>631</x:v>
-      </x:c>
-      <x:c r="D263" s="11" t="s">
-        <x:v>632</x:v>
       </x:c>
       <x:c r="E263" s="17"/>
       <x:c r="F263" s="17"/>
@@ -8933,16 +8927,16 @@
     </x:row>
     <x:row r="264" ht="30" customHeight="1">
       <x:c r="A264" s="20" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="B264" s="14" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C264" s="8" t="s">
         <x:v>633</x:v>
       </x:c>
-      <x:c r="B264" s="14" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="C264" s="8" t="s">
-        <x:v>635</x:v>
-      </x:c>
       <x:c r="D264" s="11" t="s">
-        <x:v>592</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E264" s="17"/>
       <x:c r="F264" s="17"/>
@@ -8955,16 +8949,16 @@
     </x:row>
     <x:row r="265" ht="30" customHeight="1">
       <x:c r="A265" s="20" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="B265" s="14" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C265" s="8" t="s">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="D265" s="11" t="s">
         <x:v>636</x:v>
-      </x:c>
-      <x:c r="B265" s="14" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="C265" s="8" t="s">
-        <x:v>637</x:v>
-      </x:c>
-      <x:c r="D265" s="11" t="s">
-        <x:v>638</x:v>
       </x:c>
       <x:c r="E265" s="17"/>
       <x:c r="F265" s="17"/>
@@ -8977,16 +8971,16 @@
     </x:row>
     <x:row r="266" ht="30" customHeight="1">
       <x:c r="A266" s="20" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="B266" s="14" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C266" s="8" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="D266" s="11" t="s">
         <x:v>639</x:v>
-      </x:c>
-      <x:c r="B266" s="14" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="C266" s="8" t="s">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="D266" s="11" t="s">
-        <x:v>641</x:v>
       </x:c>
       <x:c r="E266" s="17"/>
       <x:c r="F266" s="17"/>
@@ -8999,16 +8993,16 @@
     </x:row>
     <x:row r="267" ht="30" customHeight="1">
       <x:c r="A267" s="20" t="s">
-        <x:v>642</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="B267" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C267" s="8" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D267" s="11" t="s">
-        <x:v>592</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E267" s="17"/>
       <x:c r="F267" s="17"/>
@@ -9021,16 +9015,16 @@
     </x:row>
     <x:row r="268" ht="30" customHeight="1">
       <x:c r="A268" s="20" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="B268" s="14" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C268" s="8" t="s">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="D268" s="11" t="s">
         <x:v>643</x:v>
-      </x:c>
-      <x:c r="B268" s="14" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="C268" s="8" t="s">
-        <x:v>644</x:v>
-      </x:c>
-      <x:c r="D268" s="11" t="s">
-        <x:v>645</x:v>
       </x:c>
       <x:c r="E268" s="17"/>
       <x:c r="F268" s="17"/>
@@ -9043,16 +9037,16 @@
     </x:row>
     <x:row r="269" ht="30" customHeight="1">
       <x:c r="A269" s="20" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="B269" s="14" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C269" s="8" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="D269" s="11" t="s">
         <x:v>646</x:v>
-      </x:c>
-      <x:c r="B269" s="14" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="C269" s="8" t="s">
-        <x:v>647</x:v>
-      </x:c>
-      <x:c r="D269" s="11" t="s">
-        <x:v>648</x:v>
       </x:c>
       <x:c r="E269" s="17"/>
       <x:c r="F269" s="17"/>
@@ -9065,16 +9059,16 @@
     </x:row>
     <x:row r="270" ht="30" customHeight="1">
       <x:c r="A270" s="20" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="B270" s="14" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C270" s="8" t="s">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="D270" s="11" t="s">
         <x:v>649</x:v>
-      </x:c>
-      <x:c r="B270" s="14" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="C270" s="8" t="s">
-        <x:v>650</x:v>
-      </x:c>
-      <x:c r="D270" s="11" t="s">
-        <x:v>651</x:v>
       </x:c>
       <x:c r="E270" s="17"/>
       <x:c r="F270" s="17"/>
@@ -9087,16 +9081,16 @@
     </x:row>
     <x:row r="271" ht="30" customHeight="1">
       <x:c r="A271" s="20" t="s">
-        <x:v>652</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="B271" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C271" s="8" t="s">
-        <x:v>650</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="D271" s="11" t="s">
-        <x:v>653</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="E271" s="17"/>
       <x:c r="F271" s="17"/>
@@ -9109,16 +9103,16 @@
     </x:row>
     <x:row r="272" ht="30" customHeight="1">
       <x:c r="A272" s="20" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="B272" s="14" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C272" s="8" t="s">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="D272" s="11" t="s">
         <x:v>654</x:v>
-      </x:c>
-      <x:c r="B272" s="14" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="C272" s="8" t="s">
-        <x:v>655</x:v>
-      </x:c>
-      <x:c r="D272" s="11" t="s">
-        <x:v>656</x:v>
       </x:c>
       <x:c r="E272" s="17"/>
       <x:c r="F272" s="17"/>
@@ -9131,16 +9125,16 @@
     </x:row>
     <x:row r="273" ht="30" customHeight="1">
       <x:c r="A273" s="20" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="B273" s="14" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C273" s="8" t="s">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="D273" s="11" t="s">
         <x:v>657</x:v>
-      </x:c>
-      <x:c r="B273" s="14" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="C273" s="8" t="s">
-        <x:v>658</x:v>
-      </x:c>
-      <x:c r="D273" s="11" t="s">
-        <x:v>659</x:v>
       </x:c>
       <x:c r="E273" s="17"/>
       <x:c r="F273" s="17"/>
@@ -9153,16 +9147,16 @@
     </x:row>
     <x:row r="274" ht="30" customHeight="1">
       <x:c r="A274" s="20" t="s">
-        <x:v>660</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="B274" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C274" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D274" s="11" t="s">
-        <x:v>661</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="E274" s="17"/>
       <x:c r="F274" s="17"/>
@@ -9175,16 +9169,16 @@
     </x:row>
     <x:row r="275" ht="30" customHeight="1">
       <x:c r="A275" s="20" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="B275" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C275" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D275" s="11" t="s">
-        <x:v>663</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="E275" s="17"/>
       <x:c r="F275" s="17"/>
@@ -9197,16 +9191,16 @@
     </x:row>
     <x:row r="276" ht="30" customHeight="1">
       <x:c r="A276" s="20" t="s">
-        <x:v>664</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="B276" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C276" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D276" s="11" t="s">
-        <x:v>665</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="E276" s="17"/>
       <x:c r="F276" s="17"/>
@@ -9219,16 +9213,16 @@
     </x:row>
     <x:row r="277" ht="30" customHeight="1">
       <x:c r="A277" s="20" t="s">
-        <x:v>666</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="B277" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C277" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D277" s="11" t="s">
-        <x:v>667</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="E277" s="17"/>
       <x:c r="F277" s="17"/>
@@ -9241,16 +9235,16 @@
     </x:row>
     <x:row r="278" ht="30" customHeight="1">
       <x:c r="A278" s="20" t="s">
-        <x:v>668</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="B278" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C278" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D278" s="11" t="s">
-        <x:v>669</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="E278" s="17"/>
       <x:c r="F278" s="17"/>
@@ -9263,16 +9257,16 @@
     </x:row>
     <x:row r="279" ht="30" customHeight="1">
       <x:c r="A279" s="20" t="s">
-        <x:v>670</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="B279" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C279" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D279" s="11" t="s">
-        <x:v>671</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="E279" s="17"/>
       <x:c r="F279" s="17"/>
@@ -9285,16 +9279,16 @@
     </x:row>
     <x:row r="280" ht="30" customHeight="1">
       <x:c r="A280" s="20" t="s">
-        <x:v>672</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="B280" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C280" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D280" s="11" t="s">
-        <x:v>673</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="E280" s="17"/>
       <x:c r="F280" s="17"/>
@@ -9307,16 +9301,16 @@
     </x:row>
     <x:row r="281" ht="30" customHeight="1">
       <x:c r="A281" s="20" t="s">
-        <x:v>674</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="B281" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C281" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D281" s="11" t="s">
-        <x:v>675</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="E281" s="17"/>
       <x:c r="F281" s="17"/>
@@ -9329,16 +9323,16 @@
     </x:row>
     <x:row r="282" ht="30" customHeight="1">
       <x:c r="A282" s="20" t="s">
-        <x:v>676</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="B282" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C282" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D282" s="11" t="s">
-        <x:v>677</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="E282" s="17"/>
       <x:c r="F282" s="17"/>
@@ -9351,16 +9345,16 @@
     </x:row>
     <x:row r="283" ht="30" customHeight="1">
       <x:c r="A283" s="20" t="s">
-        <x:v>678</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="B283" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C283" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D283" s="11" t="s">
-        <x:v>679</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="E283" s="17"/>
       <x:c r="F283" s="17"/>
@@ -9373,16 +9367,16 @@
     </x:row>
     <x:row r="284" ht="30" customHeight="1">
       <x:c r="A284" s="20" t="s">
-        <x:v>680</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B284" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C284" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D284" s="11" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="E284" s="17"/>
       <x:c r="F284" s="17"/>
@@ -9395,16 +9389,16 @@
     </x:row>
     <x:row r="285" ht="30" customHeight="1">
       <x:c r="A285" s="20" t="s">
-        <x:v>682</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="B285" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C285" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D285" s="11" t="s">
-        <x:v>683</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="E285" s="17"/>
       <x:c r="F285" s="17"/>
@@ -9417,16 +9411,16 @@
     </x:row>
     <x:row r="286" ht="30" customHeight="1">
       <x:c r="A286" s="20" t="s">
-        <x:v>684</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="B286" s="14" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C286" s="8" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D286" s="11" t="s">
-        <x:v>685</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="E286" s="17"/>
       <x:c r="F286" s="17"/>
@@ -9439,16 +9433,16 @@
     </x:row>
     <x:row r="287" ht="30" customHeight="1">
       <x:c r="A287" s="20" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="B287" s="14" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C287" s="8" t="s">
         <x:v>686</x:v>
       </x:c>
-      <x:c r="B287" s="14" t="s">
+      <x:c r="D287" s="11" t="s">
         <x:v>687</x:v>
-      </x:c>
-      <x:c r="C287" s="8" t="s">
-        <x:v>688</x:v>
-      </x:c>
-      <x:c r="D287" s="11" t="s">
-        <x:v>689</x:v>
       </x:c>
       <x:c r="E287" s="17"/>
       <x:c r="F287" s="17"/>
@@ -9461,16 +9455,16 @@
     </x:row>
     <x:row r="288" ht="30" customHeight="1">
       <x:c r="A288" s="20" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="B288" s="14" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C288" s="8" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="D288" s="11" t="s">
         <x:v>690</x:v>
-      </x:c>
-      <x:c r="B288" s="14" t="s">
-        <x:v>687</x:v>
-      </x:c>
-      <x:c r="C288" s="8" t="s">
-        <x:v>691</x:v>
-      </x:c>
-      <x:c r="D288" s="11" t="s">
-        <x:v>692</x:v>
       </x:c>
       <x:c r="E288" s="17"/>
       <x:c r="F288" s="17"/>
@@ -9483,16 +9477,16 @@
     </x:row>
     <x:row r="289" ht="30" customHeight="1">
       <x:c r="A289" s="20" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="B289" s="14" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C289" s="8" t="s">
+        <x:v>692</x:v>
+      </x:c>
+      <x:c r="D289" s="11" t="s">
         <x:v>693</x:v>
-      </x:c>
-      <x:c r="B289" s="14" t="s">
-        <x:v>687</x:v>
-      </x:c>
-      <x:c r="C289" s="8" t="s">
-        <x:v>694</x:v>
-      </x:c>
-      <x:c r="D289" s="11" t="s">
-        <x:v>695</x:v>
       </x:c>
       <x:c r="E289" s="17"/>
       <x:c r="F289" s="17"/>
@@ -9505,16 +9499,16 @@
     </x:row>
     <x:row r="290" ht="30" customHeight="1">
       <x:c r="A290" s="20" t="s">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="B290" s="14" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C290" s="8" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="D290" s="11" t="s">
         <x:v>696</x:v>
-      </x:c>
-      <x:c r="B290" s="14" t="s">
-        <x:v>687</x:v>
-      </x:c>
-      <x:c r="C290" s="8" t="s">
-        <x:v>697</x:v>
-      </x:c>
-      <x:c r="D290" s="11" t="s">
-        <x:v>698</x:v>
       </x:c>
       <x:c r="E290" s="17"/>
       <x:c r="F290" s="17"/>
@@ -9527,16 +9521,16 @@
     </x:row>
     <x:row r="291" ht="30" customHeight="1">
       <x:c r="A291" s="20" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="B291" s="14" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C291" s="8" t="s">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="D291" s="11" t="s">
         <x:v>699</x:v>
-      </x:c>
-      <x:c r="B291" s="14" t="s">
-        <x:v>687</x:v>
-      </x:c>
-      <x:c r="C291" s="8" t="s">
-        <x:v>700</x:v>
-      </x:c>
-      <x:c r="D291" s="11" t="s">
-        <x:v>701</x:v>
       </x:c>
       <x:c r="E291" s="17"/>
       <x:c r="F291" s="17"/>
@@ -9549,16 +9543,16 @@
     </x:row>
     <x:row r="292" ht="30" customHeight="1">
       <x:c r="A292" s="20" t="s">
-        <x:v>702</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B292" s="14" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C292" s="8" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="D292" s="11" t="s">
         <x:v>687</x:v>
-      </x:c>
-      <x:c r="C292" s="8" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="D292" s="11" t="s">
-        <x:v>689</x:v>
       </x:c>
       <x:c r="E292" s="17"/>
       <x:c r="F292" s="17"/>
@@ -9571,16 +9565,16 @@
     </x:row>
     <x:row r="293" ht="30" customHeight="1">
       <x:c r="A293" s="20" t="s">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="B293" s="14" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="C293" s="8" t="s">
+        <x:v>703</x:v>
+      </x:c>
+      <x:c r="D293" s="11" t="s">
         <x:v>704</x:v>
-      </x:c>
-      <x:c r="B293" s="14" t="s">
-        <x:v>687</x:v>
-      </x:c>
-      <x:c r="C293" s="8" t="s">
-        <x:v>705</x:v>
-      </x:c>
-      <x:c r="D293" s="11" t="s">
-        <x:v>706</x:v>
       </x:c>
       <x:c r="E293" s="17"/>
       <x:c r="F293" s="17"/>
@@ -9593,16 +9587,16 @@
     </x:row>
     <x:row r="294" ht="30" customHeight="1">
       <x:c r="A294" s="20" t="s">
+        <x:v>705</x:v>
+      </x:c>
+      <x:c r="B294" s="14" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="C294" s="8" t="s">
         <x:v>707</x:v>
       </x:c>
-      <x:c r="B294" s="14" t="s">
+      <x:c r="D294" s="11" t="s">
         <x:v>708</x:v>
-      </x:c>
-      <x:c r="C294" s="8" t="s">
-        <x:v>709</x:v>
-      </x:c>
-      <x:c r="D294" s="11" t="s">
-        <x:v>710</x:v>
       </x:c>
       <x:c r="E294" s="17"/>
       <x:c r="F294" s="17"/>
@@ -9615,16 +9609,16 @@
     </x:row>
     <x:row r="295" ht="30" customHeight="1">
       <x:c r="A295" s="20" t="s">
-        <x:v>711</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="B295" s="14" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="C295" s="8" t="s">
-        <x:v>709</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D295" s="11" t="s">
-        <x:v>712</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E295" s="17"/>
       <x:c r="F295" s="17"/>
@@ -9637,16 +9631,16 @@
     </x:row>
     <x:row r="296" ht="30" customHeight="1">
       <x:c r="A296" s="20" t="s">
-        <x:v>713</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B296" s="14" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="C296" s="8" t="s">
-        <x:v>709</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D296" s="11" t="s">
-        <x:v>714</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="E296" s="17"/>
       <x:c r="F296" s="17"/>
@@ -9659,16 +9653,16 @@
     </x:row>
     <x:row r="297" ht="30" customHeight="1">
       <x:c r="A297" s="20" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B297" s="14" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="C297" s="8" t="s">
-        <x:v>709</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D297" s="11" t="s">
-        <x:v>716</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="E297" s="17"/>
       <x:c r="F297" s="17"/>
@@ -9681,16 +9675,16 @@
     </x:row>
     <x:row r="298" ht="30" customHeight="1">
       <x:c r="A298" s="20" t="s">
-        <x:v>717</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B298" s="14" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="C298" s="8" t="s">
-        <x:v>709</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D298" s="11" t="s">
-        <x:v>718</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="E298" s="17"/>
       <x:c r="F298" s="17"/>
@@ -9703,16 +9697,16 @@
     </x:row>
     <x:row r="299" ht="30" customHeight="1">
       <x:c r="A299" s="20" t="s">
-        <x:v>719</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="B299" s="14" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="C299" s="8" t="s">
-        <x:v>709</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D299" s="11" t="s">
-        <x:v>720</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="E299" s="17"/>
       <x:c r="F299" s="17"/>
@@ -9725,16 +9719,16 @@
     </x:row>
     <x:row r="300" ht="30" customHeight="1">
       <x:c r="A300" s="20" t="s">
+        <x:v>719</x:v>
+      </x:c>
+      <x:c r="B300" s="14" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="C300" s="8" t="s">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="D300" s="11" t="s">
         <x:v>721</x:v>
-      </x:c>
-      <x:c r="B300" s="14" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="C300" s="8" t="s">
-        <x:v>722</x:v>
-      </x:c>
-      <x:c r="D300" s="11" t="s">
-        <x:v>723</x:v>
       </x:c>
       <x:c r="E300" s="17"/>
       <x:c r="F300" s="17"/>
@@ -9747,16 +9741,16 @@
     </x:row>
     <x:row r="301" ht="30" customHeight="1">
       <x:c r="A301" s="20" t="s">
-        <x:v>724</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="B301" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C301" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D301" s="11" t="s">
-        <x:v>725</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="E301" s="17"/>
       <x:c r="F301" s="17"/>
@@ -9769,16 +9763,16 @@
     </x:row>
     <x:row r="302" ht="30" customHeight="1">
       <x:c r="A302" s="20" t="s">
-        <x:v>726</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="B302" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C302" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D302" s="11" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E302" s="17"/>
       <x:c r="F302" s="17"/>
@@ -9791,16 +9785,16 @@
     </x:row>
     <x:row r="303" ht="30" customHeight="1">
       <x:c r="A303" s="20" t="s">
-        <x:v>728</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="B303" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C303" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D303" s="11" t="s">
-        <x:v>729</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="E303" s="17"/>
       <x:c r="F303" s="17"/>
@@ -9813,16 +9807,16 @@
     </x:row>
     <x:row r="304" ht="30" customHeight="1">
       <x:c r="A304" s="20" t="s">
-        <x:v>730</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B304" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C304" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D304" s="11" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="E304" s="17"/>
       <x:c r="F304" s="17"/>
@@ -9835,16 +9829,16 @@
     </x:row>
     <x:row r="305" ht="30" customHeight="1">
       <x:c r="A305" s="20" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="B305" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C305" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D305" s="11" t="s">
-        <x:v>733</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="E305" s="17"/>
       <x:c r="F305" s="17"/>
@@ -9857,16 +9851,16 @@
     </x:row>
     <x:row r="306" ht="30" customHeight="1">
       <x:c r="A306" s="20" t="s">
-        <x:v>734</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="B306" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C306" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D306" s="11" t="s">
-        <x:v>735</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="E306" s="17"/>
       <x:c r="F306" s="17"/>
@@ -9879,16 +9873,16 @@
     </x:row>
     <x:row r="307" ht="30" customHeight="1">
       <x:c r="A307" s="20" t="s">
-        <x:v>736</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="B307" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C307" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D307" s="11" t="s">
-        <x:v>737</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="E307" s="17"/>
       <x:c r="F307" s="17"/>
@@ -9901,16 +9895,16 @@
     </x:row>
     <x:row r="308" ht="30" customHeight="1">
       <x:c r="A308" s="20" t="s">
-        <x:v>738</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B308" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C308" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D308" s="11" t="s">
-        <x:v>739</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="E308" s="17"/>
       <x:c r="F308" s="17"/>
@@ -9923,16 +9917,16 @@
     </x:row>
     <x:row r="309" ht="30" customHeight="1">
       <x:c r="A309" s="20" t="s">
-        <x:v>740</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="B309" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C309" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D309" s="11" t="s">
-        <x:v>741</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="E309" s="17"/>
       <x:c r="F309" s="17"/>
@@ -9945,16 +9939,16 @@
     </x:row>
     <x:row r="310" ht="30" customHeight="1">
       <x:c r="A310" s="20" t="s">
-        <x:v>742</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="B310" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C310" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="D310" s="11" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="E310" s="17"/>
       <x:c r="F310" s="17"/>
@@ -9967,16 +9961,16 @@
     </x:row>
     <x:row r="311" ht="30" customHeight="1">
       <x:c r="A311" s="20" t="s">
-        <x:v>744</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B311" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C311" s="8" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="D311" s="11" t="s">
-        <x:v>746</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="E311" s="17"/>
       <x:c r="F311" s="17"/>
@@ -9989,16 +9983,16 @@
     </x:row>
     <x:row r="312" ht="30" customHeight="1">
       <x:c r="A312" s="20" t="s">
-        <x:v>747</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="B312" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C312" s="8" t="s">
-        <x:v>748</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="D312" s="11" t="str">
-        <x:v>15 000 ₽ · разовая оплата</x:v>
+        <x:v>530 Br · разовая оплата</x:v>
       </x:c>
       <x:c r="E312" s="17"/>
       <x:c r="F312" s="17"/>
@@ -10011,16 +10005,16 @@
     </x:row>
     <x:row r="313" ht="30" customHeight="1">
       <x:c r="A313" s="20" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="B313" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C313" s="8" t="s">
-        <x:v>750</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="D313" s="11" t="s">
-        <x:v>751</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="E313" s="17"/>
       <x:c r="F313" s="17"/>
@@ -10033,13 +10027,13 @@
     </x:row>
     <x:row r="314" ht="30" customHeight="1">
       <x:c r="A314" s="20" t="s">
-        <x:v>752</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B314" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C314" s="8" t="s">
-        <x:v>753</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="D314" s="11" t="s">
         <x:v>76</x:v>
@@ -10055,13 +10049,13 @@
     </x:row>
     <x:row r="315" ht="30" customHeight="1">
       <x:c r="A315" s="20" t="s">
-        <x:v>754</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="B315" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C315" s="8" t="s">
-        <x:v>755</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="D315" s="11" t="s">
         <x:v>465</x:v>
@@ -10077,13 +10071,13 @@
     </x:row>
     <x:row r="316" ht="30" customHeight="1">
       <x:c r="A316" s="20" t="s">
-        <x:v>756</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B316" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C316" s="8" t="s">
-        <x:v>757</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="D316" s="11" t="s">
         <x:v>467</x:v>
@@ -10099,13 +10093,13 @@
     </x:row>
     <x:row r="317" ht="30" customHeight="1">
       <x:c r="A317" s="20" t="s">
-        <x:v>758</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="B317" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C317" s="8" t="s">
-        <x:v>759</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="D317" s="11" t="s">
         <x:v>469</x:v>
@@ -10121,13 +10115,13 @@
     </x:row>
     <x:row r="318" ht="30" customHeight="1">
       <x:c r="A318" s="20" t="s">
-        <x:v>760</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="B318" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C318" s="8" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="D318" s="11" t="s">
         <x:v>471</x:v>
@@ -10143,16 +10137,16 @@
     </x:row>
     <x:row r="319" ht="30" customHeight="1">
       <x:c r="A319" s="20" t="s">
-        <x:v>762</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B319" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C319" s="8" t="s">
-        <x:v>763</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="D319" s="11" t="s">
-        <x:v>764</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="E319" s="17"/>
       <x:c r="F319" s="17"/>
@@ -10165,16 +10159,16 @@
     </x:row>
     <x:row r="320" ht="30" customHeight="1">
       <x:c r="A320" s="20" t="s">
-        <x:v>765</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B320" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C320" s="8" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="D320" s="11" t="s">
-        <x:v>767</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="E320" s="17"/>
       <x:c r="F320" s="17"/>
@@ -10187,16 +10181,16 @@
     </x:row>
     <x:row r="321" ht="30" customHeight="1">
       <x:c r="A321" s="20" t="s">
-        <x:v>768</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B321" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C321" s="8" t="s">
-        <x:v>769</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="D321" s="11" t="s">
-        <x:v>770</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="E321" s="17"/>
       <x:c r="F321" s="17"/>
@@ -10209,16 +10203,16 @@
     </x:row>
     <x:row r="322" ht="30" customHeight="1">
       <x:c r="A322" s="20" t="s">
-        <x:v>771</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="B322" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C322" s="8" t="s">
-        <x:v>772</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="D322" s="11" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="E322" s="17"/>
       <x:c r="F322" s="17"/>
@@ -10231,16 +10225,16 @@
     </x:row>
     <x:row r="323" ht="30" customHeight="1">
       <x:c r="A323" s="20" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B323" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C323" s="8" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="D323" s="11" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="E323" s="17"/>
       <x:c r="F323" s="17"/>
@@ -10253,16 +10247,16 @@
     </x:row>
     <x:row r="324" ht="30" customHeight="1">
       <x:c r="A324" s="20" t="s">
-        <x:v>777</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="B324" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C324" s="8" t="s">
-        <x:v>778</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="D324" s="11" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="E324" s="17"/>
       <x:c r="F324" s="17"/>
@@ -10275,16 +10269,16 @@
     </x:row>
     <x:row r="325" ht="30" customHeight="1">
       <x:c r="A325" s="20" t="s">
-        <x:v>780</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B325" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C325" s="8" t="s">
-        <x:v>781</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="D325" s="11" t="s">
-        <x:v>782</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="E325" s="17"/>
       <x:c r="F325" s="17"/>
@@ -10297,16 +10291,16 @@
     </x:row>
     <x:row r="326" ht="30" customHeight="1">
       <x:c r="A326" s="20" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="B326" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C326" s="8" t="s">
-        <x:v>784</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="D326" s="11" t="s">
-        <x:v>785</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="E326" s="17"/>
       <x:c r="F326" s="17"/>
@@ -10319,16 +10313,16 @@
     </x:row>
     <x:row r="327" ht="30" customHeight="1">
       <x:c r="A327" s="20" t="s">
-        <x:v>786</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="B327" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C327" s="8" t="s">
-        <x:v>787</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="D327" s="11" t="s">
-        <x:v>788</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="E327" s="17"/>
       <x:c r="F327" s="17"/>
@@ -10341,16 +10335,16 @@
     </x:row>
     <x:row r="328" ht="30" customHeight="1">
       <x:c r="A328" s="20" t="s">
-        <x:v>789</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="B328" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C328" s="8" t="s">
-        <x:v>790</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="D328" s="11" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="E328" s="17"/>
       <x:c r="F328" s="17"/>
@@ -10363,16 +10357,16 @@
     </x:row>
     <x:row r="329" ht="30" customHeight="1">
       <x:c r="A329" s="20" t="s">
-        <x:v>792</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B329" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C329" s="8" t="s">
-        <x:v>793</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="D329" s="11" t="s">
-        <x:v>794</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="E329" s="17"/>
       <x:c r="F329" s="17"/>
@@ -10385,16 +10379,16 @@
     </x:row>
     <x:row r="330" ht="30" customHeight="1">
       <x:c r="A330" s="20" t="s">
-        <x:v>795</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="B330" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C330" s="8" t="s">
-        <x:v>796</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="D330" s="11" t="s">
-        <x:v>797</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="E330" s="17"/>
       <x:c r="F330" s="17"/>
@@ -10407,16 +10401,16 @@
     </x:row>
     <x:row r="331" ht="30" customHeight="1">
       <x:c r="A331" s="21" t="s">
-        <x:v>798</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="B331" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C331" s="9" t="s">
-        <x:v>799</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="D331" s="12" t="s">
-        <x:v>800</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="E331" s="18"/>
       <x:c r="F331" s="18"/>
@@ -10429,16 +10423,16 @@
     </x:row>
     <x:row r="332" ht="15">
       <x:c r="A332" s="23" t="s">
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="B332" s="24" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C332" s="25" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="D332" s="26" t="s">
         <x:v>801</x:v>
-      </x:c>
-      <x:c r="B332" s="24" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="C332" s="25" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="D332" s="26" t="s">
-        <x:v>803</x:v>
       </x:c>
       <x:c r="E332" s="22"/>
       <x:c r="F332" s="22"/>
@@ -10451,16 +10445,16 @@
     </x:row>
     <x:row r="333" ht="15">
       <x:c r="A333" s="23" t="s">
-        <x:v>804</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="B333" s="27" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C333" s="28" t="s">
-        <x:v>805</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="D333" s="29" t="s">
-        <x:v>806</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="E333" s="22"/>
       <x:c r="F333" s="22"/>
@@ -10473,16 +10467,16 @@
     </x:row>
     <x:row r="334" ht="15">
       <x:c r="A334" s="23" t="s">
-        <x:v>807</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B334" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C334" s="25" t="s">
-        <x:v>808</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="D334" s="26" t="s">
-        <x:v>809</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="E334" s="22"/>
       <x:c r="F334" s="22"/>
@@ -10495,16 +10489,16 @@
     </x:row>
     <x:row r="335" ht="15">
       <x:c r="A335" s="23" t="s">
-        <x:v>810</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="B335" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C335" s="28" t="s">
-        <x:v>811</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="D335" s="29" t="s">
-        <x:v>812</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="E335" s="22"/>
       <x:c r="F335" s="22"/>
@@ -10517,16 +10511,16 @@
     </x:row>
     <x:row r="336" ht="15">
       <x:c r="A336" s="23" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B336" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C336" s="25" t="s">
-        <x:v>814</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="D336" s="26" t="s">
-        <x:v>815</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="E336" s="22"/>
       <x:c r="F336" s="22"/>
@@ -10539,16 +10533,16 @@
     </x:row>
     <x:row r="337" ht="15">
       <x:c r="A337" s="23" t="s">
-        <x:v>816</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B337" s="27" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C337" s="28" t="s">
-        <x:v>817</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="D337" s="29" t="s">
-        <x:v>818</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="E337" s="22"/>
       <x:c r="F337" s="22"/>
@@ -10561,16 +10555,16 @@
     </x:row>
     <x:row r="338" ht="15">
       <x:c r="A338" s="23" t="s">
-        <x:v>819</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="B338" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="C338" s="25" t="s">
-        <x:v>820</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="D338" s="26" t="s">
-        <x:v>821</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="E338" s="22"/>
       <x:c r="F338" s="22"/>
@@ -10583,16 +10577,16 @@
     </x:row>
     <x:row r="339" ht="15">
       <x:c r="A339" s="23" t="s">
-        <x:v>822</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="B339" s="27" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C339" s="28" t="s">
-        <x:v>823</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="D339" s="29" t="s">
-        <x:v>824</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="E339" s="22"/>
       <x:c r="F339" s="22"/>
@@ -10605,16 +10599,16 @@
     </x:row>
     <x:row r="340" ht="15">
       <x:c r="A340" s="23" t="s">
-        <x:v>825</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="B340" s="24" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C340" s="25" t="s">
-        <x:v>826</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="D340" s="26" t="s">
-        <x:v>827</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="E340" s="22"/>
       <x:c r="F340" s="22"/>
@@ -10627,16 +10621,16 @@
     </x:row>
     <x:row r="341" ht="29.25">
       <x:c r="A341" s="23" t="s">
-        <x:v>828</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="B341" s="27" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C341" s="28" t="s">
-        <x:v>829</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="D341" s="29" t="s">
-        <x:v>830</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="E341" s="22"/>
       <x:c r="F341" s="22"/>
@@ -10649,16 +10643,16 @@
     </x:row>
     <x:row r="342" ht="29.25">
       <x:c r="A342" s="23" t="s">
-        <x:v>831</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="B342" s="24" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C342" s="25" t="s">
-        <x:v>832</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="D342" s="26" t="s">
-        <x:v>833</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="E342" s="22"/>
       <x:c r="F342" s="22"/>
@@ -10671,16 +10665,16 @@
     </x:row>
     <x:row r="343" ht="43.5">
       <x:c r="A343" s="23" t="s">
-        <x:v>834</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="B343" s="27" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C343" s="28" t="s">
-        <x:v>835</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="D343" s="29" t="s">
-        <x:v>836</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="E343" s="22"/>
       <x:c r="F343" s="22"/>
@@ -10777,63 +10771,63 @@
     </x:row>
     <x:row r="350">
       <x:c r="A350" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="B350" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C350" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="D350" t="s">
-        <x:v>838</x:v>
+        <x:v>836</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
       <x:c r="A351" t="s">
+        <x:v>837</x:v>
+      </x:c>
+      <x:c r="B351" t="s">
+        <x:v>838</x:v>
+      </x:c>
+      <x:c r="C351" t="s">
         <x:v>839</x:v>
       </x:c>
-      <x:c r="B351" t="s">
+      <x:c r="D351" t="s">
         <x:v>840</x:v>
-      </x:c>
-      <x:c r="C351" t="s">
-        <x:v>841</x:v>
-      </x:c>
-      <x:c r="D351" t="s">
-        <x:v>842</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
       <x:c r="A352" t="s">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="B352" t="s">
+        <x:v>838</x:v>
+      </x:c>
+      <x:c r="C352" t="s">
+        <x:v>842</x:v>
+      </x:c>
+      <x:c r="D352" t="s">
         <x:v>843</x:v>
-      </x:c>
-      <x:c r="B352" t="s">
-        <x:v>840</x:v>
-      </x:c>
-      <x:c r="C352" t="s">
-        <x:v>844</x:v>
-      </x:c>
-      <x:c r="D352" t="s">
-        <x:v>845</x:v>
       </x:c>
     </x:row>
     <x:row r="353">
       <x:c r="A353" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="B353" t="s">
+        <x:v>838</x:v>
+      </x:c>
+      <x:c r="C353" t="s">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="D353" t="s">
         <x:v>846</x:v>
-      </x:c>
-      <x:c r="B353" t="s">
-        <x:v>840</x:v>
-      </x:c>
-      <x:c r="C353" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="D353" t="s">
-        <x:v>848</x:v>
       </x:c>
     </x:row>
     <x:row r="354">
       <x:c r="A354" t="s">
-        <x:v>849</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B354" t="s">
         <x:v>411</x:v>
@@ -10842,12 +10836,12 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="D354" t="s">
-        <x:v>850</x:v>
+        <x:v>848</x:v>
       </x:c>
     </x:row>
     <x:row r="355">
       <x:c r="A355" t="s">
-        <x:v>851</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="B355" t="s">
         <x:v>411</x:v>
@@ -10856,7 +10850,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="D355" t="s">
-        <x:v>852</x:v>
+        <x:v>850</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10870,7 +10864,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R770a729f89a04bfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd23201682ed049e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/site-content.xlsx
+++ b/content/site-content.xlsx
@@ -2267,7 +2267,7 @@
     <t>Цена индивидуального тарифа</t>
   </si>
   <si>
-    <t>15 000 ₽ · разовая оплата</t>
+    <t>15 000 RSD · разовая оплата</t>
   </si>
   <si>
     <t>pricing.plan.custom.description</t>
@@ -2851,7 +2851,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
       <font/>
       <fill>
@@ -2862,7 +2862,10 @@
     <dxf>
       <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
       </fill>
       <border/>
     </dxf>
@@ -2876,19 +2879,12 @@
       </fill>
       <border/>
     </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle count="3" pivot="0" name="Тексты-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="1" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -3122,7 +3118,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="14.0"/>
     <col customWidth="1" min="2" max="2" width="92.0"/>
-    <col customWidth="1" min="3" max="11" width="8.71"/>
+    <col customWidth="1" min="3" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
@@ -7474,7 +7470,7 @@
       <c r="C189" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="D189" s="19" t="s">
+      <c r="D189" s="16" t="s">
         <v>460</v>
       </c>
       <c r="E189" s="17"/>
@@ -7672,7 +7668,7 @@
       <c r="C198" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="D198" s="19" t="s">
+      <c r="D198" s="16" t="s">
         <v>479</v>
       </c>
       <c r="E198" s="17"/>
@@ -7912,7 +7908,7 @@
       <c r="C209" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="D209" s="19" t="s">
+      <c r="D209" s="16" t="s">
         <v>503</v>
       </c>
       <c r="E209" s="17"/>
@@ -7978,7 +7974,7 @@
       <c r="C212" s="15" t="s">
         <v>507</v>
       </c>
-      <c r="D212" s="19" t="s">
+      <c r="D212" s="16" t="s">
         <v>510</v>
       </c>
       <c r="E212" s="17"/>
@@ -10178,7 +10174,7 @@
       <c r="C312" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="D312" s="16" t="s">
+      <c r="D312" s="19" t="s">
         <v>751</v>
       </c>
       <c r="E312" s="17"/>
